--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BFAFD8-FAA1-45F8-A47C-310F30CB1C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BFAFD8-FAA1-45F8-A47C-310F30CB1C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CFF6E8-D2DE-4486-87C8-B0BCD4259BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2318,7 +2318,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="320">
   <si>
     <t>Base stats</t>
   </si>
@@ -3689,7 +3689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3945,6 +3945,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4527,7 +4530,7 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>17</c:v>
@@ -7107,7 +7110,7 @@
       </c>
       <c r="T8" s="20">
         <f>COUNTIF(E$6:F$250, "Fighting")</f>
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13450,9 +13453,7 @@
       <c r="E165" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="F165" s="49" t="s">
-        <v>27</v>
-      </c>
+      <c r="F165" s="89"/>
       <c r="G165" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CFF6E8-D2DE-4486-87C8-B0BCD4259BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFCAFEC-116E-46A4-9C02-FD88231AEDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="227">
+  <futureMetadata name="XLRICHVALUE" count="231">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -1630,8 +1630,36 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="227"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="228"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="229"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="230"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="227">
+  <valueMetadata count="231">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -2312,13 +2340,25 @@
     </bk>
     <bk>
       <rc t="1" v="226"/>
+    </bk>
+    <bk>
+      <rc t="1" v="227"/>
+    </bk>
+    <bk>
+      <rc t="1" v="228"/>
+    </bk>
+    <bk>
+      <rc t="1" v="229"/>
+    </bk>
+    <bk>
+      <rc t="1" v="230"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="324">
   <si>
     <t>Base stats</t>
   </si>
@@ -3306,6 +3346,18 @@
   </si>
   <si>
     <t>lv.64</t>
+  </si>
+  <si>
+    <t>Ting-Lu</t>
+  </si>
+  <si>
+    <t>Wo-Chien</t>
+  </si>
+  <si>
+    <t>Chi-Yu</t>
+  </si>
+  <si>
+    <t>Chien-Pao</t>
   </si>
 </sst>
 </file>
@@ -3689,7 +3741,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -3945,9 +3997,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4518,10 +4567,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>19</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>23</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>41</c:v>
@@ -4542,7 +4591,7 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>19</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>20</c:v>
@@ -4551,10 +4600,10 @@
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>18</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>18</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>18</c:v>
@@ -5315,7 +5364,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="227">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="231">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -6222,6 +6271,22 @@
   </rv>
   <rv s="0">
     <v>226</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>227</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>228</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>229</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>230</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -6465,6 +6530,10 @@
   <rel r:id="rId225"/>
   <rel r:id="rId226"/>
   <rel r:id="rId227"/>
+  <rel r:id="rId228"/>
+  <rel r:id="rId229"/>
+  <rel r:id="rId230"/>
+  <rel r:id="rId231"/>
 </richValueRels>
 </file>
 
@@ -6876,7 +6945,7 @@
       </c>
       <c r="T4" s="19">
         <f>COUNTIF(E$6:F$250, "Grass")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -6936,7 +7005,7 @@
       </c>
       <c r="T5" s="20">
         <f>COUNTIF(E$6:F$250, "Fire")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7350,7 +7419,7 @@
       </c>
       <c r="T12" s="20">
         <f>COUNTIF(E$6:F$250, "Ground")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7482,7 +7551,7 @@
       </c>
       <c r="T15" s="20">
         <f>COUNTIF(E$6:F$250, "Dark")</f>
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7528,7 +7597,7 @@
       </c>
       <c r="T16" s="20">
         <f>COUNTIF(E$6:F$250, "Ice")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13453,7 +13522,7 @@
       <c r="E165" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="F165" s="89"/>
+      <c r="F165" s="78"/>
       <c r="G165" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -15450,15 +15519,33 @@
       </c>
     </row>
     <row r="217" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B217" s="5" t="e" vm="228">
+        <v>#VALUE!</v>
+      </c>
       <c r="C217" s="5">
         <f t="shared" si="7"/>
         <v>214</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E217" s="84"/>
-      <c r="F217" s="48"/>
+        <v>320</v>
+      </c>
+      <c r="E217" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F217" s="83" t="s">
+        <v>50</v>
+      </c>
+      <c r="G217" s="1" t="e" vm="209">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I217" s="1"/>
+      <c r="J217" s="1"/>
+      <c r="K217" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L217" s="7"/>
       <c r="M217" s="9"/>
       <c r="N217" s="11"/>
@@ -15471,15 +15558,33 @@
       </c>
     </row>
     <row r="218" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B218" s="5" t="e" vm="229">
+        <v>#VALUE!</v>
+      </c>
       <c r="C218" s="5">
         <f t="shared" si="7"/>
         <v>215</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E218" s="84"/>
-      <c r="F218" s="48"/>
+        <v>321</v>
+      </c>
+      <c r="E218" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F218" s="80" t="s">
+        <v>16</v>
+      </c>
+      <c r="G218" s="1" t="e" vm="209">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I218" s="1"/>
+      <c r="J218" s="1"/>
+      <c r="K218" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L218" s="7"/>
       <c r="M218" s="9"/>
       <c r="N218" s="11"/>
@@ -15492,15 +15597,33 @@
       </c>
     </row>
     <row r="219" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B219" s="5" t="e" vm="230">
+        <v>#VALUE!</v>
+      </c>
       <c r="C219" s="5">
         <f t="shared" si="7"/>
         <v>216</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E219" s="84"/>
-      <c r="F219" s="48"/>
+        <v>322</v>
+      </c>
+      <c r="E219" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F219" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="G219" s="1" t="e" vm="209">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I219" s="1"/>
+      <c r="J219" s="1"/>
+      <c r="K219" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L219" s="7"/>
       <c r="M219" s="9"/>
       <c r="N219" s="11"/>
@@ -15513,15 +15636,33 @@
       </c>
     </row>
     <row r="220" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B220" s="5" t="e" vm="231">
+        <v>#VALUE!</v>
+      </c>
       <c r="C220" s="5">
         <f t="shared" si="7"/>
         <v>217</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E220" s="84"/>
-      <c r="F220" s="48"/>
+        <v>323</v>
+      </c>
+      <c r="E220" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F220" s="74" t="s">
+        <v>66</v>
+      </c>
+      <c r="G220" s="1" t="e" vm="209">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H220" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I220" s="1"/>
+      <c r="J220" s="1"/>
+      <c r="K220" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L220" s="7"/>
       <c r="M220" s="9"/>
       <c r="N220" s="11"/>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFCAFEC-116E-46A4-9C02-FD88231AEDB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39EF51E-1D99-4594-B592-227FB7801A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="231">
+  <futureMetadata name="XLRICHVALUE" count="234">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -1658,8 +1658,29 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="231"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="232"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="233"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="231">
+  <valueMetadata count="234">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -2352,13 +2373,22 @@
     </bk>
     <bk>
       <rc t="1" v="230"/>
+    </bk>
+    <bk>
+      <rc t="1" v="231"/>
+    </bk>
+    <bk>
+      <rc t="1" v="232"/>
+    </bk>
+    <bk>
+      <rc t="1" v="233"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="328">
   <si>
     <t>Base stats</t>
   </si>
@@ -3358,6 +3388,18 @@
   </si>
   <si>
     <t>Chien-Pao</t>
+  </si>
+  <si>
+    <t>Tic</t>
+  </si>
+  <si>
+    <t>Clic</t>
+  </si>
+  <si>
+    <t>Cliticlic</t>
+  </si>
+  <si>
+    <t>lv.49</t>
   </si>
 </sst>
 </file>
@@ -4606,7 +4648,7 @@
                   <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>12</c:v>
@@ -5364,7 +5406,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="231">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="234">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -6287,6 +6329,18 @@
   </rv>
   <rv s="0">
     <v>230</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>231</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>232</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>233</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -6534,6 +6588,9 @@
   <rel r:id="rId229"/>
   <rel r:id="rId230"/>
   <rel r:id="rId231"/>
+  <rel r:id="rId232"/>
+  <rel r:id="rId233"/>
+  <rel r:id="rId234"/>
 </richValueRels>
 </file>
 
@@ -7643,7 +7700,7 @@
       </c>
       <c r="T17" s="20">
         <f>COUNTIF(E$6:F$250, "Steel")</f>
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15717,15 +15774,29 @@
       </c>
     </row>
     <row r="223" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B223" t="e" vm="232">
+        <v>#VALUE!</v>
+      </c>
       <c r="C223" s="5">
         <f t="shared" si="7"/>
         <v>220</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E223" s="84"/>
+        <v>324</v>
+      </c>
+      <c r="E223" s="70" t="s">
+        <v>34</v>
+      </c>
       <c r="F223" s="48"/>
+      <c r="G223" s="1" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H223" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K223" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="L223" s="7"/>
       <c r="M223" s="9"/>
       <c r="N223" s="11"/>
@@ -15738,15 +15809,29 @@
       </c>
     </row>
     <row r="224" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B224" t="e" vm="233">
+        <v>#VALUE!</v>
+      </c>
       <c r="C224" s="5">
         <f t="shared" si="7"/>
         <v>221</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E224" s="84"/>
+        <v>325</v>
+      </c>
+      <c r="E224" s="70" t="s">
+        <v>34</v>
+      </c>
       <c r="F224" s="48"/>
+      <c r="G224" s="1" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H224" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K224" s="1" t="s">
+        <v>327</v>
+      </c>
       <c r="L224" s="7"/>
       <c r="M224" s="9"/>
       <c r="N224" s="11"/>
@@ -15758,16 +15843,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B225" t="e" vm="234">
+        <v>#VALUE!</v>
+      </c>
       <c r="C225" s="5">
         <f t="shared" si="7"/>
         <v>222</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E225" s="84"/>
+        <v>326</v>
+      </c>
+      <c r="E225" s="70" t="s">
+        <v>34</v>
+      </c>
       <c r="F225" s="48"/>
+      <c r="G225" s="1" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H225" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K225" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L225" s="7"/>
       <c r="M225" s="9"/>
       <c r="N225" s="11"/>
@@ -15779,7 +15878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C226" s="5">
         <f t="shared" si="7"/>
         <v>223</v>
@@ -15800,7 +15899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C227" s="5">
         <f t="shared" si="7"/>
         <v>224</v>
@@ -15821,7 +15920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C228" s="5">
         <f t="shared" si="7"/>
         <v>225</v>
@@ -15842,7 +15941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C229" s="5">
         <f t="shared" si="7"/>
         <v>226</v>
@@ -15863,7 +15962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C230" s="5">
         <f t="shared" si="7"/>
         <v>227</v>
@@ -15884,7 +15983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C231" s="5">
         <f t="shared" si="7"/>
         <v>228</v>
@@ -15905,7 +16004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C232" s="5">
         <f t="shared" si="7"/>
         <v>229</v>
@@ -15926,7 +16025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C233" s="5">
         <f t="shared" si="7"/>
         <v>230</v>
@@ -15947,7 +16046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C234" s="5">
         <f t="shared" si="7"/>
         <v>231</v>
@@ -15968,7 +16067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C235" s="5">
         <f t="shared" si="7"/>
         <v>232</v>
@@ -15989,7 +16088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C236" s="5">
         <f t="shared" si="7"/>
         <v>233</v>
@@ -16010,7 +16109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C237" s="5">
         <f t="shared" si="7"/>
         <v>234</v>
@@ -16031,7 +16130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C238" s="5">
         <f t="shared" si="7"/>
         <v>235</v>
@@ -16052,7 +16151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C239" s="5">
         <f t="shared" si="7"/>
         <v>236</v>
@@ -16073,7 +16172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C240" s="5">
         <f t="shared" si="7"/>
         <v>237</v>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B39EF51E-1D99-4594-B592-227FB7801A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0FB9F2-6250-48DA-B26D-A3B9A9DFCA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0FB9F2-6250-48DA-B26D-A3B9A9DFCA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0BB076-400D-4122-B0D4-259A8E221B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="234">
+  <futureMetadata name="XLRICHVALUE" count="267">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -1679,8 +1679,239 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="234"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="235"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="236"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="237"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="238"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="239"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="240"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="241"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="242"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="243"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="244"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="245"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="246"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="247"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="248"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="249"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="250"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="251"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="252"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="253"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="254"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="255"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="256"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="257"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="258"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="259"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="260"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="261"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="262"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="263"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="264"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="265"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="266"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="234">
+  <valueMetadata count="267">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -2382,13 +2613,112 @@
     </bk>
     <bk>
       <rc t="1" v="233"/>
+    </bk>
+    <bk>
+      <rc t="1" v="234"/>
+    </bk>
+    <bk>
+      <rc t="1" v="235"/>
+    </bk>
+    <bk>
+      <rc t="1" v="236"/>
+    </bk>
+    <bk>
+      <rc t="1" v="237"/>
+    </bk>
+    <bk>
+      <rc t="1" v="238"/>
+    </bk>
+    <bk>
+      <rc t="1" v="239"/>
+    </bk>
+    <bk>
+      <rc t="1" v="240"/>
+    </bk>
+    <bk>
+      <rc t="1" v="241"/>
+    </bk>
+    <bk>
+      <rc t="1" v="242"/>
+    </bk>
+    <bk>
+      <rc t="1" v="243"/>
+    </bk>
+    <bk>
+      <rc t="1" v="244"/>
+    </bk>
+    <bk>
+      <rc t="1" v="245"/>
+    </bk>
+    <bk>
+      <rc t="1" v="246"/>
+    </bk>
+    <bk>
+      <rc t="1" v="247"/>
+    </bk>
+    <bk>
+      <rc t="1" v="248"/>
+    </bk>
+    <bk>
+      <rc t="1" v="249"/>
+    </bk>
+    <bk>
+      <rc t="1" v="250"/>
+    </bk>
+    <bk>
+      <rc t="1" v="251"/>
+    </bk>
+    <bk>
+      <rc t="1" v="252"/>
+    </bk>
+    <bk>
+      <rc t="1" v="253"/>
+    </bk>
+    <bk>
+      <rc t="1" v="254"/>
+    </bk>
+    <bk>
+      <rc t="1" v="255"/>
+    </bk>
+    <bk>
+      <rc t="1" v="256"/>
+    </bk>
+    <bk>
+      <rc t="1" v="257"/>
+    </bk>
+    <bk>
+      <rc t="1" v="258"/>
+    </bk>
+    <bk>
+      <rc t="1" v="259"/>
+    </bk>
+    <bk>
+      <rc t="1" v="260"/>
+    </bk>
+    <bk>
+      <rc t="1" v="261"/>
+    </bk>
+    <bk>
+      <rc t="1" v="262"/>
+    </bk>
+    <bk>
+      <rc t="1" v="263"/>
+    </bk>
+    <bk>
+      <rc t="1" v="264"/>
+    </bk>
+    <bk>
+      <rc t="1" v="265"/>
+    </bk>
+    <bk>
+      <rc t="1" v="266"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="365">
   <si>
     <t>Base stats</t>
   </si>
@@ -3400,6 +3730,117 @@
   </si>
   <si>
     <t>lv.49</t>
+  </si>
+  <si>
+    <t>Eevee</t>
+  </si>
+  <si>
+    <t>Vaporeon</t>
+  </si>
+  <si>
+    <t>Jolteon</t>
+  </si>
+  <si>
+    <t>Flareon</t>
+  </si>
+  <si>
+    <t>Espeon</t>
+  </si>
+  <si>
+    <t>Umbreon</t>
+  </si>
+  <si>
+    <t>Leafeon</t>
+  </si>
+  <si>
+    <t>Glaceon</t>
+  </si>
+  <si>
+    <t>Sylveon</t>
+  </si>
+  <si>
+    <t>Rufflet</t>
+  </si>
+  <si>
+    <t>Braviary</t>
+  </si>
+  <si>
+    <t>Vullaby</t>
+  </si>
+  <si>
+    <t>Mandibuzz</t>
+  </si>
+  <si>
+    <t>lv.54</t>
+  </si>
+  <si>
+    <t>Ditto</t>
+  </si>
+  <si>
+    <t>Scyther</t>
+  </si>
+  <si>
+    <t>Scizor</t>
+  </si>
+  <si>
+    <t>Kleavor</t>
+  </si>
+  <si>
+    <t>holding metal coat and level up (Scizor) or holding black augurite and level up (Kleavor)</t>
+  </si>
+  <si>
+    <t>holding magmarizer and level up</t>
+  </si>
+  <si>
+    <t>holding electrizer and level up</t>
+  </si>
+  <si>
+    <t>Magby</t>
+  </si>
+  <si>
+    <t>Magmar</t>
+  </si>
+  <si>
+    <t>Magmortar</t>
+  </si>
+  <si>
+    <t>Elekid</t>
+  </si>
+  <si>
+    <t>Electabuzz</t>
+  </si>
+  <si>
+    <t>Electivire</t>
+  </si>
+  <si>
+    <t>water stone (Vaporeon), thunder stone (Jolteon), fire stone (flareon), high friendship at day (Espeon), high friendship at night (Umbreon), leaf stone (Leafeon), ice stone (Glaceon), shiny stone (Sylveon)</t>
+  </si>
+  <si>
+    <t>Woobat</t>
+  </si>
+  <si>
+    <t>Swoobat</t>
+  </si>
+  <si>
+    <t>Meditite</t>
+  </si>
+  <si>
+    <t>Medicham</t>
+  </si>
+  <si>
+    <t>Zangoose</t>
+  </si>
+  <si>
+    <t>Seviper</t>
+  </si>
+  <si>
+    <t>Corphish</t>
+  </si>
+  <si>
+    <t>Crawdaunt</t>
+  </si>
+  <si>
+    <t>Tropius</t>
   </si>
 </sst>
 </file>
@@ -4609,55 +5050,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>24</c:v>
+                <c:pt idx="5">
+                  <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>13</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>19</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>20</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>22</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>21</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>12</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>15</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>15</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>15</c:v>
@@ -5406,7 +5847,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="234">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="267">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -6341,6 +6782,138 @@
   </rv>
   <rv s="0">
     <v>233</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>234</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>235</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>236</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>237</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>238</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>239</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>240</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>241</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>242</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>243</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>244</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>245</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>246</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>247</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>248</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>249</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>250</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>251</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>252</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>253</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>254</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>255</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>256</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>257</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>258</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>259</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>260</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>261</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>262</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>263</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>264</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>265</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>266</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -6591,6 +7164,39 @@
   <rel r:id="rId232"/>
   <rel r:id="rId233"/>
   <rel r:id="rId234"/>
+  <rel r:id="rId235"/>
+  <rel r:id="rId236"/>
+  <rel r:id="rId237"/>
+  <rel r:id="rId238"/>
+  <rel r:id="rId239"/>
+  <rel r:id="rId240"/>
+  <rel r:id="rId241"/>
+  <rel r:id="rId242"/>
+  <rel r:id="rId243"/>
+  <rel r:id="rId244"/>
+  <rel r:id="rId245"/>
+  <rel r:id="rId246"/>
+  <rel r:id="rId247"/>
+  <rel r:id="rId248"/>
+  <rel r:id="rId249"/>
+  <rel r:id="rId250"/>
+  <rel r:id="rId251"/>
+  <rel r:id="rId252"/>
+  <rel r:id="rId253"/>
+  <rel r:id="rId254"/>
+  <rel r:id="rId255"/>
+  <rel r:id="rId256"/>
+  <rel r:id="rId257"/>
+  <rel r:id="rId258"/>
+  <rel r:id="rId259"/>
+  <rel r:id="rId260"/>
+  <rel r:id="rId261"/>
+  <rel r:id="rId262"/>
+  <rel r:id="rId263"/>
+  <rel r:id="rId264"/>
+  <rel r:id="rId265"/>
+  <rel r:id="rId266"/>
+  <rel r:id="rId267"/>
 </richValueRels>
 </file>
 
@@ -6858,7 +7464,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:T250"/>
+  <dimension ref="B1:T265"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
@@ -7001,8 +7607,8 @@
         <v>16</v>
       </c>
       <c r="T4" s="19">
-        <f>COUNTIF(E$6:F$250, "Grass")</f>
-        <v>20</v>
+        <f>COUNTIF(E$6:F$265, "Grass")</f>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7061,8 +7667,8 @@
         <v>24</v>
       </c>
       <c r="T5" s="20">
-        <f>COUNTIF(E$6:F$250, "Fire")</f>
-        <v>24</v>
+        <f>COUNTIF(E$6:F$265, "Fire")</f>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7121,8 +7727,8 @@
         <v>30</v>
       </c>
       <c r="T6" s="20">
-        <f>COUNTIF(E$6:F$250, "Water")</f>
-        <v>41</v>
+        <f>COUNTIF(E$6:F$265, "Water")</f>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7177,8 +7783,8 @@
         <v>37</v>
       </c>
       <c r="T7" s="20">
-        <f>COUNTIF(E$6:F$250, "Normal")</f>
-        <v>16</v>
+        <f>COUNTIF(E$6:F$265, "Normal")</f>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7235,8 +7841,8 @@
         <v>27</v>
       </c>
       <c r="T8" s="20">
-        <f>COUNTIF(E$6:F$250, "Fighting")</f>
-        <v>18</v>
+        <f>COUNTIF(E$6:F$265, "Fighting")</f>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7293,8 +7899,8 @@
         <v>41</v>
       </c>
       <c r="T9" s="20">
-        <f>COUNTIF(E$6:F$250, "Flying")</f>
-        <v>17</v>
+        <f>COUNTIF(E$6:F$265, "Flying")</f>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7353,8 +7959,8 @@
         <v>63</v>
       </c>
       <c r="T10" s="20">
-        <f>COUNTIF(E$6:F$250, "Psychic")</f>
-        <v>13</v>
+        <f>COUNTIF(E$6:F$265, "Psychic")</f>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7413,8 +8019,8 @@
         <v>45</v>
       </c>
       <c r="T11" s="20">
-        <f>COUNTIF(E$6:F$250, "Bug")</f>
-        <v>19</v>
+        <f>COUNTIF(E$6:F$265, "Bug")</f>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7475,7 +8081,7 @@
         <v>50</v>
       </c>
       <c r="T12" s="20">
-        <f>COUNTIF(E$6:F$250, "Ground")</f>
+        <f>COUNTIF(E$6:F$265, "Ground")</f>
         <v>20</v>
       </c>
     </row>
@@ -7519,8 +8125,8 @@
         <v>64</v>
       </c>
       <c r="T13" s="20">
-        <f>COUNTIF(E$6:F$250, "Rock")</f>
-        <v>20</v>
+        <f>COUNTIF(E$6:F$265, "Rock")</f>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7563,7 +8169,7 @@
         <v>65</v>
       </c>
       <c r="T14" s="20">
-        <f>COUNTIF(E$6:F$250, "Ghost")</f>
+        <f>COUNTIF(E$6:F$265, "Ghost")</f>
         <v>21</v>
       </c>
     </row>
@@ -7607,8 +8213,8 @@
         <v>48</v>
       </c>
       <c r="T15" s="20">
-        <f>COUNTIF(E$6:F$250, "Dark")</f>
-        <v>22</v>
+        <f>COUNTIF(E$6:F$265, "Dark")</f>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7653,8 +8259,8 @@
         <v>66</v>
       </c>
       <c r="T16" s="20">
-        <f>COUNTIF(E$6:F$250, "Ice")</f>
-        <v>19</v>
+        <f>COUNTIF(E$6:F$265, "Ice")</f>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7699,8 +8305,8 @@
         <v>34</v>
       </c>
       <c r="T17" s="20">
-        <f>COUNTIF(E$6:F$250, "Steel")</f>
-        <v>21</v>
+        <f>COUNTIF(E$6:F$265, "Steel")</f>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7745,8 +8351,8 @@
         <v>67</v>
       </c>
       <c r="T18" s="20">
-        <f>COUNTIF(E$6:F$250, "Electrik")</f>
-        <v>12</v>
+        <f>COUNTIF(E$6:F$265, "Electrik")</f>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7789,8 +8395,8 @@
         <v>68</v>
       </c>
       <c r="T19" s="20">
-        <f>COUNTIF(E$6:F$250, "Poison")</f>
-        <v>15</v>
+        <f>COUNTIF(E$6:F$265, "Poison")</f>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7835,8 +8441,8 @@
         <v>60</v>
       </c>
       <c r="T20" s="20">
-        <f>COUNTIF(E$6:F$250, "Fairy")</f>
-        <v>15</v>
+        <f>COUNTIF(E$6:F$265, "Fairy")</f>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7879,7 +8485,7 @@
         <v>69</v>
       </c>
       <c r="T21" s="20">
-        <f>COUNTIF(E$6:F$250, "Dragon")</f>
+        <f>COUNTIF(E$6:F$265, "Dragon")</f>
         <v>15</v>
       </c>
     </row>
@@ -14843,7 +15449,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C198" s="5">
-        <f t="shared" ref="C198:C250" si="7">C197+1</f>
+        <f t="shared" ref="C198:C265" si="7">C197+1</f>
         <v>195</v>
       </c>
       <c r="D198" s="1" t="s">
@@ -15031,7 +15637,7 @@
       <c r="P202" s="15"/>
       <c r="Q202" s="17"/>
       <c r="R202" s="40">
-        <f t="shared" ref="R202:R250" si="9">SUM(L202:Q202)</f>
+        <f t="shared" ref="R202:R265" si="9">SUM(L202:Q202)</f>
         <v>0</v>
       </c>
     </row>
@@ -15732,15 +16338,29 @@
       </c>
     </row>
     <row r="221" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B221" t="e" vm="232">
+        <v>#VALUE!</v>
+      </c>
       <c r="C221" s="5">
         <f t="shared" si="7"/>
         <v>218</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E221" s="84"/>
+        <v>328</v>
+      </c>
+      <c r="E221" s="52" t="s">
+        <v>37</v>
+      </c>
       <c r="F221" s="48"/>
+      <c r="G221" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K221" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="L221" s="7"/>
       <c r="M221" s="9"/>
       <c r="N221" s="11"/>
@@ -15753,28 +16373,39 @@
       </c>
     </row>
     <row r="222" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B222" t="e" vm="233">
+        <v>#VALUE!</v>
+      </c>
       <c r="C222" s="5">
         <f t="shared" si="7"/>
         <v>219</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E222" s="84"/>
+        <v>329</v>
+      </c>
+      <c r="E222" s="50" t="s">
+        <v>30</v>
+      </c>
       <c r="F222" s="48"/>
+      <c r="G222" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H222" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K222" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L222" s="7"/>
       <c r="M222" s="9"/>
       <c r="N222" s="11"/>
       <c r="O222" s="13"/>
       <c r="P222" s="15"/>
       <c r="Q222" s="17"/>
-      <c r="R222" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R222" s="40"/>
     </row>
     <row r="223" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B223" t="e" vm="232">
+      <c r="B223" t="e" vm="234">
         <v>#VALUE!</v>
       </c>
       <c r="C223" s="5">
@@ -15782,20 +16413,20 @@
         <v>220</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E223" s="70" t="s">
-        <v>34</v>
+        <v>330</v>
+      </c>
+      <c r="E223" s="62" t="s">
+        <v>67</v>
       </c>
       <c r="F223" s="48"/>
-      <c r="G223" s="1" t="e" vm="34">
+      <c r="G223" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="K223" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="L223" s="7"/>
       <c r="M223" s="9"/>
@@ -15803,13 +16434,10 @@
       <c r="O223" s="13"/>
       <c r="P223" s="15"/>
       <c r="Q223" s="17"/>
-      <c r="R223" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R223" s="40"/>
     </row>
     <row r="224" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B224" t="e" vm="233">
+      <c r="B224" t="e" vm="235">
         <v>#VALUE!</v>
       </c>
       <c r="C224" s="5">
@@ -15817,20 +16445,20 @@
         <v>221</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="E224" s="70" t="s">
-        <v>34</v>
+        <v>331</v>
+      </c>
+      <c r="E224" s="47" t="s">
+        <v>24</v>
       </c>
       <c r="F224" s="48"/>
-      <c r="G224" s="1" t="e" vm="34">
+      <c r="G224" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>327</v>
+        <v>22</v>
       </c>
       <c r="L224" s="7"/>
       <c r="M224" s="9"/>
@@ -15838,13 +16466,10 @@
       <c r="O224" s="13"/>
       <c r="P224" s="15"/>
       <c r="Q224" s="17"/>
-      <c r="R224" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R224" s="40"/>
     </row>
     <row r="225" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B225" t="e" vm="234">
+      <c r="B225" t="e" vm="236">
         <v>#VALUE!</v>
       </c>
       <c r="C225" s="5">
@@ -15852,17 +16477,17 @@
         <v>222</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E225" s="70" t="s">
-        <v>34</v>
+        <v>332</v>
+      </c>
+      <c r="E225" s="71" t="s">
+        <v>63</v>
       </c>
       <c r="F225" s="48"/>
-      <c r="G225" s="1" t="e" vm="34">
+      <c r="G225" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="K225" s="1" t="s">
         <v>22</v>
@@ -15873,168 +16498,264 @@
       <c r="O225" s="13"/>
       <c r="P225" s="15"/>
       <c r="Q225" s="17"/>
-      <c r="R225" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R225" s="40"/>
     </row>
     <row r="226" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B226" t="e" vm="237">
+        <v>#VALUE!</v>
+      </c>
       <c r="C226" s="5">
         <f t="shared" si="7"/>
         <v>223</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E226" s="84"/>
+        <v>333</v>
+      </c>
+      <c r="E226" s="73" t="s">
+        <v>48</v>
+      </c>
       <c r="F226" s="48"/>
+      <c r="G226" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H226" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K226" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L226" s="7"/>
       <c r="M226" s="9"/>
       <c r="N226" s="11"/>
       <c r="O226" s="13"/>
       <c r="P226" s="15"/>
       <c r="Q226" s="17"/>
-      <c r="R226" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R226" s="40"/>
     </row>
     <row r="227" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B227" t="e" vm="238">
+        <v>#VALUE!</v>
+      </c>
       <c r="C227" s="5">
         <f t="shared" si="7"/>
         <v>224</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E227" s="84"/>
+        <v>334</v>
+      </c>
+      <c r="E227" s="45" t="s">
+        <v>16</v>
+      </c>
       <c r="F227" s="48"/>
+      <c r="G227" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H227" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K227" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L227" s="7"/>
       <c r="M227" s="9"/>
       <c r="N227" s="11"/>
       <c r="O227" s="13"/>
       <c r="P227" s="15"/>
       <c r="Q227" s="17"/>
-      <c r="R227" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R227" s="40"/>
     </row>
     <row r="228" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B228" t="e" vm="239">
+        <v>#VALUE!</v>
+      </c>
       <c r="C228" s="5">
         <f t="shared" si="7"/>
         <v>225</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E228" s="84"/>
+        <v>335</v>
+      </c>
+      <c r="E228" s="64" t="s">
+        <v>66</v>
+      </c>
       <c r="F228" s="48"/>
+      <c r="G228" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H228" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K228" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L228" s="7"/>
       <c r="M228" s="9"/>
       <c r="N228" s="11"/>
       <c r="O228" s="13"/>
       <c r="P228" s="15"/>
       <c r="Q228" s="17"/>
-      <c r="R228" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R228" s="40"/>
     </row>
     <row r="229" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B229" t="e" vm="240">
+        <v>#VALUE!</v>
+      </c>
       <c r="C229" s="5">
         <f t="shared" si="7"/>
         <v>226</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E229" s="84"/>
+        <v>336</v>
+      </c>
+      <c r="E229" s="72" t="s">
+        <v>60</v>
+      </c>
       <c r="F229" s="48"/>
+      <c r="G229" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H229" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K229" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L229" s="7"/>
       <c r="M229" s="9"/>
       <c r="N229" s="11"/>
       <c r="O229" s="13"/>
       <c r="P229" s="15"/>
       <c r="Q229" s="17"/>
-      <c r="R229" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R229" s="40"/>
     </row>
     <row r="230" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B230" t="e" vm="241">
+        <v>#VALUE!</v>
+      </c>
       <c r="C230" s="5">
         <f t="shared" si="7"/>
         <v>227</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E230" s="84"/>
-      <c r="F230" s="48"/>
+        <v>337</v>
+      </c>
+      <c r="E230" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="F230" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G230" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H230" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K230" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="L230" s="7"/>
       <c r="M230" s="9"/>
       <c r="N230" s="11"/>
       <c r="O230" s="13"/>
       <c r="P230" s="15"/>
       <c r="Q230" s="17"/>
-      <c r="R230" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R230" s="40"/>
     </row>
     <row r="231" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B231" t="e" vm="242">
+        <v>#VALUE!</v>
+      </c>
       <c r="C231" s="5">
         <f t="shared" si="7"/>
         <v>228</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E231" s="84"/>
-      <c r="F231" s="48"/>
+        <v>338</v>
+      </c>
+      <c r="E231" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="F231" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G231" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H231" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K231" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L231" s="7"/>
       <c r="M231" s="9"/>
       <c r="N231" s="11"/>
       <c r="O231" s="13"/>
       <c r="P231" s="15"/>
       <c r="Q231" s="17"/>
-      <c r="R231" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R231" s="40"/>
     </row>
     <row r="232" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B232" t="e" vm="243">
+        <v>#VALUE!</v>
+      </c>
       <c r="C232" s="5">
         <f t="shared" si="7"/>
         <v>229</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E232" s="84"/>
-      <c r="F232" s="48"/>
+        <v>339</v>
+      </c>
+      <c r="E232" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F232" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G232" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H232" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K232" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="L232" s="7"/>
       <c r="M232" s="9"/>
       <c r="N232" s="11"/>
       <c r="O232" s="13"/>
       <c r="P232" s="15"/>
       <c r="Q232" s="17"/>
-      <c r="R232" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R232" s="40"/>
     </row>
     <row r="233" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B233" t="e" vm="244">
+        <v>#VALUE!</v>
+      </c>
       <c r="C233" s="5">
         <f t="shared" si="7"/>
         <v>230</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E233" s="84"/>
-      <c r="F233" s="48"/>
+        <v>340</v>
+      </c>
+      <c r="E233" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F233" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G233" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H233" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K233" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L233" s="7"/>
       <c r="M233" s="9"/>
       <c r="N233" s="11"/>
@@ -16047,99 +16768,159 @@
       </c>
     </row>
     <row r="234" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B234" t="e" vm="245">
+        <v>#VALUE!</v>
+      </c>
       <c r="C234" s="5">
         <f t="shared" si="7"/>
         <v>231</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E234" s="84"/>
+        <v>342</v>
+      </c>
+      <c r="E234" s="52" t="s">
+        <v>37</v>
+      </c>
       <c r="F234" s="48"/>
+      <c r="G234" s="1" t="e" vm="246">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H234" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="K234" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L234" s="7"/>
       <c r="M234" s="9"/>
       <c r="N234" s="11"/>
       <c r="O234" s="13"/>
       <c r="P234" s="15"/>
       <c r="Q234" s="17"/>
-      <c r="R234" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R234" s="40"/>
     </row>
     <row r="235" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B235" t="e" vm="247">
+        <v>#VALUE!</v>
+      </c>
       <c r="C235" s="5">
         <f t="shared" si="7"/>
         <v>232</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E235" s="84"/>
-      <c r="F235" s="48"/>
+        <v>343</v>
+      </c>
+      <c r="E235" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="F235" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G235" s="1" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K235" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="L235" s="7"/>
       <c r="M235" s="9"/>
       <c r="N235" s="11"/>
       <c r="O235" s="13"/>
       <c r="P235" s="15"/>
       <c r="Q235" s="17"/>
-      <c r="R235" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R235" s="40"/>
     </row>
     <row r="236" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B236" t="e" vm="248">
+        <v>#VALUE!</v>
+      </c>
       <c r="C236" s="5">
         <f t="shared" si="7"/>
         <v>233</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E236" s="84"/>
-      <c r="F236" s="48"/>
+        <v>344</v>
+      </c>
+      <c r="E236" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="F236" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="G236" s="1" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K236" s="1"/>
       <c r="L236" s="7"/>
       <c r="M236" s="9"/>
       <c r="N236" s="11"/>
       <c r="O236" s="13"/>
       <c r="P236" s="15"/>
       <c r="Q236" s="17"/>
-      <c r="R236" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R236" s="40"/>
     </row>
     <row r="237" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B237" t="e" vm="249">
+        <v>#VALUE!</v>
+      </c>
       <c r="C237" s="5">
         <f t="shared" si="7"/>
         <v>234</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E237" s="84"/>
-      <c r="F237" s="48"/>
+        <v>345</v>
+      </c>
+      <c r="E237" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="F237" s="66" t="s">
+        <v>64</v>
+      </c>
+      <c r="G237" s="1" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K237" s="1"/>
       <c r="L237" s="7"/>
       <c r="M237" s="9"/>
       <c r="N237" s="11"/>
       <c r="O237" s="13"/>
       <c r="P237" s="15"/>
       <c r="Q237" s="17"/>
-      <c r="R237" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R237" s="40"/>
     </row>
     <row r="238" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B238" t="e" vm="250">
+        <v>#VALUE!</v>
+      </c>
       <c r="C238" s="5">
         <f t="shared" si="7"/>
         <v>235</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E238" s="84"/>
+        <v>349</v>
+      </c>
+      <c r="E238" s="47" t="s">
+        <v>24</v>
+      </c>
       <c r="F238" s="48"/>
+      <c r="G238" s="1" t="e" vm="209">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K238" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="L238" s="7"/>
       <c r="M238" s="9"/>
       <c r="N238" s="11"/>
@@ -16152,15 +16933,29 @@
       </c>
     </row>
     <row r="239" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B239" t="e" vm="251">
+        <v>#VALUE!</v>
+      </c>
       <c r="C239" s="5">
         <f t="shared" si="7"/>
         <v>236</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E239" s="84"/>
+        <v>350</v>
+      </c>
+      <c r="E239" s="47" t="s">
+        <v>24</v>
+      </c>
       <c r="F239" s="48"/>
+      <c r="G239" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H239" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K239" s="1" t="s">
+        <v>347</v>
+      </c>
       <c r="L239" s="7"/>
       <c r="M239" s="9"/>
       <c r="N239" s="11"/>
@@ -16173,15 +16968,29 @@
       </c>
     </row>
     <row r="240" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B240" t="e" vm="252">
+        <v>#VALUE!</v>
+      </c>
       <c r="C240" s="5">
         <f t="shared" si="7"/>
         <v>237</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E240" s="84"/>
+        <v>351</v>
+      </c>
+      <c r="E240" s="47" t="s">
+        <v>24</v>
+      </c>
       <c r="F240" s="48"/>
+      <c r="G240" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K240" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L240" s="7"/>
       <c r="M240" s="9"/>
       <c r="N240" s="11"/>
@@ -16193,16 +17002,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B241" t="e" vm="253">
+        <v>#VALUE!</v>
+      </c>
       <c r="C241" s="5">
         <f t="shared" si="7"/>
         <v>238</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E241" s="84"/>
+        <v>352</v>
+      </c>
+      <c r="E241" s="62" t="s">
+        <v>67</v>
+      </c>
       <c r="F241" s="48"/>
+      <c r="G241" s="1" t="e" vm="209">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H241" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K241" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="L241" s="7"/>
       <c r="M241" s="9"/>
       <c r="N241" s="11"/>
@@ -16214,16 +17037,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B242" t="e" vm="254">
+        <v>#VALUE!</v>
+      </c>
       <c r="C242" s="5">
         <f t="shared" si="7"/>
         <v>239</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E242" s="84"/>
+        <v>353</v>
+      </c>
+      <c r="E242" s="62" t="s">
+        <v>67</v>
+      </c>
       <c r="F242" s="48"/>
+      <c r="G242" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K242" s="1" t="s">
+        <v>348</v>
+      </c>
       <c r="L242" s="7"/>
       <c r="M242" s="9"/>
       <c r="N242" s="11"/>
@@ -16235,16 +17072,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B243" t="e" vm="255">
+        <v>#VALUE!</v>
+      </c>
       <c r="C243" s="5">
         <f t="shared" si="7"/>
         <v>240</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E243" s="84"/>
+        <v>354</v>
+      </c>
+      <c r="E243" s="62" t="s">
+        <v>67</v>
+      </c>
       <c r="F243" s="48"/>
+      <c r="G243" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K243" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L243" s="7"/>
       <c r="M243" s="9"/>
       <c r="N243" s="11"/>
@@ -16256,16 +17107,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B244" t="e" vm="256">
+        <v>#VALUE!</v>
+      </c>
       <c r="C244" s="5">
         <f t="shared" si="7"/>
         <v>241</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E244" s="84"/>
+        <v>324</v>
+      </c>
+      <c r="E244" s="70" t="s">
+        <v>34</v>
+      </c>
       <c r="F244" s="48"/>
+      <c r="G244" s="1" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K244" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="L244" s="7"/>
       <c r="M244" s="9"/>
       <c r="N244" s="11"/>
@@ -16277,16 +17142,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B245" t="e" vm="257">
+        <v>#VALUE!</v>
+      </c>
       <c r="C245" s="5">
         <f t="shared" si="7"/>
         <v>242</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E245" s="84"/>
+        <v>325</v>
+      </c>
+      <c r="E245" s="70" t="s">
+        <v>34</v>
+      </c>
       <c r="F245" s="48"/>
+      <c r="G245" s="1" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K245" s="1" t="s">
+        <v>327</v>
+      </c>
       <c r="L245" s="7"/>
       <c r="M245" s="9"/>
       <c r="N245" s="11"/>
@@ -16298,16 +17177,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B246" t="e" vm="258">
+        <v>#VALUE!</v>
+      </c>
       <c r="C246" s="5">
         <f t="shared" si="7"/>
         <v>243</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E246" s="84"/>
+        <v>326</v>
+      </c>
+      <c r="E246" s="70" t="s">
+        <v>34</v>
+      </c>
       <c r="F246" s="48"/>
+      <c r="G246" s="1" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H246" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K246" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L246" s="7"/>
       <c r="M246" s="9"/>
       <c r="N246" s="11"/>
@@ -16319,16 +17212,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B247" t="e" vm="259">
+        <v>#VALUE!</v>
+      </c>
       <c r="C247" s="5">
         <f t="shared" si="7"/>
         <v>244</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E247" s="84"/>
-      <c r="F247" s="48"/>
+        <v>356</v>
+      </c>
+      <c r="E247" s="71" t="s">
+        <v>63</v>
+      </c>
+      <c r="F247" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G247" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H247" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I247" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J247" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K247" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="L247" s="7"/>
       <c r="M247" s="9"/>
       <c r="N247" s="11"/>
@@ -16340,16 +17255,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B248" t="e" vm="260">
+        <v>#VALUE!</v>
+      </c>
       <c r="C248" s="5">
         <f t="shared" si="7"/>
         <v>245</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E248" s="84"/>
-      <c r="F248" s="48"/>
+        <v>357</v>
+      </c>
+      <c r="E248" s="71" t="s">
+        <v>63</v>
+      </c>
+      <c r="F248" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G248" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H248" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I248" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J248" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K248" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L248" s="7"/>
       <c r="M248" s="9"/>
       <c r="N248" s="11"/>
@@ -16361,16 +17298,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B249" t="e" vm="261">
+        <v>#VALUE!</v>
+      </c>
       <c r="C249" s="5">
         <f t="shared" si="7"/>
         <v>246</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E249" s="84"/>
-      <c r="F249" s="48"/>
+        <v>358</v>
+      </c>
+      <c r="E249" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="F249" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="G249" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H249" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K249" s="1" t="s">
+        <v>173</v>
+      </c>
       <c r="L249" s="7"/>
       <c r="M249" s="9"/>
       <c r="N249" s="11"/>
@@ -16382,16 +17335,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="3:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B250" t="e" vm="262">
+        <v>#VALUE!</v>
+      </c>
       <c r="C250" s="5">
         <f t="shared" si="7"/>
         <v>247</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E250" s="85"/>
-      <c r="F250" s="86"/>
+        <v>359</v>
+      </c>
+      <c r="E250" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="F250" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="G250" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H250" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K250" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L250" s="7"/>
       <c r="M250" s="9"/>
       <c r="N250" s="11"/>
@@ -16399,6 +17368,419 @@
       <c r="P250" s="15"/>
       <c r="Q250" s="17"/>
       <c r="R250" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B251" t="e" vm="263">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C251" s="5">
+        <f t="shared" si="7"/>
+        <v>248</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E251" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="F251" s="48"/>
+      <c r="G251" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H251" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K251" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L251" s="7"/>
+      <c r="M251" s="9"/>
+      <c r="N251" s="11"/>
+      <c r="O251" s="13"/>
+      <c r="P251" s="15"/>
+      <c r="Q251" s="17"/>
+      <c r="R251" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B252" t="e" vm="264">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C252" s="5">
+        <f t="shared" si="7"/>
+        <v>249</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E252" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="F252" s="48"/>
+      <c r="G252" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H252" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I252" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J252" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K252" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L252" s="7"/>
+      <c r="M252" s="9"/>
+      <c r="N252" s="11"/>
+      <c r="O252" s="13"/>
+      <c r="P252" s="15"/>
+      <c r="Q252" s="17"/>
+      <c r="R252" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B253" t="e" vm="265">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C253" s="5">
+        <f t="shared" si="7"/>
+        <v>250</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E253" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F253" s="48"/>
+      <c r="G253" s="1" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H253" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I253" s="1" t="e" vm="102">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J253" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K253" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L253" s="7"/>
+      <c r="M253" s="9"/>
+      <c r="N253" s="11"/>
+      <c r="O253" s="13"/>
+      <c r="P253" s="15"/>
+      <c r="Q253" s="17"/>
+      <c r="R253" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B254" t="e" vm="266">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C254" s="5">
+        <f t="shared" si="7"/>
+        <v>251</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E254" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F254" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="G254" s="1" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H254" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I254" s="1" t="e" vm="102">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J254" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K254" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L254" s="7"/>
+      <c r="M254" s="9"/>
+      <c r="N254" s="11"/>
+      <c r="O254" s="13"/>
+      <c r="P254" s="15"/>
+      <c r="Q254" s="17"/>
+      <c r="R254" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B255" t="e" vm="267">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C255" s="5">
+        <f t="shared" si="7"/>
+        <v>252</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E255" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="F255" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G255" s="1" t="e" vm="138">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H255" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="I255" s="1" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J255" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K255" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L255" s="7"/>
+      <c r="M255" s="9"/>
+      <c r="N255" s="11"/>
+      <c r="O255" s="13"/>
+      <c r="P255" s="15"/>
+      <c r="Q255" s="17"/>
+      <c r="R255" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C256" s="5">
+        <f t="shared" si="7"/>
+        <v>253</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E256" s="84"/>
+      <c r="F256" s="48"/>
+      <c r="L256" s="7"/>
+      <c r="M256" s="9"/>
+      <c r="N256" s="11"/>
+      <c r="O256" s="13"/>
+      <c r="P256" s="15"/>
+      <c r="Q256" s="17"/>
+      <c r="R256" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C257" s="5">
+        <f t="shared" si="7"/>
+        <v>254</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E257" s="84"/>
+      <c r="F257" s="48"/>
+      <c r="L257" s="7"/>
+      <c r="M257" s="9"/>
+      <c r="N257" s="11"/>
+      <c r="O257" s="13"/>
+      <c r="P257" s="15"/>
+      <c r="Q257" s="17"/>
+      <c r="R257" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C258" s="5">
+        <f t="shared" si="7"/>
+        <v>255</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E258" s="84"/>
+      <c r="F258" s="48"/>
+      <c r="L258" s="7"/>
+      <c r="M258" s="9"/>
+      <c r="N258" s="11"/>
+      <c r="O258" s="13"/>
+      <c r="P258" s="15"/>
+      <c r="Q258" s="17"/>
+      <c r="R258" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C259" s="5">
+        <f t="shared" si="7"/>
+        <v>256</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E259" s="84"/>
+      <c r="F259" s="48"/>
+      <c r="L259" s="7"/>
+      <c r="M259" s="9"/>
+      <c r="N259" s="11"/>
+      <c r="O259" s="13"/>
+      <c r="P259" s="15"/>
+      <c r="Q259" s="17"/>
+      <c r="R259" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C260" s="5">
+        <f t="shared" si="7"/>
+        <v>257</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E260" s="84"/>
+      <c r="F260" s="48"/>
+      <c r="L260" s="7"/>
+      <c r="M260" s="9"/>
+      <c r="N260" s="11"/>
+      <c r="O260" s="13"/>
+      <c r="P260" s="15"/>
+      <c r="Q260" s="17"/>
+      <c r="R260" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C261" s="5">
+        <f t="shared" si="7"/>
+        <v>258</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E261" s="84"/>
+      <c r="F261" s="48"/>
+      <c r="L261" s="7"/>
+      <c r="M261" s="9"/>
+      <c r="N261" s="11"/>
+      <c r="O261" s="13"/>
+      <c r="P261" s="15"/>
+      <c r="Q261" s="17"/>
+      <c r="R261" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C262" s="5">
+        <f t="shared" si="7"/>
+        <v>259</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E262" s="84"/>
+      <c r="F262" s="48"/>
+      <c r="L262" s="7"/>
+      <c r="M262" s="9"/>
+      <c r="N262" s="11"/>
+      <c r="O262" s="13"/>
+      <c r="P262" s="15"/>
+      <c r="Q262" s="17"/>
+      <c r="R262" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C263" s="5">
+        <f t="shared" si="7"/>
+        <v>260</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E263" s="84"/>
+      <c r="F263" s="48"/>
+      <c r="L263" s="7"/>
+      <c r="M263" s="9"/>
+      <c r="N263" s="11"/>
+      <c r="O263" s="13"/>
+      <c r="P263" s="15"/>
+      <c r="Q263" s="17"/>
+      <c r="R263" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C264" s="5">
+        <f t="shared" si="7"/>
+        <v>261</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E264" s="84"/>
+      <c r="F264" s="48"/>
+      <c r="L264" s="7"/>
+      <c r="M264" s="9"/>
+      <c r="N264" s="11"/>
+      <c r="O264" s="13"/>
+      <c r="P264" s="15"/>
+      <c r="Q264" s="17"/>
+      <c r="R264" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="3:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C265" s="5">
+        <f t="shared" si="7"/>
+        <v>262</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E265" s="85"/>
+      <c r="F265" s="86"/>
+      <c r="L265" s="7"/>
+      <c r="M265" s="9"/>
+      <c r="N265" s="11"/>
+      <c r="O265" s="13"/>
+      <c r="P265" s="15"/>
+      <c r="Q265" s="17"/>
+      <c r="R265" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F0BB076-400D-4122-B0D4-259A8E221B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1908D8-5A69-4EF9-A356-3C2AD90DC632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="267">
+  <futureMetadata name="XLRICHVALUE" count="270">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -1910,8 +1910,29 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="267"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="268"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="269"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="267">
+  <valueMetadata count="270">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -2712,13 +2733,22 @@
     </bk>
     <bk>
       <rc t="1" v="266"/>
+    </bk>
+    <bk>
+      <rc t="1" v="267"/>
+    </bk>
+    <bk>
+      <rc t="1" v="268"/>
+    </bk>
+    <bk>
+      <rc t="1" v="269"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="369">
   <si>
     <t>Base stats</t>
   </si>
@@ -3841,6 +3871,18 @@
   </si>
   <si>
     <t>Tropius</t>
+  </si>
+  <si>
+    <t>Fantyrm</t>
+  </si>
+  <si>
+    <t>Dispareptil</t>
+  </si>
+  <si>
+    <t>Lanssorien</t>
+  </si>
+  <si>
+    <t>lv.60</t>
   </si>
 </sst>
 </file>
@@ -4037,7 +4079,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -4190,41 +4232,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4474,8 +4486,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -5080,7 +5090,7 @@
                   <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>21</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>26</c:v>
@@ -5101,7 +5111,7 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>15</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5847,7 +5857,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="267">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="270">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -6914,6 +6924,18 @@
   </rv>
   <rv s="0">
     <v>266</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>267</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>268</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>269</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -7197,6 +7219,9 @@
   <rel r:id="rId265"/>
   <rel r:id="rId266"/>
   <rel r:id="rId267"/>
+  <rel r:id="rId268"/>
+  <rel r:id="rId269"/>
+  <rel r:id="rId270"/>
 </richValueRels>
 </file>
 
@@ -7490,14 +7515,14 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="87" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="87"/>
+      <c r="L2" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
     </row>
     <row r="3" spans="2:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
@@ -7515,14 +7540,14 @@
       <c r="F3" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="88" t="s">
+      <c r="G3" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88" t="s">
+      <c r="H3" s="86"/>
+      <c r="I3" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="88"/>
+      <c r="J3" s="86"/>
       <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
@@ -8170,7 +8195,7 @@
       </c>
       <c r="T14" s="20">
         <f>COUNTIF(E$6:F$265, "Ghost")</f>
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8486,7 +8511,7 @@
       </c>
       <c r="T21" s="20">
         <f>COUNTIF(E$6:F$265, "Dragon")</f>
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15523,7 +15548,7 @@
       </c>
     </row>
     <row r="200" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B200" s="5" t="e" vm="211">
+      <c r="B200" t="e" vm="211">
         <v>#VALUE!</v>
       </c>
       <c r="C200" s="5">
@@ -15531,26 +15556,22 @@
         <v>197</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="E200" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F200" s="46"/>
-      <c r="G200" s="1" t="e" vm="3">
+      <c r="F200" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="G200" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I200" s="1" t="e" vm="26">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J200" s="1" t="s">
         <v>54</v>
       </c>
       <c r="K200" s="1" t="s">
-        <v>295</v>
+        <v>173</v>
       </c>
       <c r="L200" s="7"/>
       <c r="M200" s="9"/>
@@ -15564,7 +15585,7 @@
       </c>
     </row>
     <row r="201" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B201" s="5" t="e" vm="212">
+      <c r="B201" t="e" vm="212">
         <v>#VALUE!</v>
       </c>
       <c r="C201" s="5">
@@ -15572,22 +15593,18 @@
         <v>198</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="E201" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F201" s="46"/>
-      <c r="G201" s="1" t="e" vm="3">
+      <c r="F201" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="G201" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I201" s="1" t="e" vm="26">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J201" s="1" t="s">
         <v>54</v>
       </c>
       <c r="K201" s="1" t="s">
@@ -17299,7 +17316,7 @@
       </c>
     </row>
     <row r="249" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B249" t="e" vm="261">
+      <c r="B249" s="5" t="e" vm="261">
         <v>#VALUE!</v>
       </c>
       <c r="C249" s="5">
@@ -17307,22 +17324,26 @@
         <v>246</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>358</v>
+        <v>294</v>
       </c>
       <c r="E249" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F249" s="67" t="s">
-        <v>63</v>
-      </c>
-      <c r="G249" s="1" t="e" vm="26">
+      <c r="F249" s="46"/>
+      <c r="G249" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="H249" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I249" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J249" s="1" t="s">
         <v>54</v>
       </c>
       <c r="K249" s="1" t="s">
-        <v>173</v>
+        <v>295</v>
       </c>
       <c r="L249" s="7"/>
       <c r="M249" s="9"/>
@@ -17331,12 +17352,12 @@
       <c r="P249" s="15"/>
       <c r="Q249" s="17"/>
       <c r="R249" s="40">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="R249:R250" si="10">SUM(L249:Q249)</f>
         <v>0</v>
       </c>
     </row>
     <row r="250" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B250" t="e" vm="262">
+      <c r="B250" s="5" t="e" vm="262">
         <v>#VALUE!</v>
       </c>
       <c r="C250" s="5">
@@ -17344,18 +17365,22 @@
         <v>247</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="E250" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F250" s="67" t="s">
-        <v>63</v>
-      </c>
-      <c r="G250" s="1" t="e" vm="26">
+      <c r="F250" s="46"/>
+      <c r="G250" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="H250" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I250" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J250" s="1" t="s">
         <v>54</v>
       </c>
       <c r="K250" s="1" t="s">
@@ -17368,7 +17393,7 @@
       <c r="P250" s="15"/>
       <c r="Q250" s="17"/>
       <c r="R250" s="40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -17576,15 +17601,37 @@
       </c>
     </row>
     <row r="256" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B256" t="e" vm="268">
+        <v>#VALUE!</v>
+      </c>
       <c r="C256" s="5">
         <f t="shared" si="7"/>
         <v>253</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E256" s="84"/>
-      <c r="F256" s="48"/>
+        <v>365</v>
+      </c>
+      <c r="E256" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="F256" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="G256" s="1" t="e" vm="74">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H256" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I256" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J256" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K256" s="1" t="s">
+        <v>295</v>
+      </c>
       <c r="L256" s="7"/>
       <c r="M256" s="9"/>
       <c r="N256" s="11"/>
@@ -17596,16 +17643,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B257" t="e" vm="269">
+        <v>#VALUE!</v>
+      </c>
       <c r="C257" s="5">
         <f t="shared" si="7"/>
         <v>254</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E257" s="84"/>
-      <c r="F257" s="48"/>
+        <v>366</v>
+      </c>
+      <c r="E257" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="F257" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="G257" s="1" t="e" vm="74">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H257" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I257" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J257" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K257" s="1" t="s">
+        <v>368</v>
+      </c>
       <c r="L257" s="7"/>
       <c r="M257" s="9"/>
       <c r="N257" s="11"/>
@@ -17617,16 +17686,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B258" t="e" vm="270">
+        <v>#VALUE!</v>
+      </c>
       <c r="C258" s="5">
         <f t="shared" si="7"/>
         <v>255</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E258" s="84"/>
-      <c r="F258" s="48"/>
+        <v>367</v>
+      </c>
+      <c r="E258" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="F258" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="G258" s="1" t="e" vm="74">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H258" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I258" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J258" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K258" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L258" s="7"/>
       <c r="M258" s="9"/>
       <c r="N258" s="11"/>
@@ -17638,7 +17729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C259" s="5">
         <f t="shared" si="7"/>
         <v>256</v>
@@ -17659,7 +17750,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B260" s="5"/>
       <c r="C260" s="5">
         <f t="shared" si="7"/>
         <v>257</v>
@@ -17669,18 +17761,21 @@
       </c>
       <c r="E260" s="84"/>
       <c r="F260" s="48"/>
+      <c r="G260" s="1"/>
+      <c r="H260" s="1"/>
+      <c r="I260" s="1"/>
+      <c r="J260" s="1"/>
+      <c r="K260" s="1"/>
       <c r="L260" s="7"/>
       <c r="M260" s="9"/>
       <c r="N260" s="11"/>
       <c r="O260" s="13"/>
       <c r="P260" s="15"/>
       <c r="Q260" s="17"/>
-      <c r="R260" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R260" s="40"/>
+    </row>
+    <row r="261" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B261" s="5"/>
       <c r="C261" s="5">
         <f t="shared" si="7"/>
         <v>258</v>
@@ -17690,18 +17785,20 @@
       </c>
       <c r="E261" s="84"/>
       <c r="F261" s="48"/>
+      <c r="G261" s="1"/>
+      <c r="H261" s="1"/>
+      <c r="I261" s="1"/>
+      <c r="J261" s="1"/>
+      <c r="K261" s="1"/>
       <c r="L261" s="7"/>
       <c r="M261" s="9"/>
       <c r="N261" s="11"/>
       <c r="O261" s="13"/>
       <c r="P261" s="15"/>
       <c r="Q261" s="17"/>
-      <c r="R261" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R261" s="40"/>
+    </row>
+    <row r="262" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C262" s="5">
         <f t="shared" si="7"/>
         <v>259</v>
@@ -17722,7 +17819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C263" s="5">
         <f t="shared" si="7"/>
         <v>260</v>
@@ -17743,7 +17840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C264" s="5">
         <f t="shared" si="7"/>
         <v>261</v>
@@ -17764,7 +17861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="3:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C265" s="5">
         <f t="shared" si="7"/>
         <v>262</v>
@@ -17772,8 +17869,8 @@
       <c r="D265" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E265" s="85"/>
-      <c r="F265" s="86"/>
+      <c r="E265" s="84"/>
+      <c r="F265" s="48"/>
       <c r="L265" s="7"/>
       <c r="M265" s="9"/>
       <c r="N265" s="11"/>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E0FB9F2-6250-48DA-B26D-A3B9A9DFCA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1908D8-5A69-4EF9-A356-3C2AD90DC632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="234">
+  <futureMetadata name="XLRICHVALUE" count="270">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -1679,8 +1679,260 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="234"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="235"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="236"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="237"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="238"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="239"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="240"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="241"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="242"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="243"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="244"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="245"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="246"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="247"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="248"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="249"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="250"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="251"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="252"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="253"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="254"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="255"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="256"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="257"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="258"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="259"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="260"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="261"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="262"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="263"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="264"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="265"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="266"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="267"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="268"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="269"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="234">
+  <valueMetadata count="270">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -2382,13 +2634,121 @@
     </bk>
     <bk>
       <rc t="1" v="233"/>
+    </bk>
+    <bk>
+      <rc t="1" v="234"/>
+    </bk>
+    <bk>
+      <rc t="1" v="235"/>
+    </bk>
+    <bk>
+      <rc t="1" v="236"/>
+    </bk>
+    <bk>
+      <rc t="1" v="237"/>
+    </bk>
+    <bk>
+      <rc t="1" v="238"/>
+    </bk>
+    <bk>
+      <rc t="1" v="239"/>
+    </bk>
+    <bk>
+      <rc t="1" v="240"/>
+    </bk>
+    <bk>
+      <rc t="1" v="241"/>
+    </bk>
+    <bk>
+      <rc t="1" v="242"/>
+    </bk>
+    <bk>
+      <rc t="1" v="243"/>
+    </bk>
+    <bk>
+      <rc t="1" v="244"/>
+    </bk>
+    <bk>
+      <rc t="1" v="245"/>
+    </bk>
+    <bk>
+      <rc t="1" v="246"/>
+    </bk>
+    <bk>
+      <rc t="1" v="247"/>
+    </bk>
+    <bk>
+      <rc t="1" v="248"/>
+    </bk>
+    <bk>
+      <rc t="1" v="249"/>
+    </bk>
+    <bk>
+      <rc t="1" v="250"/>
+    </bk>
+    <bk>
+      <rc t="1" v="251"/>
+    </bk>
+    <bk>
+      <rc t="1" v="252"/>
+    </bk>
+    <bk>
+      <rc t="1" v="253"/>
+    </bk>
+    <bk>
+      <rc t="1" v="254"/>
+    </bk>
+    <bk>
+      <rc t="1" v="255"/>
+    </bk>
+    <bk>
+      <rc t="1" v="256"/>
+    </bk>
+    <bk>
+      <rc t="1" v="257"/>
+    </bk>
+    <bk>
+      <rc t="1" v="258"/>
+    </bk>
+    <bk>
+      <rc t="1" v="259"/>
+    </bk>
+    <bk>
+      <rc t="1" v="260"/>
+    </bk>
+    <bk>
+      <rc t="1" v="261"/>
+    </bk>
+    <bk>
+      <rc t="1" v="262"/>
+    </bk>
+    <bk>
+      <rc t="1" v="263"/>
+    </bk>
+    <bk>
+      <rc t="1" v="264"/>
+    </bk>
+    <bk>
+      <rc t="1" v="265"/>
+    </bk>
+    <bk>
+      <rc t="1" v="266"/>
+    </bk>
+    <bk>
+      <rc t="1" v="267"/>
+    </bk>
+    <bk>
+      <rc t="1" v="268"/>
+    </bk>
+    <bk>
+      <rc t="1" v="269"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="369">
   <si>
     <t>Base stats</t>
   </si>
@@ -3400,6 +3760,129 @@
   </si>
   <si>
     <t>lv.49</t>
+  </si>
+  <si>
+    <t>Eevee</t>
+  </si>
+  <si>
+    <t>Vaporeon</t>
+  </si>
+  <si>
+    <t>Jolteon</t>
+  </si>
+  <si>
+    <t>Flareon</t>
+  </si>
+  <si>
+    <t>Espeon</t>
+  </si>
+  <si>
+    <t>Umbreon</t>
+  </si>
+  <si>
+    <t>Leafeon</t>
+  </si>
+  <si>
+    <t>Glaceon</t>
+  </si>
+  <si>
+    <t>Sylveon</t>
+  </si>
+  <si>
+    <t>Rufflet</t>
+  </si>
+  <si>
+    <t>Braviary</t>
+  </si>
+  <si>
+    <t>Vullaby</t>
+  </si>
+  <si>
+    <t>Mandibuzz</t>
+  </si>
+  <si>
+    <t>lv.54</t>
+  </si>
+  <si>
+    <t>Ditto</t>
+  </si>
+  <si>
+    <t>Scyther</t>
+  </si>
+  <si>
+    <t>Scizor</t>
+  </si>
+  <si>
+    <t>Kleavor</t>
+  </si>
+  <si>
+    <t>holding metal coat and level up (Scizor) or holding black augurite and level up (Kleavor)</t>
+  </si>
+  <si>
+    <t>holding magmarizer and level up</t>
+  </si>
+  <si>
+    <t>holding electrizer and level up</t>
+  </si>
+  <si>
+    <t>Magby</t>
+  </si>
+  <si>
+    <t>Magmar</t>
+  </si>
+  <si>
+    <t>Magmortar</t>
+  </si>
+  <si>
+    <t>Elekid</t>
+  </si>
+  <si>
+    <t>Electabuzz</t>
+  </si>
+  <si>
+    <t>Electivire</t>
+  </si>
+  <si>
+    <t>water stone (Vaporeon), thunder stone (Jolteon), fire stone (flareon), high friendship at day (Espeon), high friendship at night (Umbreon), leaf stone (Leafeon), ice stone (Glaceon), shiny stone (Sylveon)</t>
+  </si>
+  <si>
+    <t>Woobat</t>
+  </si>
+  <si>
+    <t>Swoobat</t>
+  </si>
+  <si>
+    <t>Meditite</t>
+  </si>
+  <si>
+    <t>Medicham</t>
+  </si>
+  <si>
+    <t>Zangoose</t>
+  </si>
+  <si>
+    <t>Seviper</t>
+  </si>
+  <si>
+    <t>Corphish</t>
+  </si>
+  <si>
+    <t>Crawdaunt</t>
+  </si>
+  <si>
+    <t>Tropius</t>
+  </si>
+  <si>
+    <t>Fantyrm</t>
+  </si>
+  <si>
+    <t>Dispareptil</t>
+  </si>
+  <si>
+    <t>Lanssorien</t>
+  </si>
+  <si>
+    <t>lv.60</t>
   </si>
 </sst>
 </file>
@@ -3596,7 +4079,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -3749,41 +4232,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4033,8 +4486,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -4609,58 +5060,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>24</c:v>
+                <c:pt idx="5">
+                  <c:v>25</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>18</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>13</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>19</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>20</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>22</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>19</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>21</c:v>
-                </c:pt>
                 <c:pt idx="14">
-                  <c:v>12</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>15</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>15</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>15</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5406,7 +5857,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="234">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="270">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -6341,6 +6792,150 @@
   </rv>
   <rv s="0">
     <v>233</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>234</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>235</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>236</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>237</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>238</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>239</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>240</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>241</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>242</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>243</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>244</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>245</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>246</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>247</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>248</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>249</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>250</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>251</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>252</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>253</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>254</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>255</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>256</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>257</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>258</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>259</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>260</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>261</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>262</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>263</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>264</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>265</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>266</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>267</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>268</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>269</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -6591,6 +7186,42 @@
   <rel r:id="rId232"/>
   <rel r:id="rId233"/>
   <rel r:id="rId234"/>
+  <rel r:id="rId235"/>
+  <rel r:id="rId236"/>
+  <rel r:id="rId237"/>
+  <rel r:id="rId238"/>
+  <rel r:id="rId239"/>
+  <rel r:id="rId240"/>
+  <rel r:id="rId241"/>
+  <rel r:id="rId242"/>
+  <rel r:id="rId243"/>
+  <rel r:id="rId244"/>
+  <rel r:id="rId245"/>
+  <rel r:id="rId246"/>
+  <rel r:id="rId247"/>
+  <rel r:id="rId248"/>
+  <rel r:id="rId249"/>
+  <rel r:id="rId250"/>
+  <rel r:id="rId251"/>
+  <rel r:id="rId252"/>
+  <rel r:id="rId253"/>
+  <rel r:id="rId254"/>
+  <rel r:id="rId255"/>
+  <rel r:id="rId256"/>
+  <rel r:id="rId257"/>
+  <rel r:id="rId258"/>
+  <rel r:id="rId259"/>
+  <rel r:id="rId260"/>
+  <rel r:id="rId261"/>
+  <rel r:id="rId262"/>
+  <rel r:id="rId263"/>
+  <rel r:id="rId264"/>
+  <rel r:id="rId265"/>
+  <rel r:id="rId266"/>
+  <rel r:id="rId267"/>
+  <rel r:id="rId268"/>
+  <rel r:id="rId269"/>
+  <rel r:id="rId270"/>
 </richValueRels>
 </file>
 
@@ -6858,7 +7489,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:T250"/>
+  <dimension ref="B1:T265"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
@@ -6884,14 +7515,14 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="87" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="87"/>
-      <c r="N2" s="87"/>
-      <c r="O2" s="87"/>
-      <c r="P2" s="87"/>
-      <c r="Q2" s="87"/>
+      <c r="L2" s="85" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="85"/>
+      <c r="Q2" s="85"/>
     </row>
     <row r="3" spans="2:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
@@ -6909,14 +7540,14 @@
       <c r="F3" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="88" t="s">
+      <c r="G3" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88" t="s">
+      <c r="H3" s="86"/>
+      <c r="I3" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="88"/>
+      <c r="J3" s="86"/>
       <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
@@ -7001,8 +7632,8 @@
         <v>16</v>
       </c>
       <c r="T4" s="19">
-        <f>COUNTIF(E$6:F$250, "Grass")</f>
-        <v>20</v>
+        <f>COUNTIF(E$6:F$265, "Grass")</f>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7061,8 +7692,8 @@
         <v>24</v>
       </c>
       <c r="T5" s="20">
-        <f>COUNTIF(E$6:F$250, "Fire")</f>
-        <v>24</v>
+        <f>COUNTIF(E$6:F$265, "Fire")</f>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7121,8 +7752,8 @@
         <v>30</v>
       </c>
       <c r="T6" s="20">
-        <f>COUNTIF(E$6:F$250, "Water")</f>
-        <v>41</v>
+        <f>COUNTIF(E$6:F$265, "Water")</f>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7177,8 +7808,8 @@
         <v>37</v>
       </c>
       <c r="T7" s="20">
-        <f>COUNTIF(E$6:F$250, "Normal")</f>
-        <v>16</v>
+        <f>COUNTIF(E$6:F$265, "Normal")</f>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7235,8 +7866,8 @@
         <v>27</v>
       </c>
       <c r="T8" s="20">
-        <f>COUNTIF(E$6:F$250, "Fighting")</f>
-        <v>18</v>
+        <f>COUNTIF(E$6:F$265, "Fighting")</f>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7293,8 +7924,8 @@
         <v>41</v>
       </c>
       <c r="T9" s="20">
-        <f>COUNTIF(E$6:F$250, "Flying")</f>
-        <v>17</v>
+        <f>COUNTIF(E$6:F$265, "Flying")</f>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7353,8 +7984,8 @@
         <v>63</v>
       </c>
       <c r="T10" s="20">
-        <f>COUNTIF(E$6:F$250, "Psychic")</f>
-        <v>13</v>
+        <f>COUNTIF(E$6:F$265, "Psychic")</f>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7413,8 +8044,8 @@
         <v>45</v>
       </c>
       <c r="T11" s="20">
-        <f>COUNTIF(E$6:F$250, "Bug")</f>
-        <v>19</v>
+        <f>COUNTIF(E$6:F$265, "Bug")</f>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7475,7 +8106,7 @@
         <v>50</v>
       </c>
       <c r="T12" s="20">
-        <f>COUNTIF(E$6:F$250, "Ground")</f>
+        <f>COUNTIF(E$6:F$265, "Ground")</f>
         <v>20</v>
       </c>
     </row>
@@ -7519,8 +8150,8 @@
         <v>64</v>
       </c>
       <c r="T13" s="20">
-        <f>COUNTIF(E$6:F$250, "Rock")</f>
-        <v>20</v>
+        <f>COUNTIF(E$6:F$265, "Rock")</f>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7563,8 +8194,8 @@
         <v>65</v>
       </c>
       <c r="T14" s="20">
-        <f>COUNTIF(E$6:F$250, "Ghost")</f>
-        <v>21</v>
+        <f>COUNTIF(E$6:F$265, "Ghost")</f>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7607,8 +8238,8 @@
         <v>48</v>
       </c>
       <c r="T15" s="20">
-        <f>COUNTIF(E$6:F$250, "Dark")</f>
-        <v>22</v>
+        <f>COUNTIF(E$6:F$265, "Dark")</f>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7653,8 +8284,8 @@
         <v>66</v>
       </c>
       <c r="T16" s="20">
-        <f>COUNTIF(E$6:F$250, "Ice")</f>
-        <v>19</v>
+        <f>COUNTIF(E$6:F$265, "Ice")</f>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7699,8 +8330,8 @@
         <v>34</v>
       </c>
       <c r="T17" s="20">
-        <f>COUNTIF(E$6:F$250, "Steel")</f>
-        <v>21</v>
+        <f>COUNTIF(E$6:F$265, "Steel")</f>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7745,8 +8376,8 @@
         <v>67</v>
       </c>
       <c r="T18" s="20">
-        <f>COUNTIF(E$6:F$250, "Electrik")</f>
-        <v>12</v>
+        <f>COUNTIF(E$6:F$265, "Electrik")</f>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7789,8 +8420,8 @@
         <v>68</v>
       </c>
       <c r="T19" s="20">
-        <f>COUNTIF(E$6:F$250, "Poison")</f>
-        <v>15</v>
+        <f>COUNTIF(E$6:F$265, "Poison")</f>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7835,8 +8466,8 @@
         <v>60</v>
       </c>
       <c r="T20" s="20">
-        <f>COUNTIF(E$6:F$250, "Fairy")</f>
-        <v>15</v>
+        <f>COUNTIF(E$6:F$265, "Fairy")</f>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7879,8 +8510,8 @@
         <v>69</v>
       </c>
       <c r="T21" s="20">
-        <f>COUNTIF(E$6:F$250, "Dragon")</f>
-        <v>15</v>
+        <f>COUNTIF(E$6:F$265, "Dragon")</f>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14843,7 +15474,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C198" s="5">
-        <f t="shared" ref="C198:C250" si="7">C197+1</f>
+        <f t="shared" ref="C198:C265" si="7">C197+1</f>
         <v>195</v>
       </c>
       <c r="D198" s="1" t="s">
@@ -14917,7 +15548,7 @@
       </c>
     </row>
     <row r="200" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B200" s="5" t="e" vm="211">
+      <c r="B200" t="e" vm="211">
         <v>#VALUE!</v>
       </c>
       <c r="C200" s="5">
@@ -14925,26 +15556,22 @@
         <v>197</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="E200" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F200" s="46"/>
-      <c r="G200" s="1" t="e" vm="3">
+      <c r="F200" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="G200" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I200" s="1" t="e" vm="26">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J200" s="1" t="s">
         <v>54</v>
       </c>
       <c r="K200" s="1" t="s">
-        <v>295</v>
+        <v>173</v>
       </c>
       <c r="L200" s="7"/>
       <c r="M200" s="9"/>
@@ -14958,7 +15585,7 @@
       </c>
     </row>
     <row r="201" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B201" s="5" t="e" vm="212">
+      <c r="B201" t="e" vm="212">
         <v>#VALUE!</v>
       </c>
       <c r="C201" s="5">
@@ -14966,22 +15593,18 @@
         <v>198</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="E201" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F201" s="46"/>
-      <c r="G201" s="1" t="e" vm="3">
+      <c r="F201" s="67" t="s">
+        <v>63</v>
+      </c>
+      <c r="G201" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I201" s="1" t="e" vm="26">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J201" s="1" t="s">
         <v>54</v>
       </c>
       <c r="K201" s="1" t="s">
@@ -15031,7 +15654,7 @@
       <c r="P202" s="15"/>
       <c r="Q202" s="17"/>
       <c r="R202" s="40">
-        <f t="shared" ref="R202:R250" si="9">SUM(L202:Q202)</f>
+        <f t="shared" ref="R202:R265" si="9">SUM(L202:Q202)</f>
         <v>0</v>
       </c>
     </row>
@@ -15732,15 +16355,29 @@
       </c>
     </row>
     <row r="221" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B221" t="e" vm="232">
+        <v>#VALUE!</v>
+      </c>
       <c r="C221" s="5">
         <f t="shared" si="7"/>
         <v>218</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E221" s="84"/>
+        <v>328</v>
+      </c>
+      <c r="E221" s="52" t="s">
+        <v>37</v>
+      </c>
       <c r="F221" s="48"/>
+      <c r="G221" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K221" s="1" t="s">
+        <v>355</v>
+      </c>
       <c r="L221" s="7"/>
       <c r="M221" s="9"/>
       <c r="N221" s="11"/>
@@ -15753,28 +16390,39 @@
       </c>
     </row>
     <row r="222" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B222" t="e" vm="233">
+        <v>#VALUE!</v>
+      </c>
       <c r="C222" s="5">
         <f t="shared" si="7"/>
         <v>219</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E222" s="84"/>
+        <v>329</v>
+      </c>
+      <c r="E222" s="50" t="s">
+        <v>30</v>
+      </c>
       <c r="F222" s="48"/>
+      <c r="G222" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H222" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K222" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L222" s="7"/>
       <c r="M222" s="9"/>
       <c r="N222" s="11"/>
       <c r="O222" s="13"/>
       <c r="P222" s="15"/>
       <c r="Q222" s="17"/>
-      <c r="R222" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R222" s="40"/>
     </row>
     <row r="223" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B223" t="e" vm="232">
+      <c r="B223" t="e" vm="234">
         <v>#VALUE!</v>
       </c>
       <c r="C223" s="5">
@@ -15782,20 +16430,20 @@
         <v>220</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E223" s="70" t="s">
-        <v>34</v>
+        <v>330</v>
+      </c>
+      <c r="E223" s="62" t="s">
+        <v>67</v>
       </c>
       <c r="F223" s="48"/>
-      <c r="G223" s="1" t="e" vm="34">
+      <c r="G223" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="K223" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="L223" s="7"/>
       <c r="M223" s="9"/>
@@ -15803,13 +16451,10 @@
       <c r="O223" s="13"/>
       <c r="P223" s="15"/>
       <c r="Q223" s="17"/>
-      <c r="R223" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R223" s="40"/>
     </row>
     <row r="224" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B224" t="e" vm="233">
+      <c r="B224" t="e" vm="235">
         <v>#VALUE!</v>
       </c>
       <c r="C224" s="5">
@@ -15817,20 +16462,20 @@
         <v>221</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="E224" s="70" t="s">
-        <v>34</v>
+        <v>331</v>
+      </c>
+      <c r="E224" s="47" t="s">
+        <v>24</v>
       </c>
       <c r="F224" s="48"/>
-      <c r="G224" s="1" t="e" vm="34">
+      <c r="G224" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>327</v>
+        <v>22</v>
       </c>
       <c r="L224" s="7"/>
       <c r="M224" s="9"/>
@@ -15838,13 +16483,10 @@
       <c r="O224" s="13"/>
       <c r="P224" s="15"/>
       <c r="Q224" s="17"/>
-      <c r="R224" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R224" s="40"/>
     </row>
     <row r="225" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B225" t="e" vm="234">
+      <c r="B225" t="e" vm="236">
         <v>#VALUE!</v>
       </c>
       <c r="C225" s="5">
@@ -15852,17 +16494,17 @@
         <v>222</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E225" s="70" t="s">
-        <v>34</v>
+        <v>332</v>
+      </c>
+      <c r="E225" s="71" t="s">
+        <v>63</v>
       </c>
       <c r="F225" s="48"/>
-      <c r="G225" s="1" t="e" vm="34">
+      <c r="G225" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="K225" s="1" t="s">
         <v>22</v>
@@ -15873,168 +16515,264 @@
       <c r="O225" s="13"/>
       <c r="P225" s="15"/>
       <c r="Q225" s="17"/>
-      <c r="R225" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R225" s="40"/>
     </row>
     <row r="226" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B226" t="e" vm="237">
+        <v>#VALUE!</v>
+      </c>
       <c r="C226" s="5">
         <f t="shared" si="7"/>
         <v>223</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E226" s="84"/>
+        <v>333</v>
+      </c>
+      <c r="E226" s="73" t="s">
+        <v>48</v>
+      </c>
       <c r="F226" s="48"/>
+      <c r="G226" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H226" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K226" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L226" s="7"/>
       <c r="M226" s="9"/>
       <c r="N226" s="11"/>
       <c r="O226" s="13"/>
       <c r="P226" s="15"/>
       <c r="Q226" s="17"/>
-      <c r="R226" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R226" s="40"/>
     </row>
     <row r="227" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B227" t="e" vm="238">
+        <v>#VALUE!</v>
+      </c>
       <c r="C227" s="5">
         <f t="shared" si="7"/>
         <v>224</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E227" s="84"/>
+        <v>334</v>
+      </c>
+      <c r="E227" s="45" t="s">
+        <v>16</v>
+      </c>
       <c r="F227" s="48"/>
+      <c r="G227" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H227" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K227" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L227" s="7"/>
       <c r="M227" s="9"/>
       <c r="N227" s="11"/>
       <c r="O227" s="13"/>
       <c r="P227" s="15"/>
       <c r="Q227" s="17"/>
-      <c r="R227" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R227" s="40"/>
     </row>
     <row r="228" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B228" t="e" vm="239">
+        <v>#VALUE!</v>
+      </c>
       <c r="C228" s="5">
         <f t="shared" si="7"/>
         <v>225</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E228" s="84"/>
+        <v>335</v>
+      </c>
+      <c r="E228" s="64" t="s">
+        <v>66</v>
+      </c>
       <c r="F228" s="48"/>
+      <c r="G228" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H228" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K228" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L228" s="7"/>
       <c r="M228" s="9"/>
       <c r="N228" s="11"/>
       <c r="O228" s="13"/>
       <c r="P228" s="15"/>
       <c r="Q228" s="17"/>
-      <c r="R228" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R228" s="40"/>
     </row>
     <row r="229" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B229" t="e" vm="240">
+        <v>#VALUE!</v>
+      </c>
       <c r="C229" s="5">
         <f t="shared" si="7"/>
         <v>226</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E229" s="84"/>
+        <v>336</v>
+      </c>
+      <c r="E229" s="72" t="s">
+        <v>60</v>
+      </c>
       <c r="F229" s="48"/>
+      <c r="G229" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H229" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K229" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L229" s="7"/>
       <c r="M229" s="9"/>
       <c r="N229" s="11"/>
       <c r="O229" s="13"/>
       <c r="P229" s="15"/>
       <c r="Q229" s="17"/>
-      <c r="R229" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R229" s="40"/>
     </row>
     <row r="230" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B230" t="e" vm="241">
+        <v>#VALUE!</v>
+      </c>
       <c r="C230" s="5">
         <f t="shared" si="7"/>
         <v>227</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E230" s="84"/>
-      <c r="F230" s="48"/>
+        <v>337</v>
+      </c>
+      <c r="E230" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="F230" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G230" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H230" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K230" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="L230" s="7"/>
       <c r="M230" s="9"/>
       <c r="N230" s="11"/>
       <c r="O230" s="13"/>
       <c r="P230" s="15"/>
       <c r="Q230" s="17"/>
-      <c r="R230" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R230" s="40"/>
     </row>
     <row r="231" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B231" t="e" vm="242">
+        <v>#VALUE!</v>
+      </c>
       <c r="C231" s="5">
         <f t="shared" si="7"/>
         <v>228</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E231" s="84"/>
-      <c r="F231" s="48"/>
+        <v>338</v>
+      </c>
+      <c r="E231" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="F231" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G231" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H231" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K231" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L231" s="7"/>
       <c r="M231" s="9"/>
       <c r="N231" s="11"/>
       <c r="O231" s="13"/>
       <c r="P231" s="15"/>
       <c r="Q231" s="17"/>
-      <c r="R231" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R231" s="40"/>
     </row>
     <row r="232" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B232" t="e" vm="243">
+        <v>#VALUE!</v>
+      </c>
       <c r="C232" s="5">
         <f t="shared" si="7"/>
         <v>229</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E232" s="84"/>
-      <c r="F232" s="48"/>
+        <v>339</v>
+      </c>
+      <c r="E232" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F232" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G232" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H232" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K232" s="1" t="s">
+        <v>341</v>
+      </c>
       <c r="L232" s="7"/>
       <c r="M232" s="9"/>
       <c r="N232" s="11"/>
       <c r="O232" s="13"/>
       <c r="P232" s="15"/>
       <c r="Q232" s="17"/>
-      <c r="R232" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R232" s="40"/>
     </row>
     <row r="233" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B233" t="e" vm="244">
+        <v>#VALUE!</v>
+      </c>
       <c r="C233" s="5">
         <f t="shared" si="7"/>
         <v>230</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E233" s="84"/>
-      <c r="F233" s="48"/>
+        <v>340</v>
+      </c>
+      <c r="E233" s="73" t="s">
+        <v>48</v>
+      </c>
+      <c r="F233" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G233" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H233" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K233" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L233" s="7"/>
       <c r="M233" s="9"/>
       <c r="N233" s="11"/>
@@ -16047,99 +16785,159 @@
       </c>
     </row>
     <row r="234" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B234" t="e" vm="245">
+        <v>#VALUE!</v>
+      </c>
       <c r="C234" s="5">
         <f t="shared" si="7"/>
         <v>231</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E234" s="84"/>
+        <v>342</v>
+      </c>
+      <c r="E234" s="52" t="s">
+        <v>37</v>
+      </c>
       <c r="F234" s="48"/>
+      <c r="G234" s="1" t="e" vm="246">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H234" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="K234" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L234" s="7"/>
       <c r="M234" s="9"/>
       <c r="N234" s="11"/>
       <c r="O234" s="13"/>
       <c r="P234" s="15"/>
       <c r="Q234" s="17"/>
-      <c r="R234" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R234" s="40"/>
     </row>
     <row r="235" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B235" t="e" vm="247">
+        <v>#VALUE!</v>
+      </c>
       <c r="C235" s="5">
         <f t="shared" si="7"/>
         <v>232</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E235" s="84"/>
-      <c r="F235" s="48"/>
+        <v>343</v>
+      </c>
+      <c r="E235" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="F235" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G235" s="1" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K235" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="L235" s="7"/>
       <c r="M235" s="9"/>
       <c r="N235" s="11"/>
       <c r="O235" s="13"/>
       <c r="P235" s="15"/>
       <c r="Q235" s="17"/>
-      <c r="R235" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R235" s="40"/>
     </row>
     <row r="236" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B236" t="e" vm="248">
+        <v>#VALUE!</v>
+      </c>
       <c r="C236" s="5">
         <f t="shared" si="7"/>
         <v>233</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E236" s="84"/>
-      <c r="F236" s="48"/>
+        <v>344</v>
+      </c>
+      <c r="E236" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="F236" s="51" t="s">
+        <v>34</v>
+      </c>
+      <c r="G236" s="1" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K236" s="1"/>
       <c r="L236" s="7"/>
       <c r="M236" s="9"/>
       <c r="N236" s="11"/>
       <c r="O236" s="13"/>
       <c r="P236" s="15"/>
       <c r="Q236" s="17"/>
-      <c r="R236" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R236" s="40"/>
     </row>
     <row r="237" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B237" t="e" vm="249">
+        <v>#VALUE!</v>
+      </c>
       <c r="C237" s="5">
         <f t="shared" si="7"/>
         <v>234</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E237" s="84"/>
-      <c r="F237" s="48"/>
+        <v>345</v>
+      </c>
+      <c r="E237" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="F237" s="66" t="s">
+        <v>64</v>
+      </c>
+      <c r="G237" s="1" t="e" vm="21">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K237" s="1"/>
       <c r="L237" s="7"/>
       <c r="M237" s="9"/>
       <c r="N237" s="11"/>
       <c r="O237" s="13"/>
       <c r="P237" s="15"/>
       <c r="Q237" s="17"/>
-      <c r="R237" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="R237" s="40"/>
     </row>
     <row r="238" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B238" t="e" vm="250">
+        <v>#VALUE!</v>
+      </c>
       <c r="C238" s="5">
         <f t="shared" si="7"/>
         <v>235</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E238" s="84"/>
+        <v>349</v>
+      </c>
+      <c r="E238" s="47" t="s">
+        <v>24</v>
+      </c>
       <c r="F238" s="48"/>
+      <c r="G238" s="1" t="e" vm="209">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K238" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="L238" s="7"/>
       <c r="M238" s="9"/>
       <c r="N238" s="11"/>
@@ -16152,15 +16950,29 @@
       </c>
     </row>
     <row r="239" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B239" t="e" vm="251">
+        <v>#VALUE!</v>
+      </c>
       <c r="C239" s="5">
         <f t="shared" si="7"/>
         <v>236</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E239" s="84"/>
+        <v>350</v>
+      </c>
+      <c r="E239" s="47" t="s">
+        <v>24</v>
+      </c>
       <c r="F239" s="48"/>
+      <c r="G239" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H239" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K239" s="1" t="s">
+        <v>347</v>
+      </c>
       <c r="L239" s="7"/>
       <c r="M239" s="9"/>
       <c r="N239" s="11"/>
@@ -16173,15 +16985,29 @@
       </c>
     </row>
     <row r="240" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B240" t="e" vm="252">
+        <v>#VALUE!</v>
+      </c>
       <c r="C240" s="5">
         <f t="shared" si="7"/>
         <v>237</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E240" s="84"/>
+        <v>351</v>
+      </c>
+      <c r="E240" s="47" t="s">
+        <v>24</v>
+      </c>
       <c r="F240" s="48"/>
+      <c r="G240" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K240" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L240" s="7"/>
       <c r="M240" s="9"/>
       <c r="N240" s="11"/>
@@ -16193,16 +17019,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B241" t="e" vm="253">
+        <v>#VALUE!</v>
+      </c>
       <c r="C241" s="5">
         <f t="shared" si="7"/>
         <v>238</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E241" s="84"/>
+        <v>352</v>
+      </c>
+      <c r="E241" s="62" t="s">
+        <v>67</v>
+      </c>
       <c r="F241" s="48"/>
+      <c r="G241" s="1" t="e" vm="209">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H241" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="K241" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="L241" s="7"/>
       <c r="M241" s="9"/>
       <c r="N241" s="11"/>
@@ -16214,16 +17054,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B242" t="e" vm="254">
+        <v>#VALUE!</v>
+      </c>
       <c r="C242" s="5">
         <f t="shared" si="7"/>
         <v>239</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E242" s="84"/>
+        <v>353</v>
+      </c>
+      <c r="E242" s="62" t="s">
+        <v>67</v>
+      </c>
       <c r="F242" s="48"/>
+      <c r="G242" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K242" s="1" t="s">
+        <v>348</v>
+      </c>
       <c r="L242" s="7"/>
       <c r="M242" s="9"/>
       <c r="N242" s="11"/>
@@ -16235,16 +17089,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B243" t="e" vm="255">
+        <v>#VALUE!</v>
+      </c>
       <c r="C243" s="5">
         <f t="shared" si="7"/>
         <v>240</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E243" s="84"/>
+        <v>354</v>
+      </c>
+      <c r="E243" s="62" t="s">
+        <v>67</v>
+      </c>
       <c r="F243" s="48"/>
+      <c r="G243" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H243" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K243" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L243" s="7"/>
       <c r="M243" s="9"/>
       <c r="N243" s="11"/>
@@ -16256,16 +17124,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B244" t="e" vm="256">
+        <v>#VALUE!</v>
+      </c>
       <c r="C244" s="5">
         <f t="shared" si="7"/>
         <v>241</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E244" s="84"/>
+        <v>324</v>
+      </c>
+      <c r="E244" s="70" t="s">
+        <v>34</v>
+      </c>
       <c r="F244" s="48"/>
+      <c r="G244" s="1" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H244" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K244" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="L244" s="7"/>
       <c r="M244" s="9"/>
       <c r="N244" s="11"/>
@@ -16277,16 +17159,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B245" t="e" vm="257">
+        <v>#VALUE!</v>
+      </c>
       <c r="C245" s="5">
         <f t="shared" si="7"/>
         <v>242</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E245" s="84"/>
+        <v>325</v>
+      </c>
+      <c r="E245" s="70" t="s">
+        <v>34</v>
+      </c>
       <c r="F245" s="48"/>
+      <c r="G245" s="1" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H245" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K245" s="1" t="s">
+        <v>327</v>
+      </c>
       <c r="L245" s="7"/>
       <c r="M245" s="9"/>
       <c r="N245" s="11"/>
@@ -16298,16 +17194,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B246" t="e" vm="258">
+        <v>#VALUE!</v>
+      </c>
       <c r="C246" s="5">
         <f t="shared" si="7"/>
         <v>243</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E246" s="84"/>
+        <v>326</v>
+      </c>
+      <c r="E246" s="70" t="s">
+        <v>34</v>
+      </c>
       <c r="F246" s="48"/>
+      <c r="G246" s="1" t="e" vm="34">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H246" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K246" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L246" s="7"/>
       <c r="M246" s="9"/>
       <c r="N246" s="11"/>
@@ -16319,16 +17229,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B247" t="e" vm="259">
+        <v>#VALUE!</v>
+      </c>
       <c r="C247" s="5">
         <f t="shared" si="7"/>
         <v>244</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E247" s="84"/>
-      <c r="F247" s="48"/>
+        <v>356</v>
+      </c>
+      <c r="E247" s="71" t="s">
+        <v>63</v>
+      </c>
+      <c r="F247" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G247" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H247" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I247" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J247" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K247" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="L247" s="7"/>
       <c r="M247" s="9"/>
       <c r="N247" s="11"/>
@@ -16340,16 +17272,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B248" t="e" vm="260">
+        <v>#VALUE!</v>
+      </c>
       <c r="C248" s="5">
         <f t="shared" si="7"/>
         <v>245</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E248" s="84"/>
-      <c r="F248" s="48"/>
+        <v>357</v>
+      </c>
+      <c r="E248" s="71" t="s">
+        <v>63</v>
+      </c>
+      <c r="F248" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G248" s="1" t="e" vm="17">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H248" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I248" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J248" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K248" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L248" s="7"/>
       <c r="M248" s="9"/>
       <c r="N248" s="11"/>
@@ -16361,16 +17315,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="3:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B249" s="5" t="e" vm="261">
+        <v>#VALUE!</v>
+      </c>
       <c r="C249" s="5">
         <f t="shared" si="7"/>
         <v>246</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E249" s="84"/>
-      <c r="F249" s="48"/>
+        <v>294</v>
+      </c>
+      <c r="E249" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="F249" s="46"/>
+      <c r="G249" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H249" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I249" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J249" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K249" s="1" t="s">
+        <v>295</v>
+      </c>
       <c r="L249" s="7"/>
       <c r="M249" s="9"/>
       <c r="N249" s="11"/>
@@ -16378,20 +17352,40 @@
       <c r="P249" s="15"/>
       <c r="Q249" s="17"/>
       <c r="R249" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="3:18" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" ref="R249:R250" si="10">SUM(L249:Q249)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B250" s="5" t="e" vm="262">
+        <v>#VALUE!</v>
+      </c>
       <c r="C250" s="5">
         <f t="shared" si="7"/>
         <v>247</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E250" s="85"/>
-      <c r="F250" s="86"/>
+        <v>296</v>
+      </c>
+      <c r="E250" s="57" t="s">
+        <v>27</v>
+      </c>
+      <c r="F250" s="46"/>
+      <c r="G250" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H250" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I250" s="1" t="e" vm="26">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J250" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K250" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L250" s="7"/>
       <c r="M250" s="9"/>
       <c r="N250" s="11"/>
@@ -16399,6 +17393,491 @@
       <c r="P250" s="15"/>
       <c r="Q250" s="17"/>
       <c r="R250" s="40">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B251" t="e" vm="263">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C251" s="5">
+        <f t="shared" si="7"/>
+        <v>248</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E251" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="F251" s="48"/>
+      <c r="G251" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H251" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K251" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L251" s="7"/>
+      <c r="M251" s="9"/>
+      <c r="N251" s="11"/>
+      <c r="O251" s="13"/>
+      <c r="P251" s="15"/>
+      <c r="Q251" s="17"/>
+      <c r="R251" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B252" t="e" vm="264">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C252" s="5">
+        <f t="shared" si="7"/>
+        <v>249</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E252" s="58" t="s">
+        <v>68</v>
+      </c>
+      <c r="F252" s="48"/>
+      <c r="G252" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H252" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I252" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J252" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K252" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L252" s="7"/>
+      <c r="M252" s="9"/>
+      <c r="N252" s="11"/>
+      <c r="O252" s="13"/>
+      <c r="P252" s="15"/>
+      <c r="Q252" s="17"/>
+      <c r="R252" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B253" t="e" vm="265">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C253" s="5">
+        <f t="shared" si="7"/>
+        <v>250</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E253" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F253" s="48"/>
+      <c r="G253" s="1" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H253" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I253" s="1" t="e" vm="102">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J253" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K253" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L253" s="7"/>
+      <c r="M253" s="9"/>
+      <c r="N253" s="11"/>
+      <c r="O253" s="13"/>
+      <c r="P253" s="15"/>
+      <c r="Q253" s="17"/>
+      <c r="R253" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B254" t="e" vm="266">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C254" s="5">
+        <f t="shared" si="7"/>
+        <v>251</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E254" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F254" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="G254" s="1" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H254" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I254" s="1" t="e" vm="102">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J254" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K254" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L254" s="7"/>
+      <c r="M254" s="9"/>
+      <c r="N254" s="11"/>
+      <c r="O254" s="13"/>
+      <c r="P254" s="15"/>
+      <c r="Q254" s="17"/>
+      <c r="R254" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B255" t="e" vm="267">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C255" s="5">
+        <f t="shared" si="7"/>
+        <v>252</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E255" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="F255" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G255" s="1" t="e" vm="138">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H255" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="I255" s="1" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J255" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K255" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L255" s="7"/>
+      <c r="M255" s="9"/>
+      <c r="N255" s="11"/>
+      <c r="O255" s="13"/>
+      <c r="P255" s="15"/>
+      <c r="Q255" s="17"/>
+      <c r="R255" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B256" t="e" vm="268">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C256" s="5">
+        <f t="shared" si="7"/>
+        <v>253</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E256" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="F256" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="G256" s="1" t="e" vm="74">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H256" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I256" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J256" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K256" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="L256" s="7"/>
+      <c r="M256" s="9"/>
+      <c r="N256" s="11"/>
+      <c r="O256" s="13"/>
+      <c r="P256" s="15"/>
+      <c r="Q256" s="17"/>
+      <c r="R256" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B257" t="e" vm="269">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C257" s="5">
+        <f t="shared" si="7"/>
+        <v>254</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E257" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="F257" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="G257" s="1" t="e" vm="74">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H257" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I257" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J257" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K257" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="L257" s="7"/>
+      <c r="M257" s="9"/>
+      <c r="N257" s="11"/>
+      <c r="O257" s="13"/>
+      <c r="P257" s="15"/>
+      <c r="Q257" s="17"/>
+      <c r="R257" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B258" t="e" vm="270">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C258" s="5">
+        <f t="shared" si="7"/>
+        <v>255</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E258" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="F258" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="G258" s="1" t="e" vm="74">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H258" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I258" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J258" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K258" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L258" s="7"/>
+      <c r="M258" s="9"/>
+      <c r="N258" s="11"/>
+      <c r="O258" s="13"/>
+      <c r="P258" s="15"/>
+      <c r="Q258" s="17"/>
+      <c r="R258" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C259" s="5">
+        <f t="shared" si="7"/>
+        <v>256</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E259" s="84"/>
+      <c r="F259" s="48"/>
+      <c r="L259" s="7"/>
+      <c r="M259" s="9"/>
+      <c r="N259" s="11"/>
+      <c r="O259" s="13"/>
+      <c r="P259" s="15"/>
+      <c r="Q259" s="17"/>
+      <c r="R259" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B260" s="5"/>
+      <c r="C260" s="5">
+        <f t="shared" si="7"/>
+        <v>257</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E260" s="84"/>
+      <c r="F260" s="48"/>
+      <c r="G260" s="1"/>
+      <c r="H260" s="1"/>
+      <c r="I260" s="1"/>
+      <c r="J260" s="1"/>
+      <c r="K260" s="1"/>
+      <c r="L260" s="7"/>
+      <c r="M260" s="9"/>
+      <c r="N260" s="11"/>
+      <c r="O260" s="13"/>
+      <c r="P260" s="15"/>
+      <c r="Q260" s="17"/>
+      <c r="R260" s="40"/>
+    </row>
+    <row r="261" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B261" s="5"/>
+      <c r="C261" s="5">
+        <f t="shared" si="7"/>
+        <v>258</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E261" s="84"/>
+      <c r="F261" s="48"/>
+      <c r="G261" s="1"/>
+      <c r="H261" s="1"/>
+      <c r="I261" s="1"/>
+      <c r="J261" s="1"/>
+      <c r="K261" s="1"/>
+      <c r="L261" s="7"/>
+      <c r="M261" s="9"/>
+      <c r="N261" s="11"/>
+      <c r="O261" s="13"/>
+      <c r="P261" s="15"/>
+      <c r="Q261" s="17"/>
+      <c r="R261" s="40"/>
+    </row>
+    <row r="262" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C262" s="5">
+        <f t="shared" si="7"/>
+        <v>259</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E262" s="84"/>
+      <c r="F262" s="48"/>
+      <c r="L262" s="7"/>
+      <c r="M262" s="9"/>
+      <c r="N262" s="11"/>
+      <c r="O262" s="13"/>
+      <c r="P262" s="15"/>
+      <c r="Q262" s="17"/>
+      <c r="R262" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C263" s="5">
+        <f t="shared" si="7"/>
+        <v>260</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E263" s="84"/>
+      <c r="F263" s="48"/>
+      <c r="L263" s="7"/>
+      <c r="M263" s="9"/>
+      <c r="N263" s="11"/>
+      <c r="O263" s="13"/>
+      <c r="P263" s="15"/>
+      <c r="Q263" s="17"/>
+      <c r="R263" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C264" s="5">
+        <f t="shared" si="7"/>
+        <v>261</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E264" s="84"/>
+      <c r="F264" s="48"/>
+      <c r="L264" s="7"/>
+      <c r="M264" s="9"/>
+      <c r="N264" s="11"/>
+      <c r="O264" s="13"/>
+      <c r="P264" s="15"/>
+      <c r="Q264" s="17"/>
+      <c r="R264" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C265" s="5">
+        <f t="shared" si="7"/>
+        <v>262</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E265" s="84"/>
+      <c r="F265" s="48"/>
+      <c r="L265" s="7"/>
+      <c r="M265" s="9"/>
+      <c r="N265" s="11"/>
+      <c r="O265" s="13"/>
+      <c r="P265" s="15"/>
+      <c r="Q265" s="17"/>
+      <c r="R265" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1908D8-5A69-4EF9-A356-3C2AD90DC632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7F4F95-90BB-4F14-8CC1-E9A8D2FD5B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8136,15 +8136,27 @@
       <c r="K13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="17"/>
+      <c r="L13" s="7">
+        <v>45</v>
+      </c>
+      <c r="M13" s="9">
+        <v>60</v>
+      </c>
+      <c r="N13" s="11">
+        <v>45</v>
+      </c>
+      <c r="O13" s="13">
+        <v>25</v>
+      </c>
+      <c r="P13" s="15">
+        <v>45</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>55</v>
+      </c>
       <c r="R13" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="S13" s="29" t="s">
         <v>64</v>
@@ -8180,15 +8192,27 @@
       <c r="K14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="17"/>
+      <c r="L14" s="7">
+        <v>65</v>
+      </c>
+      <c r="M14" s="9">
+        <v>80</v>
+      </c>
+      <c r="N14" s="11">
+        <v>65</v>
+      </c>
+      <c r="O14" s="13">
+        <v>35</v>
+      </c>
+      <c r="P14" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q14" s="17">
+        <v>60</v>
+      </c>
       <c r="R14" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="S14" s="30" t="s">
         <v>65</v>
@@ -8224,15 +8248,27 @@
       <c r="K15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="17"/>
+      <c r="L15" s="7">
+        <v>85</v>
+      </c>
+      <c r="M15" s="9">
+        <v>110</v>
+      </c>
+      <c r="N15" s="11">
+        <v>90</v>
+      </c>
+      <c r="O15" s="13">
+        <v>45</v>
+      </c>
+      <c r="P15" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q15" s="17">
+        <v>80</v>
+      </c>
       <c r="R15" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="S15" s="31" t="s">
         <v>48</v>
@@ -8270,15 +8306,27 @@
       <c r="K16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L16" s="7"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="17"/>
+      <c r="L16" s="7">
+        <v>45</v>
+      </c>
+      <c r="M16" s="9">
+        <v>50</v>
+      </c>
+      <c r="N16" s="11">
+        <v>43</v>
+      </c>
+      <c r="O16" s="13">
+        <v>40</v>
+      </c>
+      <c r="P16" s="15">
+        <v>38</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>62</v>
+      </c>
       <c r="R16" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="S16" s="32" t="s">
         <v>66</v>
@@ -8316,15 +8364,27 @@
       <c r="K17" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="17"/>
+      <c r="L17" s="7">
+        <v>62</v>
+      </c>
+      <c r="M17" s="9">
+        <v>73</v>
+      </c>
+      <c r="N17" s="11">
+        <v>55</v>
+      </c>
+      <c r="O17" s="13">
+        <v>56</v>
+      </c>
+      <c r="P17" s="15">
+        <v>52</v>
+      </c>
+      <c r="Q17" s="17">
+        <v>84</v>
+      </c>
       <c r="R17" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="S17" s="33" t="s">
         <v>34</v>
@@ -8362,15 +8422,27 @@
       <c r="K18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L18" s="7"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="17"/>
+      <c r="L18" s="7">
+        <v>78</v>
+      </c>
+      <c r="M18" s="9">
+        <v>81</v>
+      </c>
+      <c r="N18" s="11">
+        <v>71</v>
+      </c>
+      <c r="O18" s="13">
+        <v>74</v>
+      </c>
+      <c r="P18" s="15">
+        <v>69</v>
+      </c>
+      <c r="Q18" s="17">
+        <v>126</v>
+      </c>
       <c r="R18" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>499</v>
       </c>
       <c r="S18" s="34" t="s">
         <v>67</v>
@@ -8406,15 +8478,27 @@
       <c r="K19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L19" s="7"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="17"/>
+      <c r="L19" s="7">
+        <v>33</v>
+      </c>
+      <c r="M19" s="9">
+        <v>46</v>
+      </c>
+      <c r="N19" s="11">
+        <v>40</v>
+      </c>
+      <c r="O19" s="13">
+        <v>21</v>
+      </c>
+      <c r="P19" s="15">
+        <v>25</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>45</v>
+      </c>
       <c r="R19" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="S19" s="35" t="s">
         <v>68</v>
@@ -8452,15 +8536,27 @@
       <c r="K20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L20" s="7"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="17"/>
+      <c r="L20" s="7">
+        <v>71</v>
+      </c>
+      <c r="M20" s="9">
+        <v>102</v>
+      </c>
+      <c r="N20" s="11">
+        <v>78</v>
+      </c>
+      <c r="O20" s="13">
+        <v>52</v>
+      </c>
+      <c r="P20" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q20" s="17">
+        <v>92</v>
+      </c>
       <c r="R20" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="S20" s="36" t="s">
         <v>60</v>
@@ -8496,15 +8592,27 @@
       <c r="K21" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L21" s="7"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="17"/>
+      <c r="L21" s="7">
+        <v>50</v>
+      </c>
+      <c r="M21" s="9">
+        <v>75</v>
+      </c>
+      <c r="N21" s="11">
+        <v>85</v>
+      </c>
+      <c r="O21" s="13">
+        <v>20</v>
+      </c>
+      <c r="P21" s="15">
+        <v>30</v>
+      </c>
+      <c r="Q21" s="17">
+        <v>40</v>
+      </c>
       <c r="R21" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S21" s="37" t="s">
         <v>69</v>
@@ -8540,15 +8648,27 @@
       <c r="K22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L22" s="7"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="13"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="17"/>
+      <c r="L22" s="7">
+        <v>75</v>
+      </c>
+      <c r="M22" s="9">
+        <v>100</v>
+      </c>
+      <c r="N22" s="11">
+        <v>110</v>
+      </c>
+      <c r="O22" s="13">
+        <v>45</v>
+      </c>
+      <c r="P22" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q22" s="17">
+        <v>65</v>
+      </c>
       <c r="R22" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>450</v>
       </c>
     </row>
     <row r="23" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8581,15 +8701,27 @@
       <c r="K23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L23" s="7"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="13"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="17"/>
+      <c r="L23" s="7">
+        <v>67</v>
+      </c>
+      <c r="M23" s="9">
+        <v>82</v>
+      </c>
+      <c r="N23" s="11">
+        <v>62</v>
+      </c>
+      <c r="O23" s="13">
+        <v>46</v>
+      </c>
+      <c r="P23" s="15">
+        <v>48</v>
+      </c>
+      <c r="Q23" s="17">
+        <v>43</v>
+      </c>
       <c r="R23" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>348</v>
       </c>
     </row>
     <row r="24" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8624,15 +8756,27 @@
       <c r="K24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L24" s="7"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="17"/>
+      <c r="L24" s="7">
+        <v>95</v>
+      </c>
+      <c r="M24" s="9">
+        <v>124</v>
+      </c>
+      <c r="N24" s="11">
+        <v>78</v>
+      </c>
+      <c r="O24" s="13">
+        <v>69</v>
+      </c>
+      <c r="P24" s="15">
+        <v>71</v>
+      </c>
+      <c r="Q24" s="17">
+        <v>58</v>
+      </c>
       <c r="R24" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>495</v>
       </c>
     </row>
     <row r="25" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8661,15 +8805,27 @@
       <c r="K25" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L25" s="7"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="17"/>
+      <c r="L25" s="7">
+        <v>45</v>
+      </c>
+      <c r="M25" s="9">
+        <v>35</v>
+      </c>
+      <c r="N25" s="11">
+        <v>50</v>
+      </c>
+      <c r="O25" s="13">
+        <v>70</v>
+      </c>
+      <c r="P25" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q25" s="17">
+        <v>30</v>
+      </c>
       <c r="R25" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8698,15 +8854,27 @@
       <c r="K26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L26" s="7"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="13"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="17"/>
+      <c r="L26" s="7">
+        <v>70</v>
+      </c>
+      <c r="M26" s="9">
+        <v>60</v>
+      </c>
+      <c r="N26" s="11">
+        <v>75</v>
+      </c>
+      <c r="O26" s="13">
+        <v>110</v>
+      </c>
+      <c r="P26" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q26" s="17">
+        <v>90</v>
+      </c>
       <c r="R26" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="27" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8741,15 +8909,27 @@
       <c r="K27" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L27" s="7"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="13"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="17"/>
+      <c r="L27" s="7">
+        <v>40</v>
+      </c>
+      <c r="M27" s="9">
+        <v>27</v>
+      </c>
+      <c r="N27" s="11">
+        <v>60</v>
+      </c>
+      <c r="O27" s="13">
+        <v>37</v>
+      </c>
+      <c r="P27" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q27" s="17">
+        <v>66</v>
+      </c>
       <c r="R27" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8784,15 +8964,27 @@
       <c r="K28" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L28" s="7"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="13"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="17"/>
+      <c r="L28" s="7">
+        <v>60</v>
+      </c>
+      <c r="M28" s="9">
+        <v>67</v>
+      </c>
+      <c r="N28" s="11">
+        <v>85</v>
+      </c>
+      <c r="O28" s="13">
+        <v>77</v>
+      </c>
+      <c r="P28" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q28" s="17">
+        <v>116</v>
+      </c>
       <c r="R28" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="29" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8821,15 +9013,27 @@
       <c r="K29" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="L29" s="7"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="17"/>
+      <c r="L29" s="7">
+        <v>55</v>
+      </c>
+      <c r="M29" s="9">
+        <v>75</v>
+      </c>
+      <c r="N29" s="11">
+        <v>85</v>
+      </c>
+      <c r="O29" s="13">
+        <v>25</v>
+      </c>
+      <c r="P29" s="15">
+        <v>25</v>
+      </c>
+      <c r="Q29" s="17">
+        <v>15</v>
+      </c>
       <c r="R29" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8858,15 +9062,27 @@
       <c r="K30" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L30" s="7"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="13"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="17"/>
+      <c r="L30" s="7">
+        <v>70</v>
+      </c>
+      <c r="M30" s="9">
+        <v>105</v>
+      </c>
+      <c r="N30" s="11">
+        <v>105</v>
+      </c>
+      <c r="O30" s="13">
+        <v>50</v>
+      </c>
+      <c r="P30" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q30" s="17">
+        <v>20</v>
+      </c>
       <c r="R30" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>390</v>
       </c>
     </row>
     <row r="31" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8895,15 +9111,27 @@
       <c r="K31" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L31" s="7"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="13"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="17"/>
+      <c r="L31" s="7">
+        <v>85</v>
+      </c>
+      <c r="M31" s="9">
+        <v>135</v>
+      </c>
+      <c r="N31" s="11">
+        <v>130</v>
+      </c>
+      <c r="O31" s="13">
+        <v>60</v>
+      </c>
+      <c r="P31" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q31" s="17">
+        <v>25</v>
+      </c>
       <c r="R31" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>515</v>
       </c>
     </row>
     <row r="32" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8936,15 +9164,27 @@
       <c r="K32" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="L32" s="7"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="13"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="17"/>
+      <c r="L32" s="7">
+        <v>60</v>
+      </c>
+      <c r="M32" s="9">
+        <v>40</v>
+      </c>
+      <c r="N32" s="11">
+        <v>60</v>
+      </c>
+      <c r="O32" s="13">
+        <v>40</v>
+      </c>
+      <c r="P32" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q32" s="17">
+        <v>35</v>
+      </c>
       <c r="R32" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8979,15 +9219,27 @@
       <c r="K33" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L33" s="7"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="13"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="17"/>
+      <c r="L33" s="7">
+        <v>60</v>
+      </c>
+      <c r="M33" s="9">
+        <v>130</v>
+      </c>
+      <c r="N33" s="11">
+        <v>80</v>
+      </c>
+      <c r="O33" s="13">
+        <v>60</v>
+      </c>
+      <c r="P33" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q33" s="17">
+        <v>70</v>
+      </c>
       <c r="R33" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="34" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9018,15 +9270,27 @@
       <c r="K34" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L34" s="7"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="13"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="17"/>
+      <c r="L34" s="7">
+        <v>40</v>
+      </c>
+      <c r="M34" s="9">
+        <v>65</v>
+      </c>
+      <c r="N34" s="11">
+        <v>35</v>
+      </c>
+      <c r="O34" s="13">
+        <v>40</v>
+      </c>
+      <c r="P34" s="15">
+        <v>35</v>
+      </c>
+      <c r="Q34" s="17">
+        <v>75</v>
+      </c>
       <c r="R34" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9057,15 +9321,27 @@
       <c r="K35" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L35" s="7"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="17"/>
+      <c r="L35" s="7">
+        <v>63</v>
+      </c>
+      <c r="M35" s="9">
+        <v>95</v>
+      </c>
+      <c r="N35" s="11">
+        <v>65</v>
+      </c>
+      <c r="O35" s="13">
+        <v>80</v>
+      </c>
+      <c r="P35" s="15">
+        <v>72</v>
+      </c>
+      <c r="Q35" s="17">
+        <v>110</v>
+      </c>
       <c r="R35" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>485</v>
       </c>
     </row>
     <row r="36" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9100,15 +9376,27 @@
       <c r="K36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L36" s="7"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="13"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="17"/>
+      <c r="L36" s="7">
+        <v>38</v>
+      </c>
+      <c r="M36" s="9">
+        <v>40</v>
+      </c>
+      <c r="N36" s="11">
+        <v>52</v>
+      </c>
+      <c r="O36" s="13">
+        <v>40</v>
+      </c>
+      <c r="P36" s="15">
+        <v>72</v>
+      </c>
+      <c r="Q36" s="17">
+        <v>27</v>
+      </c>
       <c r="R36" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9143,15 +9431,27 @@
       <c r="K37" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L37" s="7"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="17"/>
+      <c r="L37" s="7">
+        <v>68</v>
+      </c>
+      <c r="M37" s="9">
+        <v>70</v>
+      </c>
+      <c r="N37" s="11">
+        <v>92</v>
+      </c>
+      <c r="O37" s="13">
+        <v>50</v>
+      </c>
+      <c r="P37" s="15">
+        <v>132</v>
+      </c>
+      <c r="Q37" s="17">
+        <v>42</v>
+      </c>
       <c r="R37" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>454</v>
       </c>
     </row>
     <row r="38" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9180,15 +9480,27 @@
       <c r="K38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L38" s="7"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="13"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="17"/>
+      <c r="L38" s="7">
+        <v>66</v>
+      </c>
+      <c r="M38" s="9">
+        <v>65</v>
+      </c>
+      <c r="N38" s="11">
+        <v>48</v>
+      </c>
+      <c r="O38" s="13">
+        <v>62</v>
+      </c>
+      <c r="P38" s="15">
+        <v>57</v>
+      </c>
+      <c r="Q38" s="17">
+        <v>52</v>
+      </c>
       <c r="R38" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9217,15 +9529,27 @@
       <c r="K39" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L39" s="7"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="17"/>
+      <c r="L39" s="7">
+        <v>123</v>
+      </c>
+      <c r="M39" s="9">
+        <v>100</v>
+      </c>
+      <c r="N39" s="11">
+        <v>62</v>
+      </c>
+      <c r="O39" s="13">
+        <v>97</v>
+      </c>
+      <c r="P39" s="15">
+        <v>81</v>
+      </c>
+      <c r="Q39" s="17">
+        <v>68</v>
+      </c>
       <c r="R39" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>531</v>
       </c>
     </row>
     <row r="40" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9254,15 +9578,27 @@
       <c r="K40" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L40" s="7"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="13"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="17"/>
+      <c r="L40" s="7">
+        <v>60</v>
+      </c>
+      <c r="M40" s="9">
+        <v>80</v>
+      </c>
+      <c r="N40" s="11">
+        <v>50</v>
+      </c>
+      <c r="O40" s="13">
+        <v>50</v>
+      </c>
+      <c r="P40" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q40" s="17">
+        <v>40</v>
+      </c>
       <c r="R40" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="41" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9291,15 +9627,27 @@
       <c r="K41" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L41" s="7"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="13"/>
-      <c r="P41" s="15"/>
-      <c r="Q41" s="17"/>
+      <c r="L41" s="7">
+        <v>90</v>
+      </c>
+      <c r="M41" s="9">
+        <v>130</v>
+      </c>
+      <c r="N41" s="11">
+        <v>75</v>
+      </c>
+      <c r="O41" s="13">
+        <v>75</v>
+      </c>
+      <c r="P41" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q41" s="17">
+        <v>55</v>
+      </c>
       <c r="R41" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="42" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9330,15 +9678,27 @@
       <c r="K42" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L42" s="7"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="13"/>
-      <c r="P42" s="15"/>
-      <c r="Q42" s="17"/>
+      <c r="L42" s="7">
+        <v>130</v>
+      </c>
+      <c r="M42" s="9">
+        <v>140</v>
+      </c>
+      <c r="N42" s="11">
+        <v>105</v>
+      </c>
+      <c r="O42" s="13">
+        <v>45</v>
+      </c>
+      <c r="P42" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q42" s="17">
+        <v>50</v>
+      </c>
       <c r="R42" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>550</v>
       </c>
     </row>
     <row r="43" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9373,15 +9733,27 @@
       <c r="K43" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="L43" s="7"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="15"/>
-      <c r="Q43" s="17"/>
+      <c r="L43" s="7">
+        <v>40</v>
+      </c>
+      <c r="M43" s="9">
+        <v>40</v>
+      </c>
+      <c r="N43" s="11">
+        <v>80</v>
+      </c>
+      <c r="O43" s="13">
+        <v>40</v>
+      </c>
+      <c r="P43" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q43" s="17">
+        <v>20</v>
+      </c>
       <c r="R43" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>260</v>
       </c>
     </row>
     <row r="44" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9416,15 +9788,27 @@
       <c r="K44" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L44" s="7"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="13"/>
-      <c r="P44" s="15"/>
-      <c r="Q44" s="17"/>
+      <c r="L44" s="7">
+        <v>70</v>
+      </c>
+      <c r="M44" s="9">
+        <v>110</v>
+      </c>
+      <c r="N44" s="11">
+        <v>80</v>
+      </c>
+      <c r="O44" s="13">
+        <v>95</v>
+      </c>
+      <c r="P44" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q44" s="17">
+        <v>70</v>
+      </c>
       <c r="R44" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>485</v>
       </c>
     </row>
     <row r="45" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9459,15 +9843,27 @@
       <c r="K45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L45" s="7"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="15"/>
-      <c r="Q45" s="17"/>
+      <c r="L45" s="7">
+        <v>110</v>
+      </c>
+      <c r="M45" s="9">
+        <v>85</v>
+      </c>
+      <c r="N45" s="11">
+        <v>80</v>
+      </c>
+      <c r="O45" s="13">
+        <v>100</v>
+      </c>
+      <c r="P45" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q45" s="17">
+        <v>30</v>
+      </c>
       <c r="R45" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>485</v>
       </c>
     </row>
     <row r="46" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9498,15 +9894,27 @@
       <c r="K46" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L46" s="7"/>
-      <c r="M46" s="9"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="13"/>
-      <c r="P46" s="15"/>
-      <c r="Q46" s="17"/>
+      <c r="L46" s="7">
+        <v>55</v>
+      </c>
+      <c r="M46" s="9">
+        <v>75</v>
+      </c>
+      <c r="N46" s="11">
+        <v>60</v>
+      </c>
+      <c r="O46" s="13">
+        <v>75</v>
+      </c>
+      <c r="P46" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q46" s="17">
+        <v>103</v>
+      </c>
       <c r="R46" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>428</v>
       </c>
     </row>
     <row r="47" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9541,15 +9949,27 @@
       <c r="K47" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="L47" s="7"/>
-      <c r="M47" s="9"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="15"/>
-      <c r="Q47" s="17"/>
+      <c r="L47" s="7">
+        <v>50</v>
+      </c>
+      <c r="M47" s="9">
+        <v>20</v>
+      </c>
+      <c r="N47" s="11">
+        <v>40</v>
+      </c>
+      <c r="O47" s="13">
+        <v>20</v>
+      </c>
+      <c r="P47" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q47" s="17">
+        <v>20</v>
+      </c>
       <c r="R47" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9584,15 +10004,27 @@
       <c r="K48" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L48" s="7"/>
-      <c r="M48" s="9"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="13"/>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="17"/>
+      <c r="L48" s="7">
+        <v>70</v>
+      </c>
+      <c r="M48" s="9">
+        <v>20</v>
+      </c>
+      <c r="N48" s="11">
+        <v>50</v>
+      </c>
+      <c r="O48" s="13">
+        <v>20</v>
+      </c>
+      <c r="P48" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q48" s="17">
+        <v>40</v>
+      </c>
       <c r="R48" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9625,12 +10057,24 @@
         <v>60</v>
       </c>
       <c r="K49" s="1"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="9"/>
-      <c r="N49" s="11"/>
-      <c r="O49" s="13"/>
-      <c r="P49" s="15"/>
-      <c r="Q49" s="17"/>
+      <c r="L49" s="7">
+        <v>100</v>
+      </c>
+      <c r="M49" s="9">
+        <v>50</v>
+      </c>
+      <c r="N49" s="11">
+        <v>80</v>
+      </c>
+      <c r="O49" s="13">
+        <v>60</v>
+      </c>
+      <c r="P49" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q49" s="17">
+        <v>50</v>
+      </c>
       <c r="R49" s="40"/>
     </row>
     <row r="50" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9663,15 +10107,27 @@
       <c r="K50" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="L50" s="7"/>
-      <c r="M50" s="9"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="17"/>
+      <c r="L50" s="7">
+        <v>50</v>
+      </c>
+      <c r="M50" s="9">
+        <v>50</v>
+      </c>
+      <c r="N50" s="11">
+        <v>50</v>
+      </c>
+      <c r="O50" s="13">
+        <v>50</v>
+      </c>
+      <c r="P50" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q50" s="17">
+        <v>50</v>
+      </c>
       <c r="R50" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9704,15 +10160,27 @@
       <c r="K51" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L51" s="7"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="13"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="17"/>
+      <c r="L51" s="7">
+        <v>80</v>
+      </c>
+      <c r="M51" s="9">
+        <v>80</v>
+      </c>
+      <c r="N51" s="11">
+        <v>80</v>
+      </c>
+      <c r="O51" s="13">
+        <v>80</v>
+      </c>
+      <c r="P51" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q51" s="17">
+        <v>80</v>
+      </c>
       <c r="R51" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="52" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9747,15 +10215,27 @@
       <c r="K52" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L52" s="7"/>
-      <c r="M52" s="9"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="13"/>
-      <c r="P52" s="15"/>
-      <c r="Q52" s="17"/>
+      <c r="L52" s="7">
+        <v>70</v>
+      </c>
+      <c r="M52" s="9">
+        <v>80</v>
+      </c>
+      <c r="N52" s="11">
+        <v>70</v>
+      </c>
+      <c r="O52" s="13">
+        <v>80</v>
+      </c>
+      <c r="P52" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q52" s="17">
+        <v>110</v>
+      </c>
       <c r="R52" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="53" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9790,15 +10270,27 @@
       <c r="K53" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L53" s="7"/>
-      <c r="M53" s="9"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="13"/>
-      <c r="P53" s="15"/>
-      <c r="Q53" s="17"/>
+      <c r="L53" s="7">
+        <v>50</v>
+      </c>
+      <c r="M53" s="9">
+        <v>65</v>
+      </c>
+      <c r="N53" s="11">
+        <v>85</v>
+      </c>
+      <c r="O53" s="13">
+        <v>35</v>
+      </c>
+      <c r="P53" s="15">
+        <v>35</v>
+      </c>
+      <c r="Q53" s="17">
+        <v>55</v>
+      </c>
       <c r="R53" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>325</v>
       </c>
     </row>
     <row r="54" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9833,15 +10325,27 @@
       <c r="K54" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L54" s="7"/>
-      <c r="M54" s="9"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="13"/>
-      <c r="P54" s="15"/>
-      <c r="Q54" s="17"/>
+      <c r="L54" s="7">
+        <v>70</v>
+      </c>
+      <c r="M54" s="9">
+        <v>105</v>
+      </c>
+      <c r="N54" s="11">
+        <v>125</v>
+      </c>
+      <c r="O54" s="13">
+        <v>65</v>
+      </c>
+      <c r="P54" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q54" s="17">
+        <v>45</v>
+      </c>
       <c r="R54" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>485</v>
       </c>
     </row>
     <row r="55" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9870,15 +10374,27 @@
       <c r="K55" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="L55" s="7"/>
-      <c r="M55" s="9"/>
-      <c r="N55" s="11"/>
-      <c r="O55" s="13"/>
-      <c r="P55" s="15"/>
-      <c r="Q55" s="17"/>
+      <c r="L55" s="7">
+        <v>73</v>
+      </c>
+      <c r="M55" s="9">
+        <v>95</v>
+      </c>
+      <c r="N55" s="11">
+        <v>62</v>
+      </c>
+      <c r="O55" s="13">
+        <v>85</v>
+      </c>
+      <c r="P55" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q55" s="17">
+        <v>85</v>
+      </c>
       <c r="R55" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>465</v>
       </c>
     </row>
     <row r="56" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9909,15 +10425,27 @@
       <c r="K56" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L56" s="7"/>
-      <c r="M56" s="9"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="13"/>
-      <c r="P56" s="15"/>
-      <c r="Q56" s="17"/>
+      <c r="L56" s="7">
+        <v>103</v>
+      </c>
+      <c r="M56" s="9">
+        <v>105</v>
+      </c>
+      <c r="N56" s="11">
+        <v>72</v>
+      </c>
+      <c r="O56" s="13">
+        <v>105</v>
+      </c>
+      <c r="P56" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q56" s="17">
+        <v>65</v>
+      </c>
       <c r="R56" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>525</v>
       </c>
     </row>
     <row r="57" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9950,15 +10478,27 @@
       <c r="K57" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L57" s="7"/>
-      <c r="M57" s="9"/>
-      <c r="N57" s="11"/>
-      <c r="O57" s="13"/>
-      <c r="P57" s="15"/>
-      <c r="Q57" s="17"/>
+      <c r="L57" s="7">
+        <v>20</v>
+      </c>
+      <c r="M57" s="9">
+        <v>10</v>
+      </c>
+      <c r="N57" s="11">
+        <v>55</v>
+      </c>
+      <c r="O57" s="13">
+        <v>15</v>
+      </c>
+      <c r="P57" s="15">
+        <v>20</v>
+      </c>
+      <c r="Q57" s="17">
+        <v>80</v>
+      </c>
       <c r="R57" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -9993,15 +10533,27 @@
       <c r="K58" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L58" s="7"/>
-      <c r="M58" s="9"/>
-      <c r="N58" s="11"/>
-      <c r="O58" s="13"/>
-      <c r="P58" s="15"/>
-      <c r="Q58" s="17"/>
+      <c r="L58" s="7">
+        <v>95</v>
+      </c>
+      <c r="M58" s="9">
+        <v>125</v>
+      </c>
+      <c r="N58" s="11">
+        <v>79</v>
+      </c>
+      <c r="O58" s="13">
+        <v>60</v>
+      </c>
+      <c r="P58" s="15">
+        <v>100</v>
+      </c>
+      <c r="Q58" s="17">
+        <v>81</v>
+      </c>
       <c r="R58" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>540</v>
       </c>
     </row>
     <row r="59" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10032,15 +10584,27 @@
       <c r="K59" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="L59" s="7"/>
-      <c r="M59" s="9"/>
-      <c r="N59" s="11"/>
-      <c r="O59" s="13"/>
-      <c r="P59" s="15"/>
-      <c r="Q59" s="17"/>
+      <c r="L59" s="7">
+        <v>65</v>
+      </c>
+      <c r="M59" s="9">
+        <v>75</v>
+      </c>
+      <c r="N59" s="11">
+        <v>105</v>
+      </c>
+      <c r="O59" s="13">
+        <v>35</v>
+      </c>
+      <c r="P59" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q59" s="17">
+        <v>85</v>
+      </c>
       <c r="R59" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>430</v>
       </c>
     </row>
     <row r="60" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10071,15 +10635,27 @@
       <c r="K60" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L60" s="7"/>
-      <c r="M60" s="9"/>
-      <c r="N60" s="11"/>
-      <c r="O60" s="13"/>
-      <c r="P60" s="15"/>
-      <c r="Q60" s="17"/>
+      <c r="L60" s="7">
+        <v>75</v>
+      </c>
+      <c r="M60" s="9">
+        <v>95</v>
+      </c>
+      <c r="N60" s="11">
+        <v>125</v>
+      </c>
+      <c r="O60" s="13">
+        <v>45</v>
+      </c>
+      <c r="P60" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q60" s="17">
+        <v>95</v>
+      </c>
       <c r="R60" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="61" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10108,15 +10684,27 @@
       <c r="K61" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L61" s="7"/>
-      <c r="M61" s="9"/>
-      <c r="N61" s="11"/>
-      <c r="O61" s="13"/>
-      <c r="P61" s="15"/>
-      <c r="Q61" s="17"/>
+      <c r="L61" s="7">
+        <v>38</v>
+      </c>
+      <c r="M61" s="9">
+        <v>41</v>
+      </c>
+      <c r="N61" s="11">
+        <v>40</v>
+      </c>
+      <c r="O61" s="13">
+        <v>50</v>
+      </c>
+      <c r="P61" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q61" s="17">
+        <v>65</v>
+      </c>
       <c r="R61" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10145,15 +10733,27 @@
       <c r="K62" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L62" s="7"/>
-      <c r="M62" s="9"/>
-      <c r="N62" s="11"/>
-      <c r="O62" s="13"/>
-      <c r="P62" s="15"/>
-      <c r="Q62" s="17"/>
+      <c r="L62" s="7">
+        <v>73</v>
+      </c>
+      <c r="M62" s="9">
+        <v>76</v>
+      </c>
+      <c r="N62" s="11">
+        <v>75</v>
+      </c>
+      <c r="O62" s="13">
+        <v>81</v>
+      </c>
+      <c r="P62" s="15">
+        <v>100</v>
+      </c>
+      <c r="Q62" s="17">
+        <v>100</v>
+      </c>
       <c r="R62" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>505</v>
       </c>
     </row>
     <row r="63" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10182,15 +10782,27 @@
       <c r="K63" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L63" s="7"/>
-      <c r="M63" s="9"/>
-      <c r="N63" s="11"/>
-      <c r="O63" s="13"/>
-      <c r="P63" s="15"/>
-      <c r="Q63" s="17"/>
+      <c r="L63" s="7">
+        <v>40</v>
+      </c>
+      <c r="M63" s="9">
+        <v>80</v>
+      </c>
+      <c r="N63" s="11">
+        <v>35</v>
+      </c>
+      <c r="O63" s="13">
+        <v>35</v>
+      </c>
+      <c r="P63" s="15">
+        <v>45</v>
+      </c>
+      <c r="Q63" s="17">
+        <v>70</v>
+      </c>
       <c r="R63" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>305</v>
       </c>
     </row>
     <row r="64" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10219,15 +10831,27 @@
       <c r="K64" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="L64" s="7"/>
-      <c r="M64" s="9"/>
-      <c r="N64" s="11"/>
-      <c r="O64" s="13"/>
-      <c r="P64" s="15"/>
-      <c r="Q64" s="17"/>
+      <c r="L64" s="7">
+        <v>65</v>
+      </c>
+      <c r="M64" s="9">
+        <v>105</v>
+      </c>
+      <c r="N64" s="11">
+        <v>60</v>
+      </c>
+      <c r="O64" s="13">
+        <v>60</v>
+      </c>
+      <c r="P64" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q64" s="17">
+        <v>95</v>
+      </c>
       <c r="R64" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>455</v>
       </c>
     </row>
     <row r="65" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10258,15 +10882,27 @@
       <c r="K65" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L65" s="7"/>
-      <c r="M65" s="9"/>
-      <c r="N65" s="11"/>
-      <c r="O65" s="13"/>
-      <c r="P65" s="15"/>
-      <c r="Q65" s="17"/>
+      <c r="L65" s="7">
+        <v>110</v>
+      </c>
+      <c r="M65" s="9">
+        <v>115</v>
+      </c>
+      <c r="N65" s="11">
+        <v>80</v>
+      </c>
+      <c r="O65" s="13">
+        <v>50</v>
+      </c>
+      <c r="P65" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q65" s="17">
+        <v>90</v>
+      </c>
       <c r="R65" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>535</v>
       </c>
     </row>
     <row r="66" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10297,15 +10933,27 @@
       <c r="K66" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L66" s="7"/>
-      <c r="M66" s="9"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="13"/>
-      <c r="P66" s="15"/>
-      <c r="Q66" s="17"/>
+      <c r="L66" s="7">
+        <v>90</v>
+      </c>
+      <c r="M66" s="9">
+        <v>50</v>
+      </c>
+      <c r="N66" s="11">
+        <v>34</v>
+      </c>
+      <c r="O66" s="13">
+        <v>60</v>
+      </c>
+      <c r="P66" s="15">
+        <v>44</v>
+      </c>
+      <c r="Q66" s="17">
+        <v>70</v>
+      </c>
       <c r="R66" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>348</v>
       </c>
     </row>
     <row r="67" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10336,15 +10984,27 @@
       <c r="K67" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L67" s="7"/>
-      <c r="M67" s="9"/>
-      <c r="N67" s="11"/>
-      <c r="O67" s="13"/>
-      <c r="P67" s="15"/>
-      <c r="Q67" s="17"/>
+      <c r="L67" s="7">
+        <v>150</v>
+      </c>
+      <c r="M67" s="9">
+        <v>80</v>
+      </c>
+      <c r="N67" s="11">
+        <v>44</v>
+      </c>
+      <c r="O67" s="13">
+        <v>90</v>
+      </c>
+      <c r="P67" s="15">
+        <v>54</v>
+      </c>
+      <c r="Q67" s="17">
+        <v>80</v>
+      </c>
       <c r="R67" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>498</v>
       </c>
     </row>
     <row r="68" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10377,15 +11037,27 @@
       <c r="K68" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="L68" s="7"/>
-      <c r="M68" s="9"/>
-      <c r="N68" s="11"/>
-      <c r="O68" s="13"/>
-      <c r="P68" s="15"/>
-      <c r="Q68" s="17"/>
+      <c r="L68" s="7">
+        <v>35</v>
+      </c>
+      <c r="M68" s="9">
+        <v>65</v>
+      </c>
+      <c r="N68" s="11">
+        <v>35</v>
+      </c>
+      <c r="O68" s="13">
+        <v>65</v>
+      </c>
+      <c r="P68" s="15">
+        <v>35</v>
+      </c>
+      <c r="Q68" s="17">
+        <v>65</v>
+      </c>
       <c r="R68" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="69" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10418,15 +11090,27 @@
       <c r="K69" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L69" s="7"/>
-      <c r="M69" s="9"/>
-      <c r="N69" s="11"/>
-      <c r="O69" s="13"/>
-      <c r="P69" s="15"/>
-      <c r="Q69" s="17"/>
+      <c r="L69" s="7">
+        <v>75</v>
+      </c>
+      <c r="M69" s="9">
+        <v>105</v>
+      </c>
+      <c r="N69" s="11">
+        <v>75</v>
+      </c>
+      <c r="O69" s="13">
+        <v>105</v>
+      </c>
+      <c r="P69" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q69" s="17">
+        <v>45</v>
+      </c>
       <c r="R69" s="40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="70" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10461,15 +11145,27 @@
       <c r="K70" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="L70" s="7"/>
-      <c r="M70" s="9"/>
-      <c r="N70" s="11"/>
-      <c r="O70" s="13"/>
-      <c r="P70" s="15"/>
-      <c r="Q70" s="17"/>
+      <c r="L70" s="7">
+        <v>40</v>
+      </c>
+      <c r="M70" s="9">
+        <v>30</v>
+      </c>
+      <c r="N70" s="11">
+        <v>30</v>
+      </c>
+      <c r="O70" s="13">
+        <v>55</v>
+      </c>
+      <c r="P70" s="15">
+        <v>30</v>
+      </c>
+      <c r="Q70" s="17">
+        <v>85</v>
+      </c>
       <c r="R70" s="40">
         <f t="shared" ref="R70:R133" si="3">SUM(L70:Q70)</f>
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="71" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10504,15 +11200,27 @@
       <c r="K71" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L71" s="7"/>
-      <c r="M71" s="9"/>
-      <c r="N71" s="11"/>
-      <c r="O71" s="13"/>
-      <c r="P71" s="15"/>
-      <c r="Q71" s="17"/>
+      <c r="L71" s="7">
+        <v>60</v>
+      </c>
+      <c r="M71" s="9">
+        <v>50</v>
+      </c>
+      <c r="N71" s="11">
+        <v>100</v>
+      </c>
+      <c r="O71" s="13">
+        <v>95</v>
+      </c>
+      <c r="P71" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q71" s="17">
+        <v>65</v>
+      </c>
       <c r="R71" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="72" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10543,15 +11251,27 @@
       <c r="K72" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L72" s="7"/>
-      <c r="M72" s="9"/>
-      <c r="N72" s="11"/>
-      <c r="O72" s="13"/>
-      <c r="P72" s="15"/>
-      <c r="Q72" s="17"/>
+      <c r="L72" s="7">
+        <v>45</v>
+      </c>
+      <c r="M72" s="9">
+        <v>80</v>
+      </c>
+      <c r="N72" s="11">
+        <v>100</v>
+      </c>
+      <c r="O72" s="13">
+        <v>35</v>
+      </c>
+      <c r="P72" s="15">
+        <v>37</v>
+      </c>
+      <c r="Q72" s="17">
+        <v>28</v>
+      </c>
       <c r="R72" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>325</v>
       </c>
     </row>
     <row r="73" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10582,15 +11302,27 @@
       <c r="K73" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="L73" s="7"/>
-      <c r="M73" s="9"/>
-      <c r="N73" s="11"/>
-      <c r="O73" s="13"/>
-      <c r="P73" s="15"/>
-      <c r="Q73" s="17"/>
+      <c r="L73" s="7">
+        <v>59</v>
+      </c>
+      <c r="M73" s="9">
+        <v>110</v>
+      </c>
+      <c r="N73" s="11">
+        <v>150</v>
+      </c>
+      <c r="O73" s="13">
+        <v>45</v>
+      </c>
+      <c r="P73" s="15">
+        <v>49</v>
+      </c>
+      <c r="Q73" s="17">
+        <v>35</v>
+      </c>
       <c r="R73" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>448</v>
       </c>
     </row>
     <row r="74" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10621,15 +11353,27 @@
       <c r="K74" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L74" s="7"/>
-      <c r="M74" s="9"/>
-      <c r="N74" s="11"/>
-      <c r="O74" s="13"/>
-      <c r="P74" s="15"/>
-      <c r="Q74" s="17"/>
+      <c r="L74" s="7">
+        <v>60</v>
+      </c>
+      <c r="M74" s="9">
+        <v>50</v>
+      </c>
+      <c r="N74" s="11">
+        <v>140</v>
+      </c>
+      <c r="O74" s="13">
+        <v>50</v>
+      </c>
+      <c r="P74" s="15">
+        <v>140</v>
+      </c>
+      <c r="Q74" s="17">
+        <v>60</v>
+      </c>
       <c r="R74" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="75" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10658,15 +11402,27 @@
       <c r="K75" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L75" s="7"/>
-      <c r="M75" s="9"/>
-      <c r="N75" s="11"/>
-      <c r="O75" s="13"/>
-      <c r="P75" s="15"/>
-      <c r="Q75" s="17"/>
+      <c r="L75" s="7">
+        <v>36</v>
+      </c>
+      <c r="M75" s="9">
+        <v>50</v>
+      </c>
+      <c r="N75" s="11">
+        <v>50</v>
+      </c>
+      <c r="O75" s="13">
+        <v>65</v>
+      </c>
+      <c r="P75" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q75" s="17">
+        <v>44</v>
+      </c>
       <c r="R75" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>305</v>
       </c>
     </row>
     <row r="76" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10695,15 +11451,27 @@
       <c r="K76" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="L76" s="7"/>
-      <c r="M76" s="9"/>
-      <c r="N76" s="11"/>
-      <c r="O76" s="13"/>
-      <c r="P76" s="15"/>
-      <c r="Q76" s="17"/>
+      <c r="L76" s="7">
+        <v>51</v>
+      </c>
+      <c r="M76" s="9">
+        <v>65</v>
+      </c>
+      <c r="N76" s="11">
+        <v>65</v>
+      </c>
+      <c r="O76" s="13">
+        <v>80</v>
+      </c>
+      <c r="P76" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q76" s="17">
+        <v>59</v>
+      </c>
       <c r="R76" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>395</v>
       </c>
     </row>
     <row r="77" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10732,15 +11500,27 @@
       <c r="K77" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L77" s="7"/>
-      <c r="M77" s="9"/>
-      <c r="N77" s="11"/>
-      <c r="O77" s="13"/>
-      <c r="P77" s="15"/>
-      <c r="Q77" s="17"/>
+      <c r="L77" s="7">
+        <v>71</v>
+      </c>
+      <c r="M77" s="9">
+        <v>95</v>
+      </c>
+      <c r="N77" s="11">
+        <v>85</v>
+      </c>
+      <c r="O77" s="13">
+        <v>110</v>
+      </c>
+      <c r="P77" s="15">
+        <v>95</v>
+      </c>
+      <c r="Q77" s="17">
+        <v>79</v>
+      </c>
       <c r="R77" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>535</v>
       </c>
     </row>
     <row r="78" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10771,15 +11551,27 @@
       <c r="K78" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="L78" s="7"/>
-      <c r="M78" s="9"/>
-      <c r="N78" s="11"/>
-      <c r="O78" s="13"/>
-      <c r="P78" s="15"/>
-      <c r="Q78" s="17"/>
+      <c r="L78" s="7">
+        <v>30</v>
+      </c>
+      <c r="M78" s="9">
+        <v>25</v>
+      </c>
+      <c r="N78" s="11">
+        <v>35</v>
+      </c>
+      <c r="O78" s="13">
+        <v>45</v>
+      </c>
+      <c r="P78" s="15">
+        <v>30</v>
+      </c>
+      <c r="Q78" s="17">
+        <v>20</v>
+      </c>
       <c r="R78" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>185</v>
       </c>
     </row>
     <row r="79" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10810,15 +11602,27 @@
       <c r="K79" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L79" s="7"/>
-      <c r="M79" s="9"/>
-      <c r="N79" s="11"/>
-      <c r="O79" s="13"/>
-      <c r="P79" s="15"/>
-      <c r="Q79" s="17"/>
+      <c r="L79" s="7">
+        <v>70</v>
+      </c>
+      <c r="M79" s="9">
+        <v>65</v>
+      </c>
+      <c r="N79" s="11">
+        <v>60</v>
+      </c>
+      <c r="O79" s="13">
+        <v>125</v>
+      </c>
+      <c r="P79" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q79" s="17">
+        <v>65</v>
+      </c>
       <c r="R79" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>475</v>
       </c>
     </row>
     <row r="80" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10847,15 +11651,27 @@
       <c r="K80" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="L80" s="7"/>
-      <c r="M80" s="9"/>
-      <c r="N80" s="11"/>
-      <c r="O80" s="13"/>
-      <c r="P80" s="15"/>
-      <c r="Q80" s="17"/>
+      <c r="L80" s="7">
+        <v>76</v>
+      </c>
+      <c r="M80" s="9">
+        <v>25</v>
+      </c>
+      <c r="N80" s="11">
+        <v>45</v>
+      </c>
+      <c r="O80" s="13">
+        <v>67</v>
+      </c>
+      <c r="P80" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q80" s="17">
+        <v>24</v>
+      </c>
       <c r="R80" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>292</v>
       </c>
     </row>
     <row r="81" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10884,15 +11700,27 @@
       <c r="K81" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L81" s="7"/>
-      <c r="M81" s="9"/>
-      <c r="N81" s="11"/>
-      <c r="O81" s="13"/>
-      <c r="P81" s="15"/>
-      <c r="Q81" s="17"/>
+      <c r="L81" s="7">
+        <v>116</v>
+      </c>
+      <c r="M81" s="9">
+        <v>55</v>
+      </c>
+      <c r="N81" s="11">
+        <v>85</v>
+      </c>
+      <c r="O81" s="13">
+        <v>107</v>
+      </c>
+      <c r="P81" s="15">
+        <v>95</v>
+      </c>
+      <c r="Q81" s="17">
+        <v>29</v>
+      </c>
       <c r="R81" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>487</v>
       </c>
     </row>
     <row r="82" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10925,15 +11753,27 @@
       <c r="K82" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="L82" s="7"/>
-      <c r="M82" s="9"/>
-      <c r="N82" s="11"/>
-      <c r="O82" s="13"/>
-      <c r="P82" s="15"/>
-      <c r="Q82" s="17"/>
+      <c r="L82" s="7">
+        <v>50</v>
+      </c>
+      <c r="M82" s="9">
+        <v>52</v>
+      </c>
+      <c r="N82" s="11">
+        <v>48</v>
+      </c>
+      <c r="O82" s="13">
+        <v>65</v>
+      </c>
+      <c r="P82" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q82" s="17">
+        <v>55</v>
+      </c>
       <c r="R82" s="40">
         <f t="shared" ref="R82:R83" si="4">SUM(L82:Q82)</f>
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="83" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -10966,15 +11806,27 @@
       <c r="K83" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L83" s="7"/>
-      <c r="M83" s="9"/>
-      <c r="N83" s="11"/>
-      <c r="O83" s="13"/>
-      <c r="P83" s="15"/>
-      <c r="Q83" s="17"/>
+      <c r="L83" s="7">
+        <v>80</v>
+      </c>
+      <c r="M83" s="9">
+        <v>82</v>
+      </c>
+      <c r="N83" s="11">
+        <v>78</v>
+      </c>
+      <c r="O83" s="13">
+        <v>95</v>
+      </c>
+      <c r="P83" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q83" s="17">
+        <v>85</v>
+      </c>
       <c r="R83" s="40">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="84" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11007,15 +11859,27 @@
       <c r="K84" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="L84" s="7"/>
-      <c r="M84" s="9"/>
-      <c r="N84" s="11"/>
-      <c r="O84" s="13"/>
-      <c r="P84" s="15"/>
-      <c r="Q84" s="17"/>
+      <c r="L84" s="7">
+        <v>37</v>
+      </c>
+      <c r="M84" s="9">
+        <v>55</v>
+      </c>
+      <c r="N84" s="11">
+        <v>70</v>
+      </c>
+      <c r="O84" s="13">
+        <v>30</v>
+      </c>
+      <c r="P84" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q84" s="17">
+        <v>65</v>
+      </c>
       <c r="R84" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>312</v>
       </c>
     </row>
     <row r="85" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11048,15 +11912,27 @@
       <c r="K85" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L85" s="7"/>
-      <c r="M85" s="9"/>
-      <c r="N85" s="11"/>
-      <c r="O85" s="13"/>
-      <c r="P85" s="15"/>
-      <c r="Q85" s="17"/>
+      <c r="L85" s="7">
+        <v>57</v>
+      </c>
+      <c r="M85" s="9">
+        <v>80</v>
+      </c>
+      <c r="N85" s="11">
+        <v>115</v>
+      </c>
+      <c r="O85" s="13">
+        <v>50</v>
+      </c>
+      <c r="P85" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q85" s="17">
+        <v>95</v>
+      </c>
       <c r="R85" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>477</v>
       </c>
     </row>
     <row r="86" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11085,15 +11961,27 @@
       <c r="K86" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="L86" s="7"/>
-      <c r="M86" s="9"/>
-      <c r="N86" s="11"/>
-      <c r="O86" s="13"/>
-      <c r="P86" s="15"/>
-      <c r="Q86" s="17"/>
+      <c r="L86" s="7">
+        <v>41</v>
+      </c>
+      <c r="M86" s="9">
+        <v>63</v>
+      </c>
+      <c r="N86" s="11">
+        <v>40</v>
+      </c>
+      <c r="O86" s="13">
+        <v>40</v>
+      </c>
+      <c r="P86" s="15">
+        <v>30</v>
+      </c>
+      <c r="Q86" s="17">
+        <v>66</v>
+      </c>
       <c r="R86" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="87" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11122,15 +12010,27 @@
       <c r="K87" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L87" s="7"/>
-      <c r="M87" s="9"/>
-      <c r="N87" s="11"/>
-      <c r="O87" s="13"/>
-      <c r="P87" s="15"/>
-      <c r="Q87" s="17"/>
+      <c r="L87" s="7">
+        <v>61</v>
+      </c>
+      <c r="M87" s="9">
+        <v>123</v>
+      </c>
+      <c r="N87" s="11">
+        <v>60</v>
+      </c>
+      <c r="O87" s="13">
+        <v>60</v>
+      </c>
+      <c r="P87" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q87" s="17">
+        <v>136</v>
+      </c>
       <c r="R87" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>490</v>
       </c>
     </row>
     <row r="88" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11159,15 +12059,27 @@
       <c r="K88" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="L88" s="7"/>
-      <c r="M88" s="9"/>
-      <c r="N88" s="11"/>
-      <c r="O88" s="13"/>
-      <c r="P88" s="15"/>
-      <c r="Q88" s="17"/>
+      <c r="L88" s="7">
+        <v>70</v>
+      </c>
+      <c r="M88" s="9">
+        <v>92</v>
+      </c>
+      <c r="N88" s="11">
+        <v>65</v>
+      </c>
+      <c r="O88" s="13">
+        <v>80</v>
+      </c>
+      <c r="P88" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q88" s="17">
+        <v>98</v>
+      </c>
       <c r="R88" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="89" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11198,15 +12110,27 @@
       <c r="K89" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L89" s="7"/>
-      <c r="M89" s="9"/>
-      <c r="N89" s="11"/>
-      <c r="O89" s="13"/>
-      <c r="P89" s="15"/>
-      <c r="Q89" s="17"/>
+      <c r="L89" s="7">
+        <v>120</v>
+      </c>
+      <c r="M89" s="9">
+        <v>112</v>
+      </c>
+      <c r="N89" s="11">
+        <v>65</v>
+      </c>
+      <c r="O89" s="13">
+        <v>80</v>
+      </c>
+      <c r="P89" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q89" s="17">
+        <v>78</v>
+      </c>
       <c r="R89" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>530</v>
       </c>
     </row>
     <row r="90" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11235,15 +12159,27 @@
       <c r="K90" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="L90" s="7"/>
-      <c r="M90" s="9"/>
-      <c r="N90" s="11"/>
-      <c r="O90" s="13"/>
-      <c r="P90" s="15"/>
-      <c r="Q90" s="17"/>
+      <c r="L90" s="7">
+        <v>44</v>
+      </c>
+      <c r="M90" s="9">
+        <v>38</v>
+      </c>
+      <c r="N90" s="11">
+        <v>39</v>
+      </c>
+      <c r="O90" s="13">
+        <v>61</v>
+      </c>
+      <c r="P90" s="15">
+        <v>79</v>
+      </c>
+      <c r="Q90" s="17">
+        <v>42</v>
+      </c>
       <c r="R90" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>303</v>
       </c>
     </row>
     <row r="91" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11272,15 +12208,27 @@
       <c r="K91" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="L91" s="7"/>
-      <c r="M91" s="9"/>
-      <c r="N91" s="11"/>
-      <c r="O91" s="13"/>
-      <c r="P91" s="15"/>
-      <c r="Q91" s="17"/>
+      <c r="L91" s="7">
+        <v>54</v>
+      </c>
+      <c r="M91" s="9">
+        <v>45</v>
+      </c>
+      <c r="N91" s="11">
+        <v>47</v>
+      </c>
+      <c r="O91" s="13">
+        <v>75</v>
+      </c>
+      <c r="P91" s="15">
+        <v>98</v>
+      </c>
+      <c r="Q91" s="17">
+        <v>52</v>
+      </c>
       <c r="R91" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>371</v>
       </c>
     </row>
     <row r="92" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11309,15 +12257,27 @@
       <c r="K92" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L92" s="7"/>
-      <c r="M92" s="9"/>
-      <c r="N92" s="11"/>
-      <c r="O92" s="13"/>
-      <c r="P92" s="15"/>
-      <c r="Q92" s="17"/>
+      <c r="L92" s="7">
+        <v>78</v>
+      </c>
+      <c r="M92" s="9">
+        <v>65</v>
+      </c>
+      <c r="N92" s="11">
+        <v>68</v>
+      </c>
+      <c r="O92" s="13">
+        <v>112</v>
+      </c>
+      <c r="P92" s="15">
+        <v>154</v>
+      </c>
+      <c r="Q92" s="17">
+        <v>75</v>
+      </c>
       <c r="R92" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>552</v>
       </c>
     </row>
     <row r="93" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11352,15 +12312,27 @@
       <c r="K93" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L93" s="7"/>
-      <c r="M93" s="9"/>
-      <c r="N93" s="11"/>
-      <c r="O93" s="13"/>
-      <c r="P93" s="15"/>
-      <c r="Q93" s="17"/>
+      <c r="L93" s="7">
+        <v>25</v>
+      </c>
+      <c r="M93" s="9">
+        <v>35</v>
+      </c>
+      <c r="N93" s="11">
+        <v>40</v>
+      </c>
+      <c r="O93" s="13">
+        <v>20</v>
+      </c>
+      <c r="P93" s="15">
+        <v>30</v>
+      </c>
+      <c r="Q93" s="17">
+        <v>80</v>
+      </c>
       <c r="R93" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>230</v>
       </c>
     </row>
     <row r="94" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11395,15 +12367,27 @@
       <c r="K94" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L94" s="7"/>
-      <c r="M94" s="9"/>
-      <c r="N94" s="11"/>
-      <c r="O94" s="13"/>
-      <c r="P94" s="15"/>
-      <c r="Q94" s="17"/>
+      <c r="L94" s="7">
+        <v>75</v>
+      </c>
+      <c r="M94" s="9">
+        <v>125</v>
+      </c>
+      <c r="N94" s="11">
+        <v>140</v>
+      </c>
+      <c r="O94" s="13">
+        <v>60</v>
+      </c>
+      <c r="P94" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q94" s="17">
+        <v>40</v>
+      </c>
       <c r="R94" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>530</v>
       </c>
     </row>
     <row r="95" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11432,15 +12416,27 @@
       <c r="K95" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="L95" s="7"/>
-      <c r="M95" s="9"/>
-      <c r="N95" s="11"/>
-      <c r="O95" s="13"/>
-      <c r="P95" s="15"/>
-      <c r="Q95" s="17"/>
+      <c r="L95" s="7">
+        <v>35</v>
+      </c>
+      <c r="M95" s="9">
+        <v>55</v>
+      </c>
+      <c r="N95" s="11">
+        <v>40</v>
+      </c>
+      <c r="O95" s="13">
+        <v>45</v>
+      </c>
+      <c r="P95" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q95" s="17">
+        <v>60</v>
+      </c>
       <c r="R95" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>275</v>
       </c>
     </row>
     <row r="96" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11469,15 +12465,27 @@
       <c r="K96" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L96" s="7"/>
-      <c r="M96" s="9"/>
-      <c r="N96" s="11"/>
-      <c r="O96" s="13"/>
-      <c r="P96" s="15"/>
-      <c r="Q96" s="17"/>
+      <c r="L96" s="7">
+        <v>65</v>
+      </c>
+      <c r="M96" s="9">
+        <v>85</v>
+      </c>
+      <c r="N96" s="11">
+        <v>70</v>
+      </c>
+      <c r="O96" s="13">
+        <v>75</v>
+      </c>
+      <c r="P96" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q96" s="17">
+        <v>40</v>
+      </c>
       <c r="R96" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>405</v>
       </c>
     </row>
     <row r="97" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11506,15 +12514,27 @@
       <c r="K97" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L97" s="7"/>
-      <c r="M97" s="9"/>
-      <c r="N97" s="11"/>
-      <c r="O97" s="13"/>
-      <c r="P97" s="15"/>
-      <c r="Q97" s="17"/>
+      <c r="L97" s="7">
+        <v>85</v>
+      </c>
+      <c r="M97" s="9">
+        <v>115</v>
+      </c>
+      <c r="N97" s="11">
+        <v>80</v>
+      </c>
+      <c r="O97" s="13">
+        <v>105</v>
+      </c>
+      <c r="P97" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q97" s="17">
+        <v>50</v>
+      </c>
       <c r="R97" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>515</v>
       </c>
     </row>
     <row r="98" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11549,15 +12569,27 @@
       <c r="K98" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L98" s="7"/>
-      <c r="M98" s="9"/>
-      <c r="N98" s="11"/>
-      <c r="O98" s="13"/>
-      <c r="P98" s="15"/>
-      <c r="Q98" s="17"/>
+      <c r="L98" s="7">
+        <v>53</v>
+      </c>
+      <c r="M98" s="9">
+        <v>54</v>
+      </c>
+      <c r="N98" s="11">
+        <v>53</v>
+      </c>
+      <c r="O98" s="13">
+        <v>37</v>
+      </c>
+      <c r="P98" s="15">
+        <v>46</v>
+      </c>
+      <c r="Q98" s="17">
+        <v>45</v>
+      </c>
       <c r="R98" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="99" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11592,15 +12624,27 @@
       <c r="K99" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L99" s="7"/>
-      <c r="M99" s="9"/>
-      <c r="N99" s="11"/>
-      <c r="O99" s="13"/>
-      <c r="P99" s="15"/>
-      <c r="Q99" s="17"/>
+      <c r="L99" s="7">
+        <v>86</v>
+      </c>
+      <c r="M99" s="9">
+        <v>92</v>
+      </c>
+      <c r="N99" s="11">
+        <v>88</v>
+      </c>
+      <c r="O99" s="13">
+        <v>68</v>
+      </c>
+      <c r="P99" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q99" s="17">
+        <v>73</v>
+      </c>
       <c r="R99" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>482</v>
       </c>
     </row>
     <row r="100" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11633,15 +12677,27 @@
       <c r="K100" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="L100" s="7"/>
-      <c r="M100" s="9"/>
-      <c r="N100" s="11"/>
-      <c r="O100" s="13"/>
-      <c r="P100" s="15"/>
-      <c r="Q100" s="17"/>
+      <c r="L100" s="7">
+        <v>50</v>
+      </c>
+      <c r="M100" s="9">
+        <v>68</v>
+      </c>
+      <c r="N100" s="11">
+        <v>60</v>
+      </c>
+      <c r="O100" s="13">
+        <v>50</v>
+      </c>
+      <c r="P100" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q100" s="17">
+        <v>32</v>
+      </c>
       <c r="R100" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="101" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11674,15 +12730,27 @@
       <c r="K101" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L101" s="7"/>
-      <c r="M101" s="9"/>
-      <c r="N101" s="11"/>
-      <c r="O101" s="13"/>
-      <c r="P101" s="15"/>
-      <c r="Q101" s="17"/>
+      <c r="L101" s="7">
+        <v>80</v>
+      </c>
+      <c r="M101" s="9">
+        <v>118</v>
+      </c>
+      <c r="N101" s="11">
+        <v>90</v>
+      </c>
+      <c r="O101" s="13">
+        <v>70</v>
+      </c>
+      <c r="P101" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q101" s="17">
+        <v>42</v>
+      </c>
       <c r="R101" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="102" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11711,15 +12779,27 @@
       <c r="K102" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="L102" s="7"/>
-      <c r="M102" s="9"/>
-      <c r="N102" s="11"/>
-      <c r="O102" s="13"/>
-      <c r="P102" s="15"/>
-      <c r="Q102" s="17"/>
+      <c r="L102" s="7">
+        <v>30</v>
+      </c>
+      <c r="M102" s="9">
+        <v>65</v>
+      </c>
+      <c r="N102" s="11">
+        <v>100</v>
+      </c>
+      <c r="O102" s="13">
+        <v>45</v>
+      </c>
+      <c r="P102" s="15">
+        <v>25</v>
+      </c>
+      <c r="Q102" s="17">
+        <v>40</v>
+      </c>
       <c r="R102" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>305</v>
       </c>
     </row>
     <row r="103" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11750,15 +12830,27 @@
       <c r="K103" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L103" s="7"/>
-      <c r="M103" s="9"/>
-      <c r="N103" s="11"/>
-      <c r="O103" s="13"/>
-      <c r="P103" s="15"/>
-      <c r="Q103" s="17"/>
+      <c r="L103" s="7">
+        <v>50</v>
+      </c>
+      <c r="M103" s="9">
+        <v>95</v>
+      </c>
+      <c r="N103" s="11">
+        <v>180</v>
+      </c>
+      <c r="O103" s="13">
+        <v>85</v>
+      </c>
+      <c r="P103" s="15">
+        <v>45</v>
+      </c>
+      <c r="Q103" s="17">
+        <v>70</v>
+      </c>
       <c r="R103" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>525</v>
       </c>
     </row>
     <row r="104" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11791,15 +12883,27 @@
       <c r="K104" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="L104" s="7"/>
-      <c r="M104" s="9"/>
-      <c r="N104" s="11"/>
-      <c r="O104" s="13"/>
-      <c r="P104" s="15"/>
-      <c r="Q104" s="17"/>
+      <c r="L104" s="7">
+        <v>50</v>
+      </c>
+      <c r="M104" s="9">
+        <v>53</v>
+      </c>
+      <c r="N104" s="11">
+        <v>62</v>
+      </c>
+      <c r="O104" s="13">
+        <v>58</v>
+      </c>
+      <c r="P104" s="15">
+        <v>63</v>
+      </c>
+      <c r="Q104" s="17">
+        <v>44</v>
+      </c>
       <c r="R104" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="105" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11832,15 +12936,27 @@
       <c r="K105" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L105" s="7"/>
-      <c r="M105" s="9"/>
-      <c r="N105" s="11"/>
-      <c r="O105" s="13"/>
-      <c r="P105" s="15"/>
-      <c r="Q105" s="17"/>
+      <c r="L105" s="7">
+        <v>71</v>
+      </c>
+      <c r="M105" s="9">
+        <v>73</v>
+      </c>
+      <c r="N105" s="11">
+        <v>88</v>
+      </c>
+      <c r="O105" s="13">
+        <v>120</v>
+      </c>
+      <c r="P105" s="15">
+        <v>89</v>
+      </c>
+      <c r="Q105" s="17">
+        <v>59</v>
+      </c>
       <c r="R105" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="106" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11875,15 +12991,27 @@
       <c r="K106" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="L106" s="7"/>
-      <c r="M106" s="9"/>
-      <c r="N106" s="11"/>
-      <c r="O106" s="13"/>
-      <c r="P106" s="15"/>
-      <c r="Q106" s="17"/>
+      <c r="L106" s="7">
+        <v>50</v>
+      </c>
+      <c r="M106" s="9">
+        <v>60</v>
+      </c>
+      <c r="N106" s="11">
+        <v>60</v>
+      </c>
+      <c r="O106" s="13">
+        <v>60</v>
+      </c>
+      <c r="P106" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q106" s="17">
+        <v>30</v>
+      </c>
       <c r="R106" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="107" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11918,15 +13046,27 @@
       <c r="K107" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L107" s="7"/>
-      <c r="M107" s="9"/>
-      <c r="N107" s="11"/>
-      <c r="O107" s="13"/>
-      <c r="P107" s="15"/>
-      <c r="Q107" s="17"/>
+      <c r="L107" s="7">
+        <v>65</v>
+      </c>
+      <c r="M107" s="9">
+        <v>75</v>
+      </c>
+      <c r="N107" s="11">
+        <v>90</v>
+      </c>
+      <c r="O107" s="13">
+        <v>97</v>
+      </c>
+      <c r="P107" s="15">
+        <v>123</v>
+      </c>
+      <c r="Q107" s="17">
+        <v>44</v>
+      </c>
       <c r="R107" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>494</v>
       </c>
     </row>
     <row r="108" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11955,15 +13095,27 @@
       <c r="K108" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="L108" s="7"/>
-      <c r="M108" s="9"/>
-      <c r="N108" s="11"/>
-      <c r="O108" s="13"/>
-      <c r="P108" s="15"/>
-      <c r="Q108" s="17"/>
+      <c r="L108" s="7">
+        <v>50</v>
+      </c>
+      <c r="M108" s="9">
+        <v>72</v>
+      </c>
+      <c r="N108" s="11">
+        <v>35</v>
+      </c>
+      <c r="O108" s="13">
+        <v>35</v>
+      </c>
+      <c r="P108" s="15">
+        <v>35</v>
+      </c>
+      <c r="Q108" s="17">
+        <v>65</v>
+      </c>
       <c r="R108" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>292</v>
       </c>
     </row>
     <row r="109" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -11994,15 +13146,27 @@
       <c r="K109" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="L109" s="7"/>
-      <c r="M109" s="9"/>
-      <c r="N109" s="11"/>
-      <c r="O109" s="13"/>
-      <c r="P109" s="15"/>
-      <c r="Q109" s="17"/>
+      <c r="L109" s="7">
+        <v>60</v>
+      </c>
+      <c r="M109" s="9">
+        <v>82</v>
+      </c>
+      <c r="N109" s="11">
+        <v>45</v>
+      </c>
+      <c r="O109" s="13">
+        <v>45</v>
+      </c>
+      <c r="P109" s="15">
+        <v>45</v>
+      </c>
+      <c r="Q109" s="17">
+        <v>74</v>
+      </c>
       <c r="R109" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>351</v>
       </c>
     </row>
     <row r="110" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12033,15 +13197,27 @@
       <c r="K110" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L110" s="7"/>
-      <c r="M110" s="9"/>
-      <c r="N110" s="11"/>
-      <c r="O110" s="13"/>
-      <c r="P110" s="15"/>
-      <c r="Q110" s="17"/>
+      <c r="L110" s="7">
+        <v>95</v>
+      </c>
+      <c r="M110" s="9">
+        <v>117</v>
+      </c>
+      <c r="N110" s="11">
+        <v>80</v>
+      </c>
+      <c r="O110" s="13">
+        <v>65</v>
+      </c>
+      <c r="P110" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q110" s="17">
+        <v>92</v>
+      </c>
       <c r="R110" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>519</v>
       </c>
     </row>
     <row r="111" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12074,15 +13250,27 @@
       <c r="K111" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L111" s="7"/>
-      <c r="M111" s="9"/>
-      <c r="N111" s="11"/>
-      <c r="O111" s="13"/>
-      <c r="P111" s="15"/>
-      <c r="Q111" s="17"/>
+      <c r="L111" s="7">
+        <v>52</v>
+      </c>
+      <c r="M111" s="9">
+        <v>57</v>
+      </c>
+      <c r="N111" s="11">
+        <v>75</v>
+      </c>
+      <c r="O111" s="13">
+        <v>35</v>
+      </c>
+      <c r="P111" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q111" s="17">
+        <v>46</v>
+      </c>
       <c r="R111" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>315</v>
       </c>
     </row>
     <row r="112" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12115,15 +13303,27 @@
       <c r="K112" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L112" s="7"/>
-      <c r="M112" s="9"/>
-      <c r="N112" s="11"/>
-      <c r="O112" s="13"/>
-      <c r="P112" s="15"/>
-      <c r="Q112" s="17"/>
+      <c r="L112" s="7">
+        <v>72</v>
+      </c>
+      <c r="M112" s="9">
+        <v>107</v>
+      </c>
+      <c r="N112" s="11">
+        <v>125</v>
+      </c>
+      <c r="O112" s="13">
+        <v>65</v>
+      </c>
+      <c r="P112" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q112" s="17">
+        <v>71</v>
+      </c>
       <c r="R112" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="113" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12158,15 +13358,27 @@
       <c r="K113" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="L113" s="7"/>
-      <c r="M113" s="9"/>
-      <c r="N113" s="11"/>
-      <c r="O113" s="13"/>
-      <c r="P113" s="15"/>
-      <c r="Q113" s="17"/>
+      <c r="L113" s="7">
+        <v>50</v>
+      </c>
+      <c r="M113" s="9">
+        <v>75</v>
+      </c>
+      <c r="N113" s="11">
+        <v>70</v>
+      </c>
+      <c r="O113" s="13">
+        <v>35</v>
+      </c>
+      <c r="P113" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q113" s="17">
+        <v>48</v>
+      </c>
       <c r="R113" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>348</v>
       </c>
     </row>
     <row r="114" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12201,15 +13413,27 @@
       <c r="K114" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L114" s="7"/>
-      <c r="M114" s="9"/>
-      <c r="N114" s="11"/>
-      <c r="O114" s="13"/>
-      <c r="P114" s="15"/>
-      <c r="Q114" s="17"/>
+      <c r="L114" s="7">
+        <v>65</v>
+      </c>
+      <c r="M114" s="9">
+        <v>90</v>
+      </c>
+      <c r="N114" s="11">
+        <v>115</v>
+      </c>
+      <c r="O114" s="13">
+        <v>45</v>
+      </c>
+      <c r="P114" s="15">
+        <v>115</v>
+      </c>
+      <c r="Q114" s="17">
+        <v>58</v>
+      </c>
       <c r="R114" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>488</v>
       </c>
     </row>
     <row r="115" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12240,15 +13464,27 @@
       <c r="K115" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="L115" s="7"/>
-      <c r="M115" s="9"/>
-      <c r="N115" s="11"/>
-      <c r="O115" s="13"/>
-      <c r="P115" s="15"/>
-      <c r="Q115" s="17"/>
+      <c r="L115" s="7">
+        <v>50</v>
+      </c>
+      <c r="M115" s="9">
+        <v>30</v>
+      </c>
+      <c r="N115" s="11">
+        <v>55</v>
+      </c>
+      <c r="O115" s="13">
+        <v>65</v>
+      </c>
+      <c r="P115" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q115" s="17">
+        <v>20</v>
+      </c>
       <c r="R115" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>275</v>
       </c>
     </row>
     <row r="116" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12279,15 +13515,27 @@
       <c r="K116" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="L116" s="7"/>
-      <c r="M116" s="9"/>
-      <c r="N116" s="11"/>
-      <c r="O116" s="13"/>
-      <c r="P116" s="15"/>
-      <c r="Q116" s="17"/>
+      <c r="L116" s="7">
+        <v>60</v>
+      </c>
+      <c r="M116" s="9">
+        <v>40</v>
+      </c>
+      <c r="N116" s="11">
+        <v>60</v>
+      </c>
+      <c r="O116" s="13">
+        <v>95</v>
+      </c>
+      <c r="P116" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q116" s="17">
+        <v>55</v>
+      </c>
       <c r="R116" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12318,15 +13566,27 @@
       <c r="K117" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L117" s="7"/>
-      <c r="M117" s="9"/>
-      <c r="N117" s="11"/>
-      <c r="O117" s="13"/>
-      <c r="P117" s="15"/>
-      <c r="Q117" s="17"/>
+      <c r="L117" s="7">
+        <v>60</v>
+      </c>
+      <c r="M117" s="9">
+        <v>55</v>
+      </c>
+      <c r="N117" s="11">
+        <v>90</v>
+      </c>
+      <c r="O117" s="13">
+        <v>145</v>
+      </c>
+      <c r="P117" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q117" s="17">
+        <v>80</v>
+      </c>
       <c r="R117" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>520</v>
       </c>
     </row>
     <row r="118" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12357,15 +13617,27 @@
       <c r="K118" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L118" s="7"/>
-      <c r="M118" s="9"/>
-      <c r="N118" s="11"/>
-      <c r="O118" s="13"/>
-      <c r="P118" s="15"/>
-      <c r="Q118" s="17"/>
+      <c r="L118" s="7">
+        <v>30</v>
+      </c>
+      <c r="M118" s="9">
+        <v>45</v>
+      </c>
+      <c r="N118" s="11">
+        <v>59</v>
+      </c>
+      <c r="O118" s="13">
+        <v>30</v>
+      </c>
+      <c r="P118" s="15">
+        <v>39</v>
+      </c>
+      <c r="Q118" s="17">
+        <v>57</v>
+      </c>
       <c r="R118" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>260</v>
       </c>
     </row>
     <row r="119" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12396,15 +13668,27 @@
       <c r="K119" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L119" s="7"/>
-      <c r="M119" s="9"/>
-      <c r="N119" s="11"/>
-      <c r="O119" s="13"/>
-      <c r="P119" s="15"/>
-      <c r="Q119" s="17"/>
+      <c r="L119" s="7">
+        <v>40</v>
+      </c>
+      <c r="M119" s="9">
+        <v>55</v>
+      </c>
+      <c r="N119" s="11">
+        <v>99</v>
+      </c>
+      <c r="O119" s="13">
+        <v>40</v>
+      </c>
+      <c r="P119" s="15">
+        <v>79</v>
+      </c>
+      <c r="Q119" s="17">
+        <v>47</v>
+      </c>
       <c r="R119" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="120" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12435,15 +13719,27 @@
       <c r="K120" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L120" s="7"/>
-      <c r="M120" s="9"/>
-      <c r="N120" s="11"/>
-      <c r="O120" s="13"/>
-      <c r="P120" s="15"/>
-      <c r="Q120" s="17"/>
+      <c r="L120" s="7">
+        <v>60</v>
+      </c>
+      <c r="M120" s="9">
+        <v>100</v>
+      </c>
+      <c r="N120" s="11">
+        <v>89</v>
+      </c>
+      <c r="O120" s="13">
+        <v>55</v>
+      </c>
+      <c r="P120" s="15">
+        <v>69</v>
+      </c>
+      <c r="Q120" s="17">
+        <v>112</v>
+      </c>
       <c r="R120" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>485</v>
       </c>
     </row>
     <row r="121" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12472,15 +13768,27 @@
       <c r="K121" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="L121" s="7"/>
-      <c r="M121" s="9"/>
-      <c r="N121" s="11"/>
-      <c r="O121" s="13"/>
-      <c r="P121" s="15"/>
-      <c r="Q121" s="17"/>
+      <c r="L121" s="7">
+        <v>47</v>
+      </c>
+      <c r="M121" s="9">
+        <v>62</v>
+      </c>
+      <c r="N121" s="11">
+        <v>45</v>
+      </c>
+      <c r="O121" s="13">
+        <v>55</v>
+      </c>
+      <c r="P121" s="15">
+        <v>45</v>
+      </c>
+      <c r="Q121" s="17">
+        <v>46</v>
+      </c>
       <c r="R121" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="122" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12511,15 +13819,27 @@
       <c r="K122" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="L122" s="7"/>
-      <c r="M122" s="9"/>
-      <c r="N122" s="11"/>
-      <c r="O122" s="13"/>
-      <c r="P122" s="15"/>
-      <c r="Q122" s="17"/>
+      <c r="L122" s="7">
+        <v>57</v>
+      </c>
+      <c r="M122" s="9">
+        <v>82</v>
+      </c>
+      <c r="N122" s="11">
+        <v>95</v>
+      </c>
+      <c r="O122" s="13">
+        <v>55</v>
+      </c>
+      <c r="P122" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q122" s="17">
+        <v>36</v>
+      </c>
       <c r="R122" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="123" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12550,15 +13870,27 @@
       <c r="K123" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L123" s="7"/>
-      <c r="M123" s="9"/>
-      <c r="N123" s="11"/>
-      <c r="O123" s="13"/>
-      <c r="P123" s="15"/>
-      <c r="Q123" s="17"/>
+      <c r="L123" s="7">
+        <v>77</v>
+      </c>
+      <c r="M123" s="9">
+        <v>70</v>
+      </c>
+      <c r="N123" s="11">
+        <v>90</v>
+      </c>
+      <c r="O123" s="13">
+        <v>145</v>
+      </c>
+      <c r="P123" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q123" s="17">
+        <v>43</v>
+      </c>
       <c r="R123" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="124" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12589,15 +13921,27 @@
       <c r="K124" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L124" s="7"/>
-      <c r="M124" s="9"/>
-      <c r="N124" s="11"/>
-      <c r="O124" s="13"/>
-      <c r="P124" s="15"/>
-      <c r="Q124" s="17"/>
+      <c r="L124" s="7">
+        <v>50</v>
+      </c>
+      <c r="M124" s="9">
+        <v>62</v>
+      </c>
+      <c r="N124" s="11">
+        <v>40</v>
+      </c>
+      <c r="O124" s="13">
+        <v>62</v>
+      </c>
+      <c r="P124" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q124" s="17">
+        <v>50</v>
+      </c>
       <c r="R124" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>304</v>
       </c>
     </row>
     <row r="125" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12628,15 +13972,27 @@
       <c r="K125" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L125" s="7"/>
-      <c r="M125" s="9"/>
-      <c r="N125" s="11"/>
-      <c r="O125" s="13"/>
-      <c r="P125" s="15"/>
-      <c r="Q125" s="17"/>
+      <c r="L125" s="7">
+        <v>65</v>
+      </c>
+      <c r="M125" s="9">
+        <v>108</v>
+      </c>
+      <c r="N125" s="11">
+        <v>65</v>
+      </c>
+      <c r="O125" s="13">
+        <v>108</v>
+      </c>
+      <c r="P125" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q125" s="17">
+        <v>75</v>
+      </c>
       <c r="R125" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>486</v>
       </c>
     </row>
     <row r="126" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12665,15 +14021,27 @@
       <c r="K126" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L126" s="7"/>
-      <c r="M126" s="9"/>
-      <c r="N126" s="11"/>
-      <c r="O126" s="13"/>
-      <c r="P126" s="15"/>
-      <c r="Q126" s="17"/>
+      <c r="L126" s="7">
+        <v>30</v>
+      </c>
+      <c r="M126" s="9">
+        <v>35</v>
+      </c>
+      <c r="N126" s="11">
+        <v>30</v>
+      </c>
+      <c r="O126" s="13">
+        <v>55</v>
+      </c>
+      <c r="P126" s="15">
+        <v>30</v>
+      </c>
+      <c r="Q126" s="17">
+        <v>75</v>
+      </c>
       <c r="R126" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>255</v>
       </c>
     </row>
     <row r="127" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12702,15 +14070,27 @@
       <c r="K127" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L127" s="7"/>
-      <c r="M127" s="9"/>
-      <c r="N127" s="11"/>
-      <c r="O127" s="13"/>
-      <c r="P127" s="15"/>
-      <c r="Q127" s="17"/>
+      <c r="L127" s="7">
+        <v>95</v>
+      </c>
+      <c r="M127" s="9">
+        <v>60</v>
+      </c>
+      <c r="N127" s="11">
+        <v>60</v>
+      </c>
+      <c r="O127" s="13">
+        <v>101</v>
+      </c>
+      <c r="P127" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q127" s="17">
+        <v>105</v>
+      </c>
       <c r="R127" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>481</v>
       </c>
     </row>
     <row r="128" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12745,15 +14125,27 @@
       <c r="K128" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="L128" s="7"/>
-      <c r="M128" s="9"/>
-      <c r="N128" s="11"/>
-      <c r="O128" s="13"/>
-      <c r="P128" s="15"/>
-      <c r="Q128" s="17"/>
+      <c r="L128" s="7">
+        <v>80</v>
+      </c>
+      <c r="M128" s="9">
+        <v>85</v>
+      </c>
+      <c r="N128" s="11">
+        <v>95</v>
+      </c>
+      <c r="O128" s="13">
+        <v>30</v>
+      </c>
+      <c r="P128" s="15">
+        <v>30</v>
+      </c>
+      <c r="Q128" s="17">
+        <v>25</v>
+      </c>
       <c r="R128" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>345</v>
       </c>
     </row>
     <row r="129" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12788,15 +14180,27 @@
       <c r="K129" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="L129" s="7"/>
-      <c r="M129" s="9"/>
-      <c r="N129" s="11"/>
-      <c r="O129" s="13"/>
-      <c r="P129" s="15"/>
-      <c r="Q129" s="17"/>
+      <c r="L129" s="7">
+        <v>105</v>
+      </c>
+      <c r="M129" s="9">
+        <v>130</v>
+      </c>
+      <c r="N129" s="11">
+        <v>120</v>
+      </c>
+      <c r="O129" s="13">
+        <v>45</v>
+      </c>
+      <c r="P129" s="15">
+        <v>45</v>
+      </c>
+      <c r="Q129" s="17">
+        <v>40</v>
+      </c>
       <c r="R129" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>485</v>
       </c>
     </row>
     <row r="130" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12831,15 +14235,27 @@
       <c r="K130" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L130" s="7"/>
-      <c r="M130" s="9"/>
-      <c r="N130" s="11"/>
-      <c r="O130" s="13"/>
-      <c r="P130" s="15"/>
-      <c r="Q130" s="17"/>
+      <c r="L130" s="7">
+        <v>115</v>
+      </c>
+      <c r="M130" s="9">
+        <v>140</v>
+      </c>
+      <c r="N130" s="11">
+        <v>130</v>
+      </c>
+      <c r="O130" s="13">
+        <v>55</v>
+      </c>
+      <c r="P130" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q130" s="17">
+        <v>40</v>
+      </c>
       <c r="R130" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>535</v>
       </c>
     </row>
     <row r="131" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12868,15 +14284,27 @@
       <c r="K131" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="L131" s="7"/>
-      <c r="M131" s="9"/>
-      <c r="N131" s="11"/>
-      <c r="O131" s="13"/>
-      <c r="P131" s="15"/>
-      <c r="Q131" s="17"/>
+      <c r="L131" s="7">
+        <v>75</v>
+      </c>
+      <c r="M131" s="9">
+        <v>38</v>
+      </c>
+      <c r="N131" s="11">
+        <v>38</v>
+      </c>
+      <c r="O131" s="13">
+        <v>56</v>
+      </c>
+      <c r="P131" s="15">
+        <v>56</v>
+      </c>
+      <c r="Q131" s="17">
+        <v>67</v>
+      </c>
       <c r="R131" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="132" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12905,15 +14333,27 @@
       <c r="K132" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L132" s="7"/>
-      <c r="M132" s="9"/>
-      <c r="N132" s="11"/>
-      <c r="O132" s="13"/>
-      <c r="P132" s="15"/>
-      <c r="Q132" s="17"/>
+      <c r="L132" s="7">
+        <v>125</v>
+      </c>
+      <c r="M132" s="9">
+        <v>58</v>
+      </c>
+      <c r="N132" s="11">
+        <v>58</v>
+      </c>
+      <c r="O132" s="13">
+        <v>76</v>
+      </c>
+      <c r="P132" s="15">
+        <v>76</v>
+      </c>
+      <c r="Q132" s="17">
+        <v>67</v>
+      </c>
       <c r="R132" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="133" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12942,15 +14382,27 @@
       <c r="K133" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="L133" s="7"/>
-      <c r="M133" s="9"/>
-      <c r="N133" s="11"/>
-      <c r="O133" s="13"/>
-      <c r="P133" s="15"/>
-      <c r="Q133" s="17"/>
+      <c r="L133" s="7">
+        <v>60</v>
+      </c>
+      <c r="M133" s="9">
+        <v>85</v>
+      </c>
+      <c r="N133" s="11">
+        <v>40</v>
+      </c>
+      <c r="O133" s="13">
+        <v>30</v>
+      </c>
+      <c r="P133" s="15">
+        <v>45</v>
+      </c>
+      <c r="Q133" s="17">
+        <v>68</v>
+      </c>
       <c r="R133" s="40">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>328</v>
       </c>
     </row>
     <row r="134" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -12981,15 +14433,27 @@
       <c r="K134" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L134" s="7"/>
-      <c r="M134" s="9"/>
-      <c r="N134" s="11"/>
-      <c r="O134" s="13"/>
-      <c r="P134" s="15"/>
-      <c r="Q134" s="17"/>
+      <c r="L134" s="7">
+        <v>110</v>
+      </c>
+      <c r="M134" s="9">
+        <v>135</v>
+      </c>
+      <c r="N134" s="11">
+        <v>60</v>
+      </c>
+      <c r="O134" s="13">
+        <v>50</v>
+      </c>
+      <c r="P134" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q134" s="17">
+        <v>88</v>
+      </c>
       <c r="R134" s="40">
         <f t="shared" ref="R134:R197" si="6">SUM(L134:Q134)</f>
-        <v>0</v>
+        <v>508</v>
       </c>
     </row>
     <row r="135" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13018,15 +14482,27 @@
       <c r="K135" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L135" s="7"/>
-      <c r="M135" s="9"/>
-      <c r="N135" s="11"/>
-      <c r="O135" s="13"/>
-      <c r="P135" s="15"/>
-      <c r="Q135" s="17"/>
+      <c r="L135" s="7">
+        <v>30</v>
+      </c>
+      <c r="M135" s="9">
+        <v>40</v>
+      </c>
+      <c r="N135" s="11">
+        <v>50</v>
+      </c>
+      <c r="O135" s="13">
+        <v>40</v>
+      </c>
+      <c r="P135" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q135" s="17">
+        <v>30</v>
+      </c>
       <c r="R135" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="136" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13057,15 +14533,27 @@
       <c r="K136" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L136" s="7"/>
-      <c r="M136" s="9"/>
-      <c r="N136" s="11"/>
-      <c r="O136" s="13"/>
-      <c r="P136" s="15"/>
-      <c r="Q136" s="17"/>
+      <c r="L136" s="7">
+        <v>80</v>
+      </c>
+      <c r="M136" s="9">
+        <v>60</v>
+      </c>
+      <c r="N136" s="11">
+        <v>90</v>
+      </c>
+      <c r="O136" s="13">
+        <v>60</v>
+      </c>
+      <c r="P136" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q136" s="17">
+        <v>50</v>
+      </c>
       <c r="R136" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>410</v>
       </c>
     </row>
     <row r="137" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13096,15 +14584,27 @@
       <c r="K137" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L137" s="7"/>
-      <c r="M137" s="9"/>
-      <c r="N137" s="11"/>
-      <c r="O137" s="13"/>
-      <c r="P137" s="15"/>
-      <c r="Q137" s="17"/>
+      <c r="L137" s="7">
+        <v>110</v>
+      </c>
+      <c r="M137" s="9">
+        <v>80</v>
+      </c>
+      <c r="N137" s="11">
+        <v>120</v>
+      </c>
+      <c r="O137" s="13">
+        <v>80</v>
+      </c>
+      <c r="P137" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q137" s="17">
+        <v>30</v>
+      </c>
       <c r="R137" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="138" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13135,15 +14635,27 @@
       <c r="K138" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L138" s="7"/>
-      <c r="M138" s="9"/>
-      <c r="N138" s="11"/>
-      <c r="O138" s="13"/>
-      <c r="P138" s="15"/>
-      <c r="Q138" s="17"/>
+      <c r="L138" s="7">
+        <v>50</v>
+      </c>
+      <c r="M138" s="9">
+        <v>70</v>
+      </c>
+      <c r="N138" s="11">
+        <v>100</v>
+      </c>
+      <c r="O138" s="13">
+        <v>40</v>
+      </c>
+      <c r="P138" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q138" s="17">
+        <v>30</v>
+      </c>
       <c r="R138" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="139" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13174,15 +14686,27 @@
       <c r="K139" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="L139" s="7"/>
-      <c r="M139" s="9"/>
-      <c r="N139" s="11"/>
-      <c r="O139" s="13"/>
-      <c r="P139" s="15"/>
-      <c r="Q139" s="17"/>
+      <c r="L139" s="7">
+        <v>60</v>
+      </c>
+      <c r="M139" s="9">
+        <v>90</v>
+      </c>
+      <c r="N139" s="11">
+        <v>140</v>
+      </c>
+      <c r="O139" s="13">
+        <v>50</v>
+      </c>
+      <c r="P139" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q139" s="17">
+        <v>40</v>
+      </c>
       <c r="R139" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>430</v>
       </c>
     </row>
     <row r="140" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13213,15 +14737,27 @@
       <c r="K140" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L140" s="7"/>
-      <c r="M140" s="9"/>
-      <c r="N140" s="11"/>
-      <c r="O140" s="13"/>
-      <c r="P140" s="15"/>
-      <c r="Q140" s="17"/>
+      <c r="L140" s="7">
+        <v>70</v>
+      </c>
+      <c r="M140" s="9">
+        <v>110</v>
+      </c>
+      <c r="N140" s="11">
+        <v>180</v>
+      </c>
+      <c r="O140" s="13">
+        <v>60</v>
+      </c>
+      <c r="P140" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q140" s="17">
+        <v>50</v>
+      </c>
       <c r="R140" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>530</v>
       </c>
     </row>
     <row r="141" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13252,15 +14788,27 @@
       <c r="K141" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L141" s="7"/>
-      <c r="M141" s="9"/>
-      <c r="N141" s="11"/>
-      <c r="O141" s="13"/>
-      <c r="P141" s="15"/>
-      <c r="Q141" s="17"/>
+      <c r="L141" s="7">
+        <v>50</v>
+      </c>
+      <c r="M141" s="9">
+        <v>45</v>
+      </c>
+      <c r="N141" s="11">
+        <v>45</v>
+      </c>
+      <c r="O141" s="13">
+        <v>35</v>
+      </c>
+      <c r="P141" s="15">
+        <v>64</v>
+      </c>
+      <c r="Q141" s="17">
+        <v>58</v>
+      </c>
       <c r="R141" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>297</v>
       </c>
     </row>
     <row r="142" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13291,15 +14839,27 @@
       <c r="K142" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L142" s="7"/>
-      <c r="M142" s="9"/>
-      <c r="N142" s="11"/>
-      <c r="O142" s="13"/>
-      <c r="P142" s="15"/>
-      <c r="Q142" s="17"/>
+      <c r="L142" s="7">
+        <v>65</v>
+      </c>
+      <c r="M142" s="9">
+        <v>55</v>
+      </c>
+      <c r="N142" s="11">
+        <v>55</v>
+      </c>
+      <c r="O142" s="13">
+        <v>45</v>
+      </c>
+      <c r="P142" s="15">
+        <v>82</v>
+      </c>
+      <c r="Q142" s="17">
+        <v>78</v>
+      </c>
       <c r="R142" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>380</v>
       </c>
     </row>
     <row r="143" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13330,15 +14890,27 @@
       <c r="K143" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L143" s="7"/>
-      <c r="M143" s="9"/>
-      <c r="N143" s="11"/>
-      <c r="O143" s="13"/>
-      <c r="P143" s="15"/>
-      <c r="Q143" s="17"/>
+      <c r="L143" s="7">
+        <v>85</v>
+      </c>
+      <c r="M143" s="9">
+        <v>75</v>
+      </c>
+      <c r="N143" s="11">
+        <v>77</v>
+      </c>
+      <c r="O143" s="13">
+        <v>70</v>
+      </c>
+      <c r="P143" s="15">
+        <v>105</v>
+      </c>
+      <c r="Q143" s="17">
+        <v>94</v>
+      </c>
       <c r="R143" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>506</v>
       </c>
     </row>
     <row r="144" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13373,15 +14945,27 @@
       <c r="K144" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L144" s="7"/>
-      <c r="M144" s="9"/>
-      <c r="N144" s="11"/>
-      <c r="O144" s="13"/>
-      <c r="P144" s="15"/>
-      <c r="Q144" s="17"/>
+      <c r="L144" s="7">
+        <v>50</v>
+      </c>
+      <c r="M144" s="9">
+        <v>50</v>
+      </c>
+      <c r="N144" s="11">
+        <v>150</v>
+      </c>
+      <c r="O144" s="13">
+        <v>50</v>
+      </c>
+      <c r="P144" s="15">
+        <v>150</v>
+      </c>
+      <c r="Q144" s="17">
+        <v>50</v>
+      </c>
       <c r="R144" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="145" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13412,15 +14996,27 @@
       <c r="K145" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L145" s="7"/>
-      <c r="M145" s="9"/>
-      <c r="N145" s="11"/>
-      <c r="O145" s="13"/>
-      <c r="P145" s="15"/>
-      <c r="Q145" s="17"/>
+      <c r="L145" s="7">
+        <v>50</v>
+      </c>
+      <c r="M145" s="9">
+        <v>53</v>
+      </c>
+      <c r="N145" s="11">
+        <v>62</v>
+      </c>
+      <c r="O145" s="13">
+        <v>43</v>
+      </c>
+      <c r="P145" s="15">
+        <v>52</v>
+      </c>
+      <c r="Q145" s="17">
+        <v>45</v>
+      </c>
       <c r="R145" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>305</v>
       </c>
     </row>
     <row r="146" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13451,15 +15047,27 @@
       <c r="K146" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L146" s="7"/>
-      <c r="M146" s="9"/>
-      <c r="N146" s="11"/>
-      <c r="O146" s="13"/>
-      <c r="P146" s="15"/>
-      <c r="Q146" s="17"/>
+      <c r="L146" s="7">
+        <v>50</v>
+      </c>
+      <c r="M146" s="9">
+        <v>63</v>
+      </c>
+      <c r="N146" s="11">
+        <v>152</v>
+      </c>
+      <c r="O146" s="13">
+        <v>53</v>
+      </c>
+      <c r="P146" s="15">
+        <v>142</v>
+      </c>
+      <c r="Q146" s="17">
+        <v>35</v>
+      </c>
       <c r="R146" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>495</v>
       </c>
     </row>
     <row r="147" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13494,15 +15102,27 @@
       <c r="K147" s="79" t="s">
         <v>224</v>
       </c>
-      <c r="L147" s="7"/>
-      <c r="M147" s="9"/>
-      <c r="N147" s="11"/>
-      <c r="O147" s="13"/>
-      <c r="P147" s="15"/>
-      <c r="Q147" s="17"/>
+      <c r="L147" s="7">
+        <v>48</v>
+      </c>
+      <c r="M147" s="9">
+        <v>44</v>
+      </c>
+      <c r="N147" s="11">
+        <v>40</v>
+      </c>
+      <c r="O147" s="13">
+        <v>71</v>
+      </c>
+      <c r="P147" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q147" s="17">
+        <v>77</v>
+      </c>
       <c r="R147" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="148" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13537,15 +15157,27 @@
       <c r="K148" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L148" s="7"/>
-      <c r="M148" s="9"/>
-      <c r="N148" s="11"/>
-      <c r="O148" s="13"/>
-      <c r="P148" s="15"/>
-      <c r="Q148" s="17"/>
+      <c r="L148" s="7">
+        <v>68</v>
+      </c>
+      <c r="M148" s="9">
+        <v>64</v>
+      </c>
+      <c r="N148" s="11">
+        <v>60</v>
+      </c>
+      <c r="O148" s="13">
+        <v>111</v>
+      </c>
+      <c r="P148" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q148" s="17">
+        <v>117</v>
+      </c>
       <c r="R148" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="149" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13576,15 +15208,27 @@
       <c r="K149" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="L149" s="7"/>
-      <c r="M149" s="9"/>
-      <c r="N149" s="11"/>
-      <c r="O149" s="13"/>
-      <c r="P149" s="15"/>
-      <c r="Q149" s="17"/>
+      <c r="L149" s="7">
+        <v>59</v>
+      </c>
+      <c r="M149" s="9">
+        <v>74</v>
+      </c>
+      <c r="N149" s="11">
+        <v>50</v>
+      </c>
+      <c r="O149" s="13">
+        <v>35</v>
+      </c>
+      <c r="P149" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q149" s="17">
+        <v>35</v>
+      </c>
       <c r="R149" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>303</v>
       </c>
     </row>
     <row r="150" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13615,15 +15259,27 @@
       <c r="K150" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L150" s="7"/>
-      <c r="M150" s="9"/>
-      <c r="N150" s="11"/>
-      <c r="O150" s="13"/>
-      <c r="P150" s="15"/>
-      <c r="Q150" s="17"/>
+      <c r="L150" s="7">
+        <v>89</v>
+      </c>
+      <c r="M150" s="9">
+        <v>124</v>
+      </c>
+      <c r="N150" s="11">
+        <v>80</v>
+      </c>
+      <c r="O150" s="13">
+        <v>55</v>
+      </c>
+      <c r="P150" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q150" s="17">
+        <v>55</v>
+      </c>
       <c r="R150" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>483</v>
       </c>
     </row>
     <row r="151" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13654,15 +15310,27 @@
       <c r="K151" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="L151" s="7"/>
-      <c r="M151" s="9"/>
-      <c r="N151" s="11"/>
-      <c r="O151" s="13"/>
-      <c r="P151" s="15"/>
-      <c r="Q151" s="17"/>
+      <c r="L151" s="7">
+        <v>45</v>
+      </c>
+      <c r="M151" s="9">
+        <v>85</v>
+      </c>
+      <c r="N151" s="11">
+        <v>70</v>
+      </c>
+      <c r="O151" s="13">
+        <v>40</v>
+      </c>
+      <c r="P151" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q151" s="17">
+        <v>60</v>
+      </c>
       <c r="R151" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="152" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13693,15 +15361,27 @@
       <c r="K152" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="L152" s="7"/>
-      <c r="M152" s="9"/>
-      <c r="N152" s="11"/>
-      <c r="O152" s="13"/>
-      <c r="P152" s="15"/>
-      <c r="Q152" s="17"/>
+      <c r="L152" s="7">
+        <v>65</v>
+      </c>
+      <c r="M152" s="9">
+        <v>125</v>
+      </c>
+      <c r="N152" s="11">
+        <v>100</v>
+      </c>
+      <c r="O152" s="13">
+        <v>60</v>
+      </c>
+      <c r="P152" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q152" s="17">
+        <v>70</v>
+      </c>
       <c r="R152" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>490</v>
       </c>
     </row>
     <row r="153" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13732,15 +15412,27 @@
       <c r="K153" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L153" s="7"/>
-      <c r="M153" s="9"/>
-      <c r="N153" s="11"/>
-      <c r="O153" s="13"/>
-      <c r="P153" s="15"/>
-      <c r="Q153" s="17"/>
+      <c r="L153" s="7">
+        <v>100</v>
+      </c>
+      <c r="M153" s="9">
+        <v>135</v>
+      </c>
+      <c r="N153" s="11">
+        <v>120</v>
+      </c>
+      <c r="O153" s="13">
+        <v>60</v>
+      </c>
+      <c r="P153" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q153" s="17">
+        <v>50</v>
+      </c>
       <c r="R153" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>550</v>
       </c>
     </row>
     <row r="154" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13773,15 +15465,27 @@
       <c r="K154" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L154" s="7"/>
-      <c r="M154" s="9"/>
-      <c r="N154" s="11"/>
-      <c r="O154" s="13"/>
-      <c r="P154" s="15"/>
-      <c r="Q154" s="17"/>
+      <c r="L154" s="7">
+        <v>38</v>
+      </c>
+      <c r="M154" s="9">
+        <v>30</v>
+      </c>
+      <c r="N154" s="11">
+        <v>85</v>
+      </c>
+      <c r="O154" s="13">
+        <v>55</v>
+      </c>
+      <c r="P154" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q154" s="17">
+        <v>30</v>
+      </c>
       <c r="R154" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>303</v>
       </c>
     </row>
     <row r="155" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13814,15 +15518,27 @@
       <c r="K155" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L155" s="7"/>
-      <c r="M155" s="9"/>
-      <c r="N155" s="11"/>
-      <c r="O155" s="13"/>
-      <c r="P155" s="15"/>
-      <c r="Q155" s="17"/>
+      <c r="L155" s="7">
+        <v>58</v>
+      </c>
+      <c r="M155" s="9">
+        <v>50</v>
+      </c>
+      <c r="N155" s="11">
+        <v>145</v>
+      </c>
+      <c r="O155" s="13">
+        <v>95</v>
+      </c>
+      <c r="P155" s="15">
+        <v>105</v>
+      </c>
+      <c r="Q155" s="17">
+        <v>30</v>
+      </c>
       <c r="R155" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>483</v>
       </c>
     </row>
     <row r="156" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13853,15 +15569,27 @@
       <c r="K156" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L156" s="7"/>
-      <c r="M156" s="9"/>
-      <c r="N156" s="11"/>
-      <c r="O156" s="13"/>
-      <c r="P156" s="15"/>
-      <c r="Q156" s="17"/>
+      <c r="L156" s="7">
+        <v>70</v>
+      </c>
+      <c r="M156" s="9">
+        <v>131</v>
+      </c>
+      <c r="N156" s="11">
+        <v>100</v>
+      </c>
+      <c r="O156" s="13">
+        <v>86</v>
+      </c>
+      <c r="P156" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q156" s="17">
+        <v>40</v>
+      </c>
       <c r="R156" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>517</v>
       </c>
     </row>
     <row r="157" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13896,15 +15624,27 @@
       <c r="K157" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L157" s="7"/>
-      <c r="M157" s="9"/>
-      <c r="N157" s="11"/>
-      <c r="O157" s="13"/>
-      <c r="P157" s="15"/>
-      <c r="Q157" s="17"/>
+      <c r="L157" s="7">
+        <v>70</v>
+      </c>
+      <c r="M157" s="9">
+        <v>40</v>
+      </c>
+      <c r="N157" s="11">
+        <v>50</v>
+      </c>
+      <c r="O157" s="13">
+        <v>55</v>
+      </c>
+      <c r="P157" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q157" s="17">
+        <v>25</v>
+      </c>
       <c r="R157" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>290</v>
       </c>
     </row>
     <row r="158" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13939,15 +15679,27 @@
       <c r="K158" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="L158" s="7"/>
-      <c r="M158" s="9"/>
-      <c r="N158" s="11"/>
-      <c r="O158" s="13"/>
-      <c r="P158" s="15"/>
-      <c r="Q158" s="17"/>
+      <c r="L158" s="7">
+        <v>90</v>
+      </c>
+      <c r="M158" s="9">
+        <v>60</v>
+      </c>
+      <c r="N158" s="11">
+        <v>70</v>
+      </c>
+      <c r="O158" s="13">
+        <v>75</v>
+      </c>
+      <c r="P158" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q158" s="17">
+        <v>45</v>
+      </c>
       <c r="R158" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>410</v>
       </c>
     </row>
     <row r="159" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13982,15 +15734,27 @@
       <c r="K159" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L159" s="7"/>
-      <c r="M159" s="9"/>
-      <c r="N159" s="11"/>
-      <c r="O159" s="13"/>
-      <c r="P159" s="15"/>
-      <c r="Q159" s="17"/>
+      <c r="L159" s="7">
+        <v>110</v>
+      </c>
+      <c r="M159" s="9">
+        <v>80</v>
+      </c>
+      <c r="N159" s="11">
+        <v>90</v>
+      </c>
+      <c r="O159" s="13">
+        <v>95</v>
+      </c>
+      <c r="P159" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q159" s="17">
+        <v>65</v>
+      </c>
       <c r="R159" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>530</v>
       </c>
     </row>
     <row r="160" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14019,15 +15783,27 @@
       <c r="K160" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="L160" s="7"/>
-      <c r="M160" s="9"/>
-      <c r="N160" s="11"/>
-      <c r="O160" s="13"/>
-      <c r="P160" s="15"/>
-      <c r="Q160" s="17"/>
+      <c r="L160" s="7">
+        <v>47</v>
+      </c>
+      <c r="M160" s="9">
+        <v>82</v>
+      </c>
+      <c r="N160" s="11">
+        <v>57</v>
+      </c>
+      <c r="O160" s="13">
+        <v>42</v>
+      </c>
+      <c r="P160" s="15">
+        <v>47</v>
+      </c>
+      <c r="Q160" s="17">
+        <v>63</v>
+      </c>
       <c r="R160" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>338</v>
       </c>
     </row>
     <row r="161" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14058,15 +15834,27 @@
       <c r="K161" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L161" s="7"/>
-      <c r="M161" s="9"/>
-      <c r="N161" s="11"/>
-      <c r="O161" s="13"/>
-      <c r="P161" s="15"/>
-      <c r="Q161" s="17"/>
+      <c r="L161" s="7">
+        <v>97</v>
+      </c>
+      <c r="M161" s="9">
+        <v>132</v>
+      </c>
+      <c r="N161" s="11">
+        <v>77</v>
+      </c>
+      <c r="O161" s="13">
+        <v>62</v>
+      </c>
+      <c r="P161" s="15">
+        <v>67</v>
+      </c>
+      <c r="Q161" s="17">
+        <v>43</v>
+      </c>
       <c r="R161" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>478</v>
       </c>
     </row>
     <row r="162" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14101,15 +15889,27 @@
       <c r="K162" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L162" s="7"/>
-      <c r="M162" s="9"/>
-      <c r="N162" s="11"/>
-      <c r="O162" s="13"/>
-      <c r="P162" s="15"/>
-      <c r="Q162" s="17"/>
+      <c r="L162" s="7">
+        <v>44</v>
+      </c>
+      <c r="M162" s="9">
+        <v>38</v>
+      </c>
+      <c r="N162" s="11">
+        <v>33</v>
+      </c>
+      <c r="O162" s="13">
+        <v>61</v>
+      </c>
+      <c r="P162" s="15">
+        <v>43</v>
+      </c>
+      <c r="Q162" s="17">
+        <v>70</v>
+      </c>
       <c r="R162" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>289</v>
       </c>
     </row>
     <row r="163" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14144,15 +15944,27 @@
       <c r="K163" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L163" s="7"/>
-      <c r="M163" s="9"/>
-      <c r="N163" s="11"/>
-      <c r="O163" s="13"/>
-      <c r="P163" s="15"/>
-      <c r="Q163" s="17"/>
+      <c r="L163" s="7">
+        <v>62</v>
+      </c>
+      <c r="M163" s="9">
+        <v>55</v>
+      </c>
+      <c r="N163" s="11">
+        <v>52</v>
+      </c>
+      <c r="O163" s="13">
+        <v>109</v>
+      </c>
+      <c r="P163" s="15">
+        <v>94</v>
+      </c>
+      <c r="Q163" s="17">
+        <v>109</v>
+      </c>
       <c r="R163" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>481</v>
       </c>
     </row>
     <row r="164" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14185,15 +15997,27 @@
       <c r="K164" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L164" s="7"/>
-      <c r="M164" s="9"/>
-      <c r="N164" s="11"/>
-      <c r="O164" s="13"/>
-      <c r="P164" s="15"/>
-      <c r="Q164" s="17"/>
+      <c r="L164" s="7">
+        <v>70</v>
+      </c>
+      <c r="M164" s="9">
+        <v>45</v>
+      </c>
+      <c r="N164" s="11">
+        <v>40</v>
+      </c>
+      <c r="O164" s="13">
+        <v>45</v>
+      </c>
+      <c r="P164" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q164" s="17">
+        <v>75</v>
+      </c>
       <c r="R164" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>315</v>
       </c>
     </row>
     <row r="165" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14226,15 +16050,27 @@
       <c r="K165" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L165" s="7"/>
-      <c r="M165" s="9"/>
-      <c r="N165" s="11"/>
-      <c r="O165" s="13"/>
-      <c r="P165" s="15"/>
-      <c r="Q165" s="17"/>
+      <c r="L165" s="7">
+        <v>100</v>
+      </c>
+      <c r="M165" s="9">
+        <v>70</v>
+      </c>
+      <c r="N165" s="11">
+        <v>72</v>
+      </c>
+      <c r="O165" s="13">
+        <v>53</v>
+      </c>
+      <c r="P165" s="15">
+        <v>62</v>
+      </c>
+      <c r="Q165" s="17">
+        <v>100</v>
+      </c>
       <c r="R165" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>457</v>
       </c>
     </row>
     <row r="166" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14265,15 +16101,27 @@
       <c r="K166" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="L166" s="7"/>
-      <c r="M166" s="9"/>
-      <c r="N166" s="11"/>
-      <c r="O166" s="13"/>
-      <c r="P166" s="15"/>
-      <c r="Q166" s="17"/>
+      <c r="L166" s="7">
+        <v>55</v>
+      </c>
+      <c r="M166" s="9">
+        <v>40</v>
+      </c>
+      <c r="N166" s="11">
+        <v>50</v>
+      </c>
+      <c r="O166" s="13">
+        <v>65</v>
+      </c>
+      <c r="P166" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q166" s="17">
+        <v>40</v>
+      </c>
       <c r="R166" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>335</v>
       </c>
     </row>
     <row r="167" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14304,15 +16152,27 @@
       <c r="K167" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L167" s="7"/>
-      <c r="M167" s="9"/>
-      <c r="N167" s="11"/>
-      <c r="O167" s="13"/>
-      <c r="P167" s="15"/>
-      <c r="Q167" s="17"/>
+      <c r="L167" s="7">
+        <v>100</v>
+      </c>
+      <c r="M167" s="9">
+        <v>60</v>
+      </c>
+      <c r="N167" s="11">
+        <v>70</v>
+      </c>
+      <c r="O167" s="13">
+        <v>85</v>
+      </c>
+      <c r="P167" s="15">
+        <v>105</v>
+      </c>
+      <c r="Q167" s="17">
+        <v>60</v>
+      </c>
       <c r="R167" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="168" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14341,15 +16201,27 @@
       <c r="K168" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="L168" s="7"/>
-      <c r="M168" s="9"/>
-      <c r="N168" s="11"/>
-      <c r="O168" s="13"/>
-      <c r="P168" s="15"/>
-      <c r="Q168" s="17"/>
+      <c r="L168" s="7">
+        <v>30</v>
+      </c>
+      <c r="M168" s="9">
+        <v>45</v>
+      </c>
+      <c r="N168" s="11">
+        <v>55</v>
+      </c>
+      <c r="O168" s="13">
+        <v>70</v>
+      </c>
+      <c r="P168" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q168" s="17">
+        <v>85</v>
+      </c>
       <c r="R168" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="169" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14380,15 +16252,27 @@
       <c r="K169" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L169" s="7"/>
-      <c r="M169" s="9"/>
-      <c r="N169" s="11"/>
-      <c r="O169" s="13"/>
-      <c r="P169" s="15"/>
-      <c r="Q169" s="17"/>
+      <c r="L169" s="7">
+        <v>60</v>
+      </c>
+      <c r="M169" s="9">
+        <v>75</v>
+      </c>
+      <c r="N169" s="11">
+        <v>85</v>
+      </c>
+      <c r="O169" s="13">
+        <v>100</v>
+      </c>
+      <c r="P169" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q169" s="17">
+        <v>115</v>
+      </c>
       <c r="R169" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>520</v>
       </c>
     </row>
     <row r="170" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14417,15 +16301,27 @@
       <c r="K170" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L170" s="7"/>
-      <c r="M170" s="9"/>
-      <c r="N170" s="11"/>
-      <c r="O170" s="13"/>
-      <c r="P170" s="15"/>
-      <c r="Q170" s="17"/>
+      <c r="L170" s="7">
+        <v>50</v>
+      </c>
+      <c r="M170" s="9">
+        <v>64</v>
+      </c>
+      <c r="N170" s="11">
+        <v>50</v>
+      </c>
+      <c r="O170" s="13">
+        <v>45</v>
+      </c>
+      <c r="P170" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q170" s="17">
+        <v>41</v>
+      </c>
       <c r="R170" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="171" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14454,15 +16350,27 @@
       <c r="K171" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="L171" s="7"/>
-      <c r="M171" s="9"/>
-      <c r="N171" s="11"/>
-      <c r="O171" s="13"/>
-      <c r="P171" s="15"/>
-      <c r="Q171" s="17"/>
+      <c r="L171" s="7">
+        <v>70</v>
+      </c>
+      <c r="M171" s="9">
+        <v>84</v>
+      </c>
+      <c r="N171" s="11">
+        <v>70</v>
+      </c>
+      <c r="O171" s="13">
+        <v>65</v>
+      </c>
+      <c r="P171" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q171" s="17">
+        <v>51</v>
+      </c>
       <c r="R171" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>410</v>
       </c>
     </row>
     <row r="172" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14491,15 +16399,27 @@
       <c r="K172" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L172" s="7"/>
-      <c r="M172" s="9"/>
-      <c r="N172" s="11"/>
-      <c r="O172" s="13"/>
-      <c r="P172" s="15"/>
-      <c r="Q172" s="17"/>
+      <c r="L172" s="7">
+        <v>100</v>
+      </c>
+      <c r="M172" s="9">
+        <v>134</v>
+      </c>
+      <c r="N172" s="11">
+        <v>110</v>
+      </c>
+      <c r="O172" s="13">
+        <v>95</v>
+      </c>
+      <c r="P172" s="15">
+        <v>100</v>
+      </c>
+      <c r="Q172" s="17">
+        <v>61</v>
+      </c>
       <c r="R172" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="173" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14532,15 +16452,27 @@
       <c r="K173" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="L173" s="7"/>
-      <c r="M173" s="9"/>
-      <c r="N173" s="11"/>
-      <c r="O173" s="13"/>
-      <c r="P173" s="15"/>
-      <c r="Q173" s="17"/>
+      <c r="L173" s="7">
+        <v>72</v>
+      </c>
+      <c r="M173" s="9">
+        <v>80</v>
+      </c>
+      <c r="N173" s="11">
+        <v>49</v>
+      </c>
+      <c r="O173" s="13">
+        <v>40</v>
+      </c>
+      <c r="P173" s="15">
+        <v>49</v>
+      </c>
+      <c r="Q173" s="17">
+        <v>40</v>
+      </c>
       <c r="R173" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="174" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14573,15 +16505,27 @@
       <c r="K174" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L174" s="7"/>
-      <c r="M174" s="9"/>
-      <c r="N174" s="11"/>
-      <c r="O174" s="13"/>
-      <c r="P174" s="15"/>
-      <c r="Q174" s="17"/>
+      <c r="L174" s="7">
+        <v>122</v>
+      </c>
+      <c r="M174" s="9">
+        <v>130</v>
+      </c>
+      <c r="N174" s="11">
+        <v>69</v>
+      </c>
+      <c r="O174" s="13">
+        <v>80</v>
+      </c>
+      <c r="P174" s="15">
+        <v>69</v>
+      </c>
+      <c r="Q174" s="17">
+        <v>30</v>
+      </c>
       <c r="R174" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="175" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14608,15 +16552,27 @@
       <c r="K175" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L175" s="7"/>
-      <c r="M175" s="9"/>
-      <c r="N175" s="11"/>
-      <c r="O175" s="13"/>
-      <c r="P175" s="15"/>
-      <c r="Q175" s="17"/>
+      <c r="L175" s="7">
+        <v>65</v>
+      </c>
+      <c r="M175" s="9">
+        <v>130</v>
+      </c>
+      <c r="N175" s="11">
+        <v>60</v>
+      </c>
+      <c r="O175" s="13">
+        <v>75</v>
+      </c>
+      <c r="P175" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q175" s="17">
+        <v>75</v>
+      </c>
       <c r="R175" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>465</v>
       </c>
     </row>
     <row r="176" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14643,15 +16599,27 @@
       <c r="K176" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L176" s="7"/>
-      <c r="M176" s="9"/>
-      <c r="N176" s="11"/>
-      <c r="O176" s="13"/>
-      <c r="P176" s="15"/>
-      <c r="Q176" s="17"/>
+      <c r="L176" s="7">
+        <v>51</v>
+      </c>
+      <c r="M176" s="9">
+        <v>52</v>
+      </c>
+      <c r="N176" s="11">
+        <v>90</v>
+      </c>
+      <c r="O176" s="13">
+        <v>82</v>
+      </c>
+      <c r="P176" s="15">
+        <v>110</v>
+      </c>
+      <c r="Q176" s="17">
+        <v>100</v>
+      </c>
       <c r="R176" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>485</v>
       </c>
     </row>
     <row r="177" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14680,15 +16648,27 @@
       <c r="K177" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="L177" s="7"/>
-      <c r="M177" s="9"/>
-      <c r="N177" s="11"/>
-      <c r="O177" s="13"/>
-      <c r="P177" s="15"/>
-      <c r="Q177" s="17"/>
+      <c r="L177" s="7">
+        <v>45</v>
+      </c>
+      <c r="M177" s="9">
+        <v>55</v>
+      </c>
+      <c r="N177" s="11">
+        <v>65</v>
+      </c>
+      <c r="O177" s="13">
+        <v>45</v>
+      </c>
+      <c r="P177" s="15">
+        <v>45</v>
+      </c>
+      <c r="Q177" s="17">
+        <v>45</v>
+      </c>
       <c r="R177" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="178" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14719,15 +16699,27 @@
       <c r="K178" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="L178" s="7"/>
-      <c r="M178" s="9"/>
-      <c r="N178" s="11"/>
-      <c r="O178" s="13"/>
-      <c r="P178" s="15"/>
-      <c r="Q178" s="17"/>
+      <c r="L178" s="7">
+        <v>55</v>
+      </c>
+      <c r="M178" s="9">
+        <v>75</v>
+      </c>
+      <c r="N178" s="11">
+        <v>90</v>
+      </c>
+      <c r="O178" s="13">
+        <v>65</v>
+      </c>
+      <c r="P178" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q178" s="17">
+        <v>65</v>
+      </c>
       <c r="R178" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="179" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14758,15 +16750,27 @@
       <c r="K179" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L179" s="7"/>
-      <c r="M179" s="9"/>
-      <c r="N179" s="11"/>
-      <c r="O179" s="13"/>
-      <c r="P179" s="15"/>
-      <c r="Q179" s="17"/>
+      <c r="L179" s="7">
+        <v>75</v>
+      </c>
+      <c r="M179" s="9">
+        <v>110</v>
+      </c>
+      <c r="N179" s="11">
+        <v>125</v>
+      </c>
+      <c r="O179" s="13">
+        <v>100</v>
+      </c>
+      <c r="P179" s="15">
+        <v>105</v>
+      </c>
+      <c r="Q179" s="17">
+        <v>85</v>
+      </c>
       <c r="R179" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="180" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14793,15 +16797,27 @@
       <c r="K180" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L180" s="7"/>
-      <c r="M180" s="9"/>
-      <c r="N180" s="11"/>
-      <c r="O180" s="13"/>
-      <c r="P180" s="15"/>
-      <c r="Q180" s="17"/>
+      <c r="L180" s="7">
+        <v>50</v>
+      </c>
+      <c r="M180" s="9">
+        <v>50</v>
+      </c>
+      <c r="N180" s="11">
+        <v>62</v>
+      </c>
+      <c r="O180" s="13">
+        <v>40</v>
+      </c>
+      <c r="P180" s="15">
+        <v>62</v>
+      </c>
+      <c r="Q180" s="17">
+        <v>65</v>
+      </c>
       <c r="R180" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="181" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14828,15 +16844,27 @@
       <c r="K181" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L181" s="7"/>
-      <c r="M181" s="9"/>
-      <c r="N181" s="11"/>
-      <c r="O181" s="13"/>
-      <c r="P181" s="15"/>
-      <c r="Q181" s="17"/>
+      <c r="L181" s="7">
+        <v>80</v>
+      </c>
+      <c r="M181" s="9">
+        <v>95</v>
+      </c>
+      <c r="N181" s="11">
+        <v>82</v>
+      </c>
+      <c r="O181" s="13">
+        <v>60</v>
+      </c>
+      <c r="P181" s="15">
+        <v>82</v>
+      </c>
+      <c r="Q181" s="17">
+        <v>75</v>
+      </c>
       <c r="R181" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>474</v>
       </c>
     </row>
     <row r="182" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14865,15 +16893,27 @@
       <c r="K182" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="L182" s="7"/>
-      <c r="M182" s="9"/>
-      <c r="N182" s="11"/>
-      <c r="O182" s="13"/>
-      <c r="P182" s="15"/>
-      <c r="Q182" s="17"/>
+      <c r="L182" s="7">
+        <v>60</v>
+      </c>
+      <c r="M182" s="9">
+        <v>85</v>
+      </c>
+      <c r="N182" s="11">
+        <v>42</v>
+      </c>
+      <c r="O182" s="13">
+        <v>85</v>
+      </c>
+      <c r="P182" s="15">
+        <v>42</v>
+      </c>
+      <c r="Q182" s="17">
+        <v>91</v>
+      </c>
       <c r="R182" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>405</v>
       </c>
     </row>
     <row r="183" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14902,15 +16942,27 @@
       <c r="K183" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L183" s="7"/>
-      <c r="M183" s="9"/>
-      <c r="N183" s="11"/>
-      <c r="O183" s="13"/>
-      <c r="P183" s="15"/>
-      <c r="Q183" s="17"/>
+      <c r="L183" s="7">
+        <v>100</v>
+      </c>
+      <c r="M183" s="9">
+        <v>125</v>
+      </c>
+      <c r="N183" s="11">
+        <v>52</v>
+      </c>
+      <c r="O183" s="13">
+        <v>105</v>
+      </c>
+      <c r="P183" s="15">
+        <v>52</v>
+      </c>
+      <c r="Q183" s="17">
+        <v>71</v>
+      </c>
       <c r="R183" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>505</v>
       </c>
     </row>
     <row r="184" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14939,15 +16991,27 @@
       <c r="K184" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="L184" s="7"/>
-      <c r="M184" s="9"/>
-      <c r="N184" s="11"/>
-      <c r="O184" s="13"/>
-      <c r="P184" s="15"/>
-      <c r="Q184" s="17"/>
+      <c r="L184" s="7">
+        <v>76</v>
+      </c>
+      <c r="M184" s="9">
+        <v>65</v>
+      </c>
+      <c r="N184" s="11">
+        <v>45</v>
+      </c>
+      <c r="O184" s="13">
+        <v>92</v>
+      </c>
+      <c r="P184" s="15">
+        <v>42</v>
+      </c>
+      <c r="Q184" s="17">
+        <v>91</v>
+      </c>
       <c r="R184" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>411</v>
       </c>
     </row>
     <row r="185" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -14978,15 +17042,27 @@
       <c r="K185" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="L185" s="7"/>
-      <c r="M185" s="9"/>
-      <c r="N185" s="11"/>
-      <c r="O185" s="13"/>
-      <c r="P185" s="15"/>
-      <c r="Q185" s="17"/>
+      <c r="L185" s="7">
+        <v>60</v>
+      </c>
+      <c r="M185" s="9">
+        <v>40</v>
+      </c>
+      <c r="N185" s="11">
+        <v>80</v>
+      </c>
+      <c r="O185" s="13">
+        <v>60</v>
+      </c>
+      <c r="P185" s="15">
+        <v>45</v>
+      </c>
+      <c r="Q185" s="17">
+        <v>40</v>
+      </c>
       <c r="R185" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>325</v>
       </c>
     </row>
     <row r="186" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15017,15 +17093,27 @@
       <c r="K186" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L186" s="7"/>
-      <c r="M186" s="9"/>
-      <c r="N186" s="11"/>
-      <c r="O186" s="13"/>
-      <c r="P186" s="15"/>
-      <c r="Q186" s="17"/>
+      <c r="L186" s="7">
+        <v>95</v>
+      </c>
+      <c r="M186" s="9">
+        <v>95</v>
+      </c>
+      <c r="N186" s="11">
+        <v>85</v>
+      </c>
+      <c r="O186" s="13">
+        <v>125</v>
+      </c>
+      <c r="P186" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q186" s="17">
+        <v>55</v>
+      </c>
       <c r="R186" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>530</v>
       </c>
     </row>
     <row r="187" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15060,15 +17148,27 @@
       <c r="K187" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="L187" s="7"/>
-      <c r="M187" s="9"/>
-      <c r="N187" s="11"/>
-      <c r="O187" s="13"/>
-      <c r="P187" s="15"/>
-      <c r="Q187" s="17"/>
+      <c r="L187" s="7">
+        <v>40</v>
+      </c>
+      <c r="M187" s="9">
+        <v>30</v>
+      </c>
+      <c r="N187" s="11">
+        <v>35</v>
+      </c>
+      <c r="O187" s="13">
+        <v>45</v>
+      </c>
+      <c r="P187" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q187" s="17">
+        <v>55</v>
+      </c>
       <c r="R187" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>245</v>
       </c>
     </row>
     <row r="188" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15103,15 +17203,27 @@
       <c r="K188" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L188" s="7"/>
-      <c r="M188" s="9"/>
-      <c r="N188" s="11"/>
-      <c r="O188" s="13"/>
-      <c r="P188" s="15"/>
-      <c r="Q188" s="17"/>
+      <c r="L188" s="7">
+        <v>85</v>
+      </c>
+      <c r="M188" s="9">
+        <v>70</v>
+      </c>
+      <c r="N188" s="11">
+        <v>80</v>
+      </c>
+      <c r="O188" s="13">
+        <v>97</v>
+      </c>
+      <c r="P188" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q188" s="17">
+        <v>123</v>
+      </c>
       <c r="R188" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>535</v>
       </c>
     </row>
     <row r="189" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15140,15 +17252,27 @@
       <c r="K189" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L189" s="7"/>
-      <c r="M189" s="9"/>
-      <c r="N189" s="11"/>
-      <c r="O189" s="13"/>
-      <c r="P189" s="15"/>
-      <c r="Q189" s="17"/>
+      <c r="L189" s="7">
+        <v>150</v>
+      </c>
+      <c r="M189" s="9">
+        <v>100</v>
+      </c>
+      <c r="N189" s="11">
+        <v>115</v>
+      </c>
+      <c r="O189" s="13">
+        <v>65</v>
+      </c>
+      <c r="P189" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q189" s="17">
+        <v>35</v>
+      </c>
       <c r="R189" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>530</v>
       </c>
     </row>
     <row r="190" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15179,15 +17303,27 @@
       <c r="K190" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L190" s="7"/>
-      <c r="M190" s="9"/>
-      <c r="N190" s="11"/>
-      <c r="O190" s="13"/>
-      <c r="P190" s="15"/>
-      <c r="Q190" s="17"/>
+      <c r="L190" s="7">
+        <v>68</v>
+      </c>
+      <c r="M190" s="9">
+        <v>50</v>
+      </c>
+      <c r="N190" s="11">
+        <v>60</v>
+      </c>
+      <c r="O190" s="13">
+        <v>120</v>
+      </c>
+      <c r="P190" s="15">
+        <v>95</v>
+      </c>
+      <c r="Q190" s="17">
+        <v>82</v>
+      </c>
       <c r="R190" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>475</v>
       </c>
     </row>
     <row r="191" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15216,15 +17352,27 @@
       <c r="K191" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="L191" s="7"/>
-      <c r="M191" s="9"/>
-      <c r="N191" s="11"/>
-      <c r="O191" s="13"/>
-      <c r="P191" s="15"/>
-      <c r="Q191" s="17"/>
+      <c r="L191" s="7">
+        <v>40</v>
+      </c>
+      <c r="M191" s="9">
+        <v>50</v>
+      </c>
+      <c r="N191" s="11">
+        <v>40</v>
+      </c>
+      <c r="O191" s="13">
+        <v>50</v>
+      </c>
+      <c r="P191" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q191" s="17">
+        <v>35</v>
+      </c>
       <c r="R191" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>255</v>
       </c>
     </row>
     <row r="192" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15255,15 +17403,27 @@
       <c r="K192" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L192" s="7"/>
-      <c r="M192" s="9"/>
-      <c r="N192" s="11"/>
-      <c r="O192" s="13"/>
-      <c r="P192" s="15"/>
-      <c r="Q192" s="17"/>
+      <c r="L192" s="7">
+        <v>85</v>
+      </c>
+      <c r="M192" s="9">
+        <v>60</v>
+      </c>
+      <c r="N192" s="11">
+        <v>100</v>
+      </c>
+      <c r="O192" s="13">
+        <v>125</v>
+      </c>
+      <c r="P192" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q192" s="17">
+        <v>75</v>
+      </c>
       <c r="R192" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>525</v>
       </c>
     </row>
     <row r="193" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15294,15 +17454,27 @@
       <c r="K193" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L193" s="7"/>
-      <c r="M193" s="9"/>
-      <c r="N193" s="11"/>
-      <c r="O193" s="13"/>
-      <c r="P193" s="15"/>
-      <c r="Q193" s="17"/>
+      <c r="L193" s="7">
+        <v>75</v>
+      </c>
+      <c r="M193" s="9">
+        <v>125</v>
+      </c>
+      <c r="N193" s="11">
+        <v>80</v>
+      </c>
+      <c r="O193" s="13">
+        <v>60</v>
+      </c>
+      <c r="P193" s="15">
+        <v>100</v>
+      </c>
+      <c r="Q193" s="17">
+        <v>85</v>
+      </c>
       <c r="R193" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>525</v>
       </c>
     </row>
     <row r="194" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15333,15 +17505,27 @@
       <c r="K194" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="L194" s="7"/>
-      <c r="M194" s="9"/>
-      <c r="N194" s="11"/>
-      <c r="O194" s="13"/>
-      <c r="P194" s="15"/>
-      <c r="Q194" s="17"/>
+      <c r="L194" s="7">
+        <v>55</v>
+      </c>
+      <c r="M194" s="9">
+        <v>85</v>
+      </c>
+      <c r="N194" s="11">
+        <v>55</v>
+      </c>
+      <c r="O194" s="13">
+        <v>50</v>
+      </c>
+      <c r="P194" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q194" s="17">
+        <v>60</v>
+      </c>
       <c r="R194" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="195" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15372,15 +17556,27 @@
       <c r="K195" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L195" s="7"/>
-      <c r="M195" s="9"/>
-      <c r="N195" s="11"/>
-      <c r="O195" s="13"/>
-      <c r="P195" s="15"/>
-      <c r="Q195" s="17"/>
+      <c r="L195" s="7">
+        <v>85</v>
+      </c>
+      <c r="M195" s="9">
+        <v>60</v>
+      </c>
+      <c r="N195" s="11">
+        <v>65</v>
+      </c>
+      <c r="O195" s="13">
+        <v>135</v>
+      </c>
+      <c r="P195" s="15">
+        <v>105</v>
+      </c>
+      <c r="Q195" s="17">
+        <v>100</v>
+      </c>
       <c r="R195" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>550</v>
       </c>
     </row>
     <row r="196" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15415,15 +17611,27 @@
       <c r="K196" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L196" s="7"/>
-      <c r="M196" s="9"/>
-      <c r="N196" s="11"/>
-      <c r="O196" s="13"/>
-      <c r="P196" s="15"/>
-      <c r="Q196" s="17"/>
+      <c r="L196" s="7">
+        <v>60</v>
+      </c>
+      <c r="M196" s="9">
+        <v>78</v>
+      </c>
+      <c r="N196" s="11">
+        <v>135</v>
+      </c>
+      <c r="O196" s="13">
+        <v>91</v>
+      </c>
+      <c r="P196" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q196" s="17">
+        <v>36</v>
+      </c>
       <c r="R196" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>485</v>
       </c>
     </row>
     <row r="197" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15458,15 +17666,27 @@
       <c r="K197" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L197" s="7"/>
-      <c r="M197" s="9"/>
-      <c r="N197" s="11"/>
-      <c r="O197" s="13"/>
-      <c r="P197" s="15"/>
-      <c r="Q197" s="17"/>
+      <c r="L197" s="7">
+        <v>78</v>
+      </c>
+      <c r="M197" s="9">
+        <v>60</v>
+      </c>
+      <c r="N197" s="11">
+        <v>85</v>
+      </c>
+      <c r="O197" s="13">
+        <v>135</v>
+      </c>
+      <c r="P197" s="15">
+        <v>91</v>
+      </c>
+      <c r="Q197" s="17">
+        <v>36</v>
+      </c>
       <c r="R197" s="40">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>485</v>
       </c>
     </row>
     <row r="198" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15497,15 +17717,27 @@
       <c r="K198" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L198" s="7"/>
-      <c r="M198" s="9"/>
-      <c r="N198" s="11"/>
-      <c r="O198" s="13"/>
-      <c r="P198" s="15"/>
-      <c r="Q198" s="17"/>
+      <c r="L198" s="7">
+        <v>40</v>
+      </c>
+      <c r="M198" s="9">
+        <v>38</v>
+      </c>
+      <c r="N198" s="11">
+        <v>35</v>
+      </c>
+      <c r="O198" s="13">
+        <v>54</v>
+      </c>
+      <c r="P198" s="15">
+        <v>35</v>
+      </c>
+      <c r="Q198" s="17">
+        <v>40</v>
+      </c>
       <c r="R198" s="40">
         <f t="shared" ref="R198:R201" si="8">SUM(L198:Q198)</f>
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="199" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15536,15 +17768,27 @@
       <c r="K199" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L199" s="7"/>
-      <c r="M199" s="9"/>
-      <c r="N199" s="11"/>
-      <c r="O199" s="13"/>
-      <c r="P199" s="15"/>
-      <c r="Q199" s="17"/>
+      <c r="L199" s="7">
+        <v>75</v>
+      </c>
+      <c r="M199" s="9">
+        <v>98</v>
+      </c>
+      <c r="N199" s="11">
+        <v>70</v>
+      </c>
+      <c r="O199" s="13">
+        <v>114</v>
+      </c>
+      <c r="P199" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q199" s="17">
+        <v>75</v>
+      </c>
       <c r="R199" s="40">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>502</v>
       </c>
     </row>
     <row r="200" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15573,15 +17817,27 @@
       <c r="K200" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="L200" s="7"/>
-      <c r="M200" s="9"/>
-      <c r="N200" s="11"/>
-      <c r="O200" s="13"/>
-      <c r="P200" s="15"/>
-      <c r="Q200" s="17"/>
+      <c r="L200" s="7">
+        <v>30</v>
+      </c>
+      <c r="M200" s="9">
+        <v>40</v>
+      </c>
+      <c r="N200" s="11">
+        <v>55</v>
+      </c>
+      <c r="O200" s="13">
+        <v>40</v>
+      </c>
+      <c r="P200" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q200" s="17">
+        <v>60</v>
+      </c>
       <c r="R200" s="40">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>280</v>
       </c>
     </row>
     <row r="201" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15610,15 +17866,27 @@
       <c r="K201" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L201" s="7"/>
-      <c r="M201" s="9"/>
-      <c r="N201" s="11"/>
-      <c r="O201" s="13"/>
-      <c r="P201" s="15"/>
-      <c r="Q201" s="17"/>
+      <c r="L201" s="7">
+        <v>60</v>
+      </c>
+      <c r="M201" s="9">
+        <v>60</v>
+      </c>
+      <c r="N201" s="11">
+        <v>75</v>
+      </c>
+      <c r="O201" s="13">
+        <v>60</v>
+      </c>
+      <c r="P201" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q201" s="17">
+        <v>80</v>
+      </c>
       <c r="R201" s="40">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>410</v>
       </c>
     </row>
     <row r="202" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15647,15 +17915,27 @@
       <c r="K202" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L202" s="7"/>
-      <c r="M202" s="9"/>
-      <c r="N202" s="11"/>
-      <c r="O202" s="13"/>
-      <c r="P202" s="15"/>
-      <c r="Q202" s="17"/>
+      <c r="L202" s="7">
+        <v>58</v>
+      </c>
+      <c r="M202" s="9">
+        <v>109</v>
+      </c>
+      <c r="N202" s="11">
+        <v>112</v>
+      </c>
+      <c r="O202" s="13">
+        <v>48</v>
+      </c>
+      <c r="P202" s="15">
+        <v>48</v>
+      </c>
+      <c r="Q202" s="17">
+        <v>109</v>
+      </c>
       <c r="R202" s="40">
         <f t="shared" ref="R202:R265" si="9">SUM(L202:Q202)</f>
-        <v>0</v>
+        <v>484</v>
       </c>
     </row>
     <row r="203" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15682,15 +17962,27 @@
       <c r="K203" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L203" s="7"/>
-      <c r="M203" s="9"/>
-      <c r="N203" s="11"/>
-      <c r="O203" s="13"/>
-      <c r="P203" s="15"/>
-      <c r="Q203" s="17"/>
+      <c r="L203" s="7">
+        <v>85</v>
+      </c>
+      <c r="M203" s="9">
+        <v>97</v>
+      </c>
+      <c r="N203" s="11">
+        <v>66</v>
+      </c>
+      <c r="O203" s="13">
+        <v>105</v>
+      </c>
+      <c r="P203" s="15">
+        <v>66</v>
+      </c>
+      <c r="Q203" s="17">
+        <v>65</v>
+      </c>
       <c r="R203" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>484</v>
       </c>
     </row>
     <row r="204" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15725,15 +18017,27 @@
       <c r="K204" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L204" s="7"/>
-      <c r="M204" s="9"/>
-      <c r="N204" s="11"/>
-      <c r="O204" s="13"/>
-      <c r="P204" s="15"/>
-      <c r="Q204" s="17"/>
+      <c r="L204" s="7">
+        <v>43</v>
+      </c>
+      <c r="M204" s="9">
+        <v>70</v>
+      </c>
+      <c r="N204" s="11">
+        <v>48</v>
+      </c>
+      <c r="O204" s="13">
+        <v>50</v>
+      </c>
+      <c r="P204" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q204" s="17">
+        <v>38</v>
+      </c>
       <c r="R204" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>309</v>
       </c>
     </row>
     <row r="205" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15768,15 +18072,27 @@
       <c r="K205" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L205" s="7"/>
-      <c r="M205" s="9"/>
-      <c r="N205" s="11"/>
-      <c r="O205" s="13"/>
-      <c r="P205" s="15"/>
-      <c r="Q205" s="17"/>
+      <c r="L205" s="7">
+        <v>85</v>
+      </c>
+      <c r="M205" s="9">
+        <v>110</v>
+      </c>
+      <c r="N205" s="11">
+        <v>76</v>
+      </c>
+      <c r="O205" s="13">
+        <v>65</v>
+      </c>
+      <c r="P205" s="15">
+        <v>82</v>
+      </c>
+      <c r="Q205" s="17">
+        <v>56</v>
+      </c>
       <c r="R205" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>474</v>
       </c>
     </row>
     <row r="206" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15809,15 +18125,27 @@
       <c r="K206" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="L206" s="7"/>
-      <c r="M206" s="9"/>
-      <c r="N206" s="11"/>
-      <c r="O206" s="13"/>
-      <c r="P206" s="15"/>
-      <c r="Q206" s="17"/>
+      <c r="L206" s="7">
+        <v>55</v>
+      </c>
+      <c r="M206" s="9">
+        <v>69</v>
+      </c>
+      <c r="N206" s="11">
+        <v>85</v>
+      </c>
+      <c r="O206" s="13">
+        <v>32</v>
+      </c>
+      <c r="P206" s="15">
+        <v>35</v>
+      </c>
+      <c r="Q206" s="17">
+        <v>28</v>
+      </c>
       <c r="R206" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>304</v>
       </c>
     </row>
     <row r="207" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15850,15 +18178,27 @@
       <c r="K207" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L207" s="7"/>
-      <c r="M207" s="9"/>
-      <c r="N207" s="11"/>
-      <c r="O207" s="13"/>
-      <c r="P207" s="15"/>
-      <c r="Q207" s="17"/>
+      <c r="L207" s="7">
+        <v>95</v>
+      </c>
+      <c r="M207" s="9">
+        <v>117</v>
+      </c>
+      <c r="N207" s="11">
+        <v>184</v>
+      </c>
+      <c r="O207" s="13">
+        <v>44</v>
+      </c>
+      <c r="P207" s="15">
+        <v>46</v>
+      </c>
+      <c r="Q207" s="17">
+        <v>28</v>
+      </c>
       <c r="R207" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>514</v>
       </c>
     </row>
     <row r="208" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15887,15 +18227,27 @@
       <c r="K208" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="L208" s="7"/>
-      <c r="M208" s="9"/>
-      <c r="N208" s="11"/>
-      <c r="O208" s="13"/>
-      <c r="P208" s="15"/>
-      <c r="Q208" s="17"/>
+      <c r="L208" s="7">
+        <v>108</v>
+      </c>
+      <c r="M208" s="9">
+        <v>68</v>
+      </c>
+      <c r="N208" s="11">
+        <v>45</v>
+      </c>
+      <c r="O208" s="13">
+        <v>30</v>
+      </c>
+      <c r="P208" s="15">
+        <v>40</v>
+      </c>
+      <c r="Q208" s="17">
+        <v>43</v>
+      </c>
       <c r="R208" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="209" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15924,15 +18276,27 @@
       <c r="K209" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L209" s="7"/>
-      <c r="M209" s="9"/>
-      <c r="N209" s="11"/>
-      <c r="O209" s="13"/>
-      <c r="P209" s="15"/>
-      <c r="Q209" s="17"/>
+      <c r="L209" s="7">
+        <v>170</v>
+      </c>
+      <c r="M209" s="9">
+        <v>113</v>
+      </c>
+      <c r="N209" s="11">
+        <v>65</v>
+      </c>
+      <c r="O209" s="13">
+        <v>45</v>
+      </c>
+      <c r="P209" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q209" s="17">
+        <v>73</v>
+      </c>
       <c r="R209" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>521</v>
       </c>
     </row>
     <row r="210" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -15965,15 +18329,27 @@
       <c r="K210" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L210" s="7"/>
-      <c r="M210" s="9"/>
-      <c r="N210" s="11"/>
-      <c r="O210" s="13"/>
-      <c r="P210" s="15"/>
-      <c r="Q210" s="17"/>
+      <c r="L210" s="7">
+        <v>75</v>
+      </c>
+      <c r="M210" s="9">
+        <v>80</v>
+      </c>
+      <c r="N210" s="11">
+        <v>110</v>
+      </c>
+      <c r="O210" s="13">
+        <v>65</v>
+      </c>
+      <c r="P210" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q210" s="17">
+        <v>50</v>
+      </c>
       <c r="R210" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>470</v>
       </c>
     </row>
     <row r="211" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16002,15 +18378,27 @@
       <c r="K211" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L211" s="7"/>
-      <c r="M211" s="9"/>
-      <c r="N211" s="11"/>
-      <c r="O211" s="13"/>
-      <c r="P211" s="15"/>
-      <c r="Q211" s="17"/>
+      <c r="L211" s="7">
+        <v>90</v>
+      </c>
+      <c r="M211" s="9">
+        <v>95</v>
+      </c>
+      <c r="N211" s="11">
+        <v>85</v>
+      </c>
+      <c r="O211" s="13">
+        <v>55</v>
+      </c>
+      <c r="P211" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q211" s="17">
+        <v>70</v>
+      </c>
       <c r="R211" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="212" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16039,15 +18427,27 @@
       <c r="K212" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L212" s="7"/>
-      <c r="M212" s="9"/>
-      <c r="N212" s="11"/>
-      <c r="O212" s="13"/>
-      <c r="P212" s="15"/>
-      <c r="Q212" s="17"/>
+      <c r="L212" s="7">
+        <v>90</v>
+      </c>
+      <c r="M212" s="9">
+        <v>55</v>
+      </c>
+      <c r="N212" s="11">
+        <v>65</v>
+      </c>
+      <c r="O212" s="13">
+        <v>95</v>
+      </c>
+      <c r="P212" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q212" s="17">
+        <v>70</v>
+      </c>
       <c r="R212" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="213" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16076,15 +18476,27 @@
       <c r="K213" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L213" s="7"/>
-      <c r="M213" s="9"/>
-      <c r="N213" s="11"/>
-      <c r="O213" s="13"/>
-      <c r="P213" s="15"/>
-      <c r="Q213" s="17"/>
+      <c r="L213" s="7">
+        <v>65</v>
+      </c>
+      <c r="M213" s="9">
+        <v>80</v>
+      </c>
+      <c r="N213" s="11">
+        <v>140</v>
+      </c>
+      <c r="O213" s="13">
+        <v>40</v>
+      </c>
+      <c r="P213" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q213" s="17">
+        <v>70</v>
+      </c>
       <c r="R213" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>465</v>
       </c>
     </row>
     <row r="214" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16113,15 +18525,27 @@
       <c r="K214" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="L214" s="7"/>
-      <c r="M214" s="9"/>
-      <c r="N214" s="11"/>
-      <c r="O214" s="13"/>
-      <c r="P214" s="15"/>
-      <c r="Q214" s="17"/>
+      <c r="L214" s="7">
+        <v>52</v>
+      </c>
+      <c r="M214" s="9">
+        <v>65</v>
+      </c>
+      <c r="N214" s="11">
+        <v>50</v>
+      </c>
+      <c r="O214" s="13">
+        <v>45</v>
+      </c>
+      <c r="P214" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q214" s="17">
+        <v>38</v>
+      </c>
       <c r="R214" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="215" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16150,15 +18574,27 @@
       <c r="K215" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="L215" s="7"/>
-      <c r="M215" s="9"/>
-      <c r="N215" s="11"/>
-      <c r="O215" s="13"/>
-      <c r="P215" s="15"/>
-      <c r="Q215" s="17"/>
+      <c r="L215" s="7">
+        <v>72</v>
+      </c>
+      <c r="M215" s="9">
+        <v>85</v>
+      </c>
+      <c r="N215" s="11">
+        <v>70</v>
+      </c>
+      <c r="O215" s="13">
+        <v>65</v>
+      </c>
+      <c r="P215" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q215" s="17">
+        <v>58</v>
+      </c>
       <c r="R215" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="216" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16187,15 +18623,27 @@
       <c r="K216" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L216" s="7"/>
-      <c r="M216" s="9"/>
-      <c r="N216" s="11"/>
-      <c r="O216" s="13"/>
-      <c r="P216" s="15"/>
-      <c r="Q216" s="17"/>
+      <c r="L216" s="7">
+        <v>92</v>
+      </c>
+      <c r="M216" s="9">
+        <v>105</v>
+      </c>
+      <c r="N216" s="11">
+        <v>90</v>
+      </c>
+      <c r="O216" s="13">
+        <v>125</v>
+      </c>
+      <c r="P216" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q216" s="17">
+        <v>98</v>
+      </c>
       <c r="R216" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="217" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16226,15 +18674,27 @@
       <c r="K217" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L217" s="7"/>
-      <c r="M217" s="9"/>
-      <c r="N217" s="11"/>
-      <c r="O217" s="13"/>
-      <c r="P217" s="15"/>
-      <c r="Q217" s="17"/>
+      <c r="L217" s="7">
+        <v>155</v>
+      </c>
+      <c r="M217" s="9">
+        <v>110</v>
+      </c>
+      <c r="N217" s="11">
+        <v>125</v>
+      </c>
+      <c r="O217" s="13">
+        <v>55</v>
+      </c>
+      <c r="P217" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q217" s="17">
+        <v>45</v>
+      </c>
       <c r="R217" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="218" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16265,15 +18725,27 @@
       <c r="K218" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L218" s="7"/>
-      <c r="M218" s="9"/>
-      <c r="N218" s="11"/>
-      <c r="O218" s="13"/>
-      <c r="P218" s="15"/>
-      <c r="Q218" s="17"/>
+      <c r="L218" s="7">
+        <v>85</v>
+      </c>
+      <c r="M218" s="9">
+        <v>85</v>
+      </c>
+      <c r="N218" s="11">
+        <v>100</v>
+      </c>
+      <c r="O218" s="13">
+        <v>95</v>
+      </c>
+      <c r="P218" s="15">
+        <v>135</v>
+      </c>
+      <c r="Q218" s="17">
+        <v>70</v>
+      </c>
       <c r="R218" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="219" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16304,15 +18776,27 @@
       <c r="K219" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L219" s="7"/>
-      <c r="M219" s="9"/>
-      <c r="N219" s="11"/>
-      <c r="O219" s="13"/>
-      <c r="P219" s="15"/>
-      <c r="Q219" s="17"/>
+      <c r="L219" s="7">
+        <v>55</v>
+      </c>
+      <c r="M219" s="9">
+        <v>80</v>
+      </c>
+      <c r="N219" s="11">
+        <v>80</v>
+      </c>
+      <c r="O219" s="13">
+        <v>135</v>
+      </c>
+      <c r="P219" s="15">
+        <v>120</v>
+      </c>
+      <c r="Q219" s="17">
+        <v>100</v>
+      </c>
       <c r="R219" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="220" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16343,15 +18827,27 @@
       <c r="K220" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L220" s="7"/>
-      <c r="M220" s="9"/>
-      <c r="N220" s="11"/>
-      <c r="O220" s="13"/>
-      <c r="P220" s="15"/>
-      <c r="Q220" s="17"/>
+      <c r="L220" s="7">
+        <v>80</v>
+      </c>
+      <c r="M220" s="9">
+        <v>120</v>
+      </c>
+      <c r="N220" s="11">
+        <v>80</v>
+      </c>
+      <c r="O220" s="13">
+        <v>90</v>
+      </c>
+      <c r="P220" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q220" s="17">
+        <v>135</v>
+      </c>
       <c r="R220" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="221" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16378,15 +18874,27 @@
       <c r="K221" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="L221" s="7"/>
-      <c r="M221" s="9"/>
-      <c r="N221" s="11"/>
-      <c r="O221" s="13"/>
-      <c r="P221" s="15"/>
-      <c r="Q221" s="17"/>
+      <c r="L221" s="7">
+        <v>55</v>
+      </c>
+      <c r="M221" s="9">
+        <v>55</v>
+      </c>
+      <c r="N221" s="11">
+        <v>50</v>
+      </c>
+      <c r="O221" s="13">
+        <v>45</v>
+      </c>
+      <c r="P221" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q221" s="17">
+        <v>55</v>
+      </c>
       <c r="R221" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>325</v>
       </c>
     </row>
     <row r="222" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16413,13 +18921,28 @@
       <c r="K222" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L222" s="7"/>
-      <c r="M222" s="9"/>
-      <c r="N222" s="11"/>
-      <c r="O222" s="13"/>
-      <c r="P222" s="15"/>
-      <c r="Q222" s="17"/>
-      <c r="R222" s="40"/>
+      <c r="L222" s="7">
+        <v>130</v>
+      </c>
+      <c r="M222" s="9">
+        <v>65</v>
+      </c>
+      <c r="N222" s="11">
+        <v>60</v>
+      </c>
+      <c r="O222" s="13">
+        <v>110</v>
+      </c>
+      <c r="P222" s="15">
+        <v>95</v>
+      </c>
+      <c r="Q222" s="17">
+        <v>65</v>
+      </c>
+      <c r="R222" s="40">
+        <f t="shared" si="9"/>
+        <v>525</v>
+      </c>
     </row>
     <row r="223" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B223" t="e" vm="234">
@@ -16445,13 +18968,28 @@
       <c r="K223" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L223" s="7"/>
-      <c r="M223" s="9"/>
-      <c r="N223" s="11"/>
-      <c r="O223" s="13"/>
-      <c r="P223" s="15"/>
-      <c r="Q223" s="17"/>
-      <c r="R223" s="40"/>
+      <c r="L223" s="7">
+        <v>65</v>
+      </c>
+      <c r="M223" s="9">
+        <v>65</v>
+      </c>
+      <c r="N223" s="11">
+        <v>60</v>
+      </c>
+      <c r="O223" s="13">
+        <v>110</v>
+      </c>
+      <c r="P223" s="15">
+        <v>95</v>
+      </c>
+      <c r="Q223" s="17">
+        <v>130</v>
+      </c>
+      <c r="R223" s="40">
+        <f t="shared" si="9"/>
+        <v>525</v>
+      </c>
     </row>
     <row r="224" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B224" t="e" vm="235">
@@ -16477,13 +19015,28 @@
       <c r="K224" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L224" s="7"/>
-      <c r="M224" s="9"/>
-      <c r="N224" s="11"/>
-      <c r="O224" s="13"/>
-      <c r="P224" s="15"/>
-      <c r="Q224" s="17"/>
-      <c r="R224" s="40"/>
+      <c r="L224" s="7">
+        <v>65</v>
+      </c>
+      <c r="M224" s="9">
+        <v>130</v>
+      </c>
+      <c r="N224" s="11">
+        <v>60</v>
+      </c>
+      <c r="O224" s="13">
+        <v>95</v>
+      </c>
+      <c r="P224" s="15">
+        <v>110</v>
+      </c>
+      <c r="Q224" s="17">
+        <v>65</v>
+      </c>
+      <c r="R224" s="40">
+        <f t="shared" si="9"/>
+        <v>525</v>
+      </c>
     </row>
     <row r="225" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B225" t="e" vm="236">
@@ -16509,13 +19062,28 @@
       <c r="K225" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L225" s="7"/>
-      <c r="M225" s="9"/>
-      <c r="N225" s="11"/>
-      <c r="O225" s="13"/>
-      <c r="P225" s="15"/>
-      <c r="Q225" s="17"/>
-      <c r="R225" s="40"/>
+      <c r="L225" s="7">
+        <v>65</v>
+      </c>
+      <c r="M225" s="9">
+        <v>65</v>
+      </c>
+      <c r="N225" s="11">
+        <v>60</v>
+      </c>
+      <c r="O225" s="13">
+        <v>130</v>
+      </c>
+      <c r="P225" s="15">
+        <v>95</v>
+      </c>
+      <c r="Q225" s="17">
+        <v>110</v>
+      </c>
+      <c r="R225" s="40">
+        <f t="shared" si="9"/>
+        <v>525</v>
+      </c>
     </row>
     <row r="226" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B226" t="e" vm="237">
@@ -16541,13 +19109,28 @@
       <c r="K226" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L226" s="7"/>
-      <c r="M226" s="9"/>
-      <c r="N226" s="11"/>
-      <c r="O226" s="13"/>
-      <c r="P226" s="15"/>
-      <c r="Q226" s="17"/>
-      <c r="R226" s="40"/>
+      <c r="L226" s="7">
+        <v>95</v>
+      </c>
+      <c r="M226" s="9">
+        <v>65</v>
+      </c>
+      <c r="N226" s="11">
+        <v>110</v>
+      </c>
+      <c r="O226" s="13">
+        <v>60</v>
+      </c>
+      <c r="P226" s="15">
+        <v>130</v>
+      </c>
+      <c r="Q226" s="17">
+        <v>65</v>
+      </c>
+      <c r="R226" s="40">
+        <f t="shared" si="9"/>
+        <v>525</v>
+      </c>
     </row>
     <row r="227" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B227" t="e" vm="238">
@@ -16573,13 +19156,28 @@
       <c r="K227" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L227" s="7"/>
-      <c r="M227" s="9"/>
-      <c r="N227" s="11"/>
-      <c r="O227" s="13"/>
-      <c r="P227" s="15"/>
-      <c r="Q227" s="17"/>
-      <c r="R227" s="40"/>
+      <c r="L227" s="7">
+        <v>65</v>
+      </c>
+      <c r="M227" s="9">
+        <v>110</v>
+      </c>
+      <c r="N227" s="11">
+        <v>130</v>
+      </c>
+      <c r="O227" s="13">
+        <v>60</v>
+      </c>
+      <c r="P227" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q227" s="17">
+        <v>95</v>
+      </c>
+      <c r="R227" s="40">
+        <f t="shared" si="9"/>
+        <v>525</v>
+      </c>
     </row>
     <row r="228" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B228" t="e" vm="239">
@@ -16605,13 +19203,28 @@
       <c r="K228" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L228" s="7"/>
-      <c r="M228" s="9"/>
-      <c r="N228" s="11"/>
-      <c r="O228" s="13"/>
-      <c r="P228" s="15"/>
-      <c r="Q228" s="17"/>
-      <c r="R228" s="40"/>
+      <c r="L228" s="7">
+        <v>65</v>
+      </c>
+      <c r="M228" s="9">
+        <v>60</v>
+      </c>
+      <c r="N228" s="11">
+        <v>110</v>
+      </c>
+      <c r="O228" s="13">
+        <v>130</v>
+      </c>
+      <c r="P228" s="15">
+        <v>95</v>
+      </c>
+      <c r="Q228" s="17">
+        <v>65</v>
+      </c>
+      <c r="R228" s="40">
+        <f t="shared" si="9"/>
+        <v>525</v>
+      </c>
     </row>
     <row r="229" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B229" t="e" vm="240">
@@ -16637,13 +19250,28 @@
       <c r="K229" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L229" s="7"/>
-      <c r="M229" s="9"/>
-      <c r="N229" s="11"/>
-      <c r="O229" s="13"/>
-      <c r="P229" s="15"/>
-      <c r="Q229" s="17"/>
-      <c r="R229" s="40"/>
+      <c r="L229" s="7">
+        <v>95</v>
+      </c>
+      <c r="M229" s="9">
+        <v>65</v>
+      </c>
+      <c r="N229" s="11">
+        <v>65</v>
+      </c>
+      <c r="O229" s="13">
+        <v>110</v>
+      </c>
+      <c r="P229" s="15">
+        <v>130</v>
+      </c>
+      <c r="Q229" s="17">
+        <v>60</v>
+      </c>
+      <c r="R229" s="40">
+        <f t="shared" si="9"/>
+        <v>525</v>
+      </c>
     </row>
     <row r="230" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B230" t="e" vm="241">
@@ -16671,13 +19299,28 @@
       <c r="K230" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="L230" s="7"/>
-      <c r="M230" s="9"/>
-      <c r="N230" s="11"/>
-      <c r="O230" s="13"/>
-      <c r="P230" s="15"/>
-      <c r="Q230" s="17"/>
-      <c r="R230" s="40"/>
+      <c r="L230" s="7">
+        <v>70</v>
+      </c>
+      <c r="M230" s="9">
+        <v>83</v>
+      </c>
+      <c r="N230" s="11">
+        <v>50</v>
+      </c>
+      <c r="O230" s="13">
+        <v>37</v>
+      </c>
+      <c r="P230" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q230" s="17">
+        <v>60</v>
+      </c>
+      <c r="R230" s="40">
+        <f t="shared" si="9"/>
+        <v>350</v>
+      </c>
     </row>
     <row r="231" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B231" t="e" vm="242">
@@ -16705,13 +19348,28 @@
       <c r="K231" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L231" s="7"/>
-      <c r="M231" s="9"/>
-      <c r="N231" s="11"/>
-      <c r="O231" s="13"/>
-      <c r="P231" s="15"/>
-      <c r="Q231" s="17"/>
-      <c r="R231" s="40"/>
+      <c r="L231" s="7">
+        <v>100</v>
+      </c>
+      <c r="M231" s="9">
+        <v>123</v>
+      </c>
+      <c r="N231" s="11">
+        <v>75</v>
+      </c>
+      <c r="O231" s="13">
+        <v>57</v>
+      </c>
+      <c r="P231" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q231" s="17">
+        <v>80</v>
+      </c>
+      <c r="R231" s="40">
+        <f t="shared" si="9"/>
+        <v>510</v>
+      </c>
     </row>
     <row r="232" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B232" t="e" vm="243">
@@ -16739,13 +19397,28 @@
       <c r="K232" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="L232" s="7"/>
-      <c r="M232" s="9"/>
-      <c r="N232" s="11"/>
-      <c r="O232" s="13"/>
-      <c r="P232" s="15"/>
-      <c r="Q232" s="17"/>
-      <c r="R232" s="40"/>
+      <c r="L232" s="7">
+        <v>70</v>
+      </c>
+      <c r="M232" s="9">
+        <v>55</v>
+      </c>
+      <c r="N232" s="11">
+        <v>75</v>
+      </c>
+      <c r="O232" s="13">
+        <v>45</v>
+      </c>
+      <c r="P232" s="15">
+        <v>65</v>
+      </c>
+      <c r="Q232" s="17">
+        <v>60</v>
+      </c>
+      <c r="R232" s="40">
+        <f t="shared" si="9"/>
+        <v>370</v>
+      </c>
     </row>
     <row r="233" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B233" t="e" vm="244">
@@ -16773,15 +19446,27 @@
       <c r="K233" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L233" s="7"/>
-      <c r="M233" s="9"/>
-      <c r="N233" s="11"/>
-      <c r="O233" s="13"/>
-      <c r="P233" s="15"/>
-      <c r="Q233" s="17"/>
+      <c r="L233" s="7">
+        <v>110</v>
+      </c>
+      <c r="M233" s="9">
+        <v>65</v>
+      </c>
+      <c r="N233" s="11">
+        <v>105</v>
+      </c>
+      <c r="O233" s="13">
+        <v>55</v>
+      </c>
+      <c r="P233" s="15">
+        <v>95</v>
+      </c>
+      <c r="Q233" s="17">
+        <v>80</v>
+      </c>
       <c r="R233" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="234" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16808,13 +19493,28 @@
       <c r="K234" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L234" s="7"/>
-      <c r="M234" s="9"/>
-      <c r="N234" s="11"/>
-      <c r="O234" s="13"/>
-      <c r="P234" s="15"/>
-      <c r="Q234" s="17"/>
-      <c r="R234" s="40"/>
+      <c r="L234" s="7">
+        <v>48</v>
+      </c>
+      <c r="M234" s="9">
+        <v>48</v>
+      </c>
+      <c r="N234" s="11">
+        <v>48</v>
+      </c>
+      <c r="O234" s="13">
+        <v>48</v>
+      </c>
+      <c r="P234" s="15">
+        <v>48</v>
+      </c>
+      <c r="Q234" s="17">
+        <v>48</v>
+      </c>
+      <c r="R234" s="40">
+        <f t="shared" si="9"/>
+        <v>288</v>
+      </c>
     </row>
     <row r="235" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B235" t="e" vm="247">
@@ -16842,13 +19542,28 @@
       <c r="K235" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="L235" s="7"/>
-      <c r="M235" s="9"/>
-      <c r="N235" s="11"/>
-      <c r="O235" s="13"/>
-      <c r="P235" s="15"/>
-      <c r="Q235" s="17"/>
-      <c r="R235" s="40"/>
+      <c r="L235" s="7">
+        <v>70</v>
+      </c>
+      <c r="M235" s="9">
+        <v>110</v>
+      </c>
+      <c r="N235" s="11">
+        <v>80</v>
+      </c>
+      <c r="O235" s="13">
+        <v>55</v>
+      </c>
+      <c r="P235" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q235" s="17">
+        <v>105</v>
+      </c>
+      <c r="R235" s="40">
+        <f t="shared" si="9"/>
+        <v>500</v>
+      </c>
     </row>
     <row r="236" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B236" t="e" vm="248">
@@ -16874,13 +19589,28 @@
         <v>45</v>
       </c>
       <c r="K236" s="1"/>
-      <c r="L236" s="7"/>
-      <c r="M236" s="9"/>
-      <c r="N236" s="11"/>
-      <c r="O236" s="13"/>
-      <c r="P236" s="15"/>
-      <c r="Q236" s="17"/>
-      <c r="R236" s="40"/>
+      <c r="L236" s="7">
+        <v>70</v>
+      </c>
+      <c r="M236" s="9">
+        <v>130</v>
+      </c>
+      <c r="N236" s="11">
+        <v>100</v>
+      </c>
+      <c r="O236" s="13">
+        <v>55</v>
+      </c>
+      <c r="P236" s="15">
+        <v>80</v>
+      </c>
+      <c r="Q236" s="17">
+        <v>65</v>
+      </c>
+      <c r="R236" s="40">
+        <f t="shared" si="9"/>
+        <v>500</v>
+      </c>
     </row>
     <row r="237" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B237" t="e" vm="249">
@@ -16906,13 +19636,28 @@
         <v>45</v>
       </c>
       <c r="K237" s="1"/>
-      <c r="L237" s="7"/>
-      <c r="M237" s="9"/>
-      <c r="N237" s="11"/>
-      <c r="O237" s="13"/>
-      <c r="P237" s="15"/>
-      <c r="Q237" s="17"/>
-      <c r="R237" s="40"/>
+      <c r="L237" s="7">
+        <v>70</v>
+      </c>
+      <c r="M237" s="9">
+        <v>135</v>
+      </c>
+      <c r="N237" s="11">
+        <v>95</v>
+      </c>
+      <c r="O237" s="13">
+        <v>45</v>
+      </c>
+      <c r="P237" s="15">
+        <v>70</v>
+      </c>
+      <c r="Q237" s="17">
+        <v>85</v>
+      </c>
+      <c r="R237" s="40">
+        <f t="shared" si="9"/>
+        <v>500</v>
+      </c>
     </row>
     <row r="238" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B238" t="e" vm="250">
@@ -16938,15 +19683,27 @@
       <c r="K238" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L238" s="7"/>
-      <c r="M238" s="9"/>
-      <c r="N238" s="11"/>
-      <c r="O238" s="13"/>
-      <c r="P238" s="15"/>
-      <c r="Q238" s="17"/>
+      <c r="L238" s="7">
+        <v>45</v>
+      </c>
+      <c r="M238" s="9">
+        <v>75</v>
+      </c>
+      <c r="N238" s="11">
+        <v>37</v>
+      </c>
+      <c r="O238" s="13">
+        <v>70</v>
+      </c>
+      <c r="P238" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q238" s="17">
+        <v>83</v>
+      </c>
       <c r="R238" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>365</v>
       </c>
     </row>
     <row r="239" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -16973,15 +19730,27 @@
       <c r="K239" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="L239" s="7"/>
-      <c r="M239" s="9"/>
-      <c r="N239" s="11"/>
-      <c r="O239" s="13"/>
-      <c r="P239" s="15"/>
-      <c r="Q239" s="17"/>
+      <c r="L239" s="7">
+        <v>65</v>
+      </c>
+      <c r="M239" s="9">
+        <v>95</v>
+      </c>
+      <c r="N239" s="11">
+        <v>57</v>
+      </c>
+      <c r="O239" s="13">
+        <v>100</v>
+      </c>
+      <c r="P239" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q239" s="17">
+        <v>93</v>
+      </c>
       <c r="R239" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>495</v>
       </c>
     </row>
     <row r="240" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17008,15 +19777,27 @@
       <c r="K240" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L240" s="7"/>
-      <c r="M240" s="9"/>
-      <c r="N240" s="11"/>
-      <c r="O240" s="13"/>
-      <c r="P240" s="15"/>
-      <c r="Q240" s="17"/>
+      <c r="L240" s="7">
+        <v>75</v>
+      </c>
+      <c r="M240" s="9">
+        <v>95</v>
+      </c>
+      <c r="N240" s="11">
+        <v>67</v>
+      </c>
+      <c r="O240" s="13">
+        <v>125</v>
+      </c>
+      <c r="P240" s="15">
+        <v>95</v>
+      </c>
+      <c r="Q240" s="17">
+        <v>83</v>
+      </c>
       <c r="R240" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>540</v>
       </c>
     </row>
     <row r="241" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17043,15 +19824,27 @@
       <c r="K241" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L241" s="7"/>
-      <c r="M241" s="9"/>
-      <c r="N241" s="11"/>
-      <c r="O241" s="13"/>
-      <c r="P241" s="15"/>
-      <c r="Q241" s="17"/>
+      <c r="L241" s="7">
+        <v>45</v>
+      </c>
+      <c r="M241" s="9">
+        <v>63</v>
+      </c>
+      <c r="N241" s="11">
+        <v>37</v>
+      </c>
+      <c r="O241" s="13">
+        <v>65</v>
+      </c>
+      <c r="P241" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q241" s="17">
+        <v>95</v>
+      </c>
       <c r="R241" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="242" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17078,15 +19871,27 @@
       <c r="K242" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="L242" s="7"/>
-      <c r="M242" s="9"/>
-      <c r="N242" s="11"/>
-      <c r="O242" s="13"/>
-      <c r="P242" s="15"/>
-      <c r="Q242" s="17"/>
+      <c r="L242" s="7">
+        <v>65</v>
+      </c>
+      <c r="M242" s="9">
+        <v>83</v>
+      </c>
+      <c r="N242" s="11">
+        <v>57</v>
+      </c>
+      <c r="O242" s="13">
+        <v>95</v>
+      </c>
+      <c r="P242" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q242" s="17">
+        <v>105</v>
+      </c>
       <c r="R242" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>490</v>
       </c>
     </row>
     <row r="243" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17113,15 +19918,27 @@
       <c r="K243" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L243" s="7"/>
-      <c r="M243" s="9"/>
-      <c r="N243" s="11"/>
-      <c r="O243" s="13"/>
-      <c r="P243" s="15"/>
-      <c r="Q243" s="17"/>
+      <c r="L243" s="7">
+        <v>75</v>
+      </c>
+      <c r="M243" s="9">
+        <v>123</v>
+      </c>
+      <c r="N243" s="11">
+        <v>67</v>
+      </c>
+      <c r="O243" s="13">
+        <v>95</v>
+      </c>
+      <c r="P243" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q243" s="17">
+        <v>95</v>
+      </c>
       <c r="R243" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>540</v>
       </c>
     </row>
     <row r="244" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17148,15 +19965,27 @@
       <c r="K244" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L244" s="7"/>
-      <c r="M244" s="9"/>
-      <c r="N244" s="11"/>
-      <c r="O244" s="13"/>
-      <c r="P244" s="15"/>
-      <c r="Q244" s="17"/>
+      <c r="L244" s="7">
+        <v>40</v>
+      </c>
+      <c r="M244" s="9">
+        <v>55</v>
+      </c>
+      <c r="N244" s="11">
+        <v>70</v>
+      </c>
+      <c r="O244" s="13">
+        <v>45</v>
+      </c>
+      <c r="P244" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q244" s="17">
+        <v>30</v>
+      </c>
       <c r="R244" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="245" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17183,15 +20012,27 @@
       <c r="K245" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="L245" s="7"/>
-      <c r="M245" s="9"/>
-      <c r="N245" s="11"/>
-      <c r="O245" s="13"/>
-      <c r="P245" s="15"/>
-      <c r="Q245" s="17"/>
+      <c r="L245" s="7">
+        <v>60</v>
+      </c>
+      <c r="M245" s="9">
+        <v>80</v>
+      </c>
+      <c r="N245" s="11">
+        <v>95</v>
+      </c>
+      <c r="O245" s="13">
+        <v>70</v>
+      </c>
+      <c r="P245" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q245" s="17">
+        <v>50</v>
+      </c>
       <c r="R245" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>440</v>
       </c>
     </row>
     <row r="246" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17218,15 +20059,27 @@
       <c r="K246" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L246" s="7"/>
-      <c r="M246" s="9"/>
-      <c r="N246" s="11"/>
-      <c r="O246" s="13"/>
-      <c r="P246" s="15"/>
-      <c r="Q246" s="17"/>
+      <c r="L246" s="7">
+        <v>60</v>
+      </c>
+      <c r="M246" s="9">
+        <v>100</v>
+      </c>
+      <c r="N246" s="11">
+        <v>115</v>
+      </c>
+      <c r="O246" s="13">
+        <v>70</v>
+      </c>
+      <c r="P246" s="15">
+        <v>85</v>
+      </c>
+      <c r="Q246" s="17">
+        <v>90</v>
+      </c>
       <c r="R246" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>520</v>
       </c>
     </row>
     <row r="247" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17261,15 +20114,27 @@
       <c r="K247" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="L247" s="7"/>
-      <c r="M247" s="9"/>
-      <c r="N247" s="11"/>
-      <c r="O247" s="13"/>
-      <c r="P247" s="15"/>
-      <c r="Q247" s="17"/>
+      <c r="L247" s="7">
+        <v>55</v>
+      </c>
+      <c r="M247" s="9">
+        <v>45</v>
+      </c>
+      <c r="N247" s="11">
+        <v>43</v>
+      </c>
+      <c r="O247" s="13">
+        <v>55</v>
+      </c>
+      <c r="P247" s="15">
+        <v>43</v>
+      </c>
+      <c r="Q247" s="17">
+        <v>72</v>
+      </c>
       <c r="R247" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>313</v>
       </c>
     </row>
     <row r="248" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17304,15 +20169,27 @@
       <c r="K248" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L248" s="7"/>
-      <c r="M248" s="9"/>
-      <c r="N248" s="11"/>
-      <c r="O248" s="13"/>
-      <c r="P248" s="15"/>
-      <c r="Q248" s="17"/>
+      <c r="L248" s="7">
+        <v>67</v>
+      </c>
+      <c r="M248" s="9">
+        <v>57</v>
+      </c>
+      <c r="N248" s="11">
+        <v>55</v>
+      </c>
+      <c r="O248" s="13">
+        <v>77</v>
+      </c>
+      <c r="P248" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q248" s="17">
+        <v>114</v>
+      </c>
       <c r="R248" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>425</v>
       </c>
     </row>
     <row r="249" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17345,15 +20222,27 @@
       <c r="K249" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="L249" s="7"/>
-      <c r="M249" s="9"/>
-      <c r="N249" s="11"/>
-      <c r="O249" s="13"/>
-      <c r="P249" s="15"/>
-      <c r="Q249" s="17"/>
+      <c r="L249" s="7">
+        <v>45</v>
+      </c>
+      <c r="M249" s="9">
+        <v>85</v>
+      </c>
+      <c r="N249" s="11">
+        <v>50</v>
+      </c>
+      <c r="O249" s="13">
+        <v>55</v>
+      </c>
+      <c r="P249" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q249" s="17">
+        <v>65</v>
+      </c>
       <c r="R249" s="40">
-        <f t="shared" ref="R249:R250" si="10">SUM(L249:Q249)</f>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>350</v>
       </c>
     </row>
     <row r="250" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17386,15 +20275,27 @@
       <c r="K250" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L250" s="7"/>
-      <c r="M250" s="9"/>
-      <c r="N250" s="11"/>
-      <c r="O250" s="13"/>
-      <c r="P250" s="15"/>
-      <c r="Q250" s="17"/>
+      <c r="L250" s="7">
+        <v>65</v>
+      </c>
+      <c r="M250" s="9">
+        <v>125</v>
+      </c>
+      <c r="N250" s="11">
+        <v>60</v>
+      </c>
+      <c r="O250" s="13">
+        <v>95</v>
+      </c>
+      <c r="P250" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q250" s="17">
+        <v>105</v>
+      </c>
       <c r="R250" s="40">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>510</v>
       </c>
     </row>
     <row r="251" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17421,15 +20322,27 @@
       <c r="K251" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L251" s="7"/>
-      <c r="M251" s="9"/>
-      <c r="N251" s="11"/>
-      <c r="O251" s="13"/>
-      <c r="P251" s="15"/>
-      <c r="Q251" s="17"/>
+      <c r="L251" s="7">
+        <v>73</v>
+      </c>
+      <c r="M251" s="9">
+        <v>115</v>
+      </c>
+      <c r="N251" s="11">
+        <v>60</v>
+      </c>
+      <c r="O251" s="13">
+        <v>60</v>
+      </c>
+      <c r="P251" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q251" s="17">
+        <v>90</v>
+      </c>
       <c r="R251" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>458</v>
       </c>
     </row>
     <row r="252" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17462,15 +20375,27 @@
       <c r="K252" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L252" s="7"/>
-      <c r="M252" s="9"/>
-      <c r="N252" s="11"/>
-      <c r="O252" s="13"/>
-      <c r="P252" s="15"/>
-      <c r="Q252" s="17"/>
+      <c r="L252" s="7">
+        <v>73</v>
+      </c>
+      <c r="M252" s="9">
+        <v>100</v>
+      </c>
+      <c r="N252" s="11">
+        <v>60</v>
+      </c>
+      <c r="O252" s="13">
+        <v>100</v>
+      </c>
+      <c r="P252" s="15">
+        <v>60</v>
+      </c>
+      <c r="Q252" s="17">
+        <v>65</v>
+      </c>
       <c r="R252" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>458</v>
       </c>
     </row>
     <row r="253" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17503,15 +20428,27 @@
       <c r="K253" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="L253" s="7"/>
-      <c r="M253" s="9"/>
-      <c r="N253" s="11"/>
-      <c r="O253" s="13"/>
-      <c r="P253" s="15"/>
-      <c r="Q253" s="17"/>
+      <c r="L253" s="7">
+        <v>43</v>
+      </c>
+      <c r="M253" s="9">
+        <v>80</v>
+      </c>
+      <c r="N253" s="11">
+        <v>65</v>
+      </c>
+      <c r="O253" s="13">
+        <v>50</v>
+      </c>
+      <c r="P253" s="15">
+        <v>35</v>
+      </c>
+      <c r="Q253" s="17">
+        <v>35</v>
+      </c>
       <c r="R253" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>308</v>
       </c>
     </row>
     <row r="254" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17546,15 +20483,27 @@
       <c r="K254" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L254" s="7"/>
-      <c r="M254" s="9"/>
-      <c r="N254" s="11"/>
-      <c r="O254" s="13"/>
-      <c r="P254" s="15"/>
-      <c r="Q254" s="17"/>
+      <c r="L254" s="7">
+        <v>63</v>
+      </c>
+      <c r="M254" s="9">
+        <v>120</v>
+      </c>
+      <c r="N254" s="11">
+        <v>85</v>
+      </c>
+      <c r="O254" s="13">
+        <v>90</v>
+      </c>
+      <c r="P254" s="15">
+        <v>55</v>
+      </c>
+      <c r="Q254" s="17">
+        <v>55</v>
+      </c>
       <c r="R254" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>468</v>
       </c>
     </row>
     <row r="255" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17589,15 +20538,27 @@
       <c r="K255" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L255" s="7"/>
-      <c r="M255" s="9"/>
-      <c r="N255" s="11"/>
-      <c r="O255" s="13"/>
-      <c r="P255" s="15"/>
-      <c r="Q255" s="17"/>
+      <c r="L255" s="7">
+        <v>99</v>
+      </c>
+      <c r="M255" s="9">
+        <v>68</v>
+      </c>
+      <c r="N255" s="11">
+        <v>83</v>
+      </c>
+      <c r="O255" s="13">
+        <v>72</v>
+      </c>
+      <c r="P255" s="15">
+        <v>87</v>
+      </c>
+      <c r="Q255" s="17">
+        <v>51</v>
+      </c>
       <c r="R255" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="256" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17632,15 +20593,27 @@
       <c r="K256" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="L256" s="7"/>
-      <c r="M256" s="9"/>
-      <c r="N256" s="11"/>
-      <c r="O256" s="13"/>
-      <c r="P256" s="15"/>
-      <c r="Q256" s="17"/>
+      <c r="L256" s="7">
+        <v>28</v>
+      </c>
+      <c r="M256" s="9">
+        <v>60</v>
+      </c>
+      <c r="N256" s="11">
+        <v>30</v>
+      </c>
+      <c r="O256" s="13">
+        <v>40</v>
+      </c>
+      <c r="P256" s="15">
+        <v>30</v>
+      </c>
+      <c r="Q256" s="17">
+        <v>82</v>
+      </c>
       <c r="R256" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="257" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17675,15 +20648,27 @@
       <c r="K257" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="L257" s="7"/>
-      <c r="M257" s="9"/>
-      <c r="N257" s="11"/>
-      <c r="O257" s="13"/>
-      <c r="P257" s="15"/>
-      <c r="Q257" s="17"/>
+      <c r="L257" s="7">
+        <v>68</v>
+      </c>
+      <c r="M257" s="9">
+        <v>80</v>
+      </c>
+      <c r="N257" s="11">
+        <v>50</v>
+      </c>
+      <c r="O257" s="13">
+        <v>60</v>
+      </c>
+      <c r="P257" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q257" s="17">
+        <v>102</v>
+      </c>
       <c r="R257" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>410</v>
       </c>
     </row>
     <row r="258" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17718,15 +20703,27 @@
       <c r="K258" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L258" s="7"/>
-      <c r="M258" s="9"/>
-      <c r="N258" s="11"/>
-      <c r="O258" s="13"/>
-      <c r="P258" s="15"/>
-      <c r="Q258" s="17"/>
+      <c r="L258" s="7">
+        <v>88</v>
+      </c>
+      <c r="M258" s="9">
+        <v>120</v>
+      </c>
+      <c r="N258" s="11">
+        <v>75</v>
+      </c>
+      <c r="O258" s="13">
+        <v>100</v>
+      </c>
+      <c r="P258" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q258" s="17">
+        <v>142</v>
+      </c>
       <c r="R258" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="259" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -17772,7 +20769,10 @@
       <c r="O260" s="13"/>
       <c r="P260" s="15"/>
       <c r="Q260" s="17"/>
-      <c r="R260" s="40"/>
+      <c r="R260" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="261" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B261" s="5"/>
@@ -17796,7 +20796,10 @@
       <c r="O261" s="13"/>
       <c r="P261" s="15"/>
       <c r="Q261" s="17"/>
-      <c r="R261" s="40"/>
+      <c r="R261" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="262" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C262" s="5">

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7F4F95-90BB-4F14-8CC1-E9A8D2FD5B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE4B79B-FF18-4F36-B74A-EBE4AF792ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2748,7 +2748,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="369">
   <si>
     <t>Base stats</t>
   </si>
@@ -19588,7 +19588,9 @@
       <c r="H236" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K236" s="1"/>
+      <c r="K236" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L236" s="7">
         <v>70</v>
       </c>
@@ -19635,7 +19637,9 @@
       <c r="H237" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="K237" s="1"/>
+      <c r="K237" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L237" s="7">
         <v>70</v>
       </c>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE4B79B-FF18-4F36-B74A-EBE4AF792ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FAE4B8-F5AB-4DA8-BE89-A3BF8DF3759E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="270">
+  <futureMetadata name="XLRICHVALUE" count="271">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -1931,8 +1931,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="270"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="270">
+  <valueMetadata count="271">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -2742,13 +2749,16 @@
     </bk>
     <bk>
       <rc t="1" v="269"/>
+    </bk>
+    <bk>
+      <rc t="1" v="270"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="370">
   <si>
     <t>Base stats</t>
   </si>
@@ -3883,6 +3893,9 @@
   </si>
   <si>
     <t>lv.60</t>
+  </si>
+  <si>
+    <t>Relicanth</t>
   </si>
 </sst>
 </file>
@@ -5066,7 +5079,7 @@
                   <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>44</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>21</c:v>
@@ -5087,7 +5100,7 @@
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>21</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>24</c:v>
@@ -5857,7 +5870,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="270">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="271">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -6936,6 +6949,10 @@
   </rv>
   <rv s="0">
     <v>269</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>270</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -7222,6 +7239,7 @@
   <rel r:id="rId268"/>
   <rel r:id="rId269"/>
   <rel r:id="rId270"/>
+  <rel r:id="rId271"/>
 </richValueRels>
 </file>
 
@@ -7489,7 +7507,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:T265"/>
+  <dimension ref="B1:T266"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
@@ -7632,7 +7650,7 @@
         <v>16</v>
       </c>
       <c r="T4" s="19">
-        <f>COUNTIF(E$6:F$265, "Grass")</f>
+        <f>COUNTIF(E$6:F$266, "Grass")</f>
         <v>22</v>
       </c>
     </row>
@@ -7692,7 +7710,7 @@
         <v>24</v>
       </c>
       <c r="T5" s="20">
-        <f>COUNTIF(E$6:F$265, "Fire")</f>
+        <f>COUNTIF(E$6:F$266, "Fire")</f>
         <v>28</v>
       </c>
     </row>
@@ -7752,8 +7770,8 @@
         <v>30</v>
       </c>
       <c r="T6" s="20">
-        <f>COUNTIF(E$6:F$265, "Water")</f>
-        <v>44</v>
+        <f>COUNTIF(E$6:F$266, "Water")</f>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7808,7 +7826,7 @@
         <v>37</v>
       </c>
       <c r="T7" s="20">
-        <f>COUNTIF(E$6:F$265, "Normal")</f>
+        <f>COUNTIF(E$6:F$266, "Normal")</f>
         <v>21</v>
       </c>
     </row>
@@ -7866,7 +7884,7 @@
         <v>27</v>
       </c>
       <c r="T8" s="20">
-        <f>COUNTIF(E$6:F$265, "Fighting")</f>
+        <f>COUNTIF(E$6:F$266, "Fighting")</f>
         <v>20</v>
       </c>
     </row>
@@ -7924,7 +7942,7 @@
         <v>41</v>
       </c>
       <c r="T9" s="20">
-        <f>COUNTIF(E$6:F$265, "Flying")</f>
+        <f>COUNTIF(E$6:F$266, "Flying")</f>
         <v>25</v>
       </c>
     </row>
@@ -7984,7 +8002,7 @@
         <v>63</v>
       </c>
       <c r="T10" s="20">
-        <f>COUNTIF(E$6:F$265, "Psychic")</f>
+        <f>COUNTIF(E$6:F$266, "Psychic")</f>
         <v>18</v>
       </c>
     </row>
@@ -8044,7 +8062,7 @@
         <v>45</v>
       </c>
       <c r="T11" s="20">
-        <f>COUNTIF(E$6:F$265, "Bug")</f>
+        <f>COUNTIF(E$6:F$266, "Bug")</f>
         <v>22</v>
       </c>
     </row>
@@ -8106,7 +8124,7 @@
         <v>50</v>
       </c>
       <c r="T12" s="20">
-        <f>COUNTIF(E$6:F$265, "Ground")</f>
+        <f>COUNTIF(E$6:F$266, "Ground")</f>
         <v>20</v>
       </c>
     </row>
@@ -8162,8 +8180,8 @@
         <v>64</v>
       </c>
       <c r="T13" s="20">
-        <f>COUNTIF(E$6:F$265, "Rock")</f>
-        <v>21</v>
+        <f>COUNTIF(E$6:F$266, "Rock")</f>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8218,7 +8236,7 @@
         <v>65</v>
       </c>
       <c r="T14" s="20">
-        <f>COUNTIF(E$6:F$265, "Ghost")</f>
+        <f>COUNTIF(E$6:F$266, "Ghost")</f>
         <v>24</v>
       </c>
     </row>
@@ -8274,7 +8292,7 @@
         <v>48</v>
       </c>
       <c r="T15" s="20">
-        <f>COUNTIF(E$6:F$265, "Dark")</f>
+        <f>COUNTIF(E$6:F$266, "Dark")</f>
         <v>26</v>
       </c>
     </row>
@@ -8332,7 +8350,7 @@
         <v>66</v>
       </c>
       <c r="T16" s="20">
-        <f>COUNTIF(E$6:F$265, "Ice")</f>
+        <f>COUNTIF(E$6:F$266, "Ice")</f>
         <v>20</v>
       </c>
     </row>
@@ -8390,7 +8408,7 @@
         <v>34</v>
       </c>
       <c r="T17" s="20">
-        <f>COUNTIF(E$6:F$265, "Steel")</f>
+        <f>COUNTIF(E$6:F$266, "Steel")</f>
         <v>22</v>
       </c>
     </row>
@@ -8448,7 +8466,7 @@
         <v>67</v>
       </c>
       <c r="T18" s="20">
-        <f>COUNTIF(E$6:F$265, "Electrik")</f>
+        <f>COUNTIF(E$6:F$266, "Electrik")</f>
         <v>16</v>
       </c>
     </row>
@@ -8504,7 +8522,7 @@
         <v>68</v>
       </c>
       <c r="T19" s="20">
-        <f>COUNTIF(E$6:F$265, "Poison")</f>
+        <f>COUNTIF(E$6:F$266, "Poison")</f>
         <v>16</v>
       </c>
     </row>
@@ -8562,7 +8580,7 @@
         <v>60</v>
       </c>
       <c r="T20" s="20">
-        <f>COUNTIF(E$6:F$265, "Fairy")</f>
+        <f>COUNTIF(E$6:F$266, "Fairy")</f>
         <v>16</v>
       </c>
     </row>
@@ -8618,7 +8636,7 @@
         <v>69</v>
       </c>
       <c r="T21" s="20">
-        <f>COUNTIF(E$6:F$265, "Dragon")</f>
+        <f>COUNTIF(E$6:F$266, "Dragon")</f>
         <v>18</v>
       </c>
     </row>
@@ -17694,7 +17712,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C198" s="5">
-        <f t="shared" ref="C198:C265" si="7">C197+1</f>
+        <f t="shared" ref="C198:C266" si="7">C197+1</f>
         <v>195</v>
       </c>
       <c r="D198" s="1" t="s">
@@ -17934,7 +17952,7 @@
         <v>109</v>
       </c>
       <c r="R202" s="40">
-        <f t="shared" ref="R202:R265" si="9">SUM(L202:Q202)</f>
+        <f t="shared" ref="R202:R266" si="9">SUM(L202:Q202)</f>
         <v>484</v>
       </c>
     </row>
@@ -20519,50 +20537,50 @@
         <v>252</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="E255" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="F255" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="G255" s="1" t="e" vm="138">
+        <v>369</v>
+      </c>
+      <c r="E255" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F255" s="66" t="s">
+        <v>64</v>
+      </c>
+      <c r="G255" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="I255" s="1" t="e" vm="2">
+        <v>31</v>
+      </c>
+      <c r="I255" s="1" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
       <c r="J255" s="1" t="s">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="K255" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L255" s="7">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="M255" s="9">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N255" s="11">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="O255" s="13">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="P255" s="15">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="Q255" s="17">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="R255" s="40">
-        <f t="shared" si="9"/>
-        <v>460</v>
+        <f t="shared" ref="R255" si="10">SUM(L255:Q255)</f>
+        <v>308</v>
       </c>
     </row>
     <row r="256" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -20574,50 +20592,50 @@
         <v>253</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="E256" s="81" t="s">
-        <v>69</v>
-      </c>
-      <c r="F256" s="65" t="s">
-        <v>65</v>
-      </c>
-      <c r="G256" s="1" t="e" vm="74">
+        <v>364</v>
+      </c>
+      <c r="E256" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="F256" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="G256" s="1" t="e" vm="138">
         <v>#VALUE!</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I256" s="1" t="e" vm="49">
+        <v>202</v>
+      </c>
+      <c r="I256" s="1" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="J256" s="1" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="K256" s="1" t="s">
-        <v>295</v>
+        <v>22</v>
       </c>
       <c r="L256" s="7">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="M256" s="9">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="N256" s="11">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="O256" s="13">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="P256" s="15">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="Q256" s="17">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="R256" s="40">
         <f t="shared" si="9"/>
-        <v>270</v>
+        <v>460</v>
       </c>
     </row>
     <row r="257" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -20629,7 +20647,7 @@
         <v>254</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E257" s="81" t="s">
         <v>69</v>
@@ -20650,29 +20668,29 @@
         <v>69</v>
       </c>
       <c r="K257" s="1" t="s">
-        <v>368</v>
+        <v>295</v>
       </c>
       <c r="L257" s="7">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="M257" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N257" s="11">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="O257" s="13">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="P257" s="15">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Q257" s="17">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="R257" s="40">
         <f t="shared" si="9"/>
-        <v>410</v>
+        <v>270</v>
       </c>
     </row>
     <row r="258" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -20684,7 +20702,7 @@
         <v>255</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E258" s="81" t="s">
         <v>69</v>
@@ -20705,54 +20723,87 @@
         <v>69</v>
       </c>
       <c r="K258" s="1" t="s">
-        <v>22</v>
+        <v>368</v>
       </c>
       <c r="L258" s="7">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="M258" s="9">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="N258" s="11">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="O258" s="13">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="P258" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q258" s="17">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="R258" s="40">
         <f t="shared" si="9"/>
-        <v>600</v>
+        <v>410</v>
       </c>
     </row>
     <row r="259" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B259" t="e" vm="271">
+        <v>#VALUE!</v>
+      </c>
       <c r="C259" s="5">
         <f t="shared" si="7"/>
         <v>256</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E259" s="84"/>
-      <c r="F259" s="48"/>
-      <c r="L259" s="7"/>
-      <c r="M259" s="9"/>
-      <c r="N259" s="11"/>
-      <c r="O259" s="13"/>
-      <c r="P259" s="15"/>
-      <c r="Q259" s="17"/>
+        <v>367</v>
+      </c>
+      <c r="E259" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="F259" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="G259" s="1" t="e" vm="74">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H259" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I259" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J259" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K259" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L259" s="7">
+        <v>88</v>
+      </c>
+      <c r="M259" s="9">
+        <v>120</v>
+      </c>
+      <c r="N259" s="11">
+        <v>75</v>
+      </c>
+      <c r="O259" s="13">
+        <v>100</v>
+      </c>
+      <c r="P259" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q259" s="17">
+        <v>142</v>
+      </c>
       <c r="R259" s="40">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="260" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B260" s="5"/>
       <c r="C260" s="5">
         <f t="shared" si="7"/>
         <v>257</v>
@@ -20762,11 +20813,6 @@
       </c>
       <c r="E260" s="84"/>
       <c r="F260" s="48"/>
-      <c r="G260" s="1"/>
-      <c r="H260" s="1"/>
-      <c r="I260" s="1"/>
-      <c r="J260" s="1"/>
-      <c r="K260" s="1"/>
       <c r="L260" s="7"/>
       <c r="M260" s="9"/>
       <c r="N260" s="11"/>
@@ -20806,6 +20852,7 @@
       </c>
     </row>
     <row r="262" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B262" s="5"/>
       <c r="C262" s="5">
         <f t="shared" si="7"/>
         <v>259</v>
@@ -20815,6 +20862,11 @@
       </c>
       <c r="E262" s="84"/>
       <c r="F262" s="48"/>
+      <c r="G262" s="1"/>
+      <c r="H262" s="1"/>
+      <c r="I262" s="1"/>
+      <c r="J262" s="1"/>
+      <c r="K262" s="1"/>
       <c r="L262" s="7"/>
       <c r="M262" s="9"/>
       <c r="N262" s="11"/>
@@ -20889,6 +20941,27 @@
         <v>0</v>
       </c>
     </row>
+    <row r="266" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C266" s="5">
+        <f t="shared" si="7"/>
+        <v>263</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E266" s="84"/>
+      <c r="F266" s="48"/>
+      <c r="L266" s="7"/>
+      <c r="M266" s="9"/>
+      <c r="N266" s="11"/>
+      <c r="O266" s="13"/>
+      <c r="P266" s="15"/>
+      <c r="Q266" s="17"/>
+      <c r="R266" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="L2:Q2"/>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FAE4B8-F5AB-4DA8-BE89-A3BF8DF3759E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38F39E9-D026-4F93-A01D-0F6058ADE2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="271">
+  <futureMetadata name="XLRICHVALUE" count="273">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -1938,8 +1938,22 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="271"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="272"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="271">
+  <valueMetadata count="273">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -2752,13 +2766,19 @@
     </bk>
     <bk>
       <rc t="1" v="270"/>
+    </bk>
+    <bk>
+      <rc t="1" v="271"/>
+    </bk>
+    <bk>
+      <rc t="1" v="272"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="372">
   <si>
     <t>Base stats</t>
   </si>
@@ -3896,6 +3916,12 @@
   </si>
   <si>
     <t>Relicanth</t>
+  </si>
+  <si>
+    <t>Zorua</t>
+  </si>
+  <si>
+    <t>Zoroark</t>
   </si>
 </sst>
 </file>
@@ -5106,7 +5132,7 @@
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>26</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>20</c:v>
@@ -5870,7 +5896,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="271">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="273">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -6953,6 +6979,14 @@
   </rv>
   <rv s="0">
     <v>270</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>271</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>272</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -7240,6 +7274,8 @@
   <rel r:id="rId269"/>
   <rel r:id="rId270"/>
   <rel r:id="rId271"/>
+  <rel r:id="rId272"/>
+  <rel r:id="rId273"/>
 </richValueRels>
 </file>
 
@@ -8293,7 +8329,7 @@
       </c>
       <c r="T15" s="20">
         <f>COUNTIF(E$6:F$266, "Dark")</f>
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -20804,15 +20840,28 @@
       </c>
     </row>
     <row r="260" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B260" t="e" vm="272">
+        <v>#VALUE!</v>
+      </c>
       <c r="C260" s="5">
-        <f t="shared" si="7"/>
         <v>257</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E260" s="84"/>
+        <v>370</v>
+      </c>
+      <c r="E260" s="73" t="s">
+        <v>48</v>
+      </c>
       <c r="F260" s="48"/>
+      <c r="G260" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H260" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K260" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="L260" s="7"/>
       <c r="M260" s="9"/>
       <c r="N260" s="11"/>
@@ -20825,21 +20874,30 @@
       </c>
     </row>
     <row r="261" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B261" s="5"/>
+      <c r="B261" s="5" t="e" vm="273">
+        <v>#VALUE!</v>
+      </c>
       <c r="C261" s="5">
-        <f t="shared" si="7"/>
         <v>258</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E261" s="84"/>
+        <v>371</v>
+      </c>
+      <c r="E261" s="73" t="s">
+        <v>48</v>
+      </c>
       <c r="F261" s="48"/>
-      <c r="G261" s="1"/>
-      <c r="H261" s="1"/>
+      <c r="G261" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H261" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="I261" s="1"/>
       <c r="J261" s="1"/>
-      <c r="K261" s="1"/>
+      <c r="K261" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L261" s="7"/>
       <c r="M261" s="9"/>
       <c r="N261" s="11"/>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38F39E9-D026-4F93-A01D-0F6058ADE2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8230C2-1902-41C0-B80B-7B212E81FC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20860,7 +20860,7 @@
         <v>17</v>
       </c>
       <c r="K260" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="L260" s="7"/>
       <c r="M260" s="9"/>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8230C2-1902-41C0-B80B-7B212E81FC86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F837A9C2-6085-4478-BC6B-80A12BF8F150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7543,7 +7543,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:T266"/>
+  <dimension ref="B1:T267"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
@@ -7686,7 +7686,7 @@
         <v>16</v>
       </c>
       <c r="T4" s="19">
-        <f>COUNTIF(E$6:F$266, "Grass")</f>
+        <f>COUNTIF(E$6:F$267, "Grass")</f>
         <v>22</v>
       </c>
     </row>
@@ -7746,7 +7746,7 @@
         <v>24</v>
       </c>
       <c r="T5" s="20">
-        <f>COUNTIF(E$6:F$266, "Fire")</f>
+        <f>COUNTIF(E$6:F$267, "Fire")</f>
         <v>28</v>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
         <v>30</v>
       </c>
       <c r="T6" s="20">
-        <f>COUNTIF(E$6:F$266, "Water")</f>
+        <f>COUNTIF(E$6:F$267, "Water")</f>
         <v>45</v>
       </c>
     </row>
@@ -7862,7 +7862,7 @@
         <v>37</v>
       </c>
       <c r="T7" s="20">
-        <f>COUNTIF(E$6:F$266, "Normal")</f>
+        <f>COUNTIF(E$6:F$267, "Normal")</f>
         <v>21</v>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
         <v>27</v>
       </c>
       <c r="T8" s="20">
-        <f>COUNTIF(E$6:F$266, "Fighting")</f>
+        <f>COUNTIF(E$6:F$267, "Fighting")</f>
         <v>20</v>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
         <v>41</v>
       </c>
       <c r="T9" s="20">
-        <f>COUNTIF(E$6:F$266, "Flying")</f>
+        <f>COUNTIF(E$6:F$267, "Flying")</f>
         <v>25</v>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
         <v>63</v>
       </c>
       <c r="T10" s="20">
-        <f>COUNTIF(E$6:F$266, "Psychic")</f>
+        <f>COUNTIF(E$6:F$267, "Psychic")</f>
         <v>18</v>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
         <v>45</v>
       </c>
       <c r="T11" s="20">
-        <f>COUNTIF(E$6:F$266, "Bug")</f>
+        <f>COUNTIF(E$6:F$267, "Bug")</f>
         <v>22</v>
       </c>
     </row>
@@ -8160,7 +8160,7 @@
         <v>50</v>
       </c>
       <c r="T12" s="20">
-        <f>COUNTIF(E$6:F$266, "Ground")</f>
+        <f>COUNTIF(E$6:F$267, "Ground")</f>
         <v>20</v>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
         <v>64</v>
       </c>
       <c r="T13" s="20">
-        <f>COUNTIF(E$6:F$266, "Rock")</f>
+        <f>COUNTIF(E$6:F$267, "Rock")</f>
         <v>22</v>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
         <v>65</v>
       </c>
       <c r="T14" s="20">
-        <f>COUNTIF(E$6:F$266, "Ghost")</f>
+        <f>COUNTIF(E$6:F$267, "Ghost")</f>
         <v>24</v>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
         <v>48</v>
       </c>
       <c r="T15" s="20">
-        <f>COUNTIF(E$6:F$266, "Dark")</f>
+        <f>COUNTIF(E$6:F$267, "Dark")</f>
         <v>28</v>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
         <v>66</v>
       </c>
       <c r="T16" s="20">
-        <f>COUNTIF(E$6:F$266, "Ice")</f>
+        <f>COUNTIF(E$6:F$267, "Ice")</f>
         <v>20</v>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
         <v>34</v>
       </c>
       <c r="T17" s="20">
-        <f>COUNTIF(E$6:F$266, "Steel")</f>
+        <f>COUNTIF(E$6:F$267, "Steel")</f>
         <v>22</v>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
         <v>67</v>
       </c>
       <c r="T18" s="20">
-        <f>COUNTIF(E$6:F$266, "Electrik")</f>
+        <f>COUNTIF(E$6:F$267, "Electrik")</f>
         <v>16</v>
       </c>
     </row>
@@ -8558,7 +8558,7 @@
         <v>68</v>
       </c>
       <c r="T19" s="20">
-        <f>COUNTIF(E$6:F$266, "Poison")</f>
+        <f>COUNTIF(E$6:F$267, "Poison")</f>
         <v>16</v>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
         <v>60</v>
       </c>
       <c r="T20" s="20">
-        <f>COUNTIF(E$6:F$266, "Fairy")</f>
+        <f>COUNTIF(E$6:F$267, "Fairy")</f>
         <v>16</v>
       </c>
     </row>
@@ -8672,7 +8672,7 @@
         <v>69</v>
       </c>
       <c r="T21" s="20">
-        <f>COUNTIF(E$6:F$266, "Dragon")</f>
+        <f>COUNTIF(E$6:F$267, "Dragon")</f>
         <v>18</v>
       </c>
     </row>
@@ -17748,7 +17748,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C198" s="5">
-        <f t="shared" ref="C198:C266" si="7">C197+1</f>
+        <f t="shared" ref="C198:C267" si="7">C197+1</f>
         <v>195</v>
       </c>
       <c r="D198" s="1" t="s">
@@ -17988,7 +17988,7 @@
         <v>109</v>
       </c>
       <c r="R202" s="40">
-        <f t="shared" ref="R202:R266" si="9">SUM(L202:Q202)</f>
+        <f t="shared" ref="R202:R267" si="9">SUM(L202:Q202)</f>
         <v>484</v>
       </c>
     </row>
@@ -20675,213 +20675,197 @@
       </c>
     </row>
     <row r="257" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B257" t="e" vm="269">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C257" s="5">
-        <f t="shared" si="7"/>
+      <c r="C257" s="5"/>
+      <c r="D257" s="1"/>
+      <c r="E257" s="45"/>
+      <c r="F257" s="63"/>
+      <c r="G257" s="1"/>
+      <c r="H257" s="1"/>
+      <c r="I257" s="1"/>
+      <c r="J257" s="1"/>
+      <c r="K257" s="1"/>
+      <c r="L257" s="7"/>
+      <c r="M257" s="9"/>
+      <c r="N257" s="11"/>
+      <c r="O257" s="13"/>
+      <c r="P257" s="15"/>
+      <c r="Q257" s="17"/>
+      <c r="R257" s="40"/>
+    </row>
+    <row r="258" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B258" t="e" vm="269">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C258" s="5">
+        <f>C256+1</f>
         <v>254</v>
       </c>
-      <c r="D257" s="1" t="s">
+      <c r="D258" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E257" s="81" t="s">
+      <c r="E258" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="F257" s="65" t="s">
+      <c r="F258" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="G257" s="1" t="e" vm="74">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H257" s="1" t="s">
+      <c r="G258" s="1" t="e" vm="74">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H258" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I257" s="1" t="e" vm="49">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J257" s="1" t="s">
+      <c r="I258" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J258" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K257" s="1" t="s">
+      <c r="K258" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="L257" s="7">
+      <c r="L258" s="7">
         <v>28</v>
       </c>
-      <c r="M257" s="9">
+      <c r="M258" s="9">
         <v>60</v>
       </c>
-      <c r="N257" s="11">
+      <c r="N258" s="11">
         <v>30</v>
       </c>
-      <c r="O257" s="13">
+      <c r="O258" s="13">
         <v>40</v>
       </c>
-      <c r="P257" s="15">
+      <c r="P258" s="15">
         <v>30</v>
       </c>
-      <c r="Q257" s="17">
+      <c r="Q258" s="17">
         <v>82</v>
       </c>
-      <c r="R257" s="40">
+      <c r="R258" s="40">
         <f t="shared" si="9"/>
         <v>270</v>
       </c>
     </row>
-    <row r="258" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B258" t="e" vm="270">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C258" s="5">
+    <row r="259" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B259" t="e" vm="270">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C259" s="5">
         <f t="shared" si="7"/>
         <v>255</v>
       </c>
-      <c r="D258" s="1" t="s">
+      <c r="D259" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E258" s="81" t="s">
+      <c r="E259" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="F258" s="65" t="s">
+      <c r="F259" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="G258" s="1" t="e" vm="74">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H258" s="1" t="s">
+      <c r="G259" s="1" t="e" vm="74">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H259" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I258" s="1" t="e" vm="49">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J258" s="1" t="s">
+      <c r="I259" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J259" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K258" s="1" t="s">
+      <c r="K259" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="L258" s="7">
+      <c r="L259" s="7">
         <v>68</v>
       </c>
-      <c r="M258" s="9">
+      <c r="M259" s="9">
         <v>80</v>
       </c>
-      <c r="N258" s="11">
+      <c r="N259" s="11">
         <v>50</v>
       </c>
-      <c r="O258" s="13">
+      <c r="O259" s="13">
         <v>60</v>
       </c>
-      <c r="P258" s="15">
+      <c r="P259" s="15">
         <v>50</v>
       </c>
-      <c r="Q258" s="17">
+      <c r="Q259" s="17">
         <v>102</v>
       </c>
-      <c r="R258" s="40">
+      <c r="R259" s="40">
         <f t="shared" si="9"/>
         <v>410</v>
       </c>
     </row>
-    <row r="259" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B259" t="e" vm="271">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C259" s="5">
+    <row r="260" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B260" t="e" vm="271">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C260" s="5">
         <f t="shared" si="7"/>
         <v>256</v>
       </c>
-      <c r="D259" s="1" t="s">
+      <c r="D260" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E259" s="81" t="s">
+      <c r="E260" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="F259" s="65" t="s">
+      <c r="F260" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="G259" s="1" t="e" vm="74">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H259" s="1" t="s">
+      <c r="G260" s="1" t="e" vm="74">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H260" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I259" s="1" t="e" vm="49">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J259" s="1" t="s">
+      <c r="I260" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J260" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K259" s="1" t="s">
+      <c r="K260" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L259" s="7">
+      <c r="L260" s="7">
         <v>88</v>
       </c>
-      <c r="M259" s="9">
+      <c r="M260" s="9">
         <v>120</v>
       </c>
-      <c r="N259" s="11">
+      <c r="N260" s="11">
         <v>75</v>
       </c>
-      <c r="O259" s="13">
+      <c r="O260" s="13">
         <v>100</v>
       </c>
-      <c r="P259" s="15">
+      <c r="P260" s="15">
         <v>75</v>
       </c>
-      <c r="Q259" s="17">
+      <c r="Q260" s="17">
         <v>142</v>
       </c>
-      <c r="R259" s="40">
+      <c r="R260" s="40">
         <f t="shared" si="9"/>
         <v>600</v>
       </c>
     </row>
-    <row r="260" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B260" t="e" vm="272">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C260" s="5">
+    <row r="261" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B261" t="e" vm="272">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C261" s="5">
         <v>257</v>
       </c>
-      <c r="D260" s="1" t="s">
+      <c r="D261" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="E260" s="73" t="s">
-        <v>48</v>
-      </c>
-      <c r="F260" s="48"/>
-      <c r="G260" s="1" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H260" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K260" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L260" s="7"/>
-      <c r="M260" s="9"/>
-      <c r="N260" s="11"/>
-      <c r="O260" s="13"/>
-      <c r="P260" s="15"/>
-      <c r="Q260" s="17"/>
-      <c r="R260" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B261" s="5" t="e" vm="273">
-        <v>#VALUE!</v>
-      </c>
-      <c r="C261" s="5">
-        <v>258</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="E261" s="73" t="s">
         <v>48</v>
@@ -20893,10 +20877,8 @@
       <c r="H261" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I261" s="1"/>
-      <c r="J261" s="1"/>
       <c r="K261" s="1" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="L261" s="7"/>
       <c r="M261" s="9"/>
@@ -20910,21 +20892,30 @@
       </c>
     </row>
     <row r="262" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B262" s="5"/>
+      <c r="B262" s="5" t="e" vm="273">
+        <v>#VALUE!</v>
+      </c>
       <c r="C262" s="5">
-        <f t="shared" si="7"/>
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E262" s="84"/>
+        <v>371</v>
+      </c>
+      <c r="E262" s="73" t="s">
+        <v>48</v>
+      </c>
       <c r="F262" s="48"/>
-      <c r="G262" s="1"/>
-      <c r="H262" s="1"/>
+      <c r="G262" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H262" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="I262" s="1"/>
       <c r="J262" s="1"/>
-      <c r="K262" s="1"/>
+      <c r="K262" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L262" s="7"/>
       <c r="M262" s="9"/>
       <c r="N262" s="11"/>
@@ -20937,15 +20928,21 @@
       </c>
     </row>
     <row r="263" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B263" s="5"/>
       <c r="C263" s="5">
         <f t="shared" si="7"/>
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>297</v>
       </c>
       <c r="E263" s="84"/>
       <c r="F263" s="48"/>
+      <c r="G263" s="1"/>
+      <c r="H263" s="1"/>
+      <c r="I263" s="1"/>
+      <c r="J263" s="1"/>
+      <c r="K263" s="1"/>
       <c r="L263" s="7"/>
       <c r="M263" s="9"/>
       <c r="N263" s="11"/>
@@ -20960,7 +20957,7 @@
     <row r="264" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C264" s="5">
         <f t="shared" si="7"/>
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>297</v>
@@ -20981,7 +20978,7 @@
     <row r="265" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C265" s="5">
         <f t="shared" si="7"/>
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>297</v>
@@ -21002,7 +20999,7 @@
     <row r="266" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C266" s="5">
         <f t="shared" si="7"/>
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>297</v>
@@ -21020,6 +21017,27 @@
         <v>0</v>
       </c>
     </row>
+    <row r="267" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C267" s="5">
+        <f t="shared" si="7"/>
+        <v>263</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E267" s="84"/>
+      <c r="F267" s="48"/>
+      <c r="L267" s="7"/>
+      <c r="M267" s="9"/>
+      <c r="N267" s="11"/>
+      <c r="O267" s="13"/>
+      <c r="P267" s="15"/>
+      <c r="Q267" s="17"/>
+      <c r="R267" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="L2:Q2"/>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F837A9C2-6085-4478-BC6B-80A12BF8F150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D546E631-C751-426A-A848-DCF9AEA8E525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="273">
+  <futureMetadata name="XLRICHVALUE" count="274">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -1952,8 +1952,15 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="273"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="273">
+  <valueMetadata count="274">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -2772,13 +2779,16 @@
     </bk>
     <bk>
       <rc t="1" v="272"/>
+    </bk>
+    <bk>
+      <rc t="1" v="273"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="373">
   <si>
     <t>Base stats</t>
   </si>
@@ -3922,6 +3932,9 @@
   </si>
   <si>
     <t>Zoroark</t>
+  </si>
+  <si>
+    <t>Druddigon</t>
   </si>
 </sst>
 </file>
@@ -5150,7 +5163,7 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>18</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5896,7 +5909,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="273">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="274">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -6987,6 +7000,10 @@
   </rv>
   <rv s="0">
     <v>272</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>273</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -7276,6 +7293,7 @@
   <rel r:id="rId271"/>
   <rel r:id="rId272"/>
   <rel r:id="rId273"/>
+  <rel r:id="rId274"/>
 </richValueRels>
 </file>
 
@@ -8673,7 +8691,7 @@
       </c>
       <c r="T21" s="20">
         <f>COUNTIF(E$6:F$267, "Dragon")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -20675,30 +20693,65 @@
       </c>
     </row>
     <row r="257" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C257" s="5"/>
-      <c r="D257" s="1"/>
-      <c r="E257" s="45"/>
-      <c r="F257" s="63"/>
-      <c r="G257" s="1"/>
-      <c r="H257" s="1"/>
-      <c r="I257" s="1"/>
-      <c r="J257" s="1"/>
-      <c r="K257" s="1"/>
-      <c r="L257" s="7"/>
-      <c r="M257" s="9"/>
-      <c r="N257" s="11"/>
-      <c r="O257" s="13"/>
-      <c r="P257" s="15"/>
-      <c r="Q257" s="17"/>
-      <c r="R257" s="40"/>
+      <c r="B257" t="e" vm="269">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C257" s="5">
+        <f t="shared" si="7"/>
+        <v>254</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E257" s="81" t="s">
+        <v>69</v>
+      </c>
+      <c r="F257" s="48"/>
+      <c r="G257" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H257" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I257" s="1" t="e" vm="138">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J257" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="K257" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L257" s="7">
+        <v>77</v>
+      </c>
+      <c r="M257" s="9">
+        <v>120</v>
+      </c>
+      <c r="N257" s="11">
+        <v>90</v>
+      </c>
+      <c r="O257" s="13">
+        <v>60</v>
+      </c>
+      <c r="P257" s="15">
+        <v>90</v>
+      </c>
+      <c r="Q257" s="17">
+        <v>48</v>
+      </c>
+      <c r="R257" s="40">
+        <f t="shared" si="9"/>
+        <v>485</v>
+      </c>
     </row>
     <row r="258" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B258" t="e" vm="269">
+      <c r="B258" t="e" vm="270">
         <v>#VALUE!</v>
       </c>
       <c r="C258" s="5">
-        <f>C256+1</f>
-        <v>254</v>
+        <f t="shared" si="7"/>
+        <v>255</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>365</v>
@@ -20748,12 +20801,12 @@
       </c>
     </row>
     <row r="259" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B259" t="e" vm="270">
+      <c r="B259" t="e" vm="271">
         <v>#VALUE!</v>
       </c>
       <c r="C259" s="5">
         <f t="shared" si="7"/>
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>366</v>
@@ -20803,12 +20856,12 @@
       </c>
     </row>
     <row r="260" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B260" t="e" vm="271">
+      <c r="B260" t="e" vm="272">
         <v>#VALUE!</v>
       </c>
       <c r="C260" s="5">
         <f t="shared" si="7"/>
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>367</v>
@@ -20858,11 +20911,12 @@
       </c>
     </row>
     <row r="261" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B261" t="e" vm="272">
+      <c r="B261" t="e" vm="273">
         <v>#VALUE!</v>
       </c>
       <c r="C261" s="5">
-        <v>257</v>
+        <f t="shared" si="7"/>
+        <v>258</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>370</v>
@@ -20892,11 +20946,12 @@
       </c>
     </row>
     <row r="262" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B262" s="5" t="e" vm="273">
+      <c r="B262" s="5" t="e" vm="274">
         <v>#VALUE!</v>
       </c>
       <c r="C262" s="5">
-        <v>258</v>
+        <f t="shared" si="7"/>
+        <v>259</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>371</v>
@@ -20931,7 +20986,7 @@
       <c r="B263" s="5"/>
       <c r="C263" s="5">
         <f t="shared" si="7"/>
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>297</v>
@@ -20957,7 +21012,7 @@
     <row r="264" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C264" s="5">
         <f t="shared" si="7"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>297</v>
@@ -20978,7 +21033,7 @@
     <row r="265" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C265" s="5">
         <f t="shared" si="7"/>
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>297</v>
@@ -20999,7 +21054,7 @@
     <row r="266" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C266" s="5">
         <f t="shared" si="7"/>
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>297</v>
@@ -21020,7 +21075,7 @@
     <row r="267" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C267" s="5">
         <f t="shared" si="7"/>
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>297</v>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D546E631-C751-426A-A848-DCF9AEA8E525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5B56A1-4A32-4778-A5D4-0C131852F641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5B56A1-4A32-4778-A5D4-0C131852F641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CAE4E1-A537-45FF-A95F-14ADC4980F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9CAE4E1-A537-45FF-A95F-14ADC4980F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DAF4E3-F6B9-4158-A90E-2FF8F7971BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4184,34 +4184,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -4284,11 +4256,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4350,76 +4348,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4428,120 +4366,135 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7587,14 +7540,14 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="85" t="s">
+      <c r="L2" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
     </row>
     <row r="3" spans="2:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
@@ -7606,20 +7559,20 @@
       <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="82" t="s">
+      <c r="E3" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="82" t="s">
+      <c r="F3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="86" t="s">
+      <c r="G3" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="86"/>
-      <c r="I3" s="86" t="s">
+      <c r="H3" s="68"/>
+      <c r="I3" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="86"/>
+      <c r="J3" s="68"/>
       <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
@@ -7659,10 +7612,10 @@
       <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="44"/>
+      <c r="F4" s="26"/>
       <c r="G4" s="4" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -7696,11 +7649,11 @@
       <c r="Q4" s="16">
         <v>63</v>
       </c>
-      <c r="R4" s="40">
+      <c r="R4" s="22">
         <f>SUM(L4:Q4)</f>
         <v>308</v>
       </c>
-      <c r="S4" s="38" t="s">
+      <c r="S4" s="69" t="s">
         <v>16</v>
       </c>
       <c r="T4" s="19">
@@ -7719,10 +7672,10 @@
       <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="45" t="s">
+      <c r="E5" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="46"/>
+      <c r="F5" s="28"/>
       <c r="G5" s="1" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -7756,11 +7709,11 @@
       <c r="Q5" s="17">
         <v>83</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="22">
         <f t="shared" ref="R5:R69" si="1">SUM(L5:Q5)</f>
         <v>413</v>
       </c>
-      <c r="S5" s="21" t="s">
+      <c r="S5" s="29" t="s">
         <v>24</v>
       </c>
       <c r="T5" s="20">
@@ -7779,10 +7732,10 @@
       <c r="D6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="46"/>
+      <c r="F6" s="28"/>
       <c r="G6" s="1" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -7816,11 +7769,11 @@
       <c r="Q6" s="17">
         <v>113</v>
       </c>
-      <c r="R6" s="40">
+      <c r="R6" s="22">
         <f t="shared" si="1"/>
         <v>528</v>
       </c>
-      <c r="S6" s="22" t="s">
+      <c r="S6" s="32" t="s">
         <v>30</v>
       </c>
       <c r="T6" s="20">
@@ -7839,10 +7792,10 @@
       <c r="D7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="48"/>
+      <c r="F7" s="30"/>
       <c r="G7" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -7872,11 +7825,11 @@
       <c r="Q7" s="17">
         <v>45</v>
       </c>
-      <c r="R7" s="40">
+      <c r="R7" s="22">
         <f t="shared" si="1"/>
         <v>310</v>
       </c>
-      <c r="S7" s="23" t="s">
+      <c r="S7" s="34" t="s">
         <v>37</v>
       </c>
       <c r="T7" s="20">
@@ -7895,10 +7848,10 @@
       <c r="D8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="47" t="s">
+      <c r="E8" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="F8" s="31" t="s">
         <v>27</v>
       </c>
       <c r="G8" s="1" t="e" vm="3">
@@ -7930,11 +7883,11 @@
       <c r="Q8" s="17">
         <v>55</v>
       </c>
-      <c r="R8" s="40">
+      <c r="R8" s="22">
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-      <c r="S8" s="24" t="s">
+      <c r="S8" s="39" t="s">
         <v>27</v>
       </c>
       <c r="T8" s="20">
@@ -7953,10 +7906,10 @@
       <c r="D9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="47" t="s">
+      <c r="E9" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="49" t="s">
+      <c r="F9" s="31" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="1" t="e" vm="3">
@@ -7988,11 +7941,11 @@
       <c r="Q9" s="17">
         <v>80</v>
       </c>
-      <c r="R9" s="40">
+      <c r="R9" s="22">
         <f t="shared" si="1"/>
         <v>530</v>
       </c>
-      <c r="S9" s="25" t="s">
+      <c r="S9" s="35" t="s">
         <v>41</v>
       </c>
       <c r="T9" s="20">
@@ -8011,10 +7964,10 @@
       <c r="D10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="46"/>
+      <c r="F10" s="28"/>
       <c r="G10" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -8048,11 +8001,11 @@
       <c r="Q10" s="17">
         <v>40</v>
       </c>
-      <c r="R10" s="40">
+      <c r="R10" s="22">
         <f t="shared" si="1"/>
         <v>314</v>
       </c>
-      <c r="S10" s="26" t="s">
+      <c r="S10" s="53" t="s">
         <v>63</v>
       </c>
       <c r="T10" s="20">
@@ -8071,10 +8024,10 @@
       <c r="D11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="46"/>
+      <c r="F11" s="28"/>
       <c r="G11" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -8108,11 +8061,11 @@
       <c r="Q11" s="17">
         <v>50</v>
       </c>
-      <c r="R11" s="40">
+      <c r="R11" s="22">
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-      <c r="S11" s="27" t="s">
+      <c r="S11" s="36" t="s">
         <v>45</v>
       </c>
       <c r="T11" s="20">
@@ -8131,10 +8084,10 @@
       <c r="D12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="51" t="s">
+      <c r="F12" s="33" t="s">
         <v>34</v>
       </c>
       <c r="G12" s="1" t="e" vm="10">
@@ -8170,11 +8123,11 @@
       <c r="Q12" s="17">
         <v>60</v>
       </c>
-      <c r="R12" s="40">
+      <c r="R12" s="22">
         <f t="shared" si="1"/>
         <v>530</v>
       </c>
-      <c r="S12" s="28" t="s">
+      <c r="S12" s="38" t="s">
         <v>50</v>
       </c>
       <c r="T12" s="20">
@@ -8193,10 +8146,10 @@
       <c r="D13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="52" t="s">
+      <c r="E13" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F13" s="46"/>
+      <c r="F13" s="28"/>
       <c r="G13" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -8226,11 +8179,11 @@
       <c r="Q13" s="17">
         <v>55</v>
       </c>
-      <c r="R13" s="40">
+      <c r="R13" s="22">
         <f t="shared" si="1"/>
         <v>275</v>
       </c>
-      <c r="S13" s="29" t="s">
+      <c r="S13" s="23" t="s">
         <v>64</v>
       </c>
       <c r="T13" s="20">
@@ -8249,10 +8202,10 @@
       <c r="D14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="52" t="s">
+      <c r="E14" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="46"/>
+      <c r="F14" s="28"/>
       <c r="G14" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -8282,11 +8235,11 @@
       <c r="Q14" s="17">
         <v>60</v>
       </c>
-      <c r="R14" s="40">
+      <c r="R14" s="22">
         <f t="shared" si="1"/>
         <v>370</v>
       </c>
-      <c r="S14" s="30" t="s">
+      <c r="S14" s="50" t="s">
         <v>65</v>
       </c>
       <c r="T14" s="20">
@@ -8305,10 +8258,10 @@
       <c r="D15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="52" t="s">
+      <c r="E15" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="46"/>
+      <c r="F15" s="28"/>
       <c r="G15" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -8338,11 +8291,11 @@
       <c r="Q15" s="17">
         <v>80</v>
       </c>
-      <c r="R15" s="40">
+      <c r="R15" s="22">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="S15" s="31" t="s">
+      <c r="S15" s="55" t="s">
         <v>48</v>
       </c>
       <c r="T15" s="20">
@@ -8361,10 +8314,10 @@
       <c r="D16" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="E16" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F16" s="63" t="s">
+      <c r="F16" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G16" s="1" t="e" vm="17">
@@ -8396,11 +8349,11 @@
       <c r="Q16" s="17">
         <v>62</v>
       </c>
-      <c r="R16" s="40">
+      <c r="R16" s="22">
         <f t="shared" si="1"/>
         <v>278</v>
       </c>
-      <c r="S16" s="32" t="s">
+      <c r="S16" s="46" t="s">
         <v>66</v>
       </c>
       <c r="T16" s="20">
@@ -8419,10 +8372,10 @@
       <c r="D17" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="E17" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="63" t="s">
+      <c r="F17" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G17" s="1" t="e" vm="17">
@@ -8454,11 +8407,11 @@
       <c r="Q17" s="17">
         <v>84</v>
       </c>
-      <c r="R17" s="40">
+      <c r="R17" s="22">
         <f t="shared" si="1"/>
         <v>382</v>
       </c>
-      <c r="S17" s="33" t="s">
+      <c r="S17" s="52" t="s">
         <v>34</v>
       </c>
       <c r="T17" s="20">
@@ -8477,10 +8430,10 @@
       <c r="D18" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E18" s="47" t="s">
+      <c r="E18" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="63" t="s">
+      <c r="F18" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G18" s="1" t="e" vm="17">
@@ -8512,11 +8465,11 @@
       <c r="Q18" s="17">
         <v>126</v>
       </c>
-      <c r="R18" s="40">
+      <c r="R18" s="22">
         <f t="shared" si="1"/>
         <v>499</v>
       </c>
-      <c r="S18" s="34" t="s">
+      <c r="S18" s="44" t="s">
         <v>67</v>
       </c>
       <c r="T18" s="20">
@@ -8535,10 +8488,10 @@
       <c r="D19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="54" t="s">
+      <c r="E19" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="46"/>
+      <c r="F19" s="28"/>
       <c r="G19" s="1" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
@@ -8568,11 +8521,11 @@
       <c r="Q19" s="17">
         <v>45</v>
       </c>
-      <c r="R19" s="40">
+      <c r="R19" s="22">
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="S19" s="35" t="s">
+      <c r="S19" s="40" t="s">
         <v>68</v>
       </c>
       <c r="T19" s="20">
@@ -8591,10 +8544,10 @@
       <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="54" t="s">
+      <c r="E20" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="55" t="s">
+      <c r="F20" s="37" t="s">
         <v>48</v>
       </c>
       <c r="G20" s="1" t="e" vm="21">
@@ -8626,11 +8579,11 @@
       <c r="Q20" s="17">
         <v>92</v>
       </c>
-      <c r="R20" s="40">
+      <c r="R20" s="22">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
-      <c r="S20" s="36" t="s">
+      <c r="S20" s="54" t="s">
         <v>60</v>
       </c>
       <c r="T20" s="20">
@@ -8638,7 +8591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
@@ -8649,10 +8602,10 @@
       <c r="D21" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="56" t="s">
+      <c r="E21" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F21" s="46"/>
+      <c r="F21" s="28"/>
       <c r="G21" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -8682,14 +8635,14 @@
       <c r="Q21" s="17">
         <v>40</v>
       </c>
-      <c r="R21" s="40">
+      <c r="R21" s="22">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="S21" s="37" t="s">
+      <c r="S21" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="T21" s="20">
+      <c r="T21" s="71">
         <f>COUNTIF(E$6:F$267, "Dragon")</f>
         <v>19</v>
       </c>
@@ -8705,10 +8658,10 @@
       <c r="D22" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="56" t="s">
+      <c r="E22" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="46"/>
+      <c r="F22" s="28"/>
       <c r="G22" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -8738,7 +8691,7 @@
       <c r="Q22" s="17">
         <v>65</v>
       </c>
-      <c r="R22" s="40">
+      <c r="R22" s="22">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
@@ -8754,10 +8707,10 @@
       <c r="D23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="57" t="s">
+      <c r="E23" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="46"/>
+      <c r="F23" s="28"/>
       <c r="G23" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -8791,7 +8744,7 @@
       <c r="Q23" s="17">
         <v>43</v>
       </c>
-      <c r="R23" s="40">
+      <c r="R23" s="22">
         <f t="shared" si="1"/>
         <v>348</v>
       </c>
@@ -8807,10 +8760,10 @@
       <c r="D24" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E24" s="57" t="s">
+      <c r="E24" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="55" t="s">
+      <c r="F24" s="37" t="s">
         <v>48</v>
       </c>
       <c r="G24" s="1" t="e" vm="3">
@@ -8846,7 +8799,7 @@
       <c r="Q24" s="17">
         <v>58</v>
       </c>
-      <c r="R24" s="40">
+      <c r="R24" s="22">
         <f t="shared" si="1"/>
         <v>495</v>
       </c>
@@ -8862,10 +8815,10 @@
       <c r="D25" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E25" s="45" t="s">
+      <c r="E25" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="46"/>
+      <c r="F25" s="28"/>
       <c r="G25" s="1" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -8895,7 +8848,7 @@
       <c r="Q25" s="17">
         <v>30</v>
       </c>
-      <c r="R25" s="40">
+      <c r="R25" s="22">
         <f t="shared" si="1"/>
         <v>280</v>
       </c>
@@ -8911,10 +8864,10 @@
       <c r="D26" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E26" s="45" t="s">
+      <c r="E26" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F26" s="46"/>
+      <c r="F26" s="28"/>
       <c r="G26" s="1" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -8944,7 +8897,7 @@
       <c r="Q26" s="17">
         <v>90</v>
       </c>
-      <c r="R26" s="40">
+      <c r="R26" s="22">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
@@ -8960,10 +8913,10 @@
       <c r="D27" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G27" s="1" t="e" vm="2">
@@ -8999,7 +8952,7 @@
       <c r="Q27" s="17">
         <v>66</v>
       </c>
-      <c r="R27" s="40">
+      <c r="R27" s="22">
         <f t="shared" si="1"/>
         <v>280</v>
       </c>
@@ -9015,10 +8968,10 @@
       <c r="D28" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="45" t="s">
+      <c r="E28" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F28" s="42" t="s">
+      <c r="F28" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G28" s="1" t="e" vm="2">
@@ -9054,7 +9007,7 @@
       <c r="Q28" s="17">
         <v>116</v>
       </c>
-      <c r="R28" s="40">
+      <c r="R28" s="22">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
@@ -9070,10 +9023,10 @@
       <c r="D29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E29" s="41" t="s">
+      <c r="E29" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="46"/>
+      <c r="F29" s="28"/>
       <c r="G29" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -9103,7 +9056,7 @@
       <c r="Q29" s="17">
         <v>15</v>
       </c>
-      <c r="R29" s="40">
+      <c r="R29" s="22">
         <f t="shared" si="1"/>
         <v>280</v>
       </c>
@@ -9119,10 +9072,10 @@
       <c r="D30" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E30" s="41" t="s">
+      <c r="E30" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F30" s="46"/>
+      <c r="F30" s="28"/>
       <c r="G30" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -9152,7 +9105,7 @@
       <c r="Q30" s="17">
         <v>20</v>
       </c>
-      <c r="R30" s="40">
+      <c r="R30" s="22">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
@@ -9168,10 +9121,10 @@
       <c r="D31" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="41" t="s">
+      <c r="E31" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F31" s="46"/>
+      <c r="F31" s="28"/>
       <c r="G31" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -9201,7 +9154,7 @@
       <c r="Q31" s="17">
         <v>25</v>
       </c>
-      <c r="R31" s="40">
+      <c r="R31" s="22">
         <f t="shared" si="1"/>
         <v>515</v>
       </c>
@@ -9217,10 +9170,10 @@
       <c r="D32" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E32" s="45" t="s">
+      <c r="E32" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="46"/>
+      <c r="F32" s="28"/>
       <c r="G32" s="1" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
@@ -9254,7 +9207,7 @@
       <c r="Q32" s="17">
         <v>35</v>
       </c>
-      <c r="R32" s="40">
+      <c r="R32" s="22">
         <f t="shared" si="1"/>
         <v>295</v>
       </c>
@@ -9270,10 +9223,10 @@
       <c r="D33" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="45" t="s">
+      <c r="E33" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F33" s="49" t="s">
+      <c r="F33" s="31" t="s">
         <v>27</v>
       </c>
       <c r="G33" s="1" t="e" vm="31">
@@ -9309,7 +9262,7 @@
       <c r="Q33" s="17">
         <v>70</v>
       </c>
-      <c r="R33" s="40">
+      <c r="R33" s="22">
         <f t="shared" si="1"/>
         <v>460</v>
       </c>
@@ -9325,10 +9278,10 @@
       <c r="D34" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E34" s="58" t="s">
+      <c r="E34" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F34" s="59" t="s">
+      <c r="F34" s="41" t="s">
         <v>37</v>
       </c>
       <c r="G34" s="1" t="e" vm="3">
@@ -9360,7 +9313,7 @@
       <c r="Q34" s="17">
         <v>75</v>
       </c>
-      <c r="R34" s="40">
+      <c r="R34" s="22">
         <f t="shared" si="1"/>
         <v>290</v>
       </c>
@@ -9376,10 +9329,10 @@
       <c r="D35" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E35" s="58" t="s">
+      <c r="E35" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="59" t="s">
+      <c r="F35" s="41" t="s">
         <v>37</v>
       </c>
       <c r="G35" s="1" t="e" vm="3">
@@ -9411,7 +9364,7 @@
       <c r="Q35" s="17">
         <v>110</v>
       </c>
-      <c r="R35" s="40">
+      <c r="R35" s="22">
         <f t="shared" si="1"/>
         <v>485</v>
       </c>
@@ -9427,10 +9380,10 @@
       <c r="D36" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E36" s="50" t="s">
+      <c r="E36" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="60" t="s">
+      <c r="F36" s="42" t="s">
         <v>45</v>
       </c>
       <c r="G36" s="1" t="e" vm="10">
@@ -9466,7 +9419,7 @@
       <c r="Q36" s="17">
         <v>27</v>
       </c>
-      <c r="R36" s="40">
+      <c r="R36" s="22">
         <f t="shared" si="1"/>
         <v>269</v>
       </c>
@@ -9482,10 +9435,10 @@
       <c r="D37" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E37" s="50" t="s">
+      <c r="E37" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F37" s="60" t="s">
+      <c r="F37" s="42" t="s">
         <v>45</v>
       </c>
       <c r="G37" s="1" t="e" vm="10">
@@ -9521,7 +9474,7 @@
       <c r="Q37" s="17">
         <v>42</v>
       </c>
-      <c r="R37" s="40">
+      <c r="R37" s="22">
         <f t="shared" si="1"/>
         <v>454</v>
       </c>
@@ -9537,10 +9490,10 @@
       <c r="D38" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F38" s="46"/>
+      <c r="F38" s="28"/>
       <c r="G38" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -9570,7 +9523,7 @@
       <c r="Q38" s="17">
         <v>52</v>
       </c>
-      <c r="R38" s="40">
+      <c r="R38" s="22">
         <f t="shared" si="1"/>
         <v>350</v>
       </c>
@@ -9586,10 +9539,10 @@
       <c r="D39" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F39" s="46"/>
+      <c r="F39" s="28"/>
       <c r="G39" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -9619,7 +9572,7 @@
       <c r="Q39" s="17">
         <v>68</v>
       </c>
-      <c r="R39" s="40">
+      <c r="R39" s="22">
         <f t="shared" si="1"/>
         <v>531</v>
       </c>
@@ -9635,10 +9588,10 @@
       <c r="D40" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E40" s="52" t="s">
+      <c r="E40" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F40" s="46"/>
+      <c r="F40" s="28"/>
       <c r="G40" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -9668,7 +9621,7 @@
       <c r="Q40" s="17">
         <v>40</v>
       </c>
-      <c r="R40" s="40">
+      <c r="R40" s="22">
         <f t="shared" si="1"/>
         <v>330</v>
       </c>
@@ -9684,10 +9637,10 @@
       <c r="D41" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E41" s="52" t="s">
+      <c r="E41" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F41" s="46"/>
+      <c r="F41" s="28"/>
       <c r="G41" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -9717,7 +9670,7 @@
       <c r="Q41" s="17">
         <v>55</v>
       </c>
-      <c r="R41" s="40">
+      <c r="R41" s="22">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
@@ -9733,10 +9686,10 @@
       <c r="D42" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E42" s="56" t="s">
+      <c r="E42" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F42" s="59" t="s">
+      <c r="F42" s="41" t="s">
         <v>37</v>
       </c>
       <c r="G42" s="1" t="e" vm="3">
@@ -9768,7 +9721,7 @@
       <c r="Q42" s="17">
         <v>50</v>
       </c>
-      <c r="R42" s="40">
+      <c r="R42" s="22">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
@@ -9784,10 +9737,10 @@
       <c r="D43" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E43" s="45" t="s">
+      <c r="E43" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F43" s="61" t="s">
+      <c r="F43" s="43" t="s">
         <v>69</v>
       </c>
       <c r="G43" s="1" t="e" vm="2">
@@ -9823,7 +9776,7 @@
       <c r="Q43" s="17">
         <v>20</v>
       </c>
-      <c r="R43" s="40">
+      <c r="R43" s="22">
         <f t="shared" si="1"/>
         <v>260</v>
       </c>
@@ -9839,10 +9792,10 @@
       <c r="D44" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E44" s="45" t="s">
+      <c r="E44" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="43" t="s">
         <v>69</v>
       </c>
       <c r="G44" s="1" t="e" vm="2">
@@ -9878,7 +9831,7 @@
       <c r="Q44" s="17">
         <v>70</v>
       </c>
-      <c r="R44" s="40">
+      <c r="R44" s="22">
         <f t="shared" si="1"/>
         <v>485</v>
       </c>
@@ -9894,10 +9847,10 @@
       <c r="D45" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E45" s="45" t="s">
+      <c r="E45" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F45" s="61" t="s">
+      <c r="F45" s="43" t="s">
         <v>69</v>
       </c>
       <c r="G45" s="1" t="e" vm="2">
@@ -9933,7 +9886,7 @@
       <c r="Q45" s="17">
         <v>30</v>
       </c>
-      <c r="R45" s="40">
+      <c r="R45" s="22">
         <f t="shared" si="1"/>
         <v>485</v>
       </c>
@@ -9949,10 +9902,10 @@
       <c r="D46" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E46" s="62" t="s">
+      <c r="E46" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F46" s="63" t="s">
+      <c r="F46" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G46" s="1" t="e" vm="3">
@@ -9984,7 +9937,7 @@
       <c r="Q46" s="17">
         <v>103</v>
       </c>
-      <c r="R46" s="40">
+      <c r="R46" s="22">
         <f t="shared" si="1"/>
         <v>428</v>
       </c>
@@ -10000,10 +9953,10 @@
       <c r="D47" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="E47" s="52" t="s">
+      <c r="E47" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F47" s="42" t="s">
+      <c r="F47" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G47" s="1" t="e" vm="10">
@@ -10039,7 +9992,7 @@
       <c r="Q47" s="17">
         <v>20</v>
       </c>
-      <c r="R47" s="40">
+      <c r="R47" s="22">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
@@ -10055,10 +10008,10 @@
       <c r="D48" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="E48" s="50" t="s">
+      <c r="E48" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F48" s="42" t="s">
+      <c r="F48" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G48" s="1" t="e" vm="10">
@@ -10094,7 +10047,7 @@
       <c r="Q48" s="17">
         <v>40</v>
       </c>
-      <c r="R48" s="40">
+      <c r="R48" s="22">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
@@ -10110,10 +10063,10 @@
       <c r="D49" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="E49" s="50" t="s">
+      <c r="E49" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F49" s="42" t="s">
+      <c r="F49" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G49" s="1" t="e" vm="10">
@@ -10147,7 +10100,7 @@
       <c r="Q49" s="17">
         <v>50</v>
       </c>
-      <c r="R49" s="40"/>
+      <c r="R49" s="22"/>
     </row>
     <row r="50" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="5" t="e" vm="56">
@@ -10160,10 +10113,10 @@
       <c r="D50" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E50" s="64" t="s">
+      <c r="E50" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F50" s="46"/>
+      <c r="F50" s="28"/>
       <c r="G50" s="1" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
@@ -10197,7 +10150,7 @@
       <c r="Q50" s="17">
         <v>50</v>
       </c>
-      <c r="R50" s="40">
+      <c r="R50" s="22">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
@@ -10213,10 +10166,10 @@
       <c r="D51" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E51" s="64" t="s">
+      <c r="E51" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F51" s="46"/>
+      <c r="F51" s="28"/>
       <c r="G51" s="1" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
@@ -10250,7 +10203,7 @@
       <c r="Q51" s="17">
         <v>80</v>
       </c>
-      <c r="R51" s="40">
+      <c r="R51" s="22">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
@@ -10266,10 +10219,10 @@
       <c r="D52" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E52" s="64" t="s">
+      <c r="E52" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F52" s="65" t="s">
+      <c r="F52" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G52" s="1" t="e" vm="31">
@@ -10305,7 +10258,7 @@
       <c r="Q52" s="17">
         <v>110</v>
       </c>
-      <c r="R52" s="40">
+      <c r="R52" s="22">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
@@ -10321,10 +10274,10 @@
       <c r="D53" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E53" s="54" t="s">
+      <c r="E53" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F53" s="66" t="s">
+      <c r="F53" s="48" t="s">
         <v>64</v>
       </c>
       <c r="G53" s="1" t="e" vm="21">
@@ -10360,7 +10313,7 @@
       <c r="Q53" s="17">
         <v>55</v>
       </c>
-      <c r="R53" s="40">
+      <c r="R53" s="22">
         <f t="shared" si="1"/>
         <v>325</v>
       </c>
@@ -10376,10 +10329,10 @@
       <c r="D54" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E54" s="54" t="s">
+      <c r="E54" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F54" s="66" t="s">
+      <c r="F54" s="48" t="s">
         <v>64</v>
       </c>
       <c r="G54" s="1" t="e" vm="21">
@@ -10415,7 +10368,7 @@
       <c r="Q54" s="17">
         <v>45</v>
       </c>
-      <c r="R54" s="40">
+      <c r="R54" s="22">
         <f t="shared" si="1"/>
         <v>485</v>
       </c>
@@ -10431,10 +10384,10 @@
       <c r="D55" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E55" s="52" t="s">
+      <c r="E55" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F55" s="46"/>
+      <c r="F55" s="28"/>
       <c r="G55" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -10464,7 +10417,7 @@
       <c r="Q55" s="17">
         <v>85</v>
       </c>
-      <c r="R55" s="40">
+      <c r="R55" s="22">
         <f t="shared" si="1"/>
         <v>465</v>
       </c>
@@ -10480,10 +10433,10 @@
       <c r="D56" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="52" t="s">
+      <c r="E56" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F56" s="67" t="s">
+      <c r="F56" s="49" t="s">
         <v>63</v>
       </c>
       <c r="G56" s="1" t="e" vm="3">
@@ -10515,7 +10468,7 @@
       <c r="Q56" s="17">
         <v>65</v>
       </c>
-      <c r="R56" s="40">
+      <c r="R56" s="22">
         <f t="shared" si="1"/>
         <v>525</v>
       </c>
@@ -10531,10 +10484,10 @@
       <c r="D57" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E57" s="50" t="s">
+      <c r="E57" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F57" s="46"/>
+      <c r="F57" s="28"/>
       <c r="G57" s="1" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
@@ -10568,7 +10521,7 @@
       <c r="Q57" s="17">
         <v>80</v>
       </c>
-      <c r="R57" s="40">
+      <c r="R57" s="22">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
@@ -10584,10 +10537,10 @@
       <c r="D58" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E58" s="50" t="s">
+      <c r="E58" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F58" s="63" t="s">
+      <c r="F58" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G58" s="1" t="e" vm="64">
@@ -10623,7 +10576,7 @@
       <c r="Q58" s="17">
         <v>81</v>
       </c>
-      <c r="R58" s="40">
+      <c r="R58" s="22">
         <f t="shared" si="1"/>
         <v>540</v>
       </c>
@@ -10639,10 +10592,10 @@
       <c r="D59" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E59" s="56" t="s">
+      <c r="E59" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F59" s="63" t="s">
+      <c r="F59" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G59" s="1" t="e" vm="21">
@@ -10674,7 +10627,7 @@
       <c r="Q59" s="17">
         <v>85</v>
       </c>
-      <c r="R59" s="40">
+      <c r="R59" s="22">
         <f t="shared" si="1"/>
         <v>430</v>
       </c>
@@ -10690,10 +10643,10 @@
       <c r="D60" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E60" s="56" t="s">
+      <c r="E60" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F60" s="63" t="s">
+      <c r="F60" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G60" s="1" t="e" vm="21">
@@ -10725,7 +10678,7 @@
       <c r="Q60" s="17">
         <v>95</v>
       </c>
-      <c r="R60" s="40">
+      <c r="R60" s="22">
         <f t="shared" si="1"/>
         <v>510</v>
       </c>
@@ -10741,10 +10694,10 @@
       <c r="D61" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E61" s="47" t="s">
+      <c r="E61" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F61" s="46"/>
+      <c r="F61" s="28"/>
       <c r="G61" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -10774,7 +10727,7 @@
       <c r="Q61" s="17">
         <v>65</v>
       </c>
-      <c r="R61" s="40">
+      <c r="R61" s="22">
         <f t="shared" si="1"/>
         <v>299</v>
       </c>
@@ -10790,10 +10743,10 @@
       <c r="D62" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E62" s="47" t="s">
+      <c r="E62" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F62" s="46"/>
+      <c r="F62" s="28"/>
       <c r="G62" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -10823,7 +10776,7 @@
       <c r="Q62" s="17">
         <v>100</v>
       </c>
-      <c r="R62" s="40">
+      <c r="R62" s="22">
         <f t="shared" si="1"/>
         <v>505</v>
       </c>
@@ -10839,10 +10792,10 @@
       <c r="D63" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E63" s="57" t="s">
+      <c r="E63" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F63" s="46"/>
+      <c r="F63" s="28"/>
       <c r="G63" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -10872,7 +10825,7 @@
       <c r="Q63" s="17">
         <v>70</v>
       </c>
-      <c r="R63" s="40">
+      <c r="R63" s="22">
         <f t="shared" si="1"/>
         <v>305</v>
       </c>
@@ -10888,10 +10841,10 @@
       <c r="D64" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E64" s="57" t="s">
+      <c r="E64" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F64" s="46"/>
+      <c r="F64" s="28"/>
       <c r="G64" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -10921,7 +10874,7 @@
       <c r="Q64" s="17">
         <v>95</v>
       </c>
-      <c r="R64" s="40">
+      <c r="R64" s="22">
         <f t="shared" si="1"/>
         <v>455</v>
       </c>
@@ -10937,10 +10890,10 @@
       <c r="D65" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E65" s="57" t="s">
+      <c r="E65" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F65" s="65" t="s">
+      <c r="F65" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G65" s="1" t="e" vm="3">
@@ -10972,7 +10925,7 @@
       <c r="Q65" s="17">
         <v>90</v>
       </c>
-      <c r="R65" s="40">
+      <c r="R65" s="22">
         <f t="shared" si="1"/>
         <v>535</v>
       </c>
@@ -10988,10 +10941,10 @@
       <c r="D66" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E66" s="68" t="s">
+      <c r="E66" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F66" s="63" t="s">
+      <c r="F66" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G66" s="1" t="e" vm="74">
@@ -11023,7 +10976,7 @@
       <c r="Q66" s="17">
         <v>70</v>
       </c>
-      <c r="R66" s="40">
+      <c r="R66" s="22">
         <f t="shared" si="1"/>
         <v>348</v>
       </c>
@@ -11039,10 +10992,10 @@
       <c r="D67" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E67" s="68" t="s">
+      <c r="E67" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F67" s="63" t="s">
+      <c r="F67" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G67" s="1" t="e" vm="74">
@@ -11074,7 +11027,7 @@
       <c r="Q67" s="17">
         <v>80</v>
       </c>
-      <c r="R67" s="40">
+      <c r="R67" s="22">
         <f t="shared" si="1"/>
         <v>498</v>
       </c>
@@ -11090,10 +11043,10 @@
       <c r="D68" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E68" s="50" t="s">
+      <c r="E68" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F68" s="46"/>
+      <c r="F68" s="28"/>
       <c r="G68" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -11127,7 +11080,7 @@
       <c r="Q68" s="17">
         <v>65</v>
       </c>
-      <c r="R68" s="40">
+      <c r="R68" s="22">
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
@@ -11143,10 +11096,10 @@
       <c r="D69" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E69" s="50" t="s">
+      <c r="E69" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F69" s="46"/>
+      <c r="F69" s="28"/>
       <c r="G69" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -11180,7 +11133,7 @@
       <c r="Q69" s="17">
         <v>45</v>
       </c>
-      <c r="R69" s="40">
+      <c r="R69" s="22">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
@@ -11196,10 +11149,10 @@
       <c r="D70" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E70" s="53" t="s">
+      <c r="E70" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="F70" s="69" t="s">
+      <c r="F70" s="51" t="s">
         <v>30</v>
       </c>
       <c r="G70" s="1" t="e" vm="10">
@@ -11235,7 +11188,7 @@
       <c r="Q70" s="17">
         <v>85</v>
       </c>
-      <c r="R70" s="40">
+      <c r="R70" s="22">
         <f t="shared" ref="R70:R133" si="3">SUM(L70:Q70)</f>
         <v>270</v>
       </c>
@@ -11251,10 +11204,10 @@
       <c r="D71" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E71" s="53" t="s">
+      <c r="E71" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="F71" s="69" t="s">
+      <c r="F71" s="51" t="s">
         <v>30</v>
       </c>
       <c r="G71" s="1" t="e" vm="10">
@@ -11290,7 +11243,7 @@
       <c r="Q71" s="17">
         <v>65</v>
       </c>
-      <c r="R71" s="40">
+      <c r="R71" s="22">
         <f t="shared" si="3"/>
         <v>440</v>
       </c>
@@ -11306,10 +11259,10 @@
       <c r="D72" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E72" s="70" t="s">
+      <c r="E72" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F72" s="65" t="s">
+      <c r="F72" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G72" s="1" t="e" vm="34">
@@ -11341,7 +11294,7 @@
       <c r="Q72" s="17">
         <v>28</v>
       </c>
-      <c r="R72" s="40">
+      <c r="R72" s="22">
         <f t="shared" si="3"/>
         <v>325</v>
       </c>
@@ -11357,10 +11310,10 @@
       <c r="D73" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E73" s="70" t="s">
+      <c r="E73" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F73" s="65" t="s">
+      <c r="F73" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G73" s="1" t="e" vm="34">
@@ -11392,7 +11345,7 @@
       <c r="Q73" s="17">
         <v>35</v>
       </c>
-      <c r="R73" s="40">
+      <c r="R73" s="22">
         <f t="shared" si="3"/>
         <v>448</v>
       </c>
@@ -11408,10 +11361,10 @@
       <c r="D74" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E74" s="70" t="s">
+      <c r="E74" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F74" s="65" t="s">
+      <c r="F74" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G74" s="1" t="e" vm="34">
@@ -11443,7 +11396,7 @@
       <c r="Q74" s="17">
         <v>60</v>
       </c>
-      <c r="R74" s="40">
+      <c r="R74" s="22">
         <f t="shared" si="3"/>
         <v>500</v>
       </c>
@@ -11459,10 +11412,10 @@
       <c r="D75" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="E75" s="64" t="s">
+      <c r="E75" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F75" s="46"/>
+      <c r="F75" s="28"/>
       <c r="G75" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -11492,7 +11445,7 @@
       <c r="Q75" s="17">
         <v>44</v>
       </c>
-      <c r="R75" s="40">
+      <c r="R75" s="22">
         <f t="shared" si="3"/>
         <v>305</v>
       </c>
@@ -11508,10 +11461,10 @@
       <c r="D76" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E76" s="64" t="s">
+      <c r="E76" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F76" s="46"/>
+      <c r="F76" s="28"/>
       <c r="G76" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -11541,7 +11494,7 @@
       <c r="Q76" s="17">
         <v>59</v>
       </c>
-      <c r="R76" s="40">
+      <c r="R76" s="22">
         <f t="shared" si="3"/>
         <v>395</v>
       </c>
@@ -11557,10 +11510,10 @@
       <c r="D77" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E77" s="64" t="s">
+      <c r="E77" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F77" s="46"/>
+      <c r="F77" s="28"/>
       <c r="G77" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -11590,7 +11543,7 @@
       <c r="Q77" s="17">
         <v>79</v>
       </c>
-      <c r="R77" s="40">
+      <c r="R77" s="22">
         <f t="shared" si="3"/>
         <v>535</v>
       </c>
@@ -11606,10 +11559,10 @@
       <c r="D78" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E78" s="64" t="s">
+      <c r="E78" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F78" s="60" t="s">
+      <c r="F78" s="42" t="s">
         <v>45</v>
       </c>
       <c r="G78" s="1" t="e" vm="21">
@@ -11641,7 +11594,7 @@
       <c r="Q78" s="17">
         <v>20</v>
       </c>
-      <c r="R78" s="40">
+      <c r="R78" s="22">
         <f t="shared" si="3"/>
         <v>185</v>
       </c>
@@ -11657,10 +11610,10 @@
       <c r="D79" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E79" s="64" t="s">
+      <c r="E79" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F79" s="60" t="s">
+      <c r="F79" s="42" t="s">
         <v>45</v>
       </c>
       <c r="G79" s="1" t="e" vm="21">
@@ -11692,7 +11645,7 @@
       <c r="Q79" s="17">
         <v>65</v>
       </c>
-      <c r="R79" s="40">
+      <c r="R79" s="22">
         <f t="shared" si="3"/>
         <v>475</v>
       </c>
@@ -11708,10 +11661,10 @@
       <c r="D80" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E80" s="71" t="s">
+      <c r="E80" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="F80" s="46"/>
+      <c r="F80" s="28"/>
       <c r="G80" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -11741,7 +11694,7 @@
       <c r="Q80" s="17">
         <v>24</v>
       </c>
-      <c r="R80" s="40">
+      <c r="R80" s="22">
         <f t="shared" si="3"/>
         <v>292</v>
       </c>
@@ -11757,10 +11710,10 @@
       <c r="D81" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E81" s="71" t="s">
+      <c r="E81" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="F81" s="46"/>
+      <c r="F81" s="28"/>
       <c r="G81" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -11790,7 +11743,7 @@
       <c r="Q81" s="17">
         <v>29</v>
       </c>
-      <c r="R81" s="40">
+      <c r="R81" s="22">
         <f t="shared" si="3"/>
         <v>487</v>
       </c>
@@ -11806,10 +11759,10 @@
       <c r="D82" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="E82" s="50" t="s">
+      <c r="E82" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F82" s="46"/>
+      <c r="F82" s="28"/>
       <c r="G82" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -11843,7 +11796,7 @@
       <c r="Q82" s="17">
         <v>55</v>
       </c>
-      <c r="R82" s="40">
+      <c r="R82" s="22">
         <f t="shared" ref="R82:R83" si="4">SUM(L82:Q82)</f>
         <v>320</v>
       </c>
@@ -11859,10 +11812,10 @@
       <c r="D83" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E83" s="50" t="s">
+      <c r="E83" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F83" s="46"/>
+      <c r="F83" s="28"/>
       <c r="G83" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -11896,7 +11849,7 @@
       <c r="Q83" s="17">
         <v>85</v>
       </c>
-      <c r="R83" s="40">
+      <c r="R83" s="22">
         <f t="shared" si="4"/>
         <v>500</v>
       </c>
@@ -11912,10 +11865,10 @@
       <c r="D84" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E84" s="72" t="s">
+      <c r="E84" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="F84" s="46"/>
+      <c r="F84" s="28"/>
       <c r="G84" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -11949,7 +11902,7 @@
       <c r="Q84" s="17">
         <v>65</v>
       </c>
-      <c r="R84" s="40">
+      <c r="R84" s="22">
         <f t="shared" si="3"/>
         <v>312</v>
       </c>
@@ -11965,10 +11918,10 @@
       <c r="D85" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E85" s="72" t="s">
+      <c r="E85" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="F85" s="46"/>
+      <c r="F85" s="28"/>
       <c r="G85" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -12002,7 +11955,7 @@
       <c r="Q85" s="17">
         <v>95</v>
       </c>
-      <c r="R85" s="40">
+      <c r="R85" s="22">
         <f t="shared" si="3"/>
         <v>477</v>
       </c>
@@ -12018,10 +11971,10 @@
       <c r="D86" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E86" s="50" t="s">
+      <c r="E86" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F86" s="46"/>
+      <c r="F86" s="28"/>
       <c r="G86" s="1" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
@@ -12051,7 +12004,7 @@
       <c r="Q86" s="17">
         <v>66</v>
       </c>
-      <c r="R86" s="40">
+      <c r="R86" s="22">
         <f t="shared" si="3"/>
         <v>280</v>
       </c>
@@ -12067,10 +12020,10 @@
       <c r="D87" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E87" s="50" t="s">
+      <c r="E87" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F87" s="46"/>
+      <c r="F87" s="28"/>
       <c r="G87" s="1" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
@@ -12100,7 +12053,7 @@
       <c r="Q87" s="17">
         <v>136</v>
       </c>
-      <c r="R87" s="40">
+      <c r="R87" s="22">
         <f t="shared" si="3"/>
         <v>490</v>
       </c>
@@ -12116,10 +12069,10 @@
       <c r="D88" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E88" s="50" t="s">
+      <c r="E88" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F88" s="46"/>
+      <c r="F88" s="28"/>
       <c r="G88" s="1" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
@@ -12149,7 +12102,7 @@
       <c r="Q88" s="17">
         <v>98</v>
       </c>
-      <c r="R88" s="40">
+      <c r="R88" s="22">
         <f t="shared" si="3"/>
         <v>460</v>
       </c>
@@ -12165,10 +12118,10 @@
       <c r="D89" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E89" s="50" t="s">
+      <c r="E89" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F89" s="65" t="s">
+      <c r="F89" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G89" s="1" t="e" vm="64">
@@ -12200,13 +12153,13 @@
       <c r="Q89" s="17">
         <v>78</v>
       </c>
-      <c r="R89" s="40">
+      <c r="R89" s="22">
         <f t="shared" si="3"/>
         <v>530</v>
       </c>
     </row>
     <row r="90" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="39" t="e" vm="98">
+      <c r="B90" s="21" t="e" vm="98">
         <v>#VALUE!</v>
       </c>
       <c r="C90" s="5">
@@ -12216,10 +12169,10 @@
       <c r="D90" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E90" s="72" t="s">
+      <c r="E90" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="F90" s="46"/>
+      <c r="F90" s="28"/>
       <c r="G90" s="1" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
@@ -12249,13 +12202,13 @@
       <c r="Q90" s="17">
         <v>42</v>
       </c>
-      <c r="R90" s="40">
+      <c r="R90" s="22">
         <f t="shared" si="3"/>
         <v>303</v>
       </c>
     </row>
     <row r="91" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="39" t="e" vm="99">
+      <c r="B91" s="21" t="e" vm="99">
         <v>#VALUE!</v>
       </c>
       <c r="C91" s="5">
@@ -12265,10 +12218,10 @@
       <c r="D91" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E91" s="72" t="s">
+      <c r="E91" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="F91" s="46"/>
+      <c r="F91" s="28"/>
       <c r="G91" s="1" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
@@ -12298,13 +12251,13 @@
       <c r="Q91" s="17">
         <v>52</v>
       </c>
-      <c r="R91" s="40">
+      <c r="R91" s="22">
         <f t="shared" si="3"/>
         <v>371</v>
       </c>
     </row>
     <row r="92" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="39" t="e" vm="100">
+      <c r="B92" s="21" t="e" vm="100">
         <v>#VALUE!</v>
       </c>
       <c r="C92" s="5">
@@ -12314,10 +12267,10 @@
       <c r="D92" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E92" s="72" t="s">
+      <c r="E92" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="F92" s="46"/>
+      <c r="F92" s="28"/>
       <c r="G92" s="1" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
@@ -12347,7 +12300,7 @@
       <c r="Q92" s="17">
         <v>75</v>
       </c>
-      <c r="R92" s="40">
+      <c r="R92" s="22">
         <f t="shared" si="3"/>
         <v>552</v>
       </c>
@@ -12363,10 +12316,10 @@
       <c r="D93" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E93" s="54" t="s">
+      <c r="E93" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F93" s="69" t="s">
+      <c r="F93" s="51" t="s">
         <v>30</v>
       </c>
       <c r="G93" s="1" t="e" vm="21">
@@ -12402,7 +12355,7 @@
       <c r="Q93" s="17">
         <v>80</v>
       </c>
-      <c r="R93" s="40">
+      <c r="R93" s="22">
         <f t="shared" si="3"/>
         <v>230</v>
       </c>
@@ -12418,10 +12371,10 @@
       <c r="D94" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E94" s="54" t="s">
+      <c r="E94" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F94" s="69" t="s">
+      <c r="F94" s="51" t="s">
         <v>30</v>
       </c>
       <c r="G94" s="1" t="e" vm="21">
@@ -12457,7 +12410,7 @@
       <c r="Q94" s="17">
         <v>40</v>
       </c>
-      <c r="R94" s="40">
+      <c r="R94" s="22">
         <f t="shared" si="3"/>
         <v>530</v>
       </c>
@@ -12473,10 +12426,10 @@
       <c r="D95" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E95" s="62" t="s">
+      <c r="E95" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F95" s="46"/>
+      <c r="F95" s="28"/>
       <c r="G95" s="1" t="e" vm="74">
         <v>#VALUE!</v>
       </c>
@@ -12506,7 +12459,7 @@
       <c r="Q95" s="17">
         <v>60</v>
       </c>
-      <c r="R95" s="40">
+      <c r="R95" s="22">
         <f t="shared" si="3"/>
         <v>275</v>
       </c>
@@ -12522,10 +12475,10 @@
       <c r="D96" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E96" s="62" t="s">
+      <c r="E96" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F96" s="46"/>
+      <c r="F96" s="28"/>
       <c r="G96" s="1" t="e" vm="74">
         <v>#VALUE!</v>
       </c>
@@ -12555,7 +12508,7 @@
       <c r="Q96" s="17">
         <v>40</v>
       </c>
-      <c r="R96" s="40">
+      <c r="R96" s="22">
         <f t="shared" si="3"/>
         <v>405</v>
       </c>
@@ -12571,10 +12524,10 @@
       <c r="D97" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E97" s="62" t="s">
+      <c r="E97" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F97" s="46"/>
+      <c r="F97" s="28"/>
       <c r="G97" s="1" t="e" vm="74">
         <v>#VALUE!</v>
       </c>
@@ -12604,7 +12557,7 @@
       <c r="Q97" s="17">
         <v>50</v>
       </c>
-      <c r="R97" s="40">
+      <c r="R97" s="22">
         <f t="shared" si="3"/>
         <v>515</v>
       </c>
@@ -12620,10 +12573,10 @@
       <c r="D98" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="E98" s="73" t="s">
+      <c r="E98" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F98" s="67" t="s">
+      <c r="F98" s="49" t="s">
         <v>63</v>
       </c>
       <c r="G98" s="1" t="e" vm="10">
@@ -12659,7 +12612,7 @@
       <c r="Q98" s="17">
         <v>45</v>
       </c>
-      <c r="R98" s="40">
+      <c r="R98" s="22">
         <f t="shared" si="3"/>
         <v>288</v>
       </c>
@@ -12675,10 +12628,10 @@
       <c r="D99" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E99" s="73" t="s">
+      <c r="E99" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F99" s="67" t="s">
+      <c r="F99" s="49" t="s">
         <v>63</v>
       </c>
       <c r="G99" s="1" t="e" vm="10">
@@ -12714,7 +12667,7 @@
       <c r="Q99" s="17">
         <v>73</v>
       </c>
-      <c r="R99" s="40">
+      <c r="R99" s="22">
         <f t="shared" si="3"/>
         <v>482</v>
       </c>
@@ -12730,10 +12683,10 @@
       <c r="D100" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E100" s="57" t="s">
+      <c r="E100" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F100" s="46"/>
+      <c r="F100" s="28"/>
       <c r="G100" s="1" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
@@ -12767,7 +12720,7 @@
       <c r="Q100" s="17">
         <v>32</v>
       </c>
-      <c r="R100" s="40">
+      <c r="R100" s="22">
         <f t="shared" si="3"/>
         <v>310</v>
       </c>
@@ -12783,10 +12736,10 @@
       <c r="D101" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E101" s="57" t="s">
+      <c r="E101" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F101" s="46"/>
+      <c r="F101" s="28"/>
       <c r="G101" s="1" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
@@ -12820,7 +12773,7 @@
       <c r="Q101" s="17">
         <v>42</v>
       </c>
-      <c r="R101" s="40">
+      <c r="R101" s="22">
         <f t="shared" si="3"/>
         <v>480</v>
       </c>
@@ -12836,10 +12789,10 @@
       <c r="D102" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E102" s="50" t="s">
+      <c r="E102" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F102" s="46"/>
+      <c r="F102" s="28"/>
       <c r="G102" s="1" t="e" vm="102">
         <v>#VALUE!</v>
       </c>
@@ -12869,7 +12822,7 @@
       <c r="Q102" s="17">
         <v>40</v>
       </c>
-      <c r="R102" s="40">
+      <c r="R102" s="22">
         <f t="shared" si="3"/>
         <v>305</v>
       </c>
@@ -12885,10 +12838,10 @@
       <c r="D103" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E103" s="50" t="s">
+      <c r="E103" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F103" s="74" t="s">
+      <c r="F103" s="56" t="s">
         <v>66</v>
       </c>
       <c r="G103" s="1" t="e" vm="102">
@@ -12920,7 +12873,7 @@
       <c r="Q103" s="17">
         <v>70</v>
       </c>
-      <c r="R103" s="40">
+      <c r="R103" s="22">
         <f t="shared" si="3"/>
         <v>525</v>
       </c>
@@ -12936,10 +12889,10 @@
       <c r="D104" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E104" s="50" t="s">
+      <c r="E104" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F104" s="46"/>
+      <c r="F104" s="28"/>
       <c r="G104" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -12973,7 +12926,7 @@
       <c r="Q104" s="17">
         <v>44</v>
       </c>
-      <c r="R104" s="40">
+      <c r="R104" s="22">
         <f t="shared" si="3"/>
         <v>330</v>
       </c>
@@ -12989,10 +12942,10 @@
       <c r="D105" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E105" s="50" t="s">
+      <c r="E105" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F105" s="46"/>
+      <c r="F105" s="28"/>
       <c r="G105" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -13026,7 +12979,7 @@
       <c r="Q105" s="17">
         <v>59</v>
       </c>
-      <c r="R105" s="40">
+      <c r="R105" s="22">
         <f t="shared" si="3"/>
         <v>500</v>
       </c>
@@ -13042,10 +12995,10 @@
       <c r="D106" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E106" s="58" t="s">
+      <c r="E106" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F106" s="69" t="s">
+      <c r="F106" s="51" t="s">
         <v>30</v>
       </c>
       <c r="G106" s="1" t="e" vm="49">
@@ -13081,7 +13034,7 @@
       <c r="Q106" s="17">
         <v>30</v>
       </c>
-      <c r="R106" s="40">
+      <c r="R106" s="22">
         <f t="shared" si="3"/>
         <v>320</v>
       </c>
@@ -13097,10 +13050,10 @@
       <c r="D107" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="E107" s="58" t="s">
+      <c r="E107" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F107" s="61" t="s">
+      <c r="F107" s="43" t="s">
         <v>69</v>
       </c>
       <c r="G107" s="1" t="e" vm="49">
@@ -13136,7 +13089,7 @@
       <c r="Q107" s="17">
         <v>44</v>
       </c>
-      <c r="R107" s="40">
+      <c r="R107" s="22">
         <f t="shared" si="3"/>
         <v>494</v>
       </c>
@@ -13152,10 +13105,10 @@
       <c r="D108" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E108" s="56" t="s">
+      <c r="E108" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F108" s="46"/>
+      <c r="F108" s="28"/>
       <c r="G108" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -13185,7 +13138,7 @@
       <c r="Q108" s="17">
         <v>65</v>
       </c>
-      <c r="R108" s="40">
+      <c r="R108" s="22">
         <f t="shared" si="3"/>
         <v>292</v>
       </c>
@@ -13201,10 +13154,10 @@
       <c r="D109" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E109" s="56" t="s">
+      <c r="E109" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F109" s="55" t="s">
+      <c r="F109" s="37" t="s">
         <v>48</v>
       </c>
       <c r="G109" s="1" t="e" vm="3">
@@ -13236,7 +13189,7 @@
       <c r="Q109" s="17">
         <v>74</v>
       </c>
-      <c r="R109" s="40">
+      <c r="R109" s="22">
         <f t="shared" si="3"/>
         <v>351</v>
       </c>
@@ -13252,10 +13205,10 @@
       <c r="D110" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E110" s="56" t="s">
+      <c r="E110" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F110" s="55" t="s">
+      <c r="F110" s="37" t="s">
         <v>48</v>
       </c>
       <c r="G110" s="1" t="e" vm="3">
@@ -13287,7 +13240,7 @@
       <c r="Q110" s="17">
         <v>92</v>
       </c>
-      <c r="R110" s="40">
+      <c r="R110" s="22">
         <f t="shared" si="3"/>
         <v>519</v>
       </c>
@@ -13303,10 +13256,10 @@
       <c r="D111" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E111" s="56" t="s">
+      <c r="E111" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F111" s="46"/>
+      <c r="F111" s="28"/>
       <c r="G111" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -13340,7 +13293,7 @@
       <c r="Q111" s="17">
         <v>46</v>
       </c>
-      <c r="R111" s="40">
+      <c r="R111" s="22">
         <f t="shared" si="3"/>
         <v>315</v>
       </c>
@@ -13356,10 +13309,10 @@
       <c r="D112" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E112" s="56" t="s">
+      <c r="E112" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F112" s="46"/>
+      <c r="F112" s="28"/>
       <c r="G112" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -13393,7 +13346,7 @@
       <c r="Q112" s="17">
         <v>71</v>
       </c>
-      <c r="R112" s="40">
+      <c r="R112" s="22">
         <f t="shared" si="3"/>
         <v>510</v>
       </c>
@@ -13409,10 +13362,10 @@
       <c r="D113" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E113" s="73" t="s">
+      <c r="E113" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F113" s="49" t="s">
+      <c r="F113" s="31" t="s">
         <v>27</v>
       </c>
       <c r="G113" s="1" t="e" vm="3">
@@ -13448,7 +13401,7 @@
       <c r="Q113" s="17">
         <v>48</v>
       </c>
-      <c r="R113" s="40">
+      <c r="R113" s="22">
         <f t="shared" si="3"/>
         <v>348</v>
       </c>
@@ -13464,10 +13417,10 @@
       <c r="D114" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E114" s="73" t="s">
+      <c r="E114" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F114" s="49" t="s">
+      <c r="F114" s="31" t="s">
         <v>27</v>
       </c>
       <c r="G114" s="1" t="e" vm="3">
@@ -13503,7 +13456,7 @@
       <c r="Q114" s="17">
         <v>58</v>
       </c>
-      <c r="R114" s="40">
+      <c r="R114" s="22">
         <f t="shared" si="3"/>
         <v>488</v>
       </c>
@@ -13519,10 +13472,10 @@
       <c r="D115" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E115" s="68" t="s">
+      <c r="E115" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F115" s="75" t="s">
+      <c r="F115" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G115" s="1" t="e" vm="74">
@@ -13554,7 +13507,7 @@
       <c r="Q115" s="17">
         <v>20</v>
       </c>
-      <c r="R115" s="40">
+      <c r="R115" s="22">
         <f t="shared" si="3"/>
         <v>275</v>
       </c>
@@ -13570,10 +13523,10 @@
       <c r="D116" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E116" s="68" t="s">
+      <c r="E116" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F116" s="75" t="s">
+      <c r="F116" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G116" s="1" t="e" vm="74">
@@ -13605,7 +13558,7 @@
       <c r="Q116" s="17">
         <v>55</v>
       </c>
-      <c r="R116" s="40">
+      <c r="R116" s="22">
         <f t="shared" si="3"/>
         <v>370</v>
       </c>
@@ -13621,10 +13574,10 @@
       <c r="D117" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E117" s="68" t="s">
+      <c r="E117" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F117" s="75" t="s">
+      <c r="F117" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G117" s="1" t="e" vm="74">
@@ -13656,7 +13609,7 @@
       <c r="Q117" s="17">
         <v>80</v>
       </c>
-      <c r="R117" s="40">
+      <c r="R117" s="22">
         <f t="shared" si="3"/>
         <v>520</v>
       </c>
@@ -13672,10 +13625,10 @@
       <c r="D118" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E118" s="54" t="s">
+      <c r="E118" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F118" s="76" t="s">
+      <c r="F118" s="58" t="s">
         <v>68</v>
       </c>
       <c r="G118" s="1" t="e" vm="21">
@@ -13707,7 +13660,7 @@
       <c r="Q118" s="17">
         <v>57</v>
       </c>
-      <c r="R118" s="40">
+      <c r="R118" s="22">
         <f t="shared" si="3"/>
         <v>260</v>
       </c>
@@ -13723,10 +13676,10 @@
       <c r="D119" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E119" s="54" t="s">
+      <c r="E119" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F119" s="76" t="s">
+      <c r="F119" s="58" t="s">
         <v>68</v>
       </c>
       <c r="G119" s="1" t="e" vm="21">
@@ -13758,7 +13711,7 @@
       <c r="Q119" s="17">
         <v>47</v>
       </c>
-      <c r="R119" s="40">
+      <c r="R119" s="22">
         <f t="shared" si="3"/>
         <v>360</v>
       </c>
@@ -13774,10 +13727,10 @@
       <c r="D120" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E120" s="54" t="s">
+      <c r="E120" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F120" s="76" t="s">
+      <c r="F120" s="58" t="s">
         <v>68</v>
       </c>
       <c r="G120" s="1" t="e" vm="21">
@@ -13809,7 +13762,7 @@
       <c r="Q120" s="17">
         <v>112</v>
       </c>
-      <c r="R120" s="40">
+      <c r="R120" s="22">
         <f t="shared" si="3"/>
         <v>485</v>
       </c>
@@ -13825,10 +13778,10 @@
       <c r="D121" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E121" s="54" t="s">
+      <c r="E121" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F121" s="46"/>
+      <c r="F121" s="28"/>
       <c r="G121" s="1" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
@@ -13858,7 +13811,7 @@
       <c r="Q121" s="17">
         <v>46</v>
       </c>
-      <c r="R121" s="40">
+      <c r="R121" s="22">
         <f t="shared" si="3"/>
         <v>300</v>
       </c>
@@ -13874,10 +13827,10 @@
       <c r="D122" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E122" s="54" t="s">
+      <c r="E122" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F122" s="77" t="s">
+      <c r="F122" s="59" t="s">
         <v>67</v>
       </c>
       <c r="G122" s="1" t="e" vm="21">
@@ -13909,7 +13862,7 @@
       <c r="Q122" s="17">
         <v>36</v>
       </c>
-      <c r="R122" s="40">
+      <c r="R122" s="22">
         <f t="shared" si="3"/>
         <v>400</v>
       </c>
@@ -13925,10 +13878,10 @@
       <c r="D123" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E123" s="54" t="s">
+      <c r="E123" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F123" s="77" t="s">
+      <c r="F123" s="59" t="s">
         <v>67</v>
       </c>
       <c r="G123" s="1" t="e" vm="21">
@@ -13960,7 +13913,7 @@
       <c r="Q123" s="17">
         <v>43</v>
       </c>
-      <c r="R123" s="40">
+      <c r="R123" s="22">
         <f t="shared" si="3"/>
         <v>500</v>
       </c>
@@ -13976,10 +13929,10 @@
       <c r="D124" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E124" s="45" t="s">
+      <c r="E124" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F124" s="75" t="s">
+      <c r="F124" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G124" s="1" t="e" vm="2">
@@ -14011,7 +13964,7 @@
       <c r="Q124" s="17">
         <v>50</v>
       </c>
-      <c r="R124" s="40">
+      <c r="R124" s="22">
         <f t="shared" si="3"/>
         <v>304</v>
       </c>
@@ -14027,10 +13980,10 @@
       <c r="D125" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E125" s="45" t="s">
+      <c r="E125" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F125" s="75" t="s">
+      <c r="F125" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G125" s="1" t="e" vm="2">
@@ -14062,7 +14015,7 @@
       <c r="Q125" s="17">
         <v>75</v>
       </c>
-      <c r="R125" s="40">
+      <c r="R125" s="22">
         <f t="shared" si="3"/>
         <v>486</v>
       </c>
@@ -14078,10 +14031,10 @@
       <c r="D126" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E126" s="71" t="s">
+      <c r="E126" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="F126" s="46"/>
+      <c r="F126" s="28"/>
       <c r="G126" s="1" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
@@ -14111,7 +14064,7 @@
       <c r="Q126" s="17">
         <v>75</v>
       </c>
-      <c r="R126" s="40">
+      <c r="R126" s="22">
         <f t="shared" si="3"/>
         <v>255</v>
       </c>
@@ -14127,10 +14080,10 @@
       <c r="D127" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E127" s="71" t="s">
+      <c r="E127" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="F127" s="46"/>
+      <c r="F127" s="28"/>
       <c r="G127" s="1" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
@@ -14160,7 +14113,7 @@
       <c r="Q127" s="17">
         <v>105</v>
       </c>
-      <c r="R127" s="40">
+      <c r="R127" s="22">
         <f t="shared" si="3"/>
         <v>481</v>
       </c>
@@ -14176,10 +14129,10 @@
       <c r="D128" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E128" s="56" t="s">
+      <c r="E128" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F128" s="66" t="s">
+      <c r="F128" s="48" t="s">
         <v>64</v>
       </c>
       <c r="G128" s="1" t="e" vm="138">
@@ -14215,7 +14168,7 @@
       <c r="Q128" s="17">
         <v>25</v>
       </c>
-      <c r="R128" s="40">
+      <c r="R128" s="22">
         <f t="shared" si="3"/>
         <v>345</v>
       </c>
@@ -14231,10 +14184,10 @@
       <c r="D129" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E129" s="56" t="s">
+      <c r="E129" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F129" s="66" t="s">
+      <c r="F129" s="48" t="s">
         <v>64</v>
       </c>
       <c r="G129" s="1" t="e" vm="138">
@@ -14270,7 +14223,7 @@
       <c r="Q129" s="17">
         <v>40</v>
       </c>
-      <c r="R129" s="40">
+      <c r="R129" s="22">
         <f t="shared" si="3"/>
         <v>485</v>
       </c>
@@ -14286,10 +14239,10 @@
       <c r="D130" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E130" s="56" t="s">
+      <c r="E130" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F130" s="66" t="s">
+      <c r="F130" s="48" t="s">
         <v>64</v>
       </c>
       <c r="G130" s="1" t="e" vm="138">
@@ -14325,7 +14278,7 @@
       <c r="Q130" s="17">
         <v>40</v>
       </c>
-      <c r="R130" s="40">
+      <c r="R130" s="22">
         <f t="shared" si="3"/>
         <v>535</v>
       </c>
@@ -14341,10 +14294,10 @@
       <c r="D131" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E131" s="50" t="s">
+      <c r="E131" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F131" s="77" t="s">
+      <c r="F131" s="59" t="s">
         <v>67</v>
       </c>
       <c r="G131" s="1" t="e" vm="64">
@@ -14374,7 +14327,7 @@
       <c r="Q131" s="17">
         <v>67</v>
       </c>
-      <c r="R131" s="40">
+      <c r="R131" s="22">
         <f t="shared" si="3"/>
         <v>330</v>
       </c>
@@ -14390,10 +14343,10 @@
       <c r="D132" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E132" s="50" t="s">
+      <c r="E132" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F132" s="77" t="s">
+      <c r="F132" s="59" t="s">
         <v>67</v>
       </c>
       <c r="G132" s="1" t="e" vm="64">
@@ -14423,7 +14376,7 @@
       <c r="Q132" s="17">
         <v>67</v>
       </c>
-      <c r="R132" s="40">
+      <c r="R132" s="22">
         <f t="shared" si="3"/>
         <v>460</v>
       </c>
@@ -14439,10 +14392,10 @@
       <c r="D133" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E133" s="56" t="s">
+      <c r="E133" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F133" s="46"/>
+      <c r="F133" s="28"/>
       <c r="G133" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -14472,7 +14425,7 @@
       <c r="Q133" s="17">
         <v>68</v>
       </c>
-      <c r="R133" s="40">
+      <c r="R133" s="22">
         <f t="shared" si="3"/>
         <v>328</v>
       </c>
@@ -14488,10 +14441,10 @@
       <c r="D134" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E134" s="56" t="s">
+      <c r="E134" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F134" s="51" t="s">
+      <c r="F134" s="33" t="s">
         <v>34</v>
       </c>
       <c r="G134" s="1" t="e" vm="3">
@@ -14523,7 +14476,7 @@
       <c r="Q134" s="17">
         <v>88</v>
       </c>
-      <c r="R134" s="40">
+      <c r="R134" s="22">
         <f t="shared" ref="R134:R197" si="6">SUM(L134:Q134)</f>
         <v>508</v>
       </c>
@@ -14539,10 +14492,10 @@
       <c r="D135" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E135" s="41" t="s">
+      <c r="E135" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F135" s="78"/>
+      <c r="F135" s="60"/>
       <c r="G135" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -14572,7 +14525,7 @@
       <c r="Q135" s="17">
         <v>30</v>
       </c>
-      <c r="R135" s="40">
+      <c r="R135" s="22">
         <f t="shared" si="6"/>
         <v>240</v>
       </c>
@@ -14588,10 +14541,10 @@
       <c r="D136" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E136" s="41" t="s">
+      <c r="E136" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F136" s="75" t="s">
+      <c r="F136" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G136" s="1" t="e" vm="34">
@@ -14623,7 +14576,7 @@
       <c r="Q136" s="17">
         <v>50</v>
       </c>
-      <c r="R136" s="40">
+      <c r="R136" s="22">
         <f t="shared" si="6"/>
         <v>410</v>
       </c>
@@ -14639,10 +14592,10 @@
       <c r="D137" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E137" s="41" t="s">
+      <c r="E137" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F137" s="75" t="s">
+      <c r="F137" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G137" s="1" t="e" vm="34">
@@ -14674,7 +14627,7 @@
       <c r="Q137" s="17">
         <v>30</v>
       </c>
-      <c r="R137" s="40">
+      <c r="R137" s="22">
         <f t="shared" si="6"/>
         <v>510</v>
       </c>
@@ -14690,10 +14643,10 @@
       <c r="D138" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E138" s="70" t="s">
+      <c r="E138" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F138" s="66" t="s">
+      <c r="F138" s="48" t="s">
         <v>64</v>
       </c>
       <c r="G138" s="1" t="e" vm="138">
@@ -14725,7 +14678,7 @@
       <c r="Q138" s="17">
         <v>30</v>
       </c>
-      <c r="R138" s="40">
+      <c r="R138" s="22">
         <f t="shared" si="6"/>
         <v>330</v>
       </c>
@@ -14741,10 +14694,10 @@
       <c r="D139" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E139" s="70" t="s">
+      <c r="E139" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F139" s="66" t="s">
+      <c r="F139" s="48" t="s">
         <v>64</v>
       </c>
       <c r="G139" s="1" t="e" vm="138">
@@ -14776,7 +14729,7 @@
       <c r="Q139" s="17">
         <v>40</v>
       </c>
-      <c r="R139" s="40">
+      <c r="R139" s="22">
         <f t="shared" si="6"/>
         <v>430</v>
       </c>
@@ -14792,10 +14745,10 @@
       <c r="D140" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="E140" s="70" t="s">
+      <c r="E140" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F140" s="66" t="s">
+      <c r="F140" s="48" t="s">
         <v>64</v>
       </c>
       <c r="G140" s="1" t="e" vm="138">
@@ -14827,7 +14780,7 @@
       <c r="Q140" s="17">
         <v>50</v>
       </c>
-      <c r="R140" s="40">
+      <c r="R140" s="22">
         <f t="shared" si="6"/>
         <v>530</v>
       </c>
@@ -14843,10 +14796,10 @@
       <c r="D141" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E141" s="72" t="s">
+      <c r="E141" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="F141" s="51" t="s">
+      <c r="F141" s="33" t="s">
         <v>34</v>
       </c>
       <c r="G141" s="1" t="e" vm="31">
@@ -14878,7 +14831,7 @@
       <c r="Q141" s="17">
         <v>58</v>
       </c>
-      <c r="R141" s="40">
+      <c r="R141" s="22">
         <f t="shared" si="6"/>
         <v>297</v>
       </c>
@@ -14894,10 +14847,10 @@
       <c r="D142" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E142" s="72" t="s">
+      <c r="E142" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="F142" s="51" t="s">
+      <c r="F142" s="33" t="s">
         <v>34</v>
       </c>
       <c r="G142" s="1" t="e" vm="31">
@@ -14929,7 +14882,7 @@
       <c r="Q142" s="17">
         <v>78</v>
       </c>
-      <c r="R142" s="40">
+      <c r="R142" s="22">
         <f t="shared" si="6"/>
         <v>380</v>
       </c>
@@ -14945,10 +14898,10 @@
       <c r="D143" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E143" s="72" t="s">
+      <c r="E143" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="F143" s="51" t="s">
+      <c r="F143" s="33" t="s">
         <v>34</v>
       </c>
       <c r="G143" s="1" t="e" vm="31">
@@ -14980,7 +14933,7 @@
       <c r="Q143" s="17">
         <v>94</v>
       </c>
-      <c r="R143" s="40">
+      <c r="R143" s="22">
         <f t="shared" si="6"/>
         <v>506</v>
       </c>
@@ -14996,10 +14949,10 @@
       <c r="D144" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E144" s="41" t="s">
+      <c r="E144" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F144" s="42" t="s">
+      <c r="F144" s="24" t="s">
         <v>60</v>
       </c>
       <c r="G144" s="1" t="e" vm="31">
@@ -15035,7 +14988,7 @@
       <c r="Q144" s="17">
         <v>50</v>
       </c>
-      <c r="R144" s="40">
+      <c r="R144" s="22">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
@@ -15051,10 +15004,10 @@
       <c r="D145" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E145" s="58" t="s">
+      <c r="E145" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F145" s="69" t="s">
+      <c r="F145" s="51" t="s">
         <v>30</v>
       </c>
       <c r="G145" s="1" t="e" vm="10">
@@ -15086,7 +15039,7 @@
       <c r="Q145" s="17">
         <v>45</v>
       </c>
-      <c r="R145" s="40">
+      <c r="R145" s="22">
         <f t="shared" si="6"/>
         <v>305</v>
       </c>
@@ -15102,10 +15055,10 @@
       <c r="D146" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E146" s="58" t="s">
+      <c r="E146" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F146" s="69" t="s">
+      <c r="F146" s="51" t="s">
         <v>30</v>
       </c>
       <c r="G146" s="1" t="e" vm="10">
@@ -15137,7 +15090,7 @@
       <c r="Q146" s="17">
         <v>35</v>
       </c>
-      <c r="R146" s="40">
+      <c r="R146" s="22">
         <f t="shared" si="6"/>
         <v>495</v>
       </c>
@@ -15153,10 +15106,10 @@
       <c r="D147" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E147" s="58" t="s">
+      <c r="E147" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F147" s="75" t="s">
+      <c r="F147" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G147" s="1" t="e" vm="138">
@@ -15171,7 +15124,7 @@
       <c r="J147" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="K147" s="79" t="s">
+      <c r="K147" s="61" t="s">
         <v>224</v>
       </c>
       <c r="L147" s="7">
@@ -15192,7 +15145,7 @@
       <c r="Q147" s="17">
         <v>77</v>
       </c>
-      <c r="R147" s="40">
+      <c r="R147" s="22">
         <f t="shared" si="6"/>
         <v>320</v>
       </c>
@@ -15208,10 +15161,10 @@
       <c r="D148" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="E148" s="58" t="s">
+      <c r="E148" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F148" s="75" t="s">
+      <c r="F148" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G148" s="1" t="e" vm="138">
@@ -15247,7 +15200,7 @@
       <c r="Q148" s="17">
         <v>117</v>
       </c>
-      <c r="R148" s="40">
+      <c r="R148" s="22">
         <f t="shared" si="6"/>
         <v>480</v>
       </c>
@@ -15263,10 +15216,10 @@
       <c r="D149" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E149" s="56" t="s">
+      <c r="E149" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F149" s="65" t="s">
+      <c r="F149" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G149" s="1" t="e" vm="34">
@@ -15298,7 +15251,7 @@
       <c r="Q149" s="17">
         <v>35</v>
       </c>
-      <c r="R149" s="40">
+      <c r="R149" s="22">
         <f t="shared" si="6"/>
         <v>303</v>
       </c>
@@ -15314,10 +15267,10 @@
       <c r="D150" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E150" s="56" t="s">
+      <c r="E150" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="F150" s="65" t="s">
+      <c r="F150" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G150" s="1" t="e" vm="34">
@@ -15349,7 +15302,7 @@
       <c r="Q150" s="17">
         <v>55</v>
       </c>
-      <c r="R150" s="40">
+      <c r="R150" s="22">
         <f t="shared" si="6"/>
         <v>483</v>
       </c>
@@ -15365,10 +15318,10 @@
       <c r="D151" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="E151" s="73" t="s">
+      <c r="E151" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F151" s="51" t="s">
+      <c r="F151" s="33" t="s">
         <v>34</v>
       </c>
       <c r="G151" s="1" t="e" vm="26">
@@ -15400,7 +15353,7 @@
       <c r="Q151" s="17">
         <v>60</v>
       </c>
-      <c r="R151" s="40">
+      <c r="R151" s="22">
         <f t="shared" si="6"/>
         <v>340</v>
       </c>
@@ -15416,10 +15369,10 @@
       <c r="D152" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E152" s="73" t="s">
+      <c r="E152" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F152" s="51" t="s">
+      <c r="F152" s="33" t="s">
         <v>34</v>
       </c>
       <c r="G152" s="1" t="e" vm="26">
@@ -15451,7 +15404,7 @@
       <c r="Q152" s="17">
         <v>70</v>
       </c>
-      <c r="R152" s="40">
+      <c r="R152" s="22">
         <f t="shared" si="6"/>
         <v>490</v>
       </c>
@@ -15467,10 +15420,10 @@
       <c r="D153" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E153" s="73" t="s">
+      <c r="E153" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F153" s="51" t="s">
+      <c r="F153" s="33" t="s">
         <v>34</v>
       </c>
       <c r="G153" s="1" t="e" vm="26">
@@ -15502,7 +15455,7 @@
       <c r="Q153" s="17">
         <v>50</v>
       </c>
-      <c r="R153" s="40">
+      <c r="R153" s="22">
         <f t="shared" si="6"/>
         <v>550</v>
       </c>
@@ -15518,10 +15471,10 @@
       <c r="D154" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E154" s="68" t="s">
+      <c r="E154" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F154" s="46"/>
+      <c r="F154" s="28"/>
       <c r="G154" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -15555,7 +15508,7 @@
       <c r="Q154" s="17">
         <v>30</v>
       </c>
-      <c r="R154" s="40">
+      <c r="R154" s="22">
         <f t="shared" si="6"/>
         <v>303</v>
       </c>
@@ -15571,10 +15524,10 @@
       <c r="D155" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E155" s="68" t="s">
+      <c r="E155" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F155" s="46"/>
+      <c r="F155" s="28"/>
       <c r="G155" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -15608,7 +15561,7 @@
       <c r="Q155" s="17">
         <v>30</v>
       </c>
-      <c r="R155" s="40">
+      <c r="R155" s="22">
         <f t="shared" si="6"/>
         <v>483</v>
       </c>
@@ -15624,10 +15577,10 @@
       <c r="D156" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E156" s="68" t="s">
+      <c r="E156" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F156" s="80" t="s">
+      <c r="F156" s="62" t="s">
         <v>16</v>
       </c>
       <c r="G156" s="1" t="e" vm="34">
@@ -15659,7 +15612,7 @@
       <c r="Q156" s="17">
         <v>40</v>
       </c>
-      <c r="R156" s="40">
+      <c r="R156" s="22">
         <f t="shared" si="6"/>
         <v>517</v>
       </c>
@@ -15675,10 +15628,10 @@
       <c r="D157" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E157" s="50" t="s">
+      <c r="E157" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F157" s="74" t="s">
+      <c r="F157" s="56" t="s">
         <v>66</v>
       </c>
       <c r="G157" s="1" t="e" vm="10">
@@ -15714,7 +15667,7 @@
       <c r="Q157" s="17">
         <v>25</v>
       </c>
-      <c r="R157" s="40">
+      <c r="R157" s="22">
         <f t="shared" si="6"/>
         <v>290</v>
       </c>
@@ -15730,10 +15683,10 @@
       <c r="D158" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E158" s="50" t="s">
+      <c r="E158" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F158" s="74" t="s">
+      <c r="F158" s="56" t="s">
         <v>66</v>
       </c>
       <c r="G158" s="1" t="e" vm="10">
@@ -15769,7 +15722,7 @@
       <c r="Q158" s="17">
         <v>45</v>
       </c>
-      <c r="R158" s="40">
+      <c r="R158" s="22">
         <f t="shared" si="6"/>
         <v>410</v>
       </c>
@@ -15785,10 +15738,10 @@
       <c r="D159" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E159" s="50" t="s">
+      <c r="E159" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F159" s="74" t="s">
+      <c r="F159" s="56" t="s">
         <v>66</v>
       </c>
       <c r="G159" s="1" t="e" vm="10">
@@ -15824,7 +15777,7 @@
       <c r="Q159" s="17">
         <v>65</v>
       </c>
-      <c r="R159" s="40">
+      <c r="R159" s="22">
         <f t="shared" si="6"/>
         <v>530</v>
       </c>
@@ -15840,10 +15793,10 @@
       <c r="D160" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E160" s="57" t="s">
+      <c r="E160" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F160" s="46"/>
+      <c r="F160" s="28"/>
       <c r="G160" s="1" t="e" vm="102">
         <v>#VALUE!</v>
       </c>
@@ -15873,7 +15826,7 @@
       <c r="Q160" s="17">
         <v>63</v>
       </c>
-      <c r="R160" s="40">
+      <c r="R160" s="22">
         <f t="shared" si="6"/>
         <v>338</v>
       </c>
@@ -15889,10 +15842,10 @@
       <c r="D161" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E161" s="57" t="s">
+      <c r="E161" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F161" s="74" t="s">
+      <c r="F161" s="56" t="s">
         <v>66</v>
       </c>
       <c r="G161" s="1" t="e" vm="102">
@@ -15924,7 +15877,7 @@
       <c r="Q161" s="17">
         <v>43</v>
       </c>
-      <c r="R161" s="40">
+      <c r="R161" s="22">
         <f t="shared" si="6"/>
         <v>478</v>
       </c>
@@ -15940,10 +15893,10 @@
       <c r="D162" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E162" s="62" t="s">
+      <c r="E162" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F162" s="59" t="s">
+      <c r="F162" s="41" t="s">
         <v>37</v>
       </c>
       <c r="G162" s="1" t="e" vm="138">
@@ -15979,7 +15932,7 @@
       <c r="Q162" s="17">
         <v>70</v>
       </c>
-      <c r="R162" s="40">
+      <c r="R162" s="22">
         <f t="shared" si="6"/>
         <v>289</v>
       </c>
@@ -15995,10 +15948,10 @@
       <c r="D163" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E163" s="62" t="s">
+      <c r="E163" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F163" s="59" t="s">
+      <c r="F163" s="41" t="s">
         <v>37</v>
       </c>
       <c r="G163" s="1" t="e" vm="138">
@@ -16034,7 +15987,7 @@
       <c r="Q163" s="17">
         <v>109</v>
       </c>
-      <c r="R163" s="40">
+      <c r="R163" s="22">
         <f t="shared" si="6"/>
         <v>481</v>
       </c>
@@ -16050,10 +16003,10 @@
       <c r="D164" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E164" s="50" t="s">
+      <c r="E164" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F164" s="46"/>
+      <c r="F164" s="28"/>
       <c r="G164" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -16087,7 +16040,7 @@
       <c r="Q164" s="17">
         <v>75</v>
       </c>
-      <c r="R164" s="40">
+      <c r="R164" s="22">
         <f t="shared" si="6"/>
         <v>315</v>
       </c>
@@ -16103,10 +16056,10 @@
       <c r="D165" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E165" s="50" t="s">
+      <c r="E165" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F165" s="78"/>
+      <c r="F165" s="60"/>
       <c r="G165" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -16140,7 +16093,7 @@
       <c r="Q165" s="17">
         <v>100</v>
       </c>
-      <c r="R165" s="40">
+      <c r="R165" s="22">
         <f t="shared" si="6"/>
         <v>457</v>
       </c>
@@ -16156,10 +16109,10 @@
       <c r="D166" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="E166" s="50" t="s">
+      <c r="E166" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F166" s="65" t="s">
+      <c r="F166" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G166" s="1" t="e" vm="74">
@@ -16191,7 +16144,7 @@
       <c r="Q166" s="17">
         <v>40</v>
       </c>
-      <c r="R166" s="40">
+      <c r="R166" s="22">
         <f t="shared" si="6"/>
         <v>335</v>
       </c>
@@ -16207,10 +16160,10 @@
       <c r="D167" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E167" s="50" t="s">
+      <c r="E167" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F167" s="65" t="s">
+      <c r="F167" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G167" s="1" t="e" vm="74">
@@ -16242,7 +16195,7 @@
       <c r="Q167" s="17">
         <v>60</v>
       </c>
-      <c r="R167" s="40">
+      <c r="R167" s="22">
         <f t="shared" si="6"/>
         <v>480</v>
       </c>
@@ -16258,10 +16211,10 @@
       <c r="D168" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E168" s="50" t="s">
+      <c r="E168" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F168" s="46"/>
+      <c r="F168" s="28"/>
       <c r="G168" s="1" t="e" vm="102">
         <v>#VALUE!</v>
       </c>
@@ -16291,7 +16244,7 @@
       <c r="Q168" s="17">
         <v>85</v>
       </c>
-      <c r="R168" s="40">
+      <c r="R168" s="22">
         <f t="shared" si="6"/>
         <v>340</v>
       </c>
@@ -16307,10 +16260,10 @@
       <c r="D169" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E169" s="50" t="s">
+      <c r="E169" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F169" s="67" t="s">
+      <c r="F169" s="49" t="s">
         <v>63</v>
       </c>
       <c r="G169" s="1" t="e" vm="102">
@@ -16342,7 +16295,7 @@
       <c r="Q169" s="17">
         <v>115</v>
       </c>
-      <c r="R169" s="40">
+      <c r="R169" s="22">
         <f t="shared" si="6"/>
         <v>520</v>
       </c>
@@ -16358,10 +16311,10 @@
       <c r="D170" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E170" s="41" t="s">
+      <c r="E170" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F170" s="83" t="s">
+      <c r="F170" s="65" t="s">
         <v>50</v>
       </c>
       <c r="G170" s="1" t="e" vm="138">
@@ -16391,7 +16344,7 @@
       <c r="Q170" s="17">
         <v>41</v>
       </c>
-      <c r="R170" s="40">
+      <c r="R170" s="22">
         <f t="shared" si="6"/>
         <v>300</v>
       </c>
@@ -16407,10 +16360,10 @@
       <c r="D171" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E171" s="41" t="s">
+      <c r="E171" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F171" s="83" t="s">
+      <c r="F171" s="65" t="s">
         <v>50</v>
       </c>
       <c r="G171" s="1" t="e" vm="138">
@@ -16440,7 +16393,7 @@
       <c r="Q171" s="17">
         <v>51</v>
       </c>
-      <c r="R171" s="40">
+      <c r="R171" s="22">
         <f t="shared" si="6"/>
         <v>410</v>
       </c>
@@ -16456,10 +16409,10 @@
       <c r="D172" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E172" s="41" t="s">
+      <c r="E172" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F172" s="55" t="s">
+      <c r="F172" s="37" t="s">
         <v>48</v>
       </c>
       <c r="G172" s="1" t="e" vm="138">
@@ -16489,7 +16442,7 @@
       <c r="Q172" s="17">
         <v>61</v>
       </c>
-      <c r="R172" s="40">
+      <c r="R172" s="22">
         <f t="shared" si="6"/>
         <v>600</v>
       </c>
@@ -16505,10 +16458,10 @@
       <c r="D173" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="E173" s="70" t="s">
+      <c r="E173" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F173" s="46"/>
+      <c r="F173" s="28"/>
       <c r="G173" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -16542,7 +16495,7 @@
       <c r="Q173" s="17">
         <v>40</v>
       </c>
-      <c r="R173" s="40">
+      <c r="R173" s="22">
         <f t="shared" si="6"/>
         <v>330</v>
       </c>
@@ -16558,10 +16511,10 @@
       <c r="D174" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E174" s="70" t="s">
+      <c r="E174" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F174" s="46"/>
+      <c r="F174" s="28"/>
       <c r="G174" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -16595,7 +16548,7 @@
       <c r="Q174" s="17">
         <v>30</v>
       </c>
-      <c r="R174" s="40">
+      <c r="R174" s="22">
         <f t="shared" si="6"/>
         <v>500</v>
       </c>
@@ -16611,10 +16564,10 @@
       <c r="D175" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E175" s="73" t="s">
+      <c r="E175" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F175" s="48"/>
+      <c r="F175" s="30"/>
       <c r="G175" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -16642,7 +16595,7 @@
       <c r="Q175" s="17">
         <v>75</v>
       </c>
-      <c r="R175" s="40">
+      <c r="R175" s="22">
         <f t="shared" si="6"/>
         <v>465</v>
       </c>
@@ -16658,10 +16611,10 @@
       <c r="D176" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E176" s="72" t="s">
+      <c r="E176" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="F176" s="48"/>
+      <c r="F176" s="30"/>
       <c r="G176" s="1" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -16689,7 +16642,7 @@
       <c r="Q176" s="17">
         <v>100</v>
       </c>
-      <c r="R176" s="40">
+      <c r="R176" s="22">
         <f t="shared" si="6"/>
         <v>485</v>
       </c>
@@ -16705,10 +16658,10 @@
       <c r="D177" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="E177" s="81" t="s">
+      <c r="E177" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F177" s="46"/>
+      <c r="F177" s="28"/>
       <c r="G177" s="1" t="e" vm="49">
         <v>#VALUE!</v>
       </c>
@@ -16738,7 +16691,7 @@
       <c r="Q177" s="17">
         <v>45</v>
       </c>
-      <c r="R177" s="40">
+      <c r="R177" s="22">
         <f t="shared" si="6"/>
         <v>300</v>
       </c>
@@ -16754,10 +16707,10 @@
       <c r="D178" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E178" s="81" t="s">
+      <c r="E178" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F178" s="49" t="s">
+      <c r="F178" s="31" t="s">
         <v>27</v>
       </c>
       <c r="G178" s="1" t="e" vm="49">
@@ -16789,7 +16742,7 @@
       <c r="Q178" s="17">
         <v>65</v>
       </c>
-      <c r="R178" s="40">
+      <c r="R178" s="22">
         <f t="shared" si="6"/>
         <v>420</v>
       </c>
@@ -16805,10 +16758,10 @@
       <c r="D179" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E179" s="81" t="s">
+      <c r="E179" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F179" s="49" t="s">
+      <c r="F179" s="31" t="s">
         <v>27</v>
       </c>
       <c r="G179" s="1" t="e" vm="49">
@@ -16840,7 +16793,7 @@
       <c r="Q179" s="17">
         <v>85</v>
       </c>
-      <c r="R179" s="40">
+      <c r="R179" s="22">
         <f t="shared" si="6"/>
         <v>600</v>
       </c>
@@ -16856,10 +16809,10 @@
       <c r="D180" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E180" s="58" t="s">
+      <c r="E180" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F180" s="48"/>
+      <c r="F180" s="30"/>
       <c r="G180" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -16887,7 +16840,7 @@
       <c r="Q180" s="17">
         <v>65</v>
       </c>
-      <c r="R180" s="40">
+      <c r="R180" s="22">
         <f t="shared" si="6"/>
         <v>329</v>
       </c>
@@ -16903,10 +16856,10 @@
       <c r="D181" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E181" s="58" t="s">
+      <c r="E181" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F181" s="48"/>
+      <c r="F181" s="30"/>
       <c r="G181" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -16934,7 +16887,7 @@
       <c r="Q181" s="17">
         <v>75</v>
       </c>
-      <c r="R181" s="40">
+      <c r="R181" s="22">
         <f t="shared" si="6"/>
         <v>474</v>
       </c>
@@ -16950,10 +16903,10 @@
       <c r="D182" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E182" s="73" t="s">
+      <c r="E182" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F182" s="63" t="s">
+      <c r="F182" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G182" s="1" t="e" vm="17">
@@ -16983,7 +16936,7 @@
       <c r="Q182" s="17">
         <v>91</v>
       </c>
-      <c r="R182" s="40">
+      <c r="R182" s="22">
         <f t="shared" si="6"/>
         <v>405</v>
       </c>
@@ -16999,10 +16952,10 @@
       <c r="D183" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E183" s="73" t="s">
+      <c r="E183" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F183" s="63" t="s">
+      <c r="F183" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G183" s="1" t="e" vm="17">
@@ -17032,7 +16985,7 @@
       <c r="Q183" s="17">
         <v>71</v>
       </c>
-      <c r="R183" s="40">
+      <c r="R183" s="22">
         <f t="shared" si="6"/>
         <v>505</v>
       </c>
@@ -17048,10 +17001,10 @@
       <c r="D184" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E184" s="52" t="s">
+      <c r="E184" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F184" s="63" t="s">
+      <c r="F184" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G184" s="1" t="e" vm="17">
@@ -17081,7 +17034,7 @@
       <c r="Q184" s="17">
         <v>91</v>
       </c>
-      <c r="R184" s="40">
+      <c r="R184" s="22">
         <f t="shared" si="6"/>
         <v>411</v>
       </c>
@@ -17097,10 +17050,10 @@
       <c r="D185" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="E185" s="45" t="s">
+      <c r="E185" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F185" s="67" t="s">
+      <c r="F185" s="49" t="s">
         <v>63</v>
       </c>
       <c r="G185" s="1" t="e" vm="2">
@@ -17132,7 +17085,7 @@
       <c r="Q185" s="17">
         <v>40</v>
       </c>
-      <c r="R185" s="40">
+      <c r="R185" s="22">
         <f t="shared" si="6"/>
         <v>325</v>
       </c>
@@ -17148,10 +17101,10 @@
       <c r="D186" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E186" s="45" t="s">
+      <c r="E186" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F186" s="67" t="s">
+      <c r="F186" s="49" t="s">
         <v>63</v>
       </c>
       <c r="G186" s="1" t="e" vm="2">
@@ -17183,7 +17136,7 @@
       <c r="Q186" s="17">
         <v>55</v>
       </c>
-      <c r="R186" s="40">
+      <c r="R186" s="22">
         <f t="shared" si="6"/>
         <v>530</v>
       </c>
@@ -17199,10 +17152,10 @@
       <c r="D187" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E187" s="53" t="s">
+      <c r="E187" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="F187" s="61" t="s">
+      <c r="F187" s="43" t="s">
         <v>69</v>
       </c>
       <c r="G187" s="1" t="e" vm="17">
@@ -17238,7 +17191,7 @@
       <c r="Q187" s="17">
         <v>55</v>
       </c>
-      <c r="R187" s="40">
+      <c r="R187" s="22">
         <f t="shared" si="6"/>
         <v>245</v>
       </c>
@@ -17254,10 +17207,10 @@
       <c r="D188" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E188" s="53" t="s">
+      <c r="E188" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="F188" s="61" t="s">
+      <c r="F188" s="43" t="s">
         <v>69</v>
       </c>
       <c r="G188" s="1" t="e" vm="17">
@@ -17293,7 +17246,7 @@
       <c r="Q188" s="17">
         <v>123</v>
       </c>
-      <c r="R188" s="40">
+      <c r="R188" s="22">
         <f t="shared" si="6"/>
         <v>535</v>
       </c>
@@ -17309,10 +17262,10 @@
       <c r="D189" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="E189" s="50" t="s">
+      <c r="E189" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F189" s="46"/>
+      <c r="F189" s="28"/>
       <c r="G189" s="1" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
@@ -17342,7 +17295,7 @@
       <c r="Q189" s="17">
         <v>35</v>
       </c>
-      <c r="R189" s="40">
+      <c r="R189" s="22">
         <f t="shared" si="6"/>
         <v>530</v>
       </c>
@@ -17358,10 +17311,10 @@
       <c r="D190" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="E190" s="81" t="s">
+      <c r="E190" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F190" s="69" t="s">
+      <c r="F190" s="51" t="s">
         <v>30</v>
       </c>
       <c r="G190" s="1" t="e" vm="64">
@@ -17393,7 +17346,7 @@
       <c r="Q190" s="17">
         <v>82</v>
       </c>
-      <c r="R190" s="40">
+      <c r="R190" s="22">
         <f t="shared" si="6"/>
         <v>475</v>
       </c>
@@ -17409,10 +17362,10 @@
       <c r="D191" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E191" s="47" t="s">
+      <c r="E191" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F191" s="46"/>
+      <c r="F191" s="28"/>
       <c r="G191" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
@@ -17442,7 +17395,7 @@
       <c r="Q191" s="17">
         <v>35</v>
       </c>
-      <c r="R191" s="40">
+      <c r="R191" s="22">
         <f t="shared" si="6"/>
         <v>255</v>
       </c>
@@ -17458,10 +17411,10 @@
       <c r="D192" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E192" s="47" t="s">
+      <c r="E192" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F192" s="67" t="s">
+      <c r="F192" s="49" t="s">
         <v>63</v>
       </c>
       <c r="G192" s="1" t="e" vm="26">
@@ -17493,7 +17446,7 @@
       <c r="Q192" s="17">
         <v>75</v>
       </c>
-      <c r="R192" s="40">
+      <c r="R192" s="22">
         <f t="shared" si="6"/>
         <v>525</v>
       </c>
@@ -17509,10 +17462,10 @@
       <c r="D193" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E193" s="47" t="s">
+      <c r="E193" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F193" s="65" t="s">
+      <c r="F193" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G193" s="1" t="e" vm="26">
@@ -17544,7 +17497,7 @@
       <c r="Q193" s="17">
         <v>85</v>
       </c>
-      <c r="R193" s="40">
+      <c r="R193" s="22">
         <f t="shared" si="6"/>
         <v>525</v>
       </c>
@@ -17560,10 +17513,10 @@
       <c r="D194" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E194" s="54" t="s">
+      <c r="E194" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F194" s="75" t="s">
+      <c r="F194" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G194" s="1" t="e" vm="21">
@@ -17595,7 +17548,7 @@
       <c r="Q194" s="17">
         <v>60</v>
       </c>
-      <c r="R194" s="40">
+      <c r="R194" s="22">
         <f t="shared" si="6"/>
         <v>360</v>
       </c>
@@ -17611,10 +17564,10 @@
       <c r="D195" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E195" s="54" t="s">
+      <c r="E195" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F195" s="75" t="s">
+      <c r="F195" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G195" s="1" t="e" vm="21">
@@ -17646,7 +17599,7 @@
       <c r="Q195" s="17">
         <v>100</v>
       </c>
-      <c r="R195" s="40">
+      <c r="R195" s="22">
         <f t="shared" si="6"/>
         <v>550</v>
       </c>
@@ -17662,10 +17615,10 @@
       <c r="D196" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E196" s="81" t="s">
+      <c r="E196" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F196" s="75" t="s">
+      <c r="F196" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G196" s="1" t="e" vm="138">
@@ -17701,7 +17654,7 @@
       <c r="Q196" s="17">
         <v>36</v>
       </c>
-      <c r="R196" s="40">
+      <c r="R196" s="22">
         <f t="shared" si="6"/>
         <v>485</v>
       </c>
@@ -17717,10 +17670,10 @@
       <c r="D197" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E197" s="81" t="s">
+      <c r="E197" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F197" s="59" t="s">
+      <c r="F197" s="41" t="s">
         <v>37</v>
       </c>
       <c r="G197" s="1" t="e" vm="138">
@@ -17756,7 +17709,7 @@
       <c r="Q197" s="17">
         <v>36</v>
       </c>
-      <c r="R197" s="40">
+      <c r="R197" s="22">
         <f t="shared" si="6"/>
         <v>485</v>
       </c>
@@ -17772,10 +17725,10 @@
       <c r="D198" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E198" s="62" t="s">
+      <c r="E198" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F198" s="76" t="s">
+      <c r="F198" s="58" t="s">
         <v>68</v>
       </c>
       <c r="G198" s="1" t="e" vm="209">
@@ -17807,7 +17760,7 @@
       <c r="Q198" s="17">
         <v>40</v>
       </c>
-      <c r="R198" s="40">
+      <c r="R198" s="22">
         <f t="shared" ref="R198:R201" si="8">SUM(L198:Q198)</f>
         <v>242</v>
       </c>
@@ -17823,10 +17776,10 @@
       <c r="D199" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E199" s="62" t="s">
+      <c r="E199" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F199" s="76" t="s">
+      <c r="F199" s="58" t="s">
         <v>68</v>
       </c>
       <c r="G199" s="1" t="e" vm="26">
@@ -17858,7 +17811,7 @@
       <c r="Q199" s="17">
         <v>75</v>
       </c>
-      <c r="R199" s="40">
+      <c r="R199" s="22">
         <f t="shared" si="8"/>
         <v>502</v>
       </c>
@@ -17874,10 +17827,10 @@
       <c r="D200" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="E200" s="57" t="s">
+      <c r="E200" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F200" s="67" t="s">
+      <c r="F200" s="49" t="s">
         <v>63</v>
       </c>
       <c r="G200" s="1" t="e" vm="26">
@@ -17907,7 +17860,7 @@
       <c r="Q200" s="17">
         <v>60</v>
       </c>
-      <c r="R200" s="40">
+      <c r="R200" s="22">
         <f t="shared" si="8"/>
         <v>280</v>
       </c>
@@ -17923,10 +17876,10 @@
       <c r="D201" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="E201" s="57" t="s">
+      <c r="E201" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F201" s="67" t="s">
+      <c r="F201" s="49" t="s">
         <v>63</v>
       </c>
       <c r="G201" s="1" t="e" vm="26">
@@ -17956,7 +17909,7 @@
       <c r="Q201" s="17">
         <v>80</v>
       </c>
-      <c r="R201" s="40">
+      <c r="R201" s="22">
         <f t="shared" si="8"/>
         <v>410</v>
       </c>
@@ -17972,10 +17925,10 @@
       <c r="D202" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E202" s="54" t="s">
+      <c r="E202" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F202" s="51" t="s">
+      <c r="F202" s="33" t="s">
         <v>34</v>
       </c>
       <c r="G202" s="1" t="e" vm="21">
@@ -18005,7 +17958,7 @@
       <c r="Q202" s="17">
         <v>109</v>
       </c>
-      <c r="R202" s="40">
+      <c r="R202" s="22">
         <f t="shared" ref="R202:R267" si="9">SUM(L202:Q202)</f>
         <v>484</v>
       </c>
@@ -18021,10 +17974,10 @@
       <c r="D203" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E203" s="47" t="s">
+      <c r="E203" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F203" s="48"/>
+      <c r="F203" s="30"/>
       <c r="G203" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -18052,7 +18005,7 @@
       <c r="Q203" s="17">
         <v>65</v>
       </c>
-      <c r="R203" s="40">
+      <c r="R203" s="22">
         <f t="shared" si="9"/>
         <v>484</v>
       </c>
@@ -18068,10 +18021,10 @@
       <c r="D204" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="E204" s="68" t="s">
+      <c r="E204" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F204" s="80" t="s">
+      <c r="F204" s="62" t="s">
         <v>16</v>
       </c>
       <c r="G204" s="1" t="e" vm="2">
@@ -18107,7 +18060,7 @@
       <c r="Q204" s="17">
         <v>38</v>
       </c>
-      <c r="R204" s="40">
+      <c r="R204" s="22">
         <f t="shared" si="9"/>
         <v>309</v>
       </c>
@@ -18123,10 +18076,10 @@
       <c r="D205" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="E205" s="68" t="s">
+      <c r="E205" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="F205" s="80" t="s">
+      <c r="F205" s="62" t="s">
         <v>16</v>
       </c>
       <c r="G205" s="1" t="e" vm="2">
@@ -18162,7 +18115,7 @@
       <c r="Q205" s="17">
         <v>56</v>
       </c>
-      <c r="R205" s="40">
+      <c r="R205" s="22">
         <f t="shared" si="9"/>
         <v>474</v>
       </c>
@@ -18178,10 +18131,10 @@
       <c r="D206" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E206" s="64" t="s">
+      <c r="E206" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F206" s="46"/>
+      <c r="F206" s="28"/>
       <c r="G206" s="1" t="e" vm="138">
         <v>#VALUE!</v>
       </c>
@@ -18215,7 +18168,7 @@
       <c r="Q206" s="17">
         <v>28</v>
       </c>
-      <c r="R206" s="40">
+      <c r="R206" s="22">
         <f t="shared" si="9"/>
         <v>304</v>
       </c>
@@ -18231,10 +18184,10 @@
       <c r="D207" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="E207" s="64" t="s">
+      <c r="E207" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F207" s="46"/>
+      <c r="F207" s="28"/>
       <c r="G207" s="1" t="e" vm="138">
         <v>#VALUE!</v>
       </c>
@@ -18268,7 +18221,7 @@
       <c r="Q207" s="17">
         <v>28</v>
       </c>
-      <c r="R207" s="40">
+      <c r="R207" s="22">
         <f t="shared" si="9"/>
         <v>514</v>
       </c>
@@ -18284,10 +18237,10 @@
       <c r="D208" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="E208" s="64" t="s">
+      <c r="E208" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F208" s="46"/>
+      <c r="F208" s="28"/>
       <c r="G208" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -18317,7 +18270,7 @@
       <c r="Q208" s="17">
         <v>43</v>
       </c>
-      <c r="R208" s="40">
+      <c r="R208" s="22">
         <f t="shared" si="9"/>
         <v>334</v>
       </c>
@@ -18333,10 +18286,10 @@
       <c r="D209" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="E209" s="64" t="s">
+      <c r="E209" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F209" s="46"/>
+      <c r="F209" s="28"/>
       <c r="G209" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -18366,7 +18319,7 @@
       <c r="Q209" s="17">
         <v>73</v>
       </c>
-      <c r="R209" s="40">
+      <c r="R209" s="22">
         <f t="shared" si="9"/>
         <v>521</v>
       </c>
@@ -18382,10 +18335,10 @@
       <c r="D210" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E210" s="64" t="s">
+      <c r="E210" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F210" s="46"/>
+      <c r="F210" s="28"/>
       <c r="G210" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -18419,7 +18372,7 @@
       <c r="Q210" s="17">
         <v>50</v>
       </c>
-      <c r="R210" s="40">
+      <c r="R210" s="22">
         <f t="shared" si="9"/>
         <v>470</v>
       </c>
@@ -18435,10 +18388,10 @@
       <c r="D211" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E211" s="41" t="s">
+      <c r="E211" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F211" s="67" t="s">
+      <c r="F211" s="49" t="s">
         <v>63</v>
       </c>
       <c r="G211" s="1" t="e" vm="34">
@@ -18468,7 +18421,7 @@
       <c r="Q211" s="17">
         <v>70</v>
       </c>
-      <c r="R211" s="40">
+      <c r="R211" s="22">
         <f t="shared" si="9"/>
         <v>460</v>
       </c>
@@ -18484,10 +18437,10 @@
       <c r="D212" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E212" s="41" t="s">
+      <c r="E212" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F212" s="67" t="s">
+      <c r="F212" s="49" t="s">
         <v>63</v>
       </c>
       <c r="G212" s="1" t="e" vm="34">
@@ -18517,7 +18470,7 @@
       <c r="Q212" s="17">
         <v>70</v>
       </c>
-      <c r="R212" s="40">
+      <c r="R212" s="22">
         <f t="shared" si="9"/>
         <v>460</v>
       </c>
@@ -18533,10 +18486,10 @@
       <c r="D213" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E213" s="70" t="s">
+      <c r="E213" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F213" s="63" t="s">
+      <c r="F213" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G213" s="1" t="e" vm="17">
@@ -18566,7 +18519,7 @@
       <c r="Q213" s="17">
         <v>70</v>
       </c>
-      <c r="R213" s="40">
+      <c r="R213" s="22">
         <f t="shared" si="9"/>
         <v>465</v>
       </c>
@@ -18582,10 +18535,10 @@
       <c r="D214" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="E214" s="81" t="s">
+      <c r="E214" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F214" s="55" t="s">
+      <c r="F214" s="37" t="s">
         <v>48</v>
       </c>
       <c r="G214" s="1" t="e" vm="49">
@@ -18615,7 +18568,7 @@
       <c r="Q214" s="17">
         <v>38</v>
       </c>
-      <c r="R214" s="40">
+      <c r="R214" s="22">
         <f t="shared" si="9"/>
         <v>300</v>
       </c>
@@ -18631,10 +18584,10 @@
       <c r="D215" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="E215" s="81" t="s">
+      <c r="E215" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F215" s="55" t="s">
+      <c r="F215" s="37" t="s">
         <v>48</v>
       </c>
       <c r="G215" s="1" t="e" vm="49">
@@ -18664,7 +18617,7 @@
       <c r="Q215" s="17">
         <v>58</v>
       </c>
-      <c r="R215" s="40">
+      <c r="R215" s="22">
         <f t="shared" si="9"/>
         <v>420</v>
       </c>
@@ -18680,10 +18633,10 @@
       <c r="D216" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E216" s="81" t="s">
+      <c r="E216" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F216" s="55" t="s">
+      <c r="F216" s="37" t="s">
         <v>48</v>
       </c>
       <c r="G216" s="1" t="e" vm="49">
@@ -18713,7 +18666,7 @@
       <c r="Q216" s="17">
         <v>98</v>
       </c>
-      <c r="R216" s="40">
+      <c r="R216" s="22">
         <f t="shared" si="9"/>
         <v>600</v>
       </c>
@@ -18729,10 +18682,10 @@
       <c r="D217" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E217" s="73" t="s">
+      <c r="E217" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F217" s="83" t="s">
+      <c r="F217" s="65" t="s">
         <v>50</v>
       </c>
       <c r="G217" s="1" t="e" vm="209">
@@ -18764,7 +18717,7 @@
       <c r="Q217" s="17">
         <v>45</v>
       </c>
-      <c r="R217" s="40">
+      <c r="R217" s="22">
         <f t="shared" si="9"/>
         <v>570</v>
       </c>
@@ -18780,10 +18733,10 @@
       <c r="D218" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="E218" s="73" t="s">
+      <c r="E218" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F218" s="80" t="s">
+      <c r="F218" s="62" t="s">
         <v>16</v>
       </c>
       <c r="G218" s="1" t="e" vm="209">
@@ -18815,7 +18768,7 @@
       <c r="Q218" s="17">
         <v>70</v>
       </c>
-      <c r="R218" s="40">
+      <c r="R218" s="22">
         <f t="shared" si="9"/>
         <v>570</v>
       </c>
@@ -18831,10 +18784,10 @@
       <c r="D219" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="E219" s="73" t="s">
+      <c r="E219" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F219" s="75" t="s">
+      <c r="F219" s="57" t="s">
         <v>24</v>
       </c>
       <c r="G219" s="1" t="e" vm="209">
@@ -18866,7 +18819,7 @@
       <c r="Q219" s="17">
         <v>100</v>
       </c>
-      <c r="R219" s="40">
+      <c r="R219" s="22">
         <f t="shared" si="9"/>
         <v>570</v>
       </c>
@@ -18882,10 +18835,10 @@
       <c r="D220" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E220" s="73" t="s">
+      <c r="E220" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F220" s="74" t="s">
+      <c r="F220" s="56" t="s">
         <v>66</v>
       </c>
       <c r="G220" s="1" t="e" vm="209">
@@ -18917,7 +18870,7 @@
       <c r="Q220" s="17">
         <v>135</v>
       </c>
-      <c r="R220" s="40">
+      <c r="R220" s="22">
         <f t="shared" si="9"/>
         <v>570</v>
       </c>
@@ -18933,10 +18886,10 @@
       <c r="D221" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E221" s="52" t="s">
+      <c r="E221" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F221" s="48"/>
+      <c r="F221" s="30"/>
       <c r="G221" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -18964,7 +18917,7 @@
       <c r="Q221" s="17">
         <v>55</v>
       </c>
-      <c r="R221" s="40">
+      <c r="R221" s="22">
         <f t="shared" si="9"/>
         <v>325</v>
       </c>
@@ -18980,10 +18933,10 @@
       <c r="D222" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E222" s="50" t="s">
+      <c r="E222" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F222" s="48"/>
+      <c r="F222" s="30"/>
       <c r="G222" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -19011,7 +18964,7 @@
       <c r="Q222" s="17">
         <v>65</v>
       </c>
-      <c r="R222" s="40">
+      <c r="R222" s="22">
         <f t="shared" si="9"/>
         <v>525</v>
       </c>
@@ -19027,10 +18980,10 @@
       <c r="D223" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E223" s="62" t="s">
+      <c r="E223" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F223" s="48"/>
+      <c r="F223" s="30"/>
       <c r="G223" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -19058,7 +19011,7 @@
       <c r="Q223" s="17">
         <v>130</v>
       </c>
-      <c r="R223" s="40">
+      <c r="R223" s="22">
         <f t="shared" si="9"/>
         <v>525</v>
       </c>
@@ -19074,10 +19027,10 @@
       <c r="D224" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="E224" s="47" t="s">
+      <c r="E224" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F224" s="48"/>
+      <c r="F224" s="30"/>
       <c r="G224" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -19105,7 +19058,7 @@
       <c r="Q224" s="17">
         <v>65</v>
       </c>
-      <c r="R224" s="40">
+      <c r="R224" s="22">
         <f t="shared" si="9"/>
         <v>525</v>
       </c>
@@ -19121,10 +19074,10 @@
       <c r="D225" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="E225" s="71" t="s">
+      <c r="E225" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="F225" s="48"/>
+      <c r="F225" s="30"/>
       <c r="G225" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -19152,7 +19105,7 @@
       <c r="Q225" s="17">
         <v>110</v>
       </c>
-      <c r="R225" s="40">
+      <c r="R225" s="22">
         <f t="shared" si="9"/>
         <v>525</v>
       </c>
@@ -19168,10 +19121,10 @@
       <c r="D226" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="E226" s="73" t="s">
+      <c r="E226" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F226" s="48"/>
+      <c r="F226" s="30"/>
       <c r="G226" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -19199,7 +19152,7 @@
       <c r="Q226" s="17">
         <v>65</v>
       </c>
-      <c r="R226" s="40">
+      <c r="R226" s="22">
         <f t="shared" si="9"/>
         <v>525</v>
       </c>
@@ -19215,10 +19168,10 @@
       <c r="D227" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="E227" s="45" t="s">
+      <c r="E227" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F227" s="48"/>
+      <c r="F227" s="30"/>
       <c r="G227" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -19246,7 +19199,7 @@
       <c r="Q227" s="17">
         <v>95</v>
       </c>
-      <c r="R227" s="40">
+      <c r="R227" s="22">
         <f t="shared" si="9"/>
         <v>525</v>
       </c>
@@ -19262,10 +19215,10 @@
       <c r="D228" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E228" s="64" t="s">
+      <c r="E228" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="F228" s="48"/>
+      <c r="F228" s="30"/>
       <c r="G228" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -19293,7 +19246,7 @@
       <c r="Q228" s="17">
         <v>65</v>
       </c>
-      <c r="R228" s="40">
+      <c r="R228" s="22">
         <f t="shared" si="9"/>
         <v>525</v>
       </c>
@@ -19309,10 +19262,10 @@
       <c r="D229" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="E229" s="72" t="s">
+      <c r="E229" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="F229" s="48"/>
+      <c r="F229" s="30"/>
       <c r="G229" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -19340,7 +19293,7 @@
       <c r="Q229" s="17">
         <v>60</v>
       </c>
-      <c r="R229" s="40">
+      <c r="R229" s="22">
         <f t="shared" si="9"/>
         <v>525</v>
       </c>
@@ -19356,10 +19309,10 @@
       <c r="D230" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="E230" s="52" t="s">
+      <c r="E230" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F230" s="63" t="s">
+      <c r="F230" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G230" s="1" t="e" vm="17">
@@ -19389,7 +19342,7 @@
       <c r="Q230" s="17">
         <v>60</v>
       </c>
-      <c r="R230" s="40">
+      <c r="R230" s="22">
         <f t="shared" si="9"/>
         <v>350</v>
       </c>
@@ -19405,10 +19358,10 @@
       <c r="D231" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="E231" s="52" t="s">
+      <c r="E231" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F231" s="63" t="s">
+      <c r="F231" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G231" s="1" t="e" vm="17">
@@ -19438,7 +19391,7 @@
       <c r="Q231" s="17">
         <v>80</v>
       </c>
-      <c r="R231" s="40">
+      <c r="R231" s="22">
         <f t="shared" si="9"/>
         <v>510</v>
       </c>
@@ -19454,10 +19407,10 @@
       <c r="D232" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="E232" s="73" t="s">
+      <c r="E232" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F232" s="63" t="s">
+      <c r="F232" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G232" s="1" t="e" vm="17">
@@ -19487,7 +19440,7 @@
       <c r="Q232" s="17">
         <v>60</v>
       </c>
-      <c r="R232" s="40">
+      <c r="R232" s="22">
         <f t="shared" si="9"/>
         <v>370</v>
       </c>
@@ -19503,10 +19456,10 @@
       <c r="D233" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E233" s="73" t="s">
+      <c r="E233" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F233" s="63" t="s">
+      <c r="F233" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G233" s="1" t="e" vm="17">
@@ -19536,7 +19489,7 @@
       <c r="Q233" s="17">
         <v>80</v>
       </c>
-      <c r="R233" s="40">
+      <c r="R233" s="22">
         <f t="shared" si="9"/>
         <v>510</v>
       </c>
@@ -19552,10 +19505,10 @@
       <c r="D234" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="E234" s="52" t="s">
+      <c r="E234" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F234" s="48"/>
+      <c r="F234" s="30"/>
       <c r="G234" s="1" t="e" vm="246">
         <v>#VALUE!</v>
       </c>
@@ -19583,7 +19536,7 @@
       <c r="Q234" s="17">
         <v>48</v>
       </c>
-      <c r="R234" s="40">
+      <c r="R234" s="22">
         <f t="shared" si="9"/>
         <v>288</v>
       </c>
@@ -19599,10 +19552,10 @@
       <c r="D235" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="E235" s="54" t="s">
+      <c r="E235" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F235" s="63" t="s">
+      <c r="F235" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G235" s="1" t="e" vm="21">
@@ -19632,7 +19585,7 @@
       <c r="Q235" s="17">
         <v>105</v>
       </c>
-      <c r="R235" s="40">
+      <c r="R235" s="22">
         <f t="shared" si="9"/>
         <v>500</v>
       </c>
@@ -19648,10 +19601,10 @@
       <c r="D236" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="E236" s="54" t="s">
+      <c r="E236" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F236" s="51" t="s">
+      <c r="F236" s="33" t="s">
         <v>34</v>
       </c>
       <c r="G236" s="1" t="e" vm="21">
@@ -19681,7 +19634,7 @@
       <c r="Q236" s="17">
         <v>65</v>
       </c>
-      <c r="R236" s="40">
+      <c r="R236" s="22">
         <f t="shared" si="9"/>
         <v>500</v>
       </c>
@@ -19697,10 +19650,10 @@
       <c r="D237" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E237" s="54" t="s">
+      <c r="E237" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="F237" s="66" t="s">
+      <c r="F237" s="48" t="s">
         <v>64</v>
       </c>
       <c r="G237" s="1" t="e" vm="21">
@@ -19730,7 +19683,7 @@
       <c r="Q237" s="17">
         <v>85</v>
       </c>
-      <c r="R237" s="40">
+      <c r="R237" s="22">
         <f t="shared" si="9"/>
         <v>500</v>
       </c>
@@ -19746,10 +19699,10 @@
       <c r="D238" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="E238" s="47" t="s">
+      <c r="E238" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F238" s="48"/>
+      <c r="F238" s="30"/>
       <c r="G238" s="1" t="e" vm="209">
         <v>#VALUE!</v>
       </c>
@@ -19777,7 +19730,7 @@
       <c r="Q238" s="17">
         <v>83</v>
       </c>
-      <c r="R238" s="40">
+      <c r="R238" s="22">
         <f t="shared" si="9"/>
         <v>365</v>
       </c>
@@ -19793,10 +19746,10 @@
       <c r="D239" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="E239" s="47" t="s">
+      <c r="E239" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F239" s="48"/>
+      <c r="F239" s="30"/>
       <c r="G239" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
@@ -19824,7 +19777,7 @@
       <c r="Q239" s="17">
         <v>93</v>
       </c>
-      <c r="R239" s="40">
+      <c r="R239" s="22">
         <f t="shared" si="9"/>
         <v>495</v>
       </c>
@@ -19840,10 +19793,10 @@
       <c r="D240" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="E240" s="47" t="s">
+      <c r="E240" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F240" s="48"/>
+      <c r="F240" s="30"/>
       <c r="G240" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
@@ -19871,7 +19824,7 @@
       <c r="Q240" s="17">
         <v>83</v>
       </c>
-      <c r="R240" s="40">
+      <c r="R240" s="22">
         <f t="shared" si="9"/>
         <v>540</v>
       </c>
@@ -19887,10 +19840,10 @@
       <c r="D241" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="E241" s="62" t="s">
+      <c r="E241" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F241" s="48"/>
+      <c r="F241" s="30"/>
       <c r="G241" s="1" t="e" vm="209">
         <v>#VALUE!</v>
       </c>
@@ -19918,7 +19871,7 @@
       <c r="Q241" s="17">
         <v>95</v>
       </c>
-      <c r="R241" s="40">
+      <c r="R241" s="22">
         <f t="shared" si="9"/>
         <v>360</v>
       </c>
@@ -19934,10 +19887,10 @@
       <c r="D242" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="E242" s="62" t="s">
+      <c r="E242" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F242" s="48"/>
+      <c r="F242" s="30"/>
       <c r="G242" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
@@ -19965,7 +19918,7 @@
       <c r="Q242" s="17">
         <v>105</v>
       </c>
-      <c r="R242" s="40">
+      <c r="R242" s="22">
         <f t="shared" si="9"/>
         <v>490</v>
       </c>
@@ -19981,10 +19934,10 @@
       <c r="D243" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="E243" s="62" t="s">
+      <c r="E243" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="F243" s="48"/>
+      <c r="F243" s="30"/>
       <c r="G243" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
@@ -20012,7 +19965,7 @@
       <c r="Q243" s="17">
         <v>95</v>
       </c>
-      <c r="R243" s="40">
+      <c r="R243" s="22">
         <f t="shared" si="9"/>
         <v>540</v>
       </c>
@@ -20028,10 +19981,10 @@
       <c r="D244" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E244" s="70" t="s">
+      <c r="E244" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F244" s="48"/>
+      <c r="F244" s="30"/>
       <c r="G244" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -20059,7 +20012,7 @@
       <c r="Q244" s="17">
         <v>30</v>
       </c>
-      <c r="R244" s="40">
+      <c r="R244" s="22">
         <f t="shared" si="9"/>
         <v>300</v>
       </c>
@@ -20075,10 +20028,10 @@
       <c r="D245" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="E245" s="70" t="s">
+      <c r="E245" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F245" s="48"/>
+      <c r="F245" s="30"/>
       <c r="G245" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -20106,7 +20059,7 @@
       <c r="Q245" s="17">
         <v>50</v>
       </c>
-      <c r="R245" s="40">
+      <c r="R245" s="22">
         <f t="shared" si="9"/>
         <v>440</v>
       </c>
@@ -20122,10 +20075,10 @@
       <c r="D246" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E246" s="70" t="s">
+      <c r="E246" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F246" s="48"/>
+      <c r="F246" s="30"/>
       <c r="G246" s="1" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -20153,7 +20106,7 @@
       <c r="Q246" s="17">
         <v>90</v>
       </c>
-      <c r="R246" s="40">
+      <c r="R246" s="22">
         <f t="shared" si="9"/>
         <v>520</v>
       </c>
@@ -20169,10 +20122,10 @@
       <c r="D247" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="E247" s="71" t="s">
+      <c r="E247" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="F247" s="63" t="s">
+      <c r="F247" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G247" s="1" t="e" vm="17">
@@ -20208,7 +20161,7 @@
       <c r="Q247" s="17">
         <v>72</v>
       </c>
-      <c r="R247" s="40">
+      <c r="R247" s="22">
         <f t="shared" si="9"/>
         <v>313</v>
       </c>
@@ -20224,10 +20177,10 @@
       <c r="D248" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E248" s="71" t="s">
+      <c r="E248" s="53" t="s">
         <v>63</v>
       </c>
-      <c r="F248" s="63" t="s">
+      <c r="F248" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G248" s="1" t="e" vm="17">
@@ -20263,7 +20216,7 @@
       <c r="Q248" s="17">
         <v>114</v>
       </c>
-      <c r="R248" s="40">
+      <c r="R248" s="22">
         <f t="shared" si="9"/>
         <v>425</v>
       </c>
@@ -20279,10 +20232,10 @@
       <c r="D249" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E249" s="57" t="s">
+      <c r="E249" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F249" s="46"/>
+      <c r="F249" s="28"/>
       <c r="G249" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -20316,7 +20269,7 @@
       <c r="Q249" s="17">
         <v>65</v>
       </c>
-      <c r="R249" s="40">
+      <c r="R249" s="22">
         <f t="shared" si="9"/>
         <v>350</v>
       </c>
@@ -20332,10 +20285,10 @@
       <c r="D250" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E250" s="57" t="s">
+      <c r="E250" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F250" s="46"/>
+      <c r="F250" s="28"/>
       <c r="G250" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -20369,7 +20322,7 @@
       <c r="Q250" s="17">
         <v>105</v>
       </c>
-      <c r="R250" s="40">
+      <c r="R250" s="22">
         <f t="shared" si="9"/>
         <v>510</v>
       </c>
@@ -20385,10 +20338,10 @@
       <c r="D251" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="E251" s="52" t="s">
+      <c r="E251" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F251" s="48"/>
+      <c r="F251" s="30"/>
       <c r="G251" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -20416,7 +20369,7 @@
       <c r="Q251" s="17">
         <v>90</v>
       </c>
-      <c r="R251" s="40">
+      <c r="R251" s="22">
         <f t="shared" si="9"/>
         <v>458</v>
       </c>
@@ -20432,10 +20385,10 @@
       <c r="D252" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="E252" s="58" t="s">
+      <c r="E252" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="F252" s="48"/>
+      <c r="F252" s="30"/>
       <c r="G252" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -20469,7 +20422,7 @@
       <c r="Q252" s="17">
         <v>65</v>
       </c>
-      <c r="R252" s="40">
+      <c r="R252" s="22">
         <f t="shared" si="9"/>
         <v>458</v>
       </c>
@@ -20485,10 +20438,10 @@
       <c r="D253" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="E253" s="50" t="s">
+      <c r="E253" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F253" s="48"/>
+      <c r="F253" s="30"/>
       <c r="G253" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -20522,7 +20475,7 @@
       <c r="Q253" s="17">
         <v>35</v>
       </c>
-      <c r="R253" s="40">
+      <c r="R253" s="22">
         <f t="shared" si="9"/>
         <v>308</v>
       </c>
@@ -20538,10 +20491,10 @@
       <c r="D254" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="E254" s="50" t="s">
+      <c r="E254" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F254" s="55" t="s">
+      <c r="F254" s="37" t="s">
         <v>48</v>
       </c>
       <c r="G254" s="1" t="e" vm="10">
@@ -20577,7 +20530,7 @@
       <c r="Q254" s="17">
         <v>55</v>
       </c>
-      <c r="R254" s="40">
+      <c r="R254" s="22">
         <f t="shared" si="9"/>
         <v>468</v>
       </c>
@@ -20593,10 +20546,10 @@
       <c r="D255" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="E255" s="50" t="s">
+      <c r="E255" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F255" s="66" t="s">
+      <c r="F255" s="48" t="s">
         <v>64</v>
       </c>
       <c r="G255" s="1" t="e" vm="10">
@@ -20632,7 +20585,7 @@
       <c r="Q255" s="17">
         <v>35</v>
       </c>
-      <c r="R255" s="40">
+      <c r="R255" s="22">
         <f t="shared" ref="R255" si="10">SUM(L255:Q255)</f>
         <v>308</v>
       </c>
@@ -20648,10 +20601,10 @@
       <c r="D256" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="E256" s="45" t="s">
+      <c r="E256" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="F256" s="63" t="s">
+      <c r="F256" s="45" t="s">
         <v>41</v>
       </c>
       <c r="G256" s="1" t="e" vm="138">
@@ -20687,7 +20640,7 @@
       <c r="Q256" s="17">
         <v>51</v>
       </c>
-      <c r="R256" s="40">
+      <c r="R256" s="22">
         <f t="shared" si="9"/>
         <v>460</v>
       </c>
@@ -20703,10 +20656,10 @@
       <c r="D257" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="E257" s="81" t="s">
+      <c r="E257" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F257" s="48"/>
+      <c r="F257" s="30"/>
       <c r="G257" s="1" t="e" vm="49">
         <v>#VALUE!</v>
       </c>
@@ -20740,7 +20693,7 @@
       <c r="Q257" s="17">
         <v>48</v>
       </c>
-      <c r="R257" s="40">
+      <c r="R257" s="22">
         <f t="shared" si="9"/>
         <v>485</v>
       </c>
@@ -20756,10 +20709,10 @@
       <c r="D258" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E258" s="81" t="s">
+      <c r="E258" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F258" s="65" t="s">
+      <c r="F258" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G258" s="1" t="e" vm="74">
@@ -20795,7 +20748,7 @@
       <c r="Q258" s="17">
         <v>82</v>
       </c>
-      <c r="R258" s="40">
+      <c r="R258" s="22">
         <f t="shared" si="9"/>
         <v>270</v>
       </c>
@@ -20811,10 +20764,10 @@
       <c r="D259" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E259" s="81" t="s">
+      <c r="E259" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F259" s="65" t="s">
+      <c r="F259" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G259" s="1" t="e" vm="74">
@@ -20850,7 +20803,7 @@
       <c r="Q259" s="17">
         <v>102</v>
       </c>
-      <c r="R259" s="40">
+      <c r="R259" s="22">
         <f t="shared" si="9"/>
         <v>410</v>
       </c>
@@ -20866,10 +20819,10 @@
       <c r="D260" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E260" s="81" t="s">
+      <c r="E260" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F260" s="65" t="s">
+      <c r="F260" s="47" t="s">
         <v>65</v>
       </c>
       <c r="G260" s="1" t="e" vm="74">
@@ -20905,7 +20858,7 @@
       <c r="Q260" s="17">
         <v>142</v>
       </c>
-      <c r="R260" s="40">
+      <c r="R260" s="22">
         <f t="shared" si="9"/>
         <v>600</v>
       </c>
@@ -20921,10 +20874,10 @@
       <c r="D261" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="E261" s="73" t="s">
+      <c r="E261" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F261" s="48"/>
+      <c r="F261" s="30"/>
       <c r="G261" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -20940,7 +20893,7 @@
       <c r="O261" s="13"/>
       <c r="P261" s="15"/>
       <c r="Q261" s="17"/>
-      <c r="R261" s="40">
+      <c r="R261" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -20956,10 +20909,10 @@
       <c r="D262" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="E262" s="73" t="s">
+      <c r="E262" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F262" s="48"/>
+      <c r="F262" s="30"/>
       <c r="G262" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -20977,7 +20930,7 @@
       <c r="O262" s="13"/>
       <c r="P262" s="15"/>
       <c r="Q262" s="17"/>
-      <c r="R262" s="40">
+      <c r="R262" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -20991,8 +20944,8 @@
       <c r="D263" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E263" s="84"/>
-      <c r="F263" s="48"/>
+      <c r="E263" s="66"/>
+      <c r="F263" s="30"/>
       <c r="G263" s="1"/>
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
@@ -21004,7 +20957,7 @@
       <c r="O263" s="13"/>
       <c r="P263" s="15"/>
       <c r="Q263" s="17"/>
-      <c r="R263" s="40">
+      <c r="R263" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -21017,15 +20970,15 @@
       <c r="D264" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E264" s="84"/>
-      <c r="F264" s="48"/>
+      <c r="E264" s="66"/>
+      <c r="F264" s="30"/>
       <c r="L264" s="7"/>
       <c r="M264" s="9"/>
       <c r="N264" s="11"/>
       <c r="O264" s="13"/>
       <c r="P264" s="15"/>
       <c r="Q264" s="17"/>
-      <c r="R264" s="40">
+      <c r="R264" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -21038,15 +20991,15 @@
       <c r="D265" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E265" s="84"/>
-      <c r="F265" s="48"/>
+      <c r="E265" s="66"/>
+      <c r="F265" s="30"/>
       <c r="L265" s="7"/>
       <c r="M265" s="9"/>
       <c r="N265" s="11"/>
       <c r="O265" s="13"/>
       <c r="P265" s="15"/>
       <c r="Q265" s="17"/>
-      <c r="R265" s="40">
+      <c r="R265" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -21059,15 +21012,15 @@
       <c r="D266" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E266" s="84"/>
-      <c r="F266" s="48"/>
+      <c r="E266" s="66"/>
+      <c r="F266" s="30"/>
       <c r="L266" s="7"/>
       <c r="M266" s="9"/>
       <c r="N266" s="11"/>
       <c r="O266" s="13"/>
       <c r="P266" s="15"/>
       <c r="Q266" s="17"/>
-      <c r="R266" s="40">
+      <c r="R266" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -21080,15 +21033,15 @@
       <c r="D267" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="E267" s="84"/>
-      <c r="F267" s="48"/>
+      <c r="E267" s="66"/>
+      <c r="F267" s="30"/>
       <c r="L267" s="7"/>
       <c r="M267" s="9"/>
       <c r="N267" s="11"/>
       <c r="O267" s="13"/>
       <c r="P267" s="15"/>
       <c r="Q267" s="17"/>
-      <c r="R267" s="40">
+      <c r="R267" s="22">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -4482,12 +4482,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4495,6 +4489,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7540,14 +7540,14 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="67" t="s">
+      <c r="L2" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
     </row>
     <row r="3" spans="2:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="2" t="s">
@@ -7565,14 +7565,14 @@
       <c r="F3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68" t="s">
+      <c r="H3" s="71"/>
+      <c r="I3" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="68"/>
+      <c r="J3" s="71"/>
       <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
@@ -7653,7 +7653,7 @@
         <f>SUM(L4:Q4)</f>
         <v>308</v>
       </c>
-      <c r="S4" s="69" t="s">
+      <c r="S4" s="67" t="s">
         <v>16</v>
       </c>
       <c r="T4" s="19">
@@ -8639,10 +8639,10 @@
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="S21" s="70" t="s">
+      <c r="S21" s="68" t="s">
         <v>69</v>
       </c>
-      <c r="T21" s="71">
+      <c r="T21" s="69">
         <f>COUNTIF(E$6:F$267, "Dragon")</f>
         <v>19</v>
       </c>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DAF4E3-F6B9-4158-A90E-2FF8F7971BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA10996F-E9E8-4C04-AED7-097F64828442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3913,15 +3913,6 @@
     <t>Tropius</t>
   </si>
   <si>
-    <t>Fantyrm</t>
-  </si>
-  <si>
-    <t>Dispareptil</t>
-  </si>
-  <si>
-    <t>Lanssorien</t>
-  </si>
-  <si>
     <t>lv.60</t>
   </si>
   <si>
@@ -3935,6 +3926,15 @@
   </si>
   <si>
     <t>Druddigon</t>
+  </si>
+  <si>
+    <t>Dreepy</t>
+  </si>
+  <si>
+    <t>Drakloak</t>
+  </si>
+  <si>
+    <t>Dragapult</t>
   </si>
 </sst>
 </file>
@@ -20544,7 +20544,7 @@
         <v>252</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E255" s="32" t="s">
         <v>30</v>
@@ -20654,7 +20654,7 @@
         <v>254</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E257" s="63" t="s">
         <v>69</v>
@@ -20707,7 +20707,7 @@
         <v>255</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E258" s="63" t="s">
         <v>69</v>
@@ -20762,7 +20762,7 @@
         <v>256</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E259" s="63" t="s">
         <v>69</v>
@@ -20783,7 +20783,7 @@
         <v>69</v>
       </c>
       <c r="K259" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="L259" s="7">
         <v>68</v>
@@ -20817,7 +20817,7 @@
         <v>257</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E260" s="63" t="s">
         <v>69</v>
@@ -20872,7 +20872,7 @@
         <v>258</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E261" s="55" t="s">
         <v>48</v>
@@ -20907,7 +20907,7 @@
         <v>259</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E262" s="55" t="s">
         <v>48</v>

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA10996F-E9E8-4C04-AED7-097F64828442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91B1DD8-D934-4D6A-B4A2-246B6BA7651B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20568,26 +20568,26 @@
         <v>22</v>
       </c>
       <c r="L255" s="7">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="M255" s="9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N255" s="11">
+        <v>130</v>
+      </c>
+      <c r="O255" s="13">
+        <v>45</v>
+      </c>
+      <c r="P255" s="15">
         <v>65</v>
       </c>
-      <c r="O255" s="13">
-        <v>50</v>
-      </c>
-      <c r="P255" s="15">
-        <v>35</v>
-      </c>
       <c r="Q255" s="17">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="R255" s="22">
         <f t="shared" ref="R255" si="10">SUM(L255:Q255)</f>
-        <v>308</v>
+        <v>485</v>
       </c>
     </row>
     <row r="256" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">

--- a/Pokédex et stats.xlsx
+++ b/Pokédex et stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PIERRE\Fakemon\POC\FANGAME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91B1DD8-D934-4D6A-B4A2-246B6BA7651B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF4C70B-377E-4925-A3B3-206D52BADCD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="274">
+  <futureMetadata name="XLRICHVALUE" count="276">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -1959,8 +1959,22 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="274"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="275"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="274">
+  <valueMetadata count="276">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -2782,13 +2796,19 @@
     </bk>
     <bk>
       <rc t="1" v="273"/>
+    </bk>
+    <bk>
+      <rc t="1" v="274"/>
+    </bk>
+    <bk>
+      <rc t="1" v="275"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="375">
   <si>
     <t>Base stats</t>
   </si>
@@ -3935,6 +3955,12 @@
   </si>
   <si>
     <t>Dragapult</t>
+  </si>
+  <si>
+    <t>Sandygast</t>
+  </si>
+  <si>
+    <t>Palossand</t>
   </si>
 </sst>
 </file>
@@ -5089,13 +5115,13 @@
                   <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>20</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>24</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>28</c:v>
@@ -5862,7 +5888,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="274">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="276">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -6957,6 +6983,14 @@
   </rv>
   <rv s="0">
     <v>273</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>274</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>275</v>
     <v>5</v>
   </rv>
 </rvData>
@@ -7247,6 +7281,8 @@
   <rel r:id="rId272"/>
   <rel r:id="rId273"/>
   <rel r:id="rId274"/>
+  <rel r:id="rId275"/>
+  <rel r:id="rId276"/>
 </richValueRels>
 </file>
 
@@ -7514,7 +7550,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:T267"/>
+  <dimension ref="B1:T269"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
@@ -7657,7 +7693,7 @@
         <v>16</v>
       </c>
       <c r="T4" s="19">
-        <f>COUNTIF(E$6:F$267, "Grass")</f>
+        <f>COUNTIF(E$6:F$269, "Grass")</f>
         <v>22</v>
       </c>
     </row>
@@ -7717,7 +7753,7 @@
         <v>24</v>
       </c>
       <c r="T5" s="20">
-        <f>COUNTIF(E$6:F$267, "Fire")</f>
+        <f>COUNTIF(E$6:F$269, "Fire")</f>
         <v>28</v>
       </c>
     </row>
@@ -7777,7 +7813,7 @@
         <v>30</v>
       </c>
       <c r="T6" s="20">
-        <f>COUNTIF(E$6:F$267, "Water")</f>
+        <f>COUNTIF(E$6:F$269, "Water")</f>
         <v>45</v>
       </c>
     </row>
@@ -7833,7 +7869,7 @@
         <v>37</v>
       </c>
       <c r="T7" s="20">
-        <f>COUNTIF(E$6:F$267, "Normal")</f>
+        <f>COUNTIF(E$6:F$269, "Normal")</f>
         <v>21</v>
       </c>
     </row>
@@ -7891,7 +7927,7 @@
         <v>27</v>
       </c>
       <c r="T8" s="20">
-        <f>COUNTIF(E$6:F$267, "Fighting")</f>
+        <f>COUNTIF(E$6:F$269, "Fighting")</f>
         <v>20</v>
       </c>
     </row>
@@ -7949,7 +7985,7 @@
         <v>41</v>
       </c>
       <c r="T9" s="20">
-        <f>COUNTIF(E$6:F$267, "Flying")</f>
+        <f>COUNTIF(E$6:F$269, "Flying")</f>
         <v>25</v>
       </c>
     </row>
@@ -8009,7 +8045,7 @@
         <v>63</v>
       </c>
       <c r="T10" s="20">
-        <f>COUNTIF(E$6:F$267, "Psychic")</f>
+        <f>COUNTIF(E$6:F$269, "Psychic")</f>
         <v>18</v>
       </c>
     </row>
@@ -8069,7 +8105,7 @@
         <v>45</v>
       </c>
       <c r="T11" s="20">
-        <f>COUNTIF(E$6:F$267, "Bug")</f>
+        <f>COUNTIF(E$6:F$269, "Bug")</f>
         <v>22</v>
       </c>
     </row>
@@ -8131,8 +8167,8 @@
         <v>50</v>
       </c>
       <c r="T12" s="20">
-        <f>COUNTIF(E$6:F$267, "Ground")</f>
-        <v>20</v>
+        <f>COUNTIF(E$6:F$269, "Ground")</f>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8187,7 +8223,7 @@
         <v>64</v>
       </c>
       <c r="T13" s="20">
-        <f>COUNTIF(E$6:F$267, "Rock")</f>
+        <f>COUNTIF(E$6:F$269, "Rock")</f>
         <v>22</v>
       </c>
     </row>
@@ -8243,8 +8279,8 @@
         <v>65</v>
       </c>
       <c r="T14" s="20">
-        <f>COUNTIF(E$6:F$267, "Ghost")</f>
-        <v>24</v>
+        <f>COUNTIF(E$6:F$269, "Ghost")</f>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8299,7 +8335,7 @@
         <v>48</v>
       </c>
       <c r="T15" s="20">
-        <f>COUNTIF(E$6:F$267, "Dark")</f>
+        <f>COUNTIF(E$6:F$269, "Dark")</f>
         <v>28</v>
       </c>
     </row>
@@ -8357,7 +8393,7 @@
         <v>66</v>
       </c>
       <c r="T16" s="20">
-        <f>COUNTIF(E$6:F$267, "Ice")</f>
+        <f>COUNTIF(E$6:F$269, "Ice")</f>
         <v>20</v>
       </c>
     </row>
@@ -8415,7 +8451,7 @@
         <v>34</v>
       </c>
       <c r="T17" s="20">
-        <f>COUNTIF(E$6:F$267, "Steel")</f>
+        <f>COUNTIF(E$6:F$269, "Steel")</f>
         <v>22</v>
       </c>
     </row>
@@ -8473,7 +8509,7 @@
         <v>67</v>
       </c>
       <c r="T18" s="20">
-        <f>COUNTIF(E$6:F$267, "Electrik")</f>
+        <f>COUNTIF(E$6:F$269, "Electrik")</f>
         <v>16</v>
       </c>
     </row>
@@ -8529,7 +8565,7 @@
         <v>68</v>
       </c>
       <c r="T19" s="20">
-        <f>COUNTIF(E$6:F$267, "Poison")</f>
+        <f>COUNTIF(E$6:F$269, "Poison")</f>
         <v>16</v>
       </c>
     </row>
@@ -8587,7 +8623,7 @@
         <v>60</v>
       </c>
       <c r="T20" s="20">
-        <f>COUNTIF(E$6:F$267, "Fairy")</f>
+        <f>COUNTIF(E$6:F$269, "Fairy")</f>
         <v>16</v>
       </c>
     </row>
@@ -8643,7 +8679,7 @@
         <v>69</v>
       </c>
       <c r="T21" s="69">
-        <f>COUNTIF(E$6:F$267, "Dragon")</f>
+        <f>COUNTIF(E$6:F$269, "Dragon")</f>
         <v>19</v>
       </c>
     </row>
@@ -17719,7 +17755,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C198" s="5">
-        <f t="shared" ref="C198:C267" si="7">C197+1</f>
+        <f t="shared" ref="C198:C269" si="7">C197+1</f>
         <v>195</v>
       </c>
       <c r="D198" s="1" t="s">
@@ -17959,7 +17995,7 @@
         <v>109</v>
       </c>
       <c r="R202" s="22">
-        <f t="shared" ref="R202:R267" si="9">SUM(L202:Q202)</f>
+        <f t="shared" ref="R202:R269" si="9">SUM(L202:Q202)</f>
         <v>484</v>
       </c>
     </row>
@@ -20544,51 +20580,32 @@
         <v>252</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="E255" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="F255" s="48" t="s">
-        <v>64</v>
-      </c>
-      <c r="G255" s="1" t="e" vm="10">
+        <v>373</v>
+      </c>
+      <c r="E255" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="F255" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="G255" s="1" t="e" vm="74">
         <v>#VALUE!</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I255" s="1" t="e" vm="64">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J255" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="I255" s="1"/>
+      <c r="J255" s="1"/>
       <c r="K255" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L255" s="7">
-        <v>100</v>
-      </c>
-      <c r="M255" s="9">
-        <v>90</v>
-      </c>
-      <c r="N255" s="11">
-        <v>130</v>
-      </c>
-      <c r="O255" s="13">
-        <v>45</v>
-      </c>
-      <c r="P255" s="15">
-        <v>65</v>
-      </c>
-      <c r="Q255" s="17">
-        <v>55</v>
-      </c>
-      <c r="R255" s="22">
-        <f t="shared" ref="R255" si="10">SUM(L255:Q255)</f>
-        <v>485</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="L255" s="7"/>
+      <c r="M255" s="9"/>
+      <c r="N255" s="11"/>
+      <c r="O255" s="13"/>
+      <c r="P255" s="15"/>
+      <c r="Q255" s="17"/>
+      <c r="R255" s="22"/>
     </row>
     <row r="256" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B256" t="e" vm="268">
@@ -20599,51 +20616,32 @@
         <v>253</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="E256" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="F256" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="G256" s="1" t="e" vm="138">
+        <v>374</v>
+      </c>
+      <c r="E256" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="F256" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="G256" s="1" t="e" vm="74">
         <v>#VALUE!</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="I256" s="1" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-      <c r="J256" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="I256" s="1"/>
+      <c r="J256" s="1"/>
       <c r="K256" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L256" s="7">
-        <v>99</v>
-      </c>
-      <c r="M256" s="9">
-        <v>68</v>
-      </c>
-      <c r="N256" s="11">
-        <v>83</v>
-      </c>
-      <c r="O256" s="13">
-        <v>72</v>
-      </c>
-      <c r="P256" s="15">
-        <v>87</v>
-      </c>
-      <c r="Q256" s="17">
-        <v>51</v>
-      </c>
-      <c r="R256" s="22">
-        <f t="shared" si="9"/>
-        <v>460</v>
-      </c>
+      <c r="L256" s="7"/>
+      <c r="M256" s="9"/>
+      <c r="N256" s="11"/>
+      <c r="O256" s="13"/>
+      <c r="P256" s="15"/>
+      <c r="Q256" s="17"/>
+      <c r="R256" s="22"/>
     </row>
     <row r="257" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B257" t="e" vm="269">
@@ -20654,47 +20652,49 @@
         <v>254</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="E257" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="F257" s="30"/>
-      <c r="G257" s="1" t="e" vm="49">
+        <v>366</v>
+      </c>
+      <c r="E257" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="F257" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="G257" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I257" s="1" t="e" vm="138">
+        <v>31</v>
+      </c>
+      <c r="I257" s="1" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
       <c r="J257" s="1" t="s">
-        <v>202</v>
+        <v>118</v>
       </c>
       <c r="K257" s="1" t="s">
         <v>22</v>
       </c>
       <c r="L257" s="7">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="M257" s="9">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N257" s="11">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="O257" s="13">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="P257" s="15">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="Q257" s="17">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="R257" s="22">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="R257" si="10">SUM(L257:Q257)</f>
         <v>485</v>
       </c>
     </row>
@@ -20707,50 +20707,50 @@
         <v>255</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="E258" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="F258" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="G258" s="1" t="e" vm="74">
+        <v>364</v>
+      </c>
+      <c r="E258" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F258" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="G258" s="1" t="e" vm="138">
         <v>#VALUE!</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I258" s="1" t="e" vm="49">
+        <v>202</v>
+      </c>
+      <c r="I258" s="1" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="J258" s="1" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="K258" s="1" t="s">
-        <v>295</v>
+        <v>22</v>
       </c>
       <c r="L258" s="7">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="M258" s="9">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="N258" s="11">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="O258" s="13">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="P258" s="15">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="Q258" s="17">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="R258" s="22">
         <f t="shared" si="9"/>
-        <v>270</v>
+        <v>460</v>
       </c>
     </row>
     <row r="259" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -20762,50 +20762,48 @@
         <v>256</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E259" s="63" t="s">
         <v>69</v>
       </c>
-      <c r="F259" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="G259" s="1" t="e" vm="74">
+      <c r="F259" s="30"/>
+      <c r="G259" s="1" t="e" vm="49">
         <v>#VALUE!</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="I259" s="1" t="e" vm="49">
+        <v>69</v>
+      </c>
+      <c r="I259" s="1" t="e" vm="138">
         <v>#VALUE!</v>
       </c>
       <c r="J259" s="1" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="K259" s="1" t="s">
-        <v>365</v>
+        <v>22</v>
       </c>
       <c r="L259" s="7">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="M259" s="9">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="N259" s="11">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="O259" s="13">
         <v>60</v>
       </c>
       <c r="P259" s="15">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="Q259" s="17">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="R259" s="22">
         <f t="shared" si="9"/>
-        <v>410</v>
+        <v>485</v>
       </c>
     </row>
     <row r="260" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -20817,7 +20815,7 @@
         <v>257</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E260" s="63" t="s">
         <v>69</v>
@@ -20838,29 +20836,29 @@
         <v>69</v>
       </c>
       <c r="K260" s="1" t="s">
-        <v>22</v>
+        <v>295</v>
       </c>
       <c r="L260" s="7">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="M260" s="9">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="N260" s="11">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="O260" s="13">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="P260" s="15">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="Q260" s="17">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="R260" s="22">
         <f t="shared" si="9"/>
-        <v>600</v>
+        <v>270</v>
       </c>
     </row>
     <row r="261" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -20872,34 +20870,54 @@
         <v>258</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="E261" s="55" t="s">
-        <v>48</v>
-      </c>
-      <c r="F261" s="30"/>
-      <c r="G261" s="1" t="e" vm="3">
+        <v>371</v>
+      </c>
+      <c r="E261" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="F261" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="G261" s="1" t="e" vm="74">
         <v>#VALUE!</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>17</v>
+        <v>114</v>
+      </c>
+      <c r="I261" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J261" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="K261" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="L261" s="7"/>
-      <c r="M261" s="9"/>
-      <c r="N261" s="11"/>
-      <c r="O261" s="13"/>
-      <c r="P261" s="15"/>
-      <c r="Q261" s="17"/>
+        <v>365</v>
+      </c>
+      <c r="L261" s="7">
+        <v>68</v>
+      </c>
+      <c r="M261" s="9">
+        <v>80</v>
+      </c>
+      <c r="N261" s="11">
+        <v>50</v>
+      </c>
+      <c r="O261" s="13">
+        <v>60</v>
+      </c>
+      <c r="P261" s="15">
+        <v>50</v>
+      </c>
+      <c r="Q261" s="17">
+        <v>102</v>
+      </c>
       <c r="R261" s="22">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>410</v>
       </c>
     </row>
     <row r="262" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B262" s="5" t="e" vm="274">
+      <c r="B262" t="e" vm="274">
         <v>#VALUE!</v>
       </c>
       <c r="C262" s="5">
@@ -20907,50 +20925,76 @@
         <v>259</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="E262" s="55" t="s">
-        <v>48</v>
-      </c>
-      <c r="F262" s="30"/>
-      <c r="G262" s="1" t="e" vm="3">
+        <v>372</v>
+      </c>
+      <c r="E262" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="F262" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="G262" s="1" t="e" vm="74">
         <v>#VALUE!</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I262" s="1"/>
-      <c r="J262" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="I262" s="1" t="e" vm="49">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J262" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="K262" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L262" s="7"/>
-      <c r="M262" s="9"/>
-      <c r="N262" s="11"/>
-      <c r="O262" s="13"/>
-      <c r="P262" s="15"/>
-      <c r="Q262" s="17"/>
+      <c r="L262" s="7">
+        <v>88</v>
+      </c>
+      <c r="M262" s="9">
+        <v>120</v>
+      </c>
+      <c r="N262" s="11">
+        <v>75</v>
+      </c>
+      <c r="O262" s="13">
+        <v>100</v>
+      </c>
+      <c r="P262" s="15">
+        <v>75</v>
+      </c>
+      <c r="Q262" s="17">
+        <v>142</v>
+      </c>
       <c r="R262" s="22">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="263" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B263" s="5"/>
+      <c r="B263" t="e" vm="275">
+        <v>#VALUE!</v>
+      </c>
       <c r="C263" s="5">
         <f t="shared" si="7"/>
         <v>260</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E263" s="66"/>
+        <v>367</v>
+      </c>
+      <c r="E263" s="55" t="s">
+        <v>48</v>
+      </c>
       <c r="F263" s="30"/>
-      <c r="G263" s="1"/>
-      <c r="H263" s="1"/>
-      <c r="I263" s="1"/>
-      <c r="J263" s="1"/>
-      <c r="K263" s="1"/>
+      <c r="G263" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H263" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K263" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="L263" s="7"/>
       <c r="M263" s="9"/>
       <c r="N263" s="11"/>
@@ -20963,15 +21007,31 @@
       </c>
     </row>
     <row r="264" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B264" s="5" t="e" vm="276">
+        <v>#VALUE!</v>
+      </c>
       <c r="C264" s="5">
         <f t="shared" si="7"/>
         <v>261</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E264" s="66"/>
+        <v>368</v>
+      </c>
+      <c r="E264" s="55" t="s">
+        <v>48</v>
+      </c>
       <c r="F264" s="30"/>
+      <c r="G264" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H264" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I264" s="1"/>
+      <c r="J264" s="1"/>
+      <c r="K264" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L264" s="7"/>
       <c r="M264" s="9"/>
       <c r="N264" s="11"/>
@@ -20984,6 +21044,7 @@
       </c>
     </row>
     <row r="265" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B265" s="5"/>
       <c r="C265" s="5">
         <f t="shared" si="7"/>
         <v>262</v>
@@ -20993,6 +21054,11 @@
       </c>
       <c r="E265" s="66"/>
       <c r="F265" s="30"/>
+      <c r="G265" s="1"/>
+      <c r="H265" s="1"/>
+      <c r="I265" s="1"/>
+      <c r="J265" s="1"/>
+      <c r="K265" s="1"/>
       <c r="L265" s="7"/>
       <c r="M265" s="9"/>
       <c r="N265" s="11"/>
@@ -21046,6 +21112,48 @@
         <v>0</v>
       </c>
     </row>
+    <row r="268" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C268" s="5">
+        <f t="shared" si="7"/>
+        <v>265</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E268" s="66"/>
+      <c r="F268" s="30"/>
+      <c r="L268" s="7"/>
+      <c r="M268" s="9"/>
+      <c r="N268" s="11"/>
+      <c r="O268" s="13"/>
+      <c r="P268" s="15"/>
+      <c r="Q268" s="17"/>
+      <c r="R268" s="22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C269" s="5">
+        <f t="shared" si="7"/>
+        <v>266</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E269" s="66"/>
+      <c r="F269" s="30"/>
+      <c r="L269" s="7"/>
+      <c r="M269" s="9"/>
+      <c r="N269" s="11"/>
+      <c r="O269" s="13"/>
+      <c r="P269" s="15"/>
+      <c r="Q269" s="17"/>
+      <c r="R269" s="22">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="L2:Q2"/>
